--- a/results_HR.xlsx
+++ b/results_HR.xlsx
@@ -456,27 +456,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava događaja Općeg servisa vijesti Hrvatska (OSV) za utorak, 25. srpnja: 
-	ZAGREB - Održat će se sjednica Gospodarsko-socijalnog vijeća na kojoj će biti i premijer Andrej Plenković. Između ostaloga, prezentirat će se prijedlog zakona o plaćama u državnoj službi i javnim službama te program Europskog socijalnog fonda plus za razdoblje 2021. - 2027. Snimatelji i fotoreporteri mogu snimiti početak sjednice nakon koje su predviđene izjave za medije (10 sati, Nacionalna i sveučilišna knjižnica, Hrvatske bratske zajednice 4).
-SISAK - Potpredsjednik Vlade i ministar prostornog uređenja, graditeljstva i državne imovine Branko Bačić, zajedno sa županom Ivanom Celjakom, posjetit će gradilišta na području Siska. Prvo će obići gradilišta konstrukcijske (samo)obnove višenamjenskih zgrada u Žitnoj ulici (10,15 sati), zatim zgradu Nove interne u krugu Opće bolnice "Dr. Ivo Pedišić" (11 sati, ulaz iz Ulice dr. Ivana Pedišića) koju obnavlja županija. Izjave za medije predviđene su u 11 sati nakon kojih će obići gradilište zamjenske obiteljske kuće (11,45 sati, Ulica Marijana Celjaka 150).
-ZAGREB - Konferencija za novinare Socijaldemokrata Grada Zagreba na kojoj će predsjednik Davor Bernardić sa suradnicima govoriti o prijedlozima za Zagreb bez ambrozije i, kako kaže, novim aferama gradonačelnika Tomaševića. Odgovarat će i na ostala nacionalna politička pitanja (9 sati, Aleja Matije Ljubeka na Jarunu, ispred Gallery Cluba).
-ZAGREB - Konferencija za novinare povodom završetka europskog projekta "Zajedno - razvoj vođen zajednicom" kojeg je zagrebačkog Gradsko društvo Crvenog križa provelo u suradnji s Gradom Zagrebom. Projekt je proveden radi jačanja sustava volonterstva i kapaciteta za pružanje učinkovitog odgovora na potrebe lokalne zajednice u kriznim situacijama te poboljšanja koordiniranog pristupa u rješavanju problema i izlazu iz krize (10 sati, Gradsko društvo Crvenog križa, Ilica 223).
-ZAGREB - Tematska konferencija za medije Policijske uprave zagrebačke povodom provedbe projekta "Sigurna turistička destinacija" na kojoj će biti predstavljen početak rada zajedničkih hrvatsko-korejskih i hrvatsko-kineskih policijskih ophodnji u gradu Zagrebu. Govorit će voditelj Službe prevencije PUZ-a Velimir Tišma i veleposlanik NR Kine u Republici Hrvatskoj NJ.E. Qi Qianjin (10 sati, Policijska uprava zagrebačka, Ulica Matice hrvatske 4).
-Dežurni urednici na desku OSV-a:
-prijepodne - Robert Koren
-poslijepodne - Mario Vrandečić
-navečer - Đurđa Beraković
-telefon: 01/48 08 600
-telefaks: 01/48 08 822
-e-mail: hina@hina.hr
-(Hina) xmhud ybdj
-</t>
+          <t>Zagreb srpanj 2023 hin najava događaj opći servis vijest Hrvatska osvti utorak srpanj Zagreb održati htjeti sjednica vijeće koji htjeti premijer Andrej Plenković između ostali prezentirati htjeti prijedlog zakon plaća državni služba javan služba program europski socijalan fond plus razdoblje 2021 2027 snimatelj fotoreporter moći snimiti početak sjednica predviđen izjava medij 10 sat nacionalan sveučilišni knjižnica hrvatski bratski zajednica 4 sisak potpredsjednik vlada ministar prostoran uređenje graditeljstvo državni imovina Branko Bačić zajedno župan ivan celjaka posjetiti htjeti gradilište područje siski prvo htjeti obići gradilište konstrukcijski obnova višenamjenski zgrada žitnoj ulica sat zatim zgrada nov interni krug opći bolnica Ivo pedišić 11 sat ulaz ulica ivati pedišić obnavljati županija izjava medij predviđen 11 sat koji htjeti obići gradilište zamjenski obiteljski kuća sat ulica marijan celjak 150 Zagreb konferencija novinar socijaldemokrat grad zagreba koji htjeti predsjednik Davor Bernardić suradnik govoriti prijedlozima Zagreb bez ambrozija kazati nov afera gradonačelnik tomaševića odgovarati htjeti ostali nacionalan politički pitanje 9 sat alej matija ljubeak jaruna ispred gallery club Zagreb konferencija novinar povodom završetak europski projekt zajedno razvoj voditi zajednica koji zagrebački gradski društvo crvean križ proveti suradnja grad zagreba projekt provediti radi jačanje sustav volonterstvo kapacitet pružanje učinkovit odgovor potreba lokalan zajednica krizan situacija poboljšanje koordiniran pristup rješavanje problem izlaz kriza 10 sat gradski društvo crvean križ ilica 223 Zagreb tematski konferencija medij policijski uprava zagrebački povodom provedba projekt siguran turistički destinacija koji htjeti predstaviti početak rad zajednički policijski ophodnja grad Zagreb govoriti htjeti voditelj služba prevencija velimir tišma veleposlanik nr kinuti republika Hrvatska qi qianjin 10 sat policijski uprava zagrebački ulica matica hrvatski 4 dežuran urednik deski prijepodne robert koren poslijepodne mariti vrandečić navečer đurđa Beraković telefon 08 600 telefaks 08 822 hin hina xmhud ybdj</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Za ovu inicijativu je glasalo osamnaest vijećnika, dva su bila "suzdržana" i jedan "protiv". Inicijativu za smjenu su pokrenuli vijećnici NiP-a, SBB i dio nezavisnih vijećnika.
-U 15:30 sati će se održati vanredna sjednica na kojoj će se odrediti datum referenduma, a bit će predložen 17. septembra. Odnosi unutar trojke u Centru su već duže vrijeme narušeni, pa je NiP na kraju okrenuo leđa Srđanu Mandiću, koji je iz Naše stranke.</t>
+          <t>ovaj inicijativa glasati osamnaest vijećnik dva suzdržan jedan protiv inicijativa smjena pokrenuti vijećnik sbb dio nezavisan vijećnik sat htjeti održati vanredan sjednica koji htjeti odrediti datum referendum biti htjeti predložiti septembri odnositi unutar trojka centar već duže vrijeme narušiti nip kraj okrenuti leđa srđan mandić naš stranka</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -487,12 +472,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Zagreb, Hina, Hrvatska, OSV, Zagreb, Gospodarsko - socijalnog vijeće, Andrej Plenković, europski socijalan fond plus za razdoblje, hrvatski bratski zajednica 4, Vlada, Branko Bačić, Ivan Celjako, Siska, Žitnoj ulica, nov interan, Opće bolnica, Ivo Pedišić, Ivan Pedišić, ulica Marijan Celjak, Zagreb, konferencija, Socijaldemokrat grad Zagreb, Davor Bernardić, Zagreb, Tomašević, Matija Ljubek, Jarun, gallery Club, Zagreb, konferencija, zajedno - razvoj, Gradsko društvo Crvenog križ, Grado Zagreb, Gradsko društvo Crvenog križ, Ilica, Zagreb, policijski uprava zagrebački, Zagreb, služba prevencija PUZ - a, Velimir Tišma, NR Kina, republika Hrvatska, NJ.E. Qi Qianjin, policijski uprava zagrebački, ulica matica hrvatski 4, Robert Koren, Mario Vrandečić, Đurđa Beraković, hina@hina.hr, Hina</t>
+          <t>Hrvatska, Zagreb, Andrej Plenković, Branko Bačić, socijaldemokrat grad zagreba, Davor Bernardić, Zagreb, Zagreb, Zagreb, velimir tišma, Hrvatska, qianjin, ulica matica, vrandečić, Beraković</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NiP - a, SBB, centar, NiP, Srđan Mandić</t>
+          <t>srđan mandić</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -502,38 +487,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava događaja Općeg servisa vijesti Hrvatska (OSV) za utorak, 25. srpnja: 
-	ZAGREB - Održat će se sjednica Gospodarsko-socijalnog vijeća na kojoj će biti i premijer Andrej Plenković. Između ostaloga, prezentirat će se prijedlog zakona o plaćama u državnoj službi i javnim službama te program Europskog socijalnog fonda plus za razdoblje 2021. - 2027. Snimatelji i fotoreporteri mogu snimiti početak sjednice nakon koje su predviđene izjave za medije (10 sati, Nacionalna i sveučilišna knjižnica, Hrvatske bratske zajednice 4).
-SISAK - Potpredsjednik Vlade i ministar prostornog uređenja, graditeljstva i državne imovine Branko Bačić, zajedno sa županom Ivanom Celjakom, posjetit će gradilišta na području Siska. Prvo će obići gradilišta konstrukcijske (samo)obnove višenamjenskih zgrada u Žitnoj ulici (10,15 sati), zatim zgradu Nove interne u krugu Opće bolnice "Dr. Ivo Pedišić" (11 sati, ulaz iz Ulice dr. Ivana Pedišića) koju obnavlja županija. Izjave za medije predviđene su u 11 sati nakon kojih će obići gradilište zamjenske obiteljske kuće (11,45 sati, Ulica Marijana Celjaka 150).
-ZAGREB - Konferencija za novinare Socijaldemokrata Grada Zagreba na kojoj će predsjednik Davor Bernardić sa suradnicima govoriti o prijedlozima za Zagreb bez ambrozije i, kako kaže, novim aferama gradonačelnika Tomaševića. Odgovarat će i na ostala nacionalna politička pitanja (9 sati, Aleja Matije Ljubeka na Jarunu, ispred Gallery Cluba).
-ZAGREB - Konferencija za novinare povodom završetka europskog projekta "Zajedno - razvoj vođen zajednicom" kojeg je zagrebačkog Gradsko društvo Crvenog križa provelo u suradnji s Gradom Zagrebom. Projekt je proveden radi jačanja sustava volonterstva i kapaciteta za pružanje učinkovitog odgovora na potrebe lokalne zajednice u kriznim situacijama te poboljšanja koordiniranog pristupa u rješavanju problema i izlazu iz krize (10 sati, Gradsko društvo Crvenog križa, Ilica 223).
-ZAGREB - Tematska konferencija za medije Policijske uprave zagrebačke povodom provedbe projekta "Sigurna turistička destinacija" na kojoj će biti predstavljen početak rada zajedničkih hrvatsko-korejskih i hrvatsko-kineskih policijskih ophodnji u gradu Zagrebu. Govorit će voditelj Službe prevencije PUZ-a Velimir Tišma i veleposlanik NR Kine u Republici Hrvatskoj NJ.E. Qi Qianjin (10 sati, Policijska uprava zagrebačka, Ulica Matice hrvatske 4).
-Dežurni urednici na desku OSV-a:
-prijepodne - Robert Koren
-poslijepodne - Mario Vrandečić
-navečer - Đurđa Beraković
-telefon: 01/48 08 600
-telefaks: 01/48 08 822
-e-mail: hina@hina.hr
-(Hina) xmhud ybdj
-</t>
+          <t>Zagreb srpanj 2023 hin najava događaj opći servis vijest Hrvatska osvti utorak srpanj Zagreb održati htjeti sjednica vijeće koji htjeti premijer Andrej Plenković između ostali prezentirati htjeti prijedlog zakon plaća državni služba javan služba program europski socijalan fond plus razdoblje 2021 2027 snimatelj fotoreporter moći snimiti početak sjednica predviđen izjava medij 10 sat nacionalan sveučilišni knjižnica hrvatski bratski zajednica 4 sisak potpredsjednik vlada ministar prostoran uređenje graditeljstvo državni imovina Branko Bačić zajedno župan ivan celjaka posjetiti htjeti gradilište područje siski prvo htjeti obići gradilište konstrukcijski obnova višenamjenski zgrada žitnoj ulica sat zatim zgrada nov interni krug opći bolnica Ivo pedišić 11 sat ulaz ulica ivati pedišić obnavljati županija izjava medij predviđen 11 sat koji htjeti obići gradilište zamjenski obiteljski kuća sat ulica marijan celjak 150 Zagreb konferencija novinar socijaldemokrat grad zagreba koji htjeti predsjednik Davor Bernardić suradnik govoriti prijedlozima Zagreb bez ambrozija kazati nov afera gradonačelnik tomaševića odgovarati htjeti ostali nacionalan politički pitanje 9 sat alej matija ljubeak jaruna ispred gallery club Zagreb konferencija novinar povodom završetak europski projekt zajedno razvoj voditi zajednica koji zagrebački gradski društvo crvean križ proveti suradnja grad zagreba projekt provediti radi jačanje sustav volonterstvo kapacitet pružanje učinkovit odgovor potreba lokalan zajednica krizan situacija poboljšanje koordiniran pristup rješavanje problem izlaz kriza 10 sat gradski društvo crvean križ ilica 223 Zagreb tematski konferencija medij policijski uprava zagrebački povodom provedba projekt siguran turistički destinacija koji htjeti predstaviti početak rad zajednički policijski ophodnja grad Zagreb govoriti htjeti voditelj služba prevencija velimir tišma veleposlanik nr kinuti republika Hrvatska qi qianjin 10 sat policijski uprava zagrebački ulica matica hrvatski 4 dežuran urednik deski prijepodne robert koren poslijepodne mariti vrandečić navečer đurđa Beraković telefon 08 600 telefaks 08 822 hin hina xmhud ybdj</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vesti Android telefoni sada mogu da otkriju uređaje za praćenje u okolini Android telefoni će automatski, ali i ručno moći da skeniraju okolinu kako bi pronašli nepoznate uređaje za praćenje. Izvor: Bizportal.rs / T.Đ. subota, 29.07.2023. | 08:15 Tweet Podeli Foto: valiantsin suprunovich / Shutterstock.com
-Pametni telefoni koji pokreću Android 6 ili noviji operativni sistem sada dobijaju ažuriranje koje će im omogućiti da prepoznaju da li nas neko prati. Ukoliko je to slučaj, dobićemo upozorenje o nepoznatom uređaju za praćenje koji putuje sa nama.
-Google je ovu funkciju najavio na svom I/O događaju održanom u maju, kao odgovor na sve veći broj slučajeva digitalnog uhođenja pomoću namenskih uređaja kao što je Apple AirTag. Zapravo, Google i Apple su blisko sarađivali na ovom projektu.
-Ažurirani telefoni će sada automatski moći da prepoznaju da li se sa nama kreće nepoznati bluetooth uređaj za praćenje, ali ne i njegov vlasnik, a kada se to desi, dobićemo notifikaciju, ali i mogućnost da saznamo više. Ovo uključuje mapu na kojoj će biti prikazana ruta po kojoj nas je takav uređaj pratio, a u nekim slučajevima i serijski broj uređaja, kao i informacije o njegovom vlasniku.
-Naravno, ovo neće biti previše korisno ukoliko ne možemo da lociramo nepoznati uređaj za praćenje, te će nam na raspolaganju biti opcija za aktiviranje njegovog zvučnog signala, kao i uputstvo za deaktivaciju. Na primer, AirTag-u je potrebno odvrnuti poklopac i izvaditi bateriju.
-Ukoliko to želimo, uvek možemo i ručno skenirati svoju okolinu kako bi pronašli nepoznate uređaje za praćenje. Kada stigne nadogradnja, potrebno je uraditi sledeće:
-Otvorite "Settings"
-Pronađite "Safety &amp; Emergency" opciju
-Izaberite "Unknown Tracker Alerts"
-Pritisnite "Scan now" dugme
-Google kaže da je za ručno skeniranje potrebno samo 10 sekundi kako bi pronašao nepoznati uređaj, a ukoliko telefon išta pronađe, na raspolaganju su iste opcije kao i kod automatskog skeniranja.
-Nažalost, nova funkcija trenutno ima mogućnost detektovanja samo AirTag uređaja, ali vremenom će se lista proširivati. Gedžet kompanije Apple je već nekoliko puta bio tema svetskih medija, te smo nakon njegovog lansiranja imali priliku da čujemo i dobre, ali i loše stvari.
-Pratite nas na našoj Facebook i Instagram stranici, Twitter nalogu i uključite se u našu Viber zajednicu.</t>
+          <t>vest Android telefon sada moći otkriju uređaj praćenje okolina android telefon htjeti automatski ručno moći skenirati okolina pronaći nepoznat uređaj praćenje izvor subota tweet podeli foto valiantsin suprunovich pametan telefon pokretati android 6 nov operativan sistem sada dobijati ažuriranje htjeti oni omogućiti prepoznati neko pratiti ukoliko slučaj dobićemo upozorenje nepoznat uređaj praćenje putovati google ovaj funkcija najaviti događaj održati mati odgovor velik broj slučaj digitalan uhođenje pomoću namenski uređaj što Apple Airtag zapravo Google apple blisko sarađivati ovaj projekt ažuriran telefon htjeti sada automatski moći prepoznati kretati nepoznat bluetooth uređaj praćenje vlasnik desiti dobićemo notifikacija mogućnost saznamo mnogo ovaj uključivati mapa koji htjeti prikazati ruta koji takav uređaj pratiti neki slučaj serijski broj uređaj informacija njegov vlasnik naravno ovaj htjeti previše korisan ukoliko moći locirati nepoznati uređaj praćenje htjeti raspolaganje opcija aktiviranje njegov zvučan signal uputstvo deaktivacija primer potreban odvrnuti poklopac izvaditi baterija ukoliko željeti uvek moći ručno skenirati svoj okolina pronaći nepoznat uređaj praćenje stignuti nadogradnja potreban uraditi sledeći otvoriti settings pronađiti safety emergency opcija izaberiti unknown tracker alerts pritisnuti scan now dugme google kazati ručan skeniranje potreban 10 sekunda pronaći nepoznati uređaj ukoliko telefon išta pronaći raspolaganje isti opcija kod automatski skeniranje nažalost nov funkcija trenutno imati mogućnost detektovanje airtag uređaj vrijeme htjeti lista proširivati gedžet kompanija apple već nekoliko put tema svetski medij njegov lansiranje imati prilika čivati dobar loš stvar pratiti naš facebook instagram stranica twitter nalog uključite naš viber zajednica</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -544,12 +503,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zagreb, Hina, Hrvatska, OSV, Zagreb, Gospodarsko - socijalnog vijeće, Andrej Plenković, europski socijalan fond plus za razdoblje, hrvatski bratski zajednica 4, Vlada, Branko Bačić, Ivan Celjako, Siska, Žitnoj ulica, nov interan, Opće bolnica, Ivo Pedišić, Ivan Pedišić, ulica Marijan Celjak, Zagreb, konferencija, Socijaldemokrat grad Zagreb, Davor Bernardić, Zagreb, Tomašević, Matija Ljubek, Jarun, gallery Club, Zagreb, konferencija, zajedno - razvoj, Gradsko društvo Crvenog križ, Grado Zagreb, Gradsko društvo Crvenog križ, Ilica, Zagreb, policijski uprava zagrebački, Zagreb, služba prevencija PUZ - a, Velimir Tišma, NR Kina, republika Hrvatska, NJ.E. Qi Qianjin, policijski uprava zagrebački, ulica matica hrvatski 4, Robert Koren, Mario Vrandečić, Đurđa Beraković, hina@hina.hr, Hina</t>
+          <t>Hrvatska, Zagreb, Andrej Plenković, Branko Bačić, socijaldemokrat grad zagreba, Davor Bernardić, Zagreb, Zagreb, Zagreb, velimir tišma, Hrvatska, qianjin, ulica matica, vrandečić, Beraković</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Android, Bizportal.rs, T.Đ., Tweet Podeli Foto, valiantsin suprunovich, Android 6, Google, i / O, Apple, Google, Apple, Safety &amp; Emergency, Unknown Tracker Alerts, Scan now, Google, Apple, Facebook, Instagram, Twitter, Viber</t>
+          <t>Android, Android, valiantsin suprunovich, Android 6, Apple Airtag, Google, apple, alerts, google, apple</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -559,38 +518,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava događaja Općeg servisa vijesti Hrvatska (OSV) za utorak, 25. srpnja: 
-	ZAGREB - Održat će se sjednica Gospodarsko-socijalnog vijeća na kojoj će biti i premijer Andrej Plenković. Između ostaloga, prezentirat će se prijedlog zakona o plaćama u državnoj službi i javnim službama te program Europskog socijalnog fonda plus za razdoblje 2021. - 2027. Snimatelji i fotoreporteri mogu snimiti početak sjednice nakon koje su predviđene izjave za medije (10 sati, Nacionalna i sveučilišna knjižnica, Hrvatske bratske zajednice 4).
-SISAK - Potpredsjednik Vlade i ministar prostornog uređenja, graditeljstva i državne imovine Branko Bačić, zajedno sa županom Ivanom Celjakom, posjetit će gradilišta na području Siska. Prvo će obići gradilišta konstrukcijske (samo)obnove višenamjenskih zgrada u Žitnoj ulici (10,15 sati), zatim zgradu Nove interne u krugu Opće bolnice "Dr. Ivo Pedišić" (11 sati, ulaz iz Ulice dr. Ivana Pedišića) koju obnavlja županija. Izjave za medije predviđene su u 11 sati nakon kojih će obići gradilište zamjenske obiteljske kuće (11,45 sati, Ulica Marijana Celjaka 150).
-ZAGREB - Konferencija za novinare Socijaldemokrata Grada Zagreba na kojoj će predsjednik Davor Bernardić sa suradnicima govoriti o prijedlozima za Zagreb bez ambrozije i, kako kaže, novim aferama gradonačelnika Tomaševića. Odgovarat će i na ostala nacionalna politička pitanja (9 sati, Aleja Matije Ljubeka na Jarunu, ispred Gallery Cluba).
-ZAGREB - Konferencija za novinare povodom završetka europskog projekta "Zajedno - razvoj vođen zajednicom" kojeg je zagrebačkog Gradsko društvo Crvenog križa provelo u suradnji s Gradom Zagrebom. Projekt je proveden radi jačanja sustava volonterstva i kapaciteta za pružanje učinkovitog odgovora na potrebe lokalne zajednice u kriznim situacijama te poboljšanja koordiniranog pristupa u rješavanju problema i izlazu iz krize (10 sati, Gradsko društvo Crvenog križa, Ilica 223).
-ZAGREB - Tematska konferencija za medije Policijske uprave zagrebačke povodom provedbe projekta "Sigurna turistička destinacija" na kojoj će biti predstavljen početak rada zajedničkih hrvatsko-korejskih i hrvatsko-kineskih policijskih ophodnji u gradu Zagrebu. Govorit će voditelj Službe prevencije PUZ-a Velimir Tišma i veleposlanik NR Kine u Republici Hrvatskoj NJ.E. Qi Qianjin (10 sati, Policijska uprava zagrebačka, Ulica Matice hrvatske 4).
-Dežurni urednici na desku OSV-a:
-prijepodne - Robert Koren
-poslijepodne - Mario Vrandečić
-navečer - Đurđa Beraković
-telefon: 01/48 08 600
-telefaks: 01/48 08 822
-e-mail: hina@hina.hr
-(Hina) xmhud ybdj
-</t>
+          <t>Zagreb srpanj 2023 hin najava događaj opći servis vijest Hrvatska osvti utorak srpanj Zagreb održati htjeti sjednica vijeće koji htjeti premijer Andrej Plenković između ostali prezentirati htjeti prijedlog zakon plaća državni služba javan služba program europski socijalan fond plus razdoblje 2021 2027 snimatelj fotoreporter moći snimiti početak sjednica predviđen izjava medij 10 sat nacionalan sveučilišni knjižnica hrvatski bratski zajednica 4 sisak potpredsjednik vlada ministar prostoran uređenje graditeljstvo državni imovina Branko Bačić zajedno župan ivan celjaka posjetiti htjeti gradilište područje siski prvo htjeti obići gradilište konstrukcijski obnova višenamjenski zgrada žitnoj ulica sat zatim zgrada nov interni krug opći bolnica Ivo pedišić 11 sat ulaz ulica ivati pedišić obnavljati županija izjava medij predviđen 11 sat koji htjeti obići gradilište zamjenski obiteljski kuća sat ulica marijan celjak 150 Zagreb konferencija novinar socijaldemokrat grad zagreba koji htjeti predsjednik Davor Bernardić suradnik govoriti prijedlozima Zagreb bez ambrozija kazati nov afera gradonačelnik tomaševića odgovarati htjeti ostali nacionalan politički pitanje 9 sat alej matija ljubeak jaruna ispred gallery club Zagreb konferencija novinar povodom završetak europski projekt zajedno razvoj voditi zajednica koji zagrebački gradski društvo crvean križ proveti suradnja grad zagreba projekt provediti radi jačanje sustav volonterstvo kapacitet pružanje učinkovit odgovor potreba lokalan zajednica krizan situacija poboljšanje koordiniran pristup rješavanje problem izlaz kriza 10 sat gradski društvo crvean križ ilica 223 Zagreb tematski konferencija medij policijski uprava zagrebački povodom provedba projekt siguran turistički destinacija koji htjeti predstaviti početak rad zajednički policijski ophodnja grad Zagreb govoriti htjeti voditelj služba prevencija velimir tišma veleposlanik nr kinuti republika Hrvatska qi qianjin 10 sat policijski uprava zagrebački ulica matica hrvatski 4 dežuran urednik deski prijepodne robert koren poslijepodne mariti vrandečić navečer đurđa Beraković telefon 08 600 telefaks 08 822 hin hina xmhud ybdj</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vesti Android telefoni sada mogu da otkriju da li nas neko prati Android telefoni će automatski, ali i ručno moći da skeniraju okolinu kako bi pronašli nepoznate uređaje za praćenje. Izvor: Bizportal.rs / T.Đ. subota, 29.07.2023. | 08:15 Tweet Podeli Foto: valiantsin suprunovich / Shutterstock.com
-Pametni telefoni koji pokreću Android 6 ili noviji operativni sistem sada dobijaju ažuriranje koje će im omogućiti da prepoznaju da li nas neko prati. Ukoliko je to slučaj, dobićemo upozorenje o nepoznatom uređaju za praćenje koji putuje sa nama.
-Google je ovu funkciju najavio na svom I/O događaju održanom u maju, kao odgovor na sve veći broj slučajeva digitalnog uhođenja pomoću namenskih uređaja kao što je Apple AirTag. Zapravo, Google i Apple su blisko sarađivali na ovom projektu.
-Ažurirani telefoni će sada automatski moći da prepoznaju da li se sa nama kreće nepoznati bluetooth uređaj za praćenje, ali ne i njegov vlasnik, a kada se to desi, dobićemo notifikaciju, ali i mogućnost da saznamo više. Ovo uključuje mapu na kojoj će biti prikazana ruta po kojoj nas je takav uređaj pratio, a u nekim slučajevima i serijski broj uređaja, kao i informacije o njegovom vlasniku.
-Naravno, ovo neće biti previše korisno ukoliko ne možemo da lociramo nepoznati uređaj za praćenje, te će nam na raspolaganju biti opcija za aktiviranje njegovog zvučnog signala, kao i uputstvo za deaktivaciju. Na primer, AirTag-u je potrebno odvrnuti poklopac i izvaditi bateriju.
-Ukoliko to želimo, uvek možemo i ručno skenirati svoju okolinu kako bi pronašli nepoznate uređaje za praćenje. Kada stigne nadogradnja, potrebno je uraditi sledeće:
-Otvorite "Settings"
-Pronađite "Safety &amp; Emergency" opciju
-Izaberite "Unknown Tracker Alerts"
-Pritisnite "Scan now" dugme
-Google kaže da je za ručno skeniranje potrebno samo 10 sekundi kako bi pronašao nepoznati uređaj, a ukoliko telefon išta pronađe, na raspolaganju su iste opcije kao i kod automatskog skeniranja.
-Nažalost, nova funkcija trenutno ima mogućnost detektovanja samo AirTag uređaja, ali vremenom će se lista proširivati. Gedžet kompanije Apple je već nekoliko puta bio tema svetskih medija, te smo nakon njegovog lansiranja imali priliku da čujemo i dobre, ali i loše stvari.
-Pratite nas na našoj Facebook i Instagram stranici, Twitter nalogu i uključite se u našu Viber zajednicu.</t>
+          <t>vest Android telefon sada moći otkriti neko pratiti android telefon htjeti automatski ručno moći skenirati okolina pronaći nepoznat uređaj praćenje izvor subota tweet podeli foto valiantsin suprunovich pametan telefon pokretati android 6 nov operativan sistem sada dobijati ažuriranje htjeti oni omogućiti prepoznati neko pratiti ukoliko slučaj dobićemo upozorenje nepoznat uređaj praćenje putovati google ovaj funkcija najaviti događaj održati mati odgovor velik broj slučaj digitalan uhođenje pomoću namenski uređaj što Apple Airtag zapravo Google apple blisko sarađivati ovaj projekt ažuriran telefon htjeti sada automatski moći prepoznati kretati nepoznat bluetooth uređaj praćenje vlasnik desiti dobićemo notifikacija mogućnost saznamo mnogo ovaj uključivati mapa koji htjeti prikazati ruta koji takav uređaj pratiti neki slučaj serijski broj uređaj informacija njegov vlasnik naravno ovaj htjeti previše korisan ukoliko moći locirati nepoznati uređaj praćenje htjeti raspolaganje opcija aktiviranje njegov zvučan signal uputstvo deaktivacija primer potreban odvrnuti poklopac izvaditi baterija ukoliko željeti uvek moći ručno skenirati svoj okolina pronaći nepoznat uređaj praćenje stignuti nadogradnja potreban uraditi sledeći otvoriti settings pronađiti safety emergency opcija izaberiti unknown tracker alerts pritisnuti scan now dugme google kazati ručan skeniranje potreban 10 sekunda pronaći nepoznati uređaj ukoliko telefon išta pronaći raspolaganje isti opcija kod automatski skeniranje nažalost nov funkcija trenutno imati mogućnost detektovanje airtag uređaj vrijeme htjeti lista proširivati gedžet kompanija apple već nekoliko put tema svetski medij njegov lansiranje imati prilika čivati dobar loš stvar pratiti naš facebook instagram stranica twitter nalog uključite naš viber zajednica</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -601,12 +534,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zagreb, Hina, Hrvatska, OSV, Zagreb, Gospodarsko - socijalnog vijeće, Andrej Plenković, europski socijalan fond plus za razdoblje, hrvatski bratski zajednica 4, Vlada, Branko Bačić, Ivan Celjako, Siska, Žitnoj ulica, nov interan, Opće bolnica, Ivo Pedišić, Ivan Pedišić, ulica Marijan Celjak, Zagreb, konferencija, Socijaldemokrat grad Zagreb, Davor Bernardić, Zagreb, Tomašević, Matija Ljubek, Jarun, gallery Club, Zagreb, konferencija, zajedno - razvoj, Gradsko društvo Crvenog križ, Grado Zagreb, Gradsko društvo Crvenog križ, Ilica, Zagreb, policijski uprava zagrebački, Zagreb, služba prevencija PUZ - a, Velimir Tišma, NR Kina, republika Hrvatska, NJ.E. Qi Qianjin, policijski uprava zagrebački, ulica matica hrvatski 4, Robert Koren, Mario Vrandečić, Đurđa Beraković, hina@hina.hr, Hina</t>
+          <t>Hrvatska, Zagreb, Andrej Plenković, Branko Bačić, socijaldemokrat grad zagreba, Davor Bernardić, Zagreb, Zagreb, Zagreb, velimir tišma, Hrvatska, qianjin, ulica matica, vrandečić, Beraković</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Android, Bizportal.rs, T.Đ., Tweet Podeli Foto, valiantsin suprunovich, Android 6, Google, i / O, Apple, Google, Apple, Safety &amp; Emergency, Unknown Tracker Alerts, Scan now, Google, Apple, Facebook, Instagram, Twitter, Viber</t>
+          <t>Android, valiantsin suprunovich, Android 6, Apple Airtag, Google, apple, alerts, google, apple</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -616,32 +549,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava događaja Općeg servisa vijesti Hrvatska (OSV) za utorak, 25. srpnja: 
-	ZAGREB - Održat će se sjednica Gospodarsko-socijalnog vijeća na kojoj će biti i premijer Andrej Plenković. Između ostaloga, prezentirat će se prijedlog zakona o plaćama u državnoj službi i javnim službama te program Europskog socijalnog fonda plus za razdoblje 2021. - 2027. Snimatelji i fotoreporteri mogu snimiti početak sjednice nakon koje su predviđene izjave za medije (10 sati, Nacionalna i sveučilišna knjižnica, Hrvatske bratske zajednice 4).
-SISAK - Potpredsjednik Vlade i ministar prostornog uređenja, graditeljstva i državne imovine Branko Bačić, zajedno sa županom Ivanom Celjakom, posjetit će gradilišta na području Siska. Prvo će obići gradilišta konstrukcijske (samo)obnove višenamjenskih zgrada u Žitnoj ulici (10,15 sati), zatim zgradu Nove interne u krugu Opće bolnice "Dr. Ivo Pedišić" (11 sati, ulaz iz Ulice dr. Ivana Pedišića) koju obnavlja županija. Izjave za medije predviđene su u 11 sati nakon kojih će obići gradilište zamjenske obiteljske kuće (11,45 sati, Ulica Marijana Celjaka 150).
-ZAGREB - Konferencija za novinare Socijaldemokrata Grada Zagreba na kojoj će predsjednik Davor Bernardić sa suradnicima govoriti o prijedlozima za Zagreb bez ambrozije i, kako kaže, novim aferama gradonačelnika Tomaševića. Odgovarat će i na ostala nacionalna politička pitanja (9 sati, Aleja Matije Ljubeka na Jarunu, ispred Gallery Cluba).
-ZAGREB - Konferencija za novinare povodom završetka europskog projekta "Zajedno - razvoj vođen zajednicom" kojeg je zagrebačkog Gradsko društvo Crvenog križa provelo u suradnji s Gradom Zagrebom. Projekt je proveden radi jačanja sustava volonterstva i kapaciteta za pružanje učinkovitog odgovora na potrebe lokalne zajednice u kriznim situacijama te poboljšanja koordiniranog pristupa u rješavanju problema i izlazu iz krize (10 sati, Gradsko društvo Crvenog križa, Ilica 223).
-ZAGREB - Tematska konferencija za medije Policijske uprave zagrebačke povodom provedbe projekta "Sigurna turistička destinacija" na kojoj će biti predstavljen početak rada zajedničkih hrvatsko-korejskih i hrvatsko-kineskih policijskih ophodnji u gradu Zagrebu. Govorit će voditelj Službe prevencije PUZ-a Velimir Tišma i veleposlanik NR Kine u Republici Hrvatskoj NJ.E. Qi Qianjin (10 sati, Policijska uprava zagrebačka, Ulica Matice hrvatske 4).
-Dežurni urednici na desku OSV-a:
-prijepodne - Robert Koren
-poslijepodne - Mario Vrandečić
-navečer - Đurđa Beraković
-telefon: 01/48 08 600
-telefaks: 01/48 08 822
-e-mail: hina@hina.hr
-(Hina) xmhud ybdj
-</t>
+          <t>Zagreb srpanj 2023 hin najava događaj opći servis vijest Hrvatska osvti utorak srpanj Zagreb održati htjeti sjednica vijeće koji htjeti premijer Andrej Plenković između ostali prezentirati htjeti prijedlog zakon plaća državni služba javan služba program europski socijalan fond plus razdoblje 2021 2027 snimatelj fotoreporter moći snimiti početak sjednica predviđen izjava medij 10 sat nacionalan sveučilišni knjižnica hrvatski bratski zajednica 4 sisak potpredsjednik vlada ministar prostoran uređenje graditeljstvo državni imovina Branko Bačić zajedno župan ivan celjaka posjetiti htjeti gradilište područje siski prvo htjeti obići gradilište konstrukcijski obnova višenamjenski zgrada žitnoj ulica sat zatim zgrada nov interni krug opći bolnica Ivo pedišić 11 sat ulaz ulica ivati pedišić obnavljati županija izjava medij predviđen 11 sat koji htjeti obići gradilište zamjenski obiteljski kuća sat ulica marijan celjak 150 Zagreb konferencija novinar socijaldemokrat grad zagreba koji htjeti predsjednik Davor Bernardić suradnik govoriti prijedlozima Zagreb bez ambrozija kazati nov afera gradonačelnik tomaševića odgovarati htjeti ostali nacionalan politički pitanje 9 sat alej matija ljubeak jaruna ispred gallery club Zagreb konferencija novinar povodom završetak europski projekt zajedno razvoj voditi zajednica koji zagrebački gradski društvo crvean križ proveti suradnja grad zagreba projekt provediti radi jačanje sustav volonterstvo kapacitet pružanje učinkovit odgovor potreba lokalan zajednica krizan situacija poboljšanje koordiniran pristup rješavanje problem izlaz kriza 10 sat gradski društvo crvean križ ilica 223 Zagreb tematski konferencija medij policijski uprava zagrebački povodom provedba projekt siguran turistički destinacija koji htjeti predstaviti početak rad zajednički policijski ophodnja grad Zagreb govoriti htjeti voditelj služba prevencija velimir tišma veleposlanik nr kinuti republika Hrvatska qi qianjin 10 sat policijski uprava zagrebački ulica matica hrvatski 4 dežuran urednik deski prijepodne robert koren poslijepodne mariti vrandečić navečer đurđa Beraković telefon 08 600 telefaks 08 822 hin hina xmhud ybdj</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Podijeli :
-N1
-Budite uz “Dan uživo” i ovog popodneva. Pratimo sjednicu Vlade FBiH na kojoj će se raspravljati i o zahtjevima rudara, iznesenim juče ispred uprave Elektroprivrede BiH. Uživo smo u Visokom, gdje se danas proslavlja Ilindan, odnosno Aliđun.
-Zahtjev za hitnu sjednicu NSRS, odnos SNSD-a prema odlukama donesenim u ovom zakonodavnom tijelu, nova imena na crnoj listi SAD, nezastupljenost istočnog dijela RS u Vladi Radovana Viškovića – teme su za razgovor sa Darkom Berjanom, poslanikom SDS-a u NSRS.
-O setu energetskih zakona za čije usvajanje se zalagala od 2019. godine, rebalansu federalnog budžeta, raspodjeli novca za kulturu, eventualnoj prekompoziciji većine u Skupštini KS, najavljenom pokretanju opoziva načelnika sarajevske opštine Centar Srđana Mandića – razgovaramo sa Sanelom Klarić, zastupnicom Naše stranke u Skupštini KS i delegatom u Domu naroda Parlamenta FBiH.
-Sinošnji remi u Bratislavi nije bio dovoljan fudbalerima Zrinjskog za nastavak puta ka Ligi prvaka. Željezničar će sutra u Bakuu pokušati da eliminiše Neftchi, a banjalučki Borac dočekuje Austriju, u pokušaju da nadoknadi gol prednosti koji Bečlije imaju iz prvog meča. Sve analizira sportski novinar Sinan Sinanović.
-Mladi Mostarac Adi Šoše nakon sjajnih koncerata u Mostaru, Zagrebu, Podgorici i drugim gradovima regiona stiže u Sarajevo. O pretstojećem koncertu, novoj pjesmu „Najljepši cvijet“ kojom se predstavio i na festivalu „Melodije Jadrana“ u Splitu, albumu – sa Adijem govorimo u muzičkim minutama današnje emisije.</t>
+          <t>podijeliti n1 budite dan uživo ovaj popodnev pratiti sjednica vlada fbih koji htjeti raspravljati zahtjev rudar iznesenim juča ispred uprava elektroprivreda uživo visok gdje danas proslavljati ilindan odnosno aliđun zahtjev hitan sjednica nsrs odnos prema odluka doneseti ovaj zakonodavni tijelo nov ime crn lista sad nezastupljenost istočni dio rs vlada radovan višković tema razgovor dark berjan poslanik nsrs set energetski zakon čiji usvajanje zalagati godina rebalans federalan budžet raspodjela novac kultura eventualan prekompozicija većina skupština ks najavljen pokretanje opoziv načelnik sarajevski opština centar srđana mandić razgovarati sanel klarić zastupnica naš stranka skupština ks delegat dom narod parlament fbih sinošnj rem bratislav dovoljan fudbalerima zrinjski nastavak put k liga prvak željezničar htjeti sutra bakuu pokušati eliminiši neftchi banjalučki borac dočekivati austrija pokušaj nadoknad gol prednost bečlija imati prvi meč analizirati sportski novinar sinan Sinanović mlad mostarac adi šoša sjajan koncert mostar Zagreb podgorika drugi grad region stizati sarajevo pretstojeć koncert nov pjesma najljepši cvijet koji predstaviti festival melodija jadran splitu album adijem govoriti muzički minuta današnji emisija</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -652,54 +565,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zagreb, Hina, Hrvatska, OSV, Zagreb, Gospodarsko - socijalnog vijeće, Andrej Plenković, europski socijalan fond plus za razdoblje, hrvatski bratski zajednica 4, Vlada, Branko Bačić, Ivan Celjako, Siska, Žitnoj ulica, nov interan, Opće bolnica, Ivo Pedišić, Ivan Pedišić, ulica Marijan Celjak, Zagreb, konferencija, Socijaldemokrat grad Zagreb, Davor Bernardić, Zagreb, Tomašević, Matija Ljubek, Jarun, gallery Club, Zagreb, konferencija, zajedno - razvoj, Gradsko društvo Crvenog križ, Grado Zagreb, Gradsko društvo Crvenog križ, Ilica, Zagreb, policijski uprava zagrebački, Zagreb, služba prevencija PUZ - a, Velimir Tišma, NR Kina, republika Hrvatska, NJ.E. Qi Qianjin, policijski uprava zagrebački, ulica matica hrvatski 4, Robert Koren, Mario Vrandečić, Đurđa Beraković, hina@hina.hr, Hina</t>
+          <t>Hrvatska, Zagreb, Andrej Plenković, Branko Bačić, socijaldemokrat grad zagreba, Davor Bernardić, Zagreb, Zagreb, Zagreb, velimir tišma, Hrvatska, qianjin, ulica matica, vrandečić, Beraković</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>N1, dan uživo, Vlada FBiH, Elektroprivrede BiH., Visokom, Ilindan, aliđun, nSRS, SNSD - a, crn lista SAD, RS, Vlada, Radovan Višković, Darko Berjan, SDS - a, nSRS, Skupština KS, Srđan Mandić, Sanel Klarić, naš stranka, Skupština KS, Domu narod Parlament FBiH. 
- Sinošnji rem, Bratislavi, zrinjski, Ligi prvak, Bakuu, Neftchi, Borac, Austrija, Bečlija, Sinan Sinanović, Mostarac, Adi Šoše, Mostar, Zagreb, Podgorica, Sarajevo, Najljepši cvijet, Melodija Jadrana, Split, Adij</t>
+          <t>srđati mandić, fbih sinošnj, Bratislav, Austrija, Sinan Sinanović, Zagreb</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.02597402597402598</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava događaja Općeg servisa vijesti Hrvatska (OSV) za utorak, 25. srpnja: 
-	ZAGREB - Održat će se sjednica Gospodarsko-socijalnog vijeća na kojoj će biti i premijer Andrej Plenković. Između ostaloga, prezentirat će se prijedlog zakona o plaćama u državnoj službi i javnim službama te program Europskog socijalnog fonda plus za razdoblje 2021. - 2027. Snimatelji i fotoreporteri mogu snimiti početak sjednice nakon koje su predviđene izjave za medije (10 sati, Nacionalna i sveučilišna knjižnica, Hrvatske bratske zajednice 4).
-SISAK - Potpredsjednik Vlade i ministar prostornog uređenja, graditeljstva i državne imovine Branko Bačić, zajedno sa županom Ivanom Celjakom, posjetit će gradilišta na području Siska. Prvo će obići gradilišta konstrukcijske (samo)obnove višenamjenskih zgrada u Žitnoj ulici (10,15 sati), zatim zgradu Nove interne u krugu Opće bolnice "Dr. Ivo Pedišić" (11 sati, ulaz iz Ulice dr. Ivana Pedišića) koju obnavlja županija. Izjave za medije predviđene su u 11 sati nakon kojih će obići gradilište zamjenske obiteljske kuće (11,45 sati, Ulica Marijana Celjaka 150).
-ZAGREB - Konferencija za novinare Socijaldemokrata Grada Zagreba na kojoj će predsjednik Davor Bernardić sa suradnicima govoriti o prijedlozima za Zagreb bez ambrozije i, kako kaže, novim aferama gradonačelnika Tomaševića. Odgovarat će i na ostala nacionalna politička pitanja (9 sati, Aleja Matije Ljubeka na Jarunu, ispred Gallery Cluba).
-ZAGREB - Konferencija za novinare povodom završetka europskog projekta "Zajedno - razvoj vođen zajednicom" kojeg je zagrebačkog Gradsko društvo Crvenog križa provelo u suradnji s Gradom Zagrebom. Projekt je proveden radi jačanja sustava volonterstva i kapaciteta za pružanje učinkovitog odgovora na potrebe lokalne zajednice u kriznim situacijama te poboljšanja koordiniranog pristupa u rješavanju problema i izlazu iz krize (10 sati, Gradsko društvo Crvenog križa, Ilica 223).
-ZAGREB - Tematska konferencija za medije Policijske uprave zagrebačke povodom provedbe projekta "Sigurna turistička destinacija" na kojoj će biti predstavljen početak rada zajedničkih hrvatsko-korejskih i hrvatsko-kineskih policijskih ophodnji u gradu Zagrebu. Govorit će voditelj Službe prevencije PUZ-a Velimir Tišma i veleposlanik NR Kine u Republici Hrvatskoj NJ.E. Qi Qianjin (10 sati, Policijska uprava zagrebačka, Ulica Matice hrvatske 4).
-Dežurni urednici na desku OSV-a:
-prijepodne - Robert Koren
-poslijepodne - Mario Vrandečić
-navečer - Đurđa Beraković
-telefon: 01/48 08 600
-telefaks: 01/48 08 822
-e-mail: hina@hina.hr
-(Hina) xmhud ybdj
-</t>
+          <t>Zagreb srpanj 2023 hin najava događaj opći servis vijest Hrvatska osvti utorak srpanj Zagreb održati htjeti sjednica vijeće koji htjeti premijer Andrej Plenković između ostali prezentirati htjeti prijedlog zakon plaća državni služba javan služba program europski socijalan fond plus razdoblje 2021 2027 snimatelj fotoreporter moći snimiti početak sjednica predviđen izjava medij 10 sat nacionalan sveučilišni knjižnica hrvatski bratski zajednica 4 sisak potpredsjednik vlada ministar prostoran uređenje graditeljstvo državni imovina Branko Bačić zajedno župan ivan celjaka posjetiti htjeti gradilište područje siski prvo htjeti obići gradilište konstrukcijski obnova višenamjenski zgrada žitnoj ulica sat zatim zgrada nov interni krug opći bolnica Ivo pedišić 11 sat ulaz ulica ivati pedišić obnavljati županija izjava medij predviđen 11 sat koji htjeti obići gradilište zamjenski obiteljski kuća sat ulica marijan celjak 150 Zagreb konferencija novinar socijaldemokrat grad zagreba koji htjeti predsjednik Davor Bernardić suradnik govoriti prijedlozima Zagreb bez ambrozija kazati nov afera gradonačelnik tomaševića odgovarati htjeti ostali nacionalan politički pitanje 9 sat alej matija ljubeak jaruna ispred gallery club Zagreb konferencija novinar povodom završetak europski projekt zajedno razvoj voditi zajednica koji zagrebački gradski društvo crvean križ proveti suradnja grad zagreba projekt provediti radi jačanje sustav volonterstvo kapacitet pružanje učinkovit odgovor potreba lokalan zajednica krizan situacija poboljšanje koordiniran pristup rješavanje problem izlaz kriza 10 sat gradski društvo crvean križ ilica 223 Zagreb tematski konferencija medij policijski uprava zagrebački povodom provedba projekt siguran turistički destinacija koji htjeti predstaviti početak rad zajednički policijski ophodnja grad Zagreb govoriti htjeti voditelj služba prevencija velimir tišma veleposlanik nr kinuti republika Hrvatska qi qianjin 10 sat policijski uprava zagrebački ulica matica hrvatski 4 dežuran urednik deski prijepodne robert koren poslijepodne mariti vrandečić navečer đurđa Beraković telefon 08 600 telefaks 08 822 hin hina xmhud ybdj</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Android telefoni će automatski, ali i ručno moći da skeniraju okolinu kako bi pronašli nepoznate uređaje za praćenje.
-Pametni telefoni koji pokreću Android 6 ili noviji operativni sistem sada dobijaju ažuriranje koje će im omogućiti da prepoznaju da li nas neko prati.
-Ukoliko je to slučaj, dobićemo upozorenje o nepoznatom uređaju za praćenje koji putuje sa nama.
-Google je ovu funkciju najavio na svom I/O događaju održanom u maju, kao odgovor na sve veći broj slučajeva digitalnog uhođenja pomoću namjenskih uređaja kao što je Apple AirTag. Zapravo, Google i Apple su blisko sarađivali na ovom projektu.
-Ažurirani telefoni će sada automatski moći da prepoznaju da li se sa nama kreće nepoznati bluetooth uređaj za praćenje, ali ne i njegov vlasnik, a kada se to desi, dobićemo notifikaciju, ali i mogućnost da saznamo više. Ovo uključuje mapu na kojoj će biti prikazana ruta po kojoj nas je takav uređaj pratio, a u nekim slučajevima i serijski broj uređaja, kao i informacije o njegovom vlasniku.
-Naravno, ovo neće biti previše korisno ukoliko ne možemo da lociramo nepoznati uređaj za praćenje, te će nam na raspolaganju biti opcija za aktiviranje njegovog zvučnog signala, kao i uputstvo za deaktivaciju. Na primjer, AirTag-u je potrebno odvrnuti poklopac i izvaditi bateriju.
-Ukoliko to želimo, uvijek možemo i ručno skenirati svoju okolinu kako bi pronašli nepoznate uređaje za praćenje. Kada stigne nadogradnja, potrebno je uraditi sljedeće:
-Otvorite “Settings”
-Pronađite “Safety &amp; Emergency” opciju
-Izaberite “Unknown Tracker Alerts”
-Pritisnite “Scan now” dugme
-Google kaže da je za ručno skeniranje potrebno samo 10 sekundi kako bi pronašao nepoznati uređaj, a ukoliko telefon išta pronađe, na raspolaganju su iste opcije kao i kod automatskog skeniranja.
-Nažalost, nova funkcija trenutno ima mogućnost detektovanja samo AirTag uređaja, ali vremenom će se lista proširivati. Gedžet kompanije Apple je već nekoliko puta bio tema svjetskih medija, te smo nakon njegovog lansiranja imali priliku da čujemo i dobre, ali i loše stvari, prenosi b92.</t>
+          <t>android telefon htjeti automatski ručno moći skenirati okolina pronaći nepoznat uređaj praćenje pametan telefon pokretati android 6 nov operativan sistem sada dobijati ažuriranje htjeti oni omogućiti prepoznati neko pratiti ukoliko slučaj dobićemo upozorenje nepoznat uređaj praćenje putovati google ovaj funkcija najaviti događaj održati mati odgovor velik broj slučaj digitalan uhođenje pomoću namjenski uređaj što Apple Airtag zapravo Google apple blisko sarađivati ovaj projekt ažuriran telefon htjeti sada automatski moći prepoznati kretati nepoznat bluetooth uređaj praćenje vlasnik desiti dobićemo notifikacija mogućnost saznamo mnogo ovaj uključivati mapa koji htjeti prikazati ruta koji takav uređaj pratiti neki slučaj serijski broj uređaj informacija njegov vlasnik naravno ovaj htjeti previše korisan ukoliko moći locirati nepoznati uređaj praćenje htjeti raspolaganje opcija aktiviranje njegov zvučan signal uputstvo deaktivacija primjer potreban odvrnuti poklopac izvaditi baterija ukoliko željeti uvijek moći ručno skenirati svoj okolina pronaći nepoznat uređaj praćenje stignuti nadogradnja potreban uraditi sljedeći otvoriti settings pronađiti safety emergency opcija izaberiti unknown tracker alerts pritisnuti scan now dugme google kazati ručan skeniranje potreban 10 sekunda pronaći nepoznati uređaj ukoliko telefon išta pronaći raspolaganje isti opcija kod automatski skeniranje nažalost nov funkcija trenutno imati mogućnost detektovanje airtag uređaj vrijeme htjeti lista proširivati gedžet kompanija apple već nekoliko put tema svjetski medij njegov lansiranje imati prilika čivati dobar loš stvar prenositi B92</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -710,13 +596,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zagreb, Hina, Hrvatska, OSV, Zagreb, Gospodarsko - socijalnog vijeće, Andrej Plenković, europski socijalan fond plus za razdoblje, hrvatski bratski zajednica 4, Vlada, Branko Bačić, Ivan Celjako, Siska, Žitnoj ulica, nov interan, Opće bolnica, Ivo Pedišić, Ivan Pedišić, ulica Marijan Celjak, Zagreb, konferencija, Socijaldemokrat grad Zagreb, Davor Bernardić, Zagreb, Tomašević, Matija Ljubek, Jarun, gallery Club, Zagreb, konferencija, zajedno - razvoj, Gradsko društvo Crvenog križ, Grado Zagreb, Gradsko društvo Crvenog križ, Ilica, Zagreb, policijski uprava zagrebački, Zagreb, služba prevencija PUZ - a, Velimir Tišma, NR Kina, republika Hrvatska, NJ.E. Qi Qianjin, policijski uprava zagrebački, ulica matica hrvatski 4, Robert Koren, Mario Vrandečić, Đurđa Beraković, hina@hina.hr, Hina</t>
+          <t>Hrvatska, Zagreb, Andrej Plenković, Branko Bačić, socijaldemokrat grad zagreba, Davor Bernardić, Zagreb, Zagreb, Zagreb, velimir tišma, Hrvatska, qianjin, ulica matica, vrandečić, Beraković</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Android, Android 6, Google, i / O, Apple, Google, Apple, Safety &amp; Emergency, opcija 
- izaberitei, Scan now, Google, Apple, B92</t>
+          <t>Android, Android 6, Apple Airtag, Google, apple, alerts, google, apple, B92</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -726,34 +611,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava događaja Općeg servisa vijesti Hrvatska (OSV) za utorak, 25. srpnja: 
-	ZAGREB - Održat će se sjednica Gospodarsko-socijalnog vijeća na kojoj će biti i premijer Andrej Plenković. Između ostaloga, prezentirat će se prijedlog zakona o plaćama u državnoj službi i javnim službama te program Europskog socijalnog fonda plus za razdoblje 2021. - 2027. Snimatelji i fotoreporteri mogu snimiti početak sjednice nakon koje su predviđene izjave za medije (10 sati, Nacionalna i sveučilišna knjižnica, Hrvatske bratske zajednice 4).
-SISAK - Potpredsjednik Vlade i ministar prostornog uređenja, graditeljstva i državne imovine Branko Bačić, zajedno sa županom Ivanom Celjakom, posjetit će gradilišta na području Siska. Prvo će obići gradilišta konstrukcijske (samo)obnove višenamjenskih zgrada u Žitnoj ulici (10,15 sati), zatim zgradu Nove interne u krugu Opće bolnice "Dr. Ivo Pedišić" (11 sati, ulaz iz Ulice dr. Ivana Pedišića) koju obnavlja županija. Izjave za medije predviđene su u 11 sati nakon kojih će obići gradilište zamjenske obiteljske kuće (11,45 sati, Ulica Marijana Celjaka 150).
-ZAGREB - Konferencija za novinare Socijaldemokrata Grada Zagreba na kojoj će predsjednik Davor Bernardić sa suradnicima govoriti o prijedlozima za Zagreb bez ambrozije i, kako kaže, novim aferama gradonačelnika Tomaševića. Odgovarat će i na ostala nacionalna politička pitanja (9 sati, Aleja Matije Ljubeka na Jarunu, ispred Gallery Cluba).
-ZAGREB - Konferencija za novinare povodom završetka europskog projekta "Zajedno - razvoj vođen zajednicom" kojeg je zagrebačkog Gradsko društvo Crvenog križa provelo u suradnji s Gradom Zagrebom. Projekt je proveden radi jačanja sustava volonterstva i kapaciteta za pružanje učinkovitog odgovora na potrebe lokalne zajednice u kriznim situacijama te poboljšanja koordiniranog pristupa u rješavanju problema i izlazu iz krize (10 sati, Gradsko društvo Crvenog križa, Ilica 223).
-ZAGREB - Tematska konferencija za medije Policijske uprave zagrebačke povodom provedbe projekta "Sigurna turistička destinacija" na kojoj će biti predstavljen početak rada zajedničkih hrvatsko-korejskih i hrvatsko-kineskih policijskih ophodnji u gradu Zagrebu. Govorit će voditelj Službe prevencije PUZ-a Velimir Tišma i veleposlanik NR Kine u Republici Hrvatskoj NJ.E. Qi Qianjin (10 sati, Policijska uprava zagrebačka, Ulica Matice hrvatske 4).
-Dežurni urednici na desku OSV-a:
-prijepodne - Robert Koren
-poslijepodne - Mario Vrandečić
-navečer - Đurđa Beraković
-telefon: 01/48 08 600
-telefaks: 01/48 08 822
-e-mail: hina@hina.hr
-(Hina) xmhud ybdj
-</t>
+          <t>Zagreb srpanj 2023 hin najava događaj opći servis vijest Hrvatska osvti utorak srpanj Zagreb održati htjeti sjednica vijeće koji htjeti premijer Andrej Plenković između ostali prezentirati htjeti prijedlog zakon plaća državni služba javan služba program europski socijalan fond plus razdoblje 2021 2027 snimatelj fotoreporter moći snimiti početak sjednica predviđen izjava medij 10 sat nacionalan sveučilišni knjižnica hrvatski bratski zajednica 4 sisak potpredsjednik vlada ministar prostoran uređenje graditeljstvo državni imovina Branko Bačić zajedno župan ivan celjaka posjetiti htjeti gradilište područje siski prvo htjeti obići gradilište konstrukcijski obnova višenamjenski zgrada žitnoj ulica sat zatim zgrada nov interni krug opći bolnica Ivo pedišić 11 sat ulaz ulica ivati pedišić obnavljati županija izjava medij predviđen 11 sat koji htjeti obići gradilište zamjenski obiteljski kuća sat ulica marijan celjak 150 Zagreb konferencija novinar socijaldemokrat grad zagreba koji htjeti predsjednik Davor Bernardić suradnik govoriti prijedlozima Zagreb bez ambrozija kazati nov afera gradonačelnik tomaševića odgovarati htjeti ostali nacionalan politički pitanje 9 sat alej matija ljubeak jaruna ispred gallery club Zagreb konferencija novinar povodom završetak europski projekt zajedno razvoj voditi zajednica koji zagrebački gradski društvo crvean križ proveti suradnja grad zagreba projekt provediti radi jačanje sustav volonterstvo kapacitet pružanje učinkovit odgovor potreba lokalan zajednica krizan situacija poboljšanje koordiniran pristup rješavanje problem izlaz kriza 10 sat gradski društvo crvean križ ilica 223 Zagreb tematski konferencija medij policijski uprava zagrebački povodom provedba projekt siguran turistički destinacija koji htjeti predstaviti početak rad zajednički policijski ophodnja grad Zagreb govoriti htjeti voditelj služba prevencija velimir tišma veleposlanik nr kinuti republika Hrvatska qi qianjin 10 sat policijski uprava zagrebački ulica matica hrvatski 4 dežuran urednik deski prijepodne robert koren poslijepodne mariti vrandečić navečer đurđa Beraković telefon 08 600 telefaks 08 822 hin hina xmhud ybdj</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Španski arhitektonski studio "Frenvik Iribaren" dobio je zadatak da osmisli kompletan izgled i izgradi ovo zdanje. Reč je o stručnjacima koji su kreirali tri od ukupno osam stadiona sa poslednjeg Mundijala u Kataru, među kojima je i čuveni "974", koji je bio sagrađen od recikliranih kontejnera, a nakon takmičenja je razmontiran.
-Španski portal "Metalocus" otkrio je nove, do sad nepoznate detalje u vezi sa stadionom na kome će igrati "orlovi".
-"Ovo će biti jedinstven arhitektonski poduhvat i prvi 'bašta stadion'. Biće kružnog oblika, sa kapacitetom od 52.000 sedećih mesta, a njegovu prirodnu fasadu činiće četiri prstena, pričvršćena kosim kablovima i ukrašena zelenilom", piše pomenuti portal, prenose Novosti.
-Ukupna površina na kojoj će biti izgrađen stadion je 32 hektara. Tu će se nalazi kafići, 4.500 parking mesta, kiosci, restorani...
-"Studio 'Frenvik Iribaren' će ovaj projekat učiniti jednim od najinovativnijih u sektoru dizajna fudbalskih stadiona. Cilj projektanata je da stadion živi 365 dana u godini, kako bi Beograđani, ali i turisti mogli da uživaju u prirodnom okruženju i ostalim pratećim objektima."
-Osim toga, vodiće se računa i o poštovanju životne sredine, kao i tehničkim stavrima poput grejanja i hlađenja.
-"Osmišljen je inovativni sistem, koji je zasnovan na tehnologiji četvorocevnih 'kulera' i aerotermalnih pumpi. To znači da će se toplota stvorena u procesu hlađenja koristiti za proizvodnju tople vode za grejanje, a pumpe će obezbediti grejanje ili hlađenje u zavisnosti od potrebe sistema", otkriva "Metalokus".
-Podsetimo da će planirana izgradnja Nacionalnog stadiona, kako je Nova ekonomija ranije pisala, samo u 2023. godini koštati oko 65 miliona evra, a da poreskim obveznicima nije javno pokazana njegova ekonomska isplativost, naveo je Fiskalni savet početkom decembra u oceni predloga budžeta za 2023. godinu.
-Takođe, prema ranijim pisanjima, od prvobitne procene da će nas ovaj objekat koštati 250 miliona evra, stiglo se i do cifre od 540 miliona evra.</t>
+          <t>španski arhitektonski studio frenvik iribaren dobiti zadatak osmisliti kompletan izgled izgraditi ovaj zdanje reč stručnjak kreirati tri ukupno osam stadion poslednji mundijal katar među čuven 974 sagraditi recikliraan kontejner takmičenje razmontirati španski portal Metalocus otkriti nov sad nepoznat detalj vezi stadion kaj htjeti igrati orl ovaj htjeti jedinstven arhitektonski poduhvat prvi stadion biće kružni oblik kapacitet sedeći mesto njegov prirodan fasada činićiti četiri prsten pričvršćiti kosim kablove ukrašen zelenila pisati pomenuti portal prenositi novost ukupan površina koji htjeti izgraditi stadion 32 hektar htjeti nalaziti kafić parking mesto kiosac restoran studio iribaren htjeti ovaj projekat učiniti jedan najinovativnijih sektor dizajn fudbalski stadion cilj projektanat stadion živjeti 365 dan godina beograđan turist moći uživati prirodan okruženje ostali prateći objekt osim taj vodića račun poštovanje životan sredina tehnički stavr poput grejanje hlađenje osmišiti inovativan sistem zasnovati tehnologija četvorocevn aerotermaln pumpa značiti htjeti toplota stvorena proces hlađenje koristiti proizvodnja tople voda grejanje pumpa htjeti obezbediti grejanje hlađenje zavisnost potreba sistem otkrivati metalokus podsetiti htjeti planirati izgradnja nacionalan stadion nov ekonomija rano pisati godina koštati oko 65 milion evro poreski obveznik javno pokazati ekonomski isplativost navesti fiskalan savet početkom decembra ocena predlog budžet godina takođe prema raan pisanj prvobitan procena htjeti ovaj objekat koštati 250 milion evra stići cifra 540 milion evro</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -764,12 +627,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zagreb, Hina, Hrvatska, OSV, Zagreb, Gospodarsko - socijalnog vijeće, Andrej Plenković, europski socijalan fond plus za razdoblje, hrvatski bratski zajednica 4, Vlada, Branko Bačić, Ivan Celjako, Siska, Žitnoj ulica, nov interan, Opće bolnica, Ivo Pedišić, Ivan Pedišić, ulica Marijan Celjak, Zagreb, konferencija, Socijaldemokrat grad Zagreb, Davor Bernardić, Zagreb, Tomašević, Matija Ljubek, Jarun, gallery Club, Zagreb, konferencija, zajedno - razvoj, Gradsko društvo Crvenog križ, Grado Zagreb, Gradsko društvo Crvenog križ, Ilica, Zagreb, policijski uprava zagrebački, Zagreb, služba prevencija PUZ - a, Velimir Tišma, NR Kina, republika Hrvatska, NJ.E. Qi Qianjin, policijski uprava zagrebački, ulica matica hrvatski 4, Robert Koren, Mario Vrandečić, Đurđa Beraković, hina@hina.hr, Hina</t>
+          <t>Hrvatska, Zagreb, Andrej Plenković, Branko Bačić, socijaldemokrat grad zagreba, Davor Bernardić, Zagreb, Zagreb, Zagreb, velimir tišma, Hrvatska, qianjin, ulica matica, vrandečić, Beraković</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Frenvik Iribaren, Mundijal, Katar, Metalocus, novosti, Frenvik Iribaren, Beograđani, Metalokus, nacionalan stadion, nov ekonomija, Fiskalni savet</t>
+          <t>Metalocus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -779,30 +642,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava događaja Općeg servisa vijesti Hrvatska (OSV) za utorak, 25. srpnja: 
-	ZAGREB - Održat će se sjednica Gospodarsko-socijalnog vijeća na kojoj će biti i premijer Andrej Plenković. Između ostaloga, prezentirat će se prijedlog zakona o plaćama u državnoj službi i javnim službama te program Europskog socijalnog fonda plus za razdoblje 2021. - 2027. Snimatelji i fotoreporteri mogu snimiti početak sjednice nakon koje su predviđene izjave za medije (10 sati, Nacionalna i sveučilišna knjižnica, Hrvatske bratske zajednice 4).
-SISAK - Potpredsjednik Vlade i ministar prostornog uređenja, graditeljstva i državne imovine Branko Bačić, zajedno sa županom Ivanom Celjakom, posjetit će gradilišta na području Siska. Prvo će obići gradilišta konstrukcijske (samo)obnove višenamjenskih zgrada u Žitnoj ulici (10,15 sati), zatim zgradu Nove interne u krugu Opće bolnice "Dr. Ivo Pedišić" (11 sati, ulaz iz Ulice dr. Ivana Pedišića) koju obnavlja županija. Izjave za medije predviđene su u 11 sati nakon kojih će obići gradilište zamjenske obiteljske kuće (11,45 sati, Ulica Marijana Celjaka 150).
-ZAGREB - Konferencija za novinare Socijaldemokrata Grada Zagreba na kojoj će predsjednik Davor Bernardić sa suradnicima govoriti o prijedlozima za Zagreb bez ambrozije i, kako kaže, novim aferama gradonačelnika Tomaševića. Odgovarat će i na ostala nacionalna politička pitanja (9 sati, Aleja Matije Ljubeka na Jarunu, ispred Gallery Cluba).
-ZAGREB - Konferencija za novinare povodom završetka europskog projekta "Zajedno - razvoj vođen zajednicom" kojeg je zagrebačkog Gradsko društvo Crvenog križa provelo u suradnji s Gradom Zagrebom. Projekt je proveden radi jačanja sustava volonterstva i kapaciteta za pružanje učinkovitog odgovora na potrebe lokalne zajednice u kriznim situacijama te poboljšanja koordiniranog pristupa u rješavanju problema i izlazu iz krize (10 sati, Gradsko društvo Crvenog križa, Ilica 223).
-ZAGREB - Tematska konferencija za medije Policijske uprave zagrebačke povodom provedbe projekta "Sigurna turistička destinacija" na kojoj će biti predstavljen početak rada zajedničkih hrvatsko-korejskih i hrvatsko-kineskih policijskih ophodnji u gradu Zagrebu. Govorit će voditelj Službe prevencije PUZ-a Velimir Tišma i veleposlanik NR Kine u Republici Hrvatskoj NJ.E. Qi Qianjin (10 sati, Policijska uprava zagrebačka, Ulica Matice hrvatske 4).
-Dežurni urednici na desku OSV-a:
-prijepodne - Robert Koren
-poslijepodne - Mario Vrandečić
-navečer - Đurđa Beraković
-telefon: 01/48 08 600
-telefaks: 01/48 08 822
-e-mail: hina@hina.hr
-(Hina) xmhud ybdj
-</t>
+          <t>Zagreb srpanj 2023 hin najava događaj opći servis vijest Hrvatska osvti utorak srpanj Zagreb održati htjeti sjednica vijeće koji htjeti premijer Andrej Plenković između ostali prezentirati htjeti prijedlog zakon plaća državni služba javan služba program europski socijalan fond plus razdoblje 2021 2027 snimatelj fotoreporter moći snimiti početak sjednica predviđen izjava medij 10 sat nacionalan sveučilišni knjižnica hrvatski bratski zajednica 4 sisak potpredsjednik vlada ministar prostoran uređenje graditeljstvo državni imovina Branko Bačić zajedno župan ivan celjaka posjetiti htjeti gradilište područje siski prvo htjeti obići gradilište konstrukcijski obnova višenamjenski zgrada žitnoj ulica sat zatim zgrada nov interni krug opći bolnica Ivo pedišić 11 sat ulaz ulica ivati pedišić obnavljati županija izjava medij predviđen 11 sat koji htjeti obići gradilište zamjenski obiteljski kuća sat ulica marijan celjak 150 Zagreb konferencija novinar socijaldemokrat grad zagreba koji htjeti predsjednik Davor Bernardić suradnik govoriti prijedlozima Zagreb bez ambrozija kazati nov afera gradonačelnik tomaševića odgovarati htjeti ostali nacionalan politički pitanje 9 sat alej matija ljubeak jaruna ispred gallery club Zagreb konferencija novinar povodom završetak europski projekt zajedno razvoj voditi zajednica koji zagrebački gradski društvo crvean križ proveti suradnja grad zagreba projekt provediti radi jačanje sustav volonterstvo kapacitet pružanje učinkovit odgovor potreba lokalan zajednica krizan situacija poboljšanje koordiniran pristup rješavanje problem izlaz kriza 10 sat gradski društvo crvean križ ilica 223 Zagreb tematski konferencija medij policijski uprava zagrebački povodom provedba projekt siguran turistički destinacija koji htjeti predstaviti početak rad zajednički policijski ophodnja grad Zagreb govoriti htjeti voditelj služba prevencija velimir tišma veleposlanik nr kinuti republika Hrvatska qi qianjin 10 sat policijski uprava zagrebački ulica matica hrvatski 4 dežuran urednik deski prijepodne robert koren poslijepodne mariti vrandečić navečer đurđa Beraković telefon 08 600 telefaks 08 822 hin hina xmhud ybdj</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U Runovićima kod Imotskog danas će se održati svečanost na kojoj će na nogometnom terenu biti otvoren pano s likovima trojice velikih igrača i reprezentativnih kapetana koji su ponikli u Mračaju iz Runovića - Ivana Buljana, Ivana Gudelja i Zvonimira Bobana.
-Program će biti zanimljiv, odigrat će se i revijalna utakmica, a očekuje se dolazak između 2000 i 3000 ljudi koji će pozdraviti uzvanike svečanosti. Također, dolaze i mnogi ljudi iz društveno-političkog života.
-Foto: Tomislav Gabelić/24sata
-Svečanosti će prisustvovati i HNS-ova delegacija predvođena izbornikom Zlatkom Dalićem, predsjednikom Marijanom Kustićem i izvršnim direktorom Tomislavom Svetinom, a među uzvanicima su se našli bivši hrvatski reprezentativci Igor Štimac, Aljoša Asanović, Alen Bokšić, Robert Jarni i Stanko Bubalo...
-Foto: Tomislav Gabelić/24sata</t>
+          <t>runovićima kod imotski danas htjeti održati svečanost koji htjeti nogometni teren otvoriti pano lik trojica velik igrač reprezentativn kapetan ponići mračati runović ivati buljan ivani gudelja zvonimir bobana program htjeti zanimljiv odigrati htjeti revijalni utakmica očekivati dolazak između 2000 3000 čovjek htjeti pozdraviti uzvanik svečanost također dolaziti mnogi čovjek život foto Tomislav svečanost htjeti prisustvovati delegacija predvoditi izbornik zlatk dalić predsjednik marijan kustić izvršn direktor tomislav svetina među uzvanik naći bivši hrvatski reprezentativac igor štimac Aljoša asanović alen bokšić robert jaran stanko bubati foto Tomislav</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -813,12 +658,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zagreb, Hina, Hrvatska, OSV, Zagreb, Gospodarsko - socijalnog vijeće, Andrej Plenković, europski socijalan fond plus za razdoblje, hrvatski bratski zajednica 4, Vlada, Branko Bačić, Ivan Celjako, Siska, Žitnoj ulica, nov interan, Opće bolnica, Ivo Pedišić, Ivan Pedišić, ulica Marijan Celjak, Zagreb, konferencija, Socijaldemokrat grad Zagreb, Davor Bernardić, Zagreb, Tomašević, Matija Ljubek, Jarun, gallery Club, Zagreb, konferencija, zajedno - razvoj, Gradsko društvo Crvenog križ, Grado Zagreb, Gradsko društvo Crvenog križ, Ilica, Zagreb, policijski uprava zagrebački, Zagreb, služba prevencija PUZ - a, Velimir Tišma, NR Kina, republika Hrvatska, NJ.E. Qi Qianjin, policijski uprava zagrebački, ulica matica hrvatski 4, Robert Koren, Mario Vrandečić, Đurđa Beraković, hina@hina.hr, Hina</t>
+          <t>Hrvatska, Zagreb, Andrej Plenković, Branko Bačić, socijaldemokrat grad zagreba, Davor Bernardić, Zagreb, Zagreb, Zagreb, velimir tišma, Hrvatska, qianjin, ulica matica, vrandečić, Beraković</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Runovićima, Imotski, Mračati, Ivan Buljan, Ivan Gudelj, Zvonimir Boban, Tomislav Gabelić/24sata, HNS - ova, Zlatko Dalić, Marijana Kustić, Tomislav Svetino, Igor Štimac, Aljoša Asanović, Alen Bokšić, Robert Jarni, Stanko Bubalo, Tomislav Gabelić/24sata</t>
+          <t>zvonimir bobana, Tomislav svečanost, zlatk dalić, marijan Kustić, Tomislav svetina, Igor štimac, Aljoša asanović alen bokšić</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -828,27 +673,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava događaja Općeg servisa vijesti Hrvatska (OSV) za utorak, 25. srpnja: 
-	ZAGREB - Održat će se sjednica Gospodarsko-socijalnog vijeća na kojoj će biti i premijer Andrej Plenković. Između ostaloga, prezentirat će se prijedlog zakona o plaćama u državnoj službi i javnim službama te program Europskog socijalnog fonda plus za razdoblje 2021. - 2027. Snimatelji i fotoreporteri mogu snimiti početak sjednice nakon koje su predviđene izjave za medije (10 sati, Nacionalna i sveučilišna knjižnica, Hrvatske bratske zajednice 4).
-SISAK - Potpredsjednik Vlade i ministar prostornog uređenja, graditeljstva i državne imovine Branko Bačić, zajedno sa županom Ivanom Celjakom, posjetit će gradilišta na području Siska. Prvo će obići gradilišta konstrukcijske (samo)obnove višenamjenskih zgrada u Žitnoj ulici (10,15 sati), zatim zgradu Nove interne u krugu Opće bolnice "Dr. Ivo Pedišić" (11 sati, ulaz iz Ulice dr. Ivana Pedišića) koju obnavlja županija. Izjave za medije predviđene su u 11 sati nakon kojih će obići gradilište zamjenske obiteljske kuće (11,45 sati, Ulica Marijana Celjaka 150).
-ZAGREB - Konferencija za novinare Socijaldemokrata Grada Zagreba na kojoj će predsjednik Davor Bernardić sa suradnicima govoriti o prijedlozima za Zagreb bez ambrozije i, kako kaže, novim aferama gradonačelnika Tomaševića. Odgovarat će i na ostala nacionalna politička pitanja (9 sati, Aleja Matije Ljubeka na Jarunu, ispred Gallery Cluba).
-ZAGREB - Konferencija za novinare povodom završetka europskog projekta "Zajedno - razvoj vođen zajednicom" kojeg je zagrebačkog Gradsko društvo Crvenog križa provelo u suradnji s Gradom Zagrebom. Projekt je proveden radi jačanja sustava volonterstva i kapaciteta za pružanje učinkovitog odgovora na potrebe lokalne zajednice u kriznim situacijama te poboljšanja koordiniranog pristupa u rješavanju problema i izlazu iz krize (10 sati, Gradsko društvo Crvenog križa, Ilica 223).
-ZAGREB - Tematska konferencija za medije Policijske uprave zagrebačke povodom provedbe projekta "Sigurna turistička destinacija" na kojoj će biti predstavljen početak rada zajedničkih hrvatsko-korejskih i hrvatsko-kineskih policijskih ophodnji u gradu Zagrebu. Govorit će voditelj Službe prevencije PUZ-a Velimir Tišma i veleposlanik NR Kine u Republici Hrvatskoj NJ.E. Qi Qianjin (10 sati, Policijska uprava zagrebačka, Ulica Matice hrvatske 4).
-Dežurni urednici na desku OSV-a:
-prijepodne - Robert Koren
-poslijepodne - Mario Vrandečić
-navečer - Đurđa Beraković
-telefon: 01/48 08 600
-telefaks: 01/48 08 822
-e-mail: hina@hina.hr
-(Hina) xmhud ybdj
-</t>
+          <t>Zagreb srpanj 2023 hin najava događaj opći servis vijest Hrvatska osvti utorak srpanj Zagreb održati htjeti sjednica vijeće koji htjeti premijer Andrej Plenković između ostali prezentirati htjeti prijedlog zakon plaća državni služba javan služba program europski socijalan fond plus razdoblje 2021 2027 snimatelj fotoreporter moći snimiti početak sjednica predviđen izjava medij 10 sat nacionalan sveučilišni knjižnica hrvatski bratski zajednica 4 sisak potpredsjednik vlada ministar prostoran uređenje graditeljstvo državni imovina Branko Bačić zajedno župan ivan celjaka posjetiti htjeti gradilište područje siski prvo htjeti obići gradilište konstrukcijski obnova višenamjenski zgrada žitnoj ulica sat zatim zgrada nov interni krug opći bolnica Ivo pedišić 11 sat ulaz ulica ivati pedišić obnavljati županija izjava medij predviđen 11 sat koji htjeti obići gradilište zamjenski obiteljski kuća sat ulica marijan celjak 150 Zagreb konferencija novinar socijaldemokrat grad zagreba koji htjeti predsjednik Davor Bernardić suradnik govoriti prijedlozima Zagreb bez ambrozija kazati nov afera gradonačelnik tomaševića odgovarati htjeti ostali nacionalan politički pitanje 9 sat alej matija ljubeak jaruna ispred gallery club Zagreb konferencija novinar povodom završetak europski projekt zajedno razvoj voditi zajednica koji zagrebački gradski društvo crvean križ proveti suradnja grad zagreba projekt provediti radi jačanje sustav volonterstvo kapacitet pružanje učinkovit odgovor potreba lokalan zajednica krizan situacija poboljšanje koordiniran pristup rješavanje problem izlaz kriza 10 sat gradski društvo crvean križ ilica 223 Zagreb tematski konferencija medij policijski uprava zagrebački povodom provedba projekt siguran turistički destinacija koji htjeti predstaviti početak rad zajednički policijski ophodnja grad Zagreb govoriti htjeti voditelj služba prevencija velimir tišma veleposlanik nr kinuti republika Hrvatska qi qianjin 10 sat policijski uprava zagrebački ulica matica hrvatski 4 dežuran urednik deski prijepodne robert koren poslijepodne mariti vrandečić navečer đurđa Beraković telefon 08 600 telefaks 08 822 hin hina xmhud ybdj</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FANOVI U EKSTAZI / Osvajačica Wimbledona otvorila OnlyFans, povećala grudi i dobila na samopouzdanju: 'Dečki, stigao je trenutak koji ste svi čekali...'
-Bivša osvajačica Wimbledona u juniorskoj kategoriji, Ruskinja Sofija Žuk sada ima 23 godine, a igračku karijeru završila je vrlo rano. Povukla se 2020., u dobi od 21 godinu, a Wimbledon je osvojila sa samo 15. Njoj su predviđali bajnu karijeru, uspoređivali su je s Marijom Šarapovom, no život ju je odveo drugim putem. Ona se nakon kraja igračke karijere počela baviti manekenstvom, a sada je otišla korak dalje - otvorila je svoju OnlyFans stranicu, na kojoj će dijeliti eksplicitniji sadržaj i zbog toga povećala grudi. Priznala je nakon toga da je tim zahvatom dobila na samopouzdanju. "Momci, trenutak koji ste svi čekali konačno je stigao. Bit će mnogo zanimljivog materijala", rekla je atraktivna Ruskinja i napomenula da fanovi ne trebaju očekivati potpuno gole fotografije.</t>
+          <t>fan ekstaziti osvajačica wimbledon otvoriti onlyfans povećati grud dobiti samopouzdanje stići trenutak čekati bivši osvajačica wimbledon juniorski kategorija ruskinja sofija žuk sada imati 23 godina igrački karijera završiti rano povuksti doba 21 godina wimbledon osvojiti 15 predviđati bajan karijera uspoređivati marija šarapov život odveti drugi put kraj igrački karijera početi baviti manekenstvo sada otići korak daleko otvoriti svoj onlyfans stranica koji htjeti dijeliti eksplicitan sadržaj zbog taj povećati grud priznati taj taj zahvat dobiti samopouzdanje momac trenutak čekati konačno stići biti htjeti mnogo zanimljiv materijal reći atraktivan ruskinja napomenuti fan trebati očekivati potpuno gol fotografija</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -859,12 +689,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zagreb, Hina, Hrvatska, OSV, Zagreb, Gospodarsko - socijalnog vijeće, Andrej Plenković, europski socijalan fond plus za razdoblje, hrvatski bratski zajednica 4, Vlada, Branko Bačić, Ivan Celjako, Siska, Žitnoj ulica, nov interan, Opće bolnica, Ivo Pedišić, Ivan Pedišić, ulica Marijan Celjak, Zagreb, konferencija, Socijaldemokrat grad Zagreb, Davor Bernardić, Zagreb, Tomašević, Matija Ljubek, Jarun, gallery Club, Zagreb, konferencija, zajedno - razvoj, Gradsko društvo Crvenog križ, Grado Zagreb, Gradsko društvo Crvenog križ, Ilica, Zagreb, policijski uprava zagrebački, Zagreb, služba prevencija PUZ - a, Velimir Tišma, NR Kina, republika Hrvatska, NJ.E. Qi Qianjin, policijski uprava zagrebački, ulica matica hrvatski 4, Robert Koren, Mario Vrandečić, Đurđa Beraković, hina@hina.hr, Hina</t>
+          <t>Hrvatska, Zagreb, Andrej Plenković, Branko Bačić, socijaldemokrat grad zagreba, Davor Bernardić, Zagreb, Zagreb, Zagreb, velimir tišma, Hrvatska, qianjin, ulica matica, vrandečić, Beraković</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>EKSTAZI, Wimbledon, OnlyFans, Wimbledon, Ruskinja, Sofija Žuk, Wimbledon, Marija Šarapov, OnlyFans, Ruskinja</t>
+          <t>wimbledon juniorski kategorija ruskinja sofija žuk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -874,27 +704,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava događaja Općeg servisa vijesti Hrvatska (OSV) za utorak, 25. srpnja: 
-	ZAGREB - Održat će se sjednica Gospodarsko-socijalnog vijeća na kojoj će biti i premijer Andrej Plenković. Između ostaloga, prezentirat će se prijedlog zakona o plaćama u državnoj službi i javnim službama te program Europskog socijalnog fonda plus za razdoblje 2021. - 2027. Snimatelji i fotoreporteri mogu snimiti početak sjednice nakon koje su predviđene izjave za medije (10 sati, Nacionalna i sveučilišna knjižnica, Hrvatske bratske zajednice 4).
-SISAK - Potpredsjednik Vlade i ministar prostornog uređenja, graditeljstva i državne imovine Branko Bačić, zajedno sa županom Ivanom Celjakom, posjetit će gradilišta na području Siska. Prvo će obići gradilišta konstrukcijske (samo)obnove višenamjenskih zgrada u Žitnoj ulici (10,15 sati), zatim zgradu Nove interne u krugu Opće bolnice "Dr. Ivo Pedišić" (11 sati, ulaz iz Ulice dr. Ivana Pedišića) koju obnavlja županija. Izjave za medije predviđene su u 11 sati nakon kojih će obići gradilište zamjenske obiteljske kuće (11,45 sati, Ulica Marijana Celjaka 150).
-ZAGREB - Konferencija za novinare Socijaldemokrata Grada Zagreba na kojoj će predsjednik Davor Bernardić sa suradnicima govoriti o prijedlozima za Zagreb bez ambrozije i, kako kaže, novim aferama gradonačelnika Tomaševića. Odgovarat će i na ostala nacionalna politička pitanja (9 sati, Aleja Matije Ljubeka na Jarunu, ispred Gallery Cluba).
-ZAGREB - Konferencija za novinare povodom završetka europskog projekta "Zajedno - razvoj vođen zajednicom" kojeg je zagrebačkog Gradsko društvo Crvenog križa provelo u suradnji s Gradom Zagrebom. Projekt je proveden radi jačanja sustava volonterstva i kapaciteta za pružanje učinkovitog odgovora na potrebe lokalne zajednice u kriznim situacijama te poboljšanja koordiniranog pristupa u rješavanju problema i izlazu iz krize (10 sati, Gradsko društvo Crvenog križa, Ilica 223).
-ZAGREB - Tematska konferencija za medije Policijske uprave zagrebačke povodom provedbe projekta "Sigurna turistička destinacija" na kojoj će biti predstavljen početak rada zajedničkih hrvatsko-korejskih i hrvatsko-kineskih policijskih ophodnji u gradu Zagrebu. Govorit će voditelj Službe prevencije PUZ-a Velimir Tišma i veleposlanik NR Kine u Republici Hrvatskoj NJ.E. Qi Qianjin (10 sati, Policijska uprava zagrebačka, Ulica Matice hrvatske 4).
-Dežurni urednici na desku OSV-a:
-prijepodne - Robert Koren
-poslijepodne - Mario Vrandečić
-navečer - Đurđa Beraković
-telefon: 01/48 08 600
-telefaks: 01/48 08 822
-e-mail: hina@hina.hr
-(Hina) xmhud ybdj
-</t>
+          <t>Zagreb srpanj 2023 hin najava događaj opći servis vijest Hrvatska osvti utorak srpanj Zagreb održati htjeti sjednica vijeće koji htjeti premijer Andrej Plenković između ostali prezentirati htjeti prijedlog zakon plaća državni služba javan služba program europski socijalan fond plus razdoblje 2021 2027 snimatelj fotoreporter moći snimiti početak sjednica predviđen izjava medij 10 sat nacionalan sveučilišni knjižnica hrvatski bratski zajednica 4 sisak potpredsjednik vlada ministar prostoran uređenje graditeljstvo državni imovina Branko Bačić zajedno župan ivan celjaka posjetiti htjeti gradilište područje siski prvo htjeti obići gradilište konstrukcijski obnova višenamjenski zgrada žitnoj ulica sat zatim zgrada nov interni krug opći bolnica Ivo pedišić 11 sat ulaz ulica ivati pedišić obnavljati županija izjava medij predviđen 11 sat koji htjeti obići gradilište zamjenski obiteljski kuća sat ulica marijan celjak 150 Zagreb konferencija novinar socijaldemokrat grad zagreba koji htjeti predsjednik Davor Bernardić suradnik govoriti prijedlozima Zagreb bez ambrozija kazati nov afera gradonačelnik tomaševića odgovarati htjeti ostali nacionalan politički pitanje 9 sat alej matija ljubeak jaruna ispred gallery club Zagreb konferencija novinar povodom završetak europski projekt zajedno razvoj voditi zajednica koji zagrebački gradski društvo crvean križ proveti suradnja grad zagreba projekt provediti radi jačanje sustav volonterstvo kapacitet pružanje učinkovit odgovor potreba lokalan zajednica krizan situacija poboljšanje koordiniran pristup rješavanje problem izlaz kriza 10 sat gradski društvo crvean križ ilica 223 Zagreb tematski konferencija medij policijski uprava zagrebački povodom provedba projekt siguran turistički destinacija koji htjeti predstaviti početak rad zajednički policijski ophodnja grad Zagreb govoriti htjeti voditelj služba prevencija velimir tišma veleposlanik nr kinuti republika Hrvatska qi qianjin 10 sat policijski uprava zagrebački ulica matica hrvatski 4 dežuran urednik deski prijepodne robert koren poslijepodne mariti vrandečić navečer đurđa Beraković telefon 08 600 telefaks 08 822 hin hina xmhud ybdj</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U Sarajevu, u prostorijama Općine Centar, danas će se održati sjednica Kolegija Općinskog vijeća na kojoj će biti razmatran zahtjev načelnika Srđana Mandića za preispitivanje odluke o njegovom opozivu i raspisivanju referenduma.
-Očekuje se žustra rasprava na sjednici Kolegija, na kojoj bi trebalo da prisustvuju članovi rukovodstva Vijeća, šefovi svih klubova i sam Mandić, koji je također član Kolegija vijeća.</t>
+          <t>sarajevu prostorija općina centar danas htjeti održati sjednica kolegija općinski vijeće koji htjeti razmatrati zahtjev načelnik srđati mandić preispitivanje odluka njegov opoziv raspisivanje referendum očekivati žustar rasprava sjednica kolegija koji trebati prisustvivati član rukovodstvo vijeće šef sav klub mandić također član kolegija vijeće</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -905,14 +720,10 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zagreb, Hina, Hrvatska, OSV, Zagreb, Gospodarsko - socijalnog vijeće, Andrej Plenković, europski socijalan fond plus za razdoblje, hrvatski bratski zajednica 4, Vlada, Branko Bačić, Ivan Celjako, Siska, Žitnoj ulica, nov interan, Opće bolnica, Ivo Pedišić, Ivan Pedišić, ulica Marijan Celjak, Zagreb, konferencija, Socijaldemokrat grad Zagreb, Davor Bernardić, Zagreb, Tomašević, Matija Ljubek, Jarun, gallery Club, Zagreb, konferencija, zajedno - razvoj, Gradsko društvo Crvenog križ, Grado Zagreb, Gradsko društvo Crvenog križ, Ilica, Zagreb, policijski uprava zagrebački, Zagreb, služba prevencija PUZ - a, Velimir Tišma, NR Kina, republika Hrvatska, NJ.E. Qi Qianjin, policijski uprava zagrebački, ulica matica hrvatski 4, Robert Koren, Mario Vrandečić, Đurđa Beraković, hina@hina.hr, Hina</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Sarajevo, općina centar, kolegija Općinskog vijeće, Srđan Mandić, kolegija, vijeće, Mandić, kolegija vijeće</t>
-        </is>
-      </c>
+          <t>Hrvatska, Zagreb, Andrej Plenković, Branko Bačić, socijaldemokrat grad zagreba, Davor Bernardić, Zagreb, Zagreb, Zagreb, velimir tišma, Hrvatska, qianjin, ulica matica, vrandečić, Beraković</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>0</v>
       </c>
@@ -920,27 +731,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava događaja Općeg servisa vijesti Hrvatska (OSV) za utorak, 25. srpnja: 
-	ZAGREB - Održat će se sjednica Gospodarsko-socijalnog vijeća na kojoj će biti i premijer Andrej Plenković. Između ostaloga, prezentirat će se prijedlog zakona o plaćama u državnoj službi i javnim službama te program Europskog socijalnog fonda plus za razdoblje 2021. - 2027. Snimatelji i fotoreporteri mogu snimiti početak sjednice nakon koje su predviđene izjave za medije (10 sati, Nacionalna i sveučilišna knjižnica, Hrvatske bratske zajednice 4).
-SISAK - Potpredsjednik Vlade i ministar prostornog uređenja, graditeljstva i državne imovine Branko Bačić, zajedno sa županom Ivanom Celjakom, posjetit će gradilišta na području Siska. Prvo će obići gradilišta konstrukcijske (samo)obnove višenamjenskih zgrada u Žitnoj ulici (10,15 sati), zatim zgradu Nove interne u krugu Opće bolnice "Dr. Ivo Pedišić" (11 sati, ulaz iz Ulice dr. Ivana Pedišića) koju obnavlja županija. Izjave za medije predviđene su u 11 sati nakon kojih će obići gradilište zamjenske obiteljske kuće (11,45 sati, Ulica Marijana Celjaka 150).
-ZAGREB - Konferencija za novinare Socijaldemokrata Grada Zagreba na kojoj će predsjednik Davor Bernardić sa suradnicima govoriti o prijedlozima za Zagreb bez ambrozije i, kako kaže, novim aferama gradonačelnika Tomaševića. Odgovarat će i na ostala nacionalna politička pitanja (9 sati, Aleja Matije Ljubeka na Jarunu, ispred Gallery Cluba).
-ZAGREB - Konferencija za novinare povodom završetka europskog projekta "Zajedno - razvoj vođen zajednicom" kojeg je zagrebačkog Gradsko društvo Crvenog križa provelo u suradnji s Gradom Zagrebom. Projekt je proveden radi jačanja sustava volonterstva i kapaciteta za pružanje učinkovitog odgovora na potrebe lokalne zajednice u kriznim situacijama te poboljšanja koordiniranog pristupa u rješavanju problema i izlazu iz krize (10 sati, Gradsko društvo Crvenog križa, Ilica 223).
-ZAGREB - Tematska konferencija za medije Policijske uprave zagrebačke povodom provedbe projekta "Sigurna turistička destinacija" na kojoj će biti predstavljen početak rada zajedničkih hrvatsko-korejskih i hrvatsko-kineskih policijskih ophodnji u gradu Zagrebu. Govorit će voditelj Službe prevencije PUZ-a Velimir Tišma i veleposlanik NR Kine u Republici Hrvatskoj NJ.E. Qi Qianjin (10 sati, Policijska uprava zagrebačka, Ulica Matice hrvatske 4).
-Dežurni urednici na desku OSV-a:
-prijepodne - Robert Koren
-poslijepodne - Mario Vrandečić
-navečer - Đurđa Beraković
-telefon: 01/48 08 600
-telefaks: 01/48 08 822
-e-mail: hina@hina.hr
-(Hina) xmhud ybdj
-</t>
+          <t>Zagreb srpanj 2023 hin najava događaj opći servis vijest Hrvatska osvti utorak srpanj Zagreb održati htjeti sjednica vijeće koji htjeti premijer Andrej Plenković između ostali prezentirati htjeti prijedlog zakon plaća državni služba javan služba program europski socijalan fond plus razdoblje 2021 2027 snimatelj fotoreporter moći snimiti početak sjednica predviđen izjava medij 10 sat nacionalan sveučilišni knjižnica hrvatski bratski zajednica 4 sisak potpredsjednik vlada ministar prostoran uređenje graditeljstvo državni imovina Branko Bačić zajedno župan ivan celjaka posjetiti htjeti gradilište područje siski prvo htjeti obići gradilište konstrukcijski obnova višenamjenski zgrada žitnoj ulica sat zatim zgrada nov interni krug opći bolnica Ivo pedišić 11 sat ulaz ulica ivati pedišić obnavljati županija izjava medij predviđen 11 sat koji htjeti obići gradilište zamjenski obiteljski kuća sat ulica marijan celjak 150 Zagreb konferencija novinar socijaldemokrat grad zagreba koji htjeti predsjednik Davor Bernardić suradnik govoriti prijedlozima Zagreb bez ambrozija kazati nov afera gradonačelnik tomaševića odgovarati htjeti ostali nacionalan politički pitanje 9 sat alej matija ljubeak jaruna ispred gallery club Zagreb konferencija novinar povodom završetak europski projekt zajedno razvoj voditi zajednica koji zagrebački gradski društvo crvean križ proveti suradnja grad zagreba projekt provediti radi jačanje sustav volonterstvo kapacitet pružanje učinkovit odgovor potreba lokalan zajednica krizan situacija poboljšanje koordiniran pristup rješavanje problem izlaz kriza 10 sat gradski društvo crvean križ ilica 223 Zagreb tematski konferencija medij policijski uprava zagrebački povodom provedba projekt siguran turistički destinacija koji htjeti predstaviti početak rad zajednički policijski ophodnja grad Zagreb govoriti htjeti voditelj služba prevencija velimir tišma veleposlanik nr kinuti republika Hrvatska qi qianjin 10 sat policijski uprava zagrebački ulica matica hrvatski 4 dežuran urednik deski prijepodne robert koren poslijepodne mariti vrandečić navečer đurđa Beraković telefon 08 600 telefaks 08 822 hin hina xmhud ybdj</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ne stišavaju se reakcije na najavu opoziva načelnika Opštine Centar, Srđana Mandića, kadra Naše stranke. Dok iz opštinskog NiP-a, ujedno i inicijatora opoziva, novim saopštenjima nastavljaju sa diskreditacijom svog koalicionog partnera, kolegijum Opštinskog odbora na današnjoj sjednici, očitao se na Mandićev prigovor o opozivu, te za 10. august zakazao sjednicu na kojoj će se o tome izjasniti. U isto vrijeme, dok traju prepucavanja šta je načelnik uradio, ili nije, pojedinim domaćinstvima, u ovoj opštini, uskraćene su osnovne potrebe. Pročitaj više
-Vaš komentar Ime</t>
+          <t>stišavati reakcija najava opoziv načelnik opština centar srđan mandić kadr naš stranka dok opštinski ujedno inicijator opozivati nov saopštenj nastavljati diskreditacija koalicioni partner kolegijum opštinski odbor današnji sjednica očitati mandićev prigovor opoziv august zakazati sjednica koji htjeti izjasniti isti vrijeme dok trati prepucavanje šta načelnik uraditi pojedini domaćinstvima ovaj opština uskratiti osnovan potreba pročitaj mnogo vaš komentar ime</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -951,12 +747,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zagreb, Hina, Hrvatska, OSV, Zagreb, Gospodarsko - socijalnog vijeće, Andrej Plenković, europski socijalan fond plus za razdoblje, hrvatski bratski zajednica 4, Vlada, Branko Bačić, Ivan Celjako, Siska, Žitnoj ulica, nov interan, Opće bolnica, Ivo Pedišić, Ivan Pedišić, ulica Marijan Celjak, Zagreb, konferencija, Socijaldemokrat grad Zagreb, Davor Bernardić, Zagreb, Tomašević, Matija Ljubek, Jarun, gallery Club, Zagreb, konferencija, zajedno - razvoj, Gradsko društvo Crvenog križ, Grado Zagreb, Gradsko društvo Crvenog križ, Ilica, Zagreb, policijski uprava zagrebački, Zagreb, služba prevencija PUZ - a, Velimir Tišma, NR Kina, republika Hrvatska, NJ.E. Qi Qianjin, policijski uprava zagrebački, ulica matica hrvatski 4, Robert Koren, Mario Vrandečić, Đurđa Beraković, hina@hina.hr, Hina</t>
+          <t>Hrvatska, Zagreb, Andrej Plenković, Branko Bačić, socijaldemokrat grad zagreba, Davor Bernardić, Zagreb, Zagreb, Zagreb, velimir tišma, Hrvatska, qianjin, ulica matica, vrandečić, Beraković</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>opština centar, Srđan Mandić, NiP - a, Opštinskog odbor, Mandićev</t>
+          <t>srđan mandić</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -966,30 +762,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava događaja Općeg servisa vijesti Hrvatska (OSV) za utorak, 25. srpnja: 
-	ZAGREB - Održat će se sjednica Gospodarsko-socijalnog vijeća na kojoj će biti i premijer Andrej Plenković. Između ostaloga, prezentirat će se prijedlog zakona o plaćama u državnoj službi i javnim službama te program Europskog socijalnog fonda plus za razdoblje 2021. - 2027. Snimatelji i fotoreporteri mogu snimiti početak sjednice nakon koje su predviđene izjave za medije (10 sati, Nacionalna i sveučilišna knjižnica, Hrvatske bratske zajednice 4).
-SISAK - Potpredsjednik Vlade i ministar prostornog uređenja, graditeljstva i državne imovine Branko Bačić, zajedno sa županom Ivanom Celjakom, posjetit će gradilišta na području Siska. Prvo će obići gradilišta konstrukcijske (samo)obnove višenamjenskih zgrada u Žitnoj ulici (10,15 sati), zatim zgradu Nove interne u krugu Opće bolnice "Dr. Ivo Pedišić" (11 sati, ulaz iz Ulice dr. Ivana Pedišića) koju obnavlja županija. Izjave za medije predviđene su u 11 sati nakon kojih će obići gradilište zamjenske obiteljske kuće (11,45 sati, Ulica Marijana Celjaka 150).
-ZAGREB - Konferencija za novinare Socijaldemokrata Grada Zagreba na kojoj će predsjednik Davor Bernardić sa suradnicima govoriti o prijedlozima za Zagreb bez ambrozije i, kako kaže, novim aferama gradonačelnika Tomaševića. Odgovarat će i na ostala nacionalna politička pitanja (9 sati, Aleja Matije Ljubeka na Jarunu, ispred Gallery Cluba).
-ZAGREB - Konferencija za novinare povodom završetka europskog projekta "Zajedno - razvoj vođen zajednicom" kojeg je zagrebačkog Gradsko društvo Crvenog križa provelo u suradnji s Gradom Zagrebom. Projekt je proveden radi jačanja sustava volonterstva i kapaciteta za pružanje učinkovitog odgovora na potrebe lokalne zajednice u kriznim situacijama te poboljšanja koordiniranog pristupa u rješavanju problema i izlazu iz krize (10 sati, Gradsko društvo Crvenog križa, Ilica 223).
-ZAGREB - Tematska konferencija za medije Policijske uprave zagrebačke povodom provedbe projekta "Sigurna turistička destinacija" na kojoj će biti predstavljen početak rada zajedničkih hrvatsko-korejskih i hrvatsko-kineskih policijskih ophodnji u gradu Zagrebu. Govorit će voditelj Službe prevencije PUZ-a Velimir Tišma i veleposlanik NR Kine u Republici Hrvatskoj NJ.E. Qi Qianjin (10 sati, Policijska uprava zagrebačka, Ulica Matice hrvatske 4).
-Dežurni urednici na desku OSV-a:
-prijepodne - Robert Koren
-poslijepodne - Mario Vrandečić
-navečer - Đurđa Beraković
-telefon: 01/48 08 600
-telefaks: 01/48 08 822
-e-mail: hina@hina.hr
-(Hina) xmhud ybdj
-</t>
+          <t>Zagreb srpanj 2023 hin najava događaj opći servis vijest Hrvatska osvti utorak srpanj Zagreb održati htjeti sjednica vijeće koji htjeti premijer Andrej Plenković između ostali prezentirati htjeti prijedlog zakon plaća državni služba javan služba program europski socijalan fond plus razdoblje 2021 2027 snimatelj fotoreporter moći snimiti početak sjednica predviđen izjava medij 10 sat nacionalan sveučilišni knjižnica hrvatski bratski zajednica 4 sisak potpredsjednik vlada ministar prostoran uređenje graditeljstvo državni imovina Branko Bačić zajedno župan ivan celjaka posjetiti htjeti gradilište područje siski prvo htjeti obići gradilište konstrukcijski obnova višenamjenski zgrada žitnoj ulica sat zatim zgrada nov interni krug opći bolnica Ivo pedišić 11 sat ulaz ulica ivati pedišić obnavljati županija izjava medij predviđen 11 sat koji htjeti obići gradilište zamjenski obiteljski kuća sat ulica marijan celjak 150 Zagreb konferencija novinar socijaldemokrat grad zagreba koji htjeti predsjednik Davor Bernardić suradnik govoriti prijedlozima Zagreb bez ambrozija kazati nov afera gradonačelnik tomaševića odgovarati htjeti ostali nacionalan politički pitanje 9 sat alej matija ljubeak jaruna ispred gallery club Zagreb konferencija novinar povodom završetak europski projekt zajedno razvoj voditi zajednica koji zagrebački gradski društvo crvean križ proveti suradnja grad zagreba projekt provediti radi jačanje sustav volonterstvo kapacitet pružanje učinkovit odgovor potreba lokalan zajednica krizan situacija poboljšanje koordiniran pristup rješavanje problem izlaz kriza 10 sat gradski društvo crvean križ ilica 223 Zagreb tematski konferencija medij policijski uprava zagrebački povodom provedba projekt siguran turistički destinacija koji htjeti predstaviti početak rad zajednički policijski ophodnja grad Zagreb govoriti htjeti voditelj služba prevencija velimir tišma veleposlanik nr kinuti republika Hrvatska qi qianjin 10 sat policijski uprava zagrebački ulica matica hrvatski 4 dežuran urednik deski prijepodne robert koren poslijepodne mariti vrandečić navečer đurđa Beraković telefon 08 600 telefaks 08 822 hin hina xmhud ybdj</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Inicijativu za opoziv Mandića pokrenuli su vijećnici iz Naroda i pravde
-U prostorijama Općine Centar danas će se održati sjednica Kolegija Općinskog Vijeća na kojoj će biti razmatran zahtjev načelnika Srđana Mandića za preispitivanje odluke o njegovom opozivu i raspisivanju referenduma.
-Očekuje se burna sjednica Kolegija kojoj bi trebalo da prisustvuju članovi rukovodstva Vijeća, šefovi svih klubova i sam Mandić, koji je također član Kolegija Vijeća.
-Inicijativu za opoziv Mandića, odnosno raspisivanje referenduma na kojem bi se građani Općine Centar izjasnili o njegovom statusu, pokrenuli su vijećnici iz Naroda i pravde.
-Uslijedile su burne reakcije, kako koalicionih partnera NiP-a iz Trojke, tako i predsjednika Naroda i pravde Elmedina Konakovića koji ne zagovara ovako radikalan potez.</t>
+          <t>inicijativa opoziv mandić pokrenuti vijećnik narod pravda prostorija općina centar danas htjeti održati sjednica kolegija općinski vijeće koji htjeti razmatrati zahtjev načelnik srđati mandić preispitivanje odluka njegov opoziv raspisivanje referendum očekivati buran sjednica kolegija koji trebati prisustvivati član rukovodstvo vijeće šef sav klub mandić također član kolegija vijeće inicijativa opoziv mandić odnosno raspisivanje referendum koji građanin općina centar izjasniti njegov status pokrenuti vijećnik narod pravda uslijediti buran reakcija koalicioni partner trojka predsjednik narod pravda elmedin konaković zagovarati ovako radikalan potez</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1000,13 +778,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zagreb, Hina, Hrvatska, OSV, Zagreb, Gospodarsko - socijalnog vijeće, Andrej Plenković, europski socijalan fond plus za razdoblje, hrvatski bratski zajednica 4, Vlada, Branko Bačić, Ivan Celjako, Siska, Žitnoj ulica, nov interan, Opće bolnica, Ivo Pedišić, Ivan Pedišić, ulica Marijan Celjak, Zagreb, konferencija, Socijaldemokrat grad Zagreb, Davor Bernardić, Zagreb, Tomašević, Matija Ljubek, Jarun, gallery Club, Zagreb, konferencija, zajedno - razvoj, Gradsko društvo Crvenog križ, Grado Zagreb, Gradsko društvo Crvenog križ, Ilica, Zagreb, policijski uprava zagrebački, Zagreb, služba prevencija PUZ - a, Velimir Tišma, NR Kina, republika Hrvatska, NJ.E. Qi Qianjin, policijski uprava zagrebački, ulica matica hrvatski 4, Robert Koren, Mario Vrandečić, Đurđa Beraković, hina@hina.hr, Hina</t>
+          <t>Hrvatska, Zagreb, Andrej Plenković, Branko Bačić, socijaldemokrat grad zagreba, Davor Bernardić, Zagreb, Zagreb, Zagreb, velimir tišma, Hrvatska, qianjin, ulica matica, vrandečić, Beraković</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Inicijativa za opoziv Mandić, narod i pravda 
- u prostorija općina centar, kolegija Općinskog vijeće, Srđan Mandić, kolegija, vijeće, Mandić, kolegija vijeće, Inicijativa za opoziv Mandić, općina centar, narod i pravda, NiP - a, Trojka, narod i pravda, Elmedin Konaković</t>
+          <t>vijeće inicijativa opoziv mandić, elmedin Konaković</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1016,29 +793,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava događaja Općeg servisa vijesti Hrvatska (OSV) za utorak, 25. srpnja: 
-	ZAGREB - Održat će se sjednica Gospodarsko-socijalnog vijeća na kojoj će biti i premijer Andrej Plenković. Između ostaloga, prezentirat će se prijedlog zakona o plaćama u državnoj službi i javnim službama te program Europskog socijalnog fonda plus za razdoblje 2021. - 2027. Snimatelji i fotoreporteri mogu snimiti početak sjednice nakon koje su predviđene izjave za medije (10 sati, Nacionalna i sveučilišna knjižnica, Hrvatske bratske zajednice 4).
-SISAK - Potpredsjednik Vlade i ministar prostornog uređenja, graditeljstva i državne imovine Branko Bačić, zajedno sa županom Ivanom Celjakom, posjetit će gradilišta na području Siska. Prvo će obići gradilišta konstrukcijske (samo)obnove višenamjenskih zgrada u Žitnoj ulici (10,15 sati), zatim zgradu Nove interne u krugu Opće bolnice "Dr. Ivo Pedišić" (11 sati, ulaz iz Ulice dr. Ivana Pedišića) koju obnavlja županija. Izjave za medije predviđene su u 11 sati nakon kojih će obići gradilište zamjenske obiteljske kuće (11,45 sati, Ulica Marijana Celjaka 150).
-ZAGREB - Konferencija za novinare Socijaldemokrata Grada Zagreba na kojoj će predsjednik Davor Bernardić sa suradnicima govoriti o prijedlozima za Zagreb bez ambrozije i, kako kaže, novim aferama gradonačelnika Tomaševića. Odgovarat će i na ostala nacionalna politička pitanja (9 sati, Aleja Matije Ljubeka na Jarunu, ispred Gallery Cluba).
-ZAGREB - Konferencija za novinare povodom završetka europskog projekta "Zajedno - razvoj vođen zajednicom" kojeg je zagrebačkog Gradsko društvo Crvenog križa provelo u suradnji s Gradom Zagrebom. Projekt je proveden radi jačanja sustava volonterstva i kapaciteta za pružanje učinkovitog odgovora na potrebe lokalne zajednice u kriznim situacijama te poboljšanja koordiniranog pristupa u rješavanju problema i izlazu iz krize (10 sati, Gradsko društvo Crvenog križa, Ilica 223).
-ZAGREB - Tematska konferencija za medije Policijske uprave zagrebačke povodom provedbe projekta "Sigurna turistička destinacija" na kojoj će biti predstavljen početak rada zajedničkih hrvatsko-korejskih i hrvatsko-kineskih policijskih ophodnji u gradu Zagrebu. Govorit će voditelj Službe prevencije PUZ-a Velimir Tišma i veleposlanik NR Kine u Republici Hrvatskoj NJ.E. Qi Qianjin (10 sati, Policijska uprava zagrebačka, Ulica Matice hrvatske 4).
-Dežurni urednici na desku OSV-a:
-prijepodne - Robert Koren
-poslijepodne - Mario Vrandečić
-navečer - Đurđa Beraković
-telefon: 01/48 08 600
-telefaks: 01/48 08 822
-e-mail: hina@hina.hr
-(Hina) xmhud ybdj
-</t>
+          <t>Zagreb srpanj 2023 hin najava događaj opći servis vijest Hrvatska osvti utorak srpanj Zagreb održati htjeti sjednica vijeće koji htjeti premijer Andrej Plenković između ostali prezentirati htjeti prijedlog zakon plaća državni služba javan služba program europski socijalan fond plus razdoblje 2021 2027 snimatelj fotoreporter moći snimiti početak sjednica predviđen izjava medij 10 sat nacionalan sveučilišni knjižnica hrvatski bratski zajednica 4 sisak potpredsjednik vlada ministar prostoran uređenje graditeljstvo državni imovina Branko Bačić zajedno župan ivan celjaka posjetiti htjeti gradilište područje siski prvo htjeti obići gradilište konstrukcijski obnova višenamjenski zgrada žitnoj ulica sat zatim zgrada nov interni krug opći bolnica Ivo pedišić 11 sat ulaz ulica ivati pedišić obnavljati županija izjava medij predviđen 11 sat koji htjeti obići gradilište zamjenski obiteljski kuća sat ulica marijan celjak 150 Zagreb konferencija novinar socijaldemokrat grad zagreba koji htjeti predsjednik Davor Bernardić suradnik govoriti prijedlozima Zagreb bez ambrozija kazati nov afera gradonačelnik tomaševića odgovarati htjeti ostali nacionalan politički pitanje 9 sat alej matija ljubeak jaruna ispred gallery club Zagreb konferencija novinar povodom završetak europski projekt zajedno razvoj voditi zajednica koji zagrebački gradski društvo crvean križ proveti suradnja grad zagreba projekt provediti radi jačanje sustav volonterstvo kapacitet pružanje učinkovit odgovor potreba lokalan zajednica krizan situacija poboljšanje koordiniran pristup rješavanje problem izlaz kriza 10 sat gradski društvo crvean križ ilica 223 Zagreb tematski konferencija medij policijski uprava zagrebački povodom provedba projekt siguran turistički destinacija koji htjeti predstaviti početak rad zajednički policijski ophodnja grad Zagreb govoriti htjeti voditelj služba prevencija velimir tišma veleposlanik nr kinuti republika Hrvatska qi qianjin 10 sat policijski uprava zagrebački ulica matica hrvatski 4 dežuran urednik deski prijepodne robert koren poslijepodne mariti vrandečić navečer đurđa Beraković telefon 08 600 telefaks 08 822 hin hina xmhud ybdj</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5.8.2023. 11:59 Podijeli na: Komentari: 0
-Dok se Mandić hvali "Sarajevskim ćilimom", pojedina naselja u općini Centar kao da nisu u 21. vijeku: Nemaju ni vode ni kanalizacije
-FOTO: N1
-Ne stišavaju se reakcije na najavu opoziva načelnika Opštine Centar, Srđana Mandića, kadra Naše stranke. Dok iz opštinskog NiP-a, ujedno i inicijatora opoziva, novim saopštenjima nastavljaju sa diskreditacijom svog koalicionog partnera, kolegijum Opštinskog odbora na današnjoj sjednici, očitao se na Mandićev prigovor o opozivu, te za 10. august zakazao sjednicu na kojoj će se o tome izjasniti. U isto vrijeme, dok traju prepucavanja šta je načelnik uradio, ili nije, pojedinim domaćinstvima, u ovoj opštini, uskraćene su osnovne potrebe.</t>
+          <t>podijeti komentar 0 dok mandić hvaliti sarajevski ćilim pojedini naselje općina centar vijeka nemati voda kanalizacija foto n1 stišavati reakcija najava opoziv načelnik opština centar srđan mandić kadr naš stranka dok opštinski ujedno inicijator opozivati nov saopštenj nastavljati diskreditacija koalicioni partner kolegijum opštinski odbor današnji sjednica očitati mandićev prigovor opoziv august zakazati sjednica koji htjeti izjasniti isti vrijeme dok trati prepucavanje šta načelnik uraditi pojedini domaćinstvima ovaj opština uskratiti osnovan potreba</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1049,12 +809,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zagreb, Hina, Hrvatska, OSV, Zagreb, Gospodarsko - socijalnog vijeće, Andrej Plenković, europski socijalan fond plus za razdoblje, hrvatski bratski zajednica 4, Vlada, Branko Bačić, Ivan Celjako, Siska, Žitnoj ulica, nov interan, Opće bolnica, Ivo Pedišić, Ivan Pedišić, ulica Marijan Celjak, Zagreb, konferencija, Socijaldemokrat grad Zagreb, Davor Bernardić, Zagreb, Tomašević, Matija Ljubek, Jarun, gallery Club, Zagreb, konferencija, zajedno - razvoj, Gradsko društvo Crvenog križ, Grado Zagreb, Gradsko društvo Crvenog križ, Ilica, Zagreb, policijski uprava zagrebački, Zagreb, služba prevencija PUZ - a, Velimir Tišma, NR Kina, republika Hrvatska, NJ.E. Qi Qianjin, policijski uprava zagrebački, ulica matica hrvatski 4, Robert Koren, Mario Vrandečić, Đurđa Beraković, hina@hina.hr, Hina</t>
+          <t>Hrvatska, Zagreb, Andrej Plenković, Branko Bačić, socijaldemokrat grad zagreba, Davor Bernardić, Zagreb, Zagreb, Zagreb, velimir tišma, Hrvatska, qianjin, ulica matica, vrandečić, Beraković</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mandić, Sarajevski ćilim, centar, N1, opština centar, Srđan Mandić, NiP - a, Opštinskog odbor, Mandićev</t>
+          <t>srđan mandić</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1064,40 +824,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava događaja Općeg servisa vijesti Hrvatska (OSV) za utorak, 25. srpnja: 
-	ZAGREB - Održat će se sjednica Gospodarsko-socijalnog vijeća na kojoj će biti i premijer Andrej Plenković. Između ostaloga, prezentirat će se prijedlog zakona o plaćama u državnoj službi i javnim službama te program Europskog socijalnog fonda plus za razdoblje 2021. - 2027. Snimatelji i fotoreporteri mogu snimiti početak sjednice nakon koje su predviđene izjave za medije (10 sati, Nacionalna i sveučilišna knjižnica, Hrvatske bratske zajednice 4).
-SISAK - Potpredsjednik Vlade i ministar prostornog uređenja, graditeljstva i državne imovine Branko Bačić, zajedno sa županom Ivanom Celjakom, posjetit će gradilišta na području Siska. Prvo će obići gradilišta konstrukcijske (samo)obnove višenamjenskih zgrada u Žitnoj ulici (10,15 sati), zatim zgradu Nove interne u krugu Opće bolnice "Dr. Ivo Pedišić" (11 sati, ulaz iz Ulice dr. Ivana Pedišića) koju obnavlja županija. Izjave za medije predviđene su u 11 sati nakon kojih će obići gradilište zamjenske obiteljske kuće (11,45 sati, Ulica Marijana Celjaka 150).
-ZAGREB - Konferencija za novinare Socijaldemokrata Grada Zagreba na kojoj će predsjednik Davor Bernardić sa suradnicima govoriti o prijedlozima za Zagreb bez ambrozije i, kako kaže, novim aferama gradonačelnika Tomaševića. Odgovarat će i na ostala nacionalna politička pitanja (9 sati, Aleja Matije Ljubeka na Jarunu, ispred Gallery Cluba).
-ZAGREB - Konferencija za novinare povodom završetka europskog projekta "Zajedno - razvoj vođen zajednicom" kojeg je zagrebačkog Gradsko društvo Crvenog križa provelo u suradnji s Gradom Zagrebom. Projekt je proveden radi jačanja sustava volonterstva i kapaciteta za pružanje učinkovitog odgovora na potrebe lokalne zajednice u kriznim situacijama te poboljšanja koordiniranog pristupa u rješavanju problema i izlazu iz krize (10 sati, Gradsko društvo Crvenog križa, Ilica 223).
-ZAGREB - Tematska konferencija za medije Policijske uprave zagrebačke povodom provedbe projekta "Sigurna turistička destinacija" na kojoj će biti predstavljen početak rada zajedničkih hrvatsko-korejskih i hrvatsko-kineskih policijskih ophodnji u gradu Zagrebu. Govorit će voditelj Službe prevencije PUZ-a Velimir Tišma i veleposlanik NR Kine u Republici Hrvatskoj NJ.E. Qi Qianjin (10 sati, Policijska uprava zagrebačka, Ulica Matice hrvatske 4).
-Dežurni urednici na desku OSV-a:
-prijepodne - Robert Koren
-poslijepodne - Mario Vrandečić
-navečer - Đurđa Beraković
-telefon: 01/48 08 600
-telefaks: 01/48 08 822
-e-mail: hina@hina.hr
-(Hina) xmhud ybdj
-</t>
+          <t>Zagreb srpanj 2023 hin najava događaj opći servis vijest Hrvatska osvti utorak srpanj Zagreb održati htjeti sjednica vijeće koji htjeti premijer Andrej Plenković između ostali prezentirati htjeti prijedlog zakon plaća državni služba javan služba program europski socijalan fond plus razdoblje 2021 2027 snimatelj fotoreporter moći snimiti početak sjednica predviđen izjava medij 10 sat nacionalan sveučilišni knjižnica hrvatski bratski zajednica 4 sisak potpredsjednik vlada ministar prostoran uređenje graditeljstvo državni imovina Branko Bačić zajedno župan ivan celjaka posjetiti htjeti gradilište područje siski prvo htjeti obići gradilište konstrukcijski obnova višenamjenski zgrada žitnoj ulica sat zatim zgrada nov interni krug opći bolnica Ivo pedišić 11 sat ulaz ulica ivati pedišić obnavljati županija izjava medij predviđen 11 sat koji htjeti obići gradilište zamjenski obiteljski kuća sat ulica marijan celjak 150 Zagreb konferencija novinar socijaldemokrat grad zagreba koji htjeti predsjednik Davor Bernardić suradnik govoriti prijedlozima Zagreb bez ambrozija kazati nov afera gradonačelnik tomaševića odgovarati htjeti ostali nacionalan politički pitanje 9 sat alej matija ljubeak jaruna ispred gallery club Zagreb konferencija novinar povodom završetak europski projekt zajedno razvoj voditi zajednica koji zagrebački gradski društvo crvean križ proveti suradnja grad zagreba projekt provediti radi jačanje sustav volonterstvo kapacitet pružanje učinkovit odgovor potreba lokalan zajednica krizan situacija poboljšanje koordiniran pristup rješavanje problem izlaz kriza 10 sat gradski društvo crvean križ ilica 223 Zagreb tematski konferencija medij policijski uprava zagrebački povodom provedba projekt siguran turistički destinacija koji htjeti predstaviti početak rad zajednički policijski ophodnja grad Zagreb govoriti htjeti voditelj služba prevencija velimir tišma veleposlanik nr kinuti republika Hrvatska qi qianjin 10 sat policijski uprava zagrebački ulica matica hrvatski 4 dežuran urednik deski prijepodne robert koren poslijepodne mariti vrandečić navečer đurđa Beraković telefon 08 600 telefaks 08 822 hin hina xmhud ybdj</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bego Gutić i još 9 osoba prijavljeni za pokušaj ubistva 14 vijećnika u Banovićima
-FOTO: SDA BANOVIĆI
-Novi predsjedavajući Općinskog vijeća Banovići ili barem onaj koji čeka da to postane, Sifet Ikanović, kazao je za Raport da je Policijskoj upravi Banovići prijavio općinskog načelnika Begu Gutića i još devet ljudi za pokušaj ubistva 14 vijećnika u ponedjeljak.
-Podsjetimo, ispred zgrade Općine Banovići u ponedjeljak se desio fizički obračun jer je nova općinska većina, izglasana 6. jula, pokušala ući u zgradu i preuzeti funkcije.
-Kako tvrdi Ikanović, sve je organizovao Gutić i to uz podršku kantonalnog Tužilaštva i MUP-a u kojem, kako kaže, ima dobre veze.
-“Opštinski načelnik Gutić je pozvao ljude pred Opštinu. Pola sata prije našeg dolaska izdvojio je 25 ljudi i odveo ih u kancelariju da im da upute. Prije toga, noć pred skup, pozvao je ljude preko Facebooka na nerede i stavio nam metu na čelo”, kaže Ikanović.
-Požalio se na to da MUP nije odradio svoj posao kako je dogovoreno, a smatra da je i za to zaslužan Gutić koji “tamo ima svoje veze”.
-“Gutić je odvojio grupu ljudi koji su učestvovali u linču na mene. MUP o tome šuti”.
-Objašnjava nam da je u srijedu prijavio Gutića i devet ljudi za pokušaj ubistva njega i 13 vijećnika koji su izglasali njegov opoziv početkom jula.
-“U Policijskoj upravi Banovići su rekli da će me zvati za sat vremena, ali me nisu nazvali evo do ovog trenutka”, žali se Ikanović koji nam kaže da je kao dokaze mislio uložiti Facebook status Gutića u noći prije napada i dva snimka na kojima se, kako tvrdi, daje upute ljudima da ga udaraju.
-Smatra da Tužilaštvo ne radi svoj posao, “jer da ga radi do ovoga ne bi došlo”.
-“Tužilaštvo je saučesnik u ovim radnjama. Oni sve čine da Gutić ostane načelnik do kraja godine jer naredne godine ne može biti opozvan”, pojašnjava Ikanović.
-Kaže da je za sutra dogovorena nova sjednica Općinskog vijeća na kojoj će biti odlučeno o daljim koracima.
-“Opcija ima nekoliko, vidjet ćemo šta je najbolje za građane Banovića”, zaključio je Ikanović za Raport.
-(Erna H.)</t>
+          <t>Bego Gutić još 9 osoba prijaviti pokušaj ubistvo 14 vijećnik banovićima foto sdati Banovići nov predsjedavajući općinski vijeće banovići barem onaj čekati postati sifet ikanović kazati raport policijski uprava banovići prijaviti općinski načelnik begu gutić još devet čovjek pokušaj ubistvo 14 vijećnik ponedjeljak podsjetiti ispred zgrada općina banovići ponedjeljak desiti fizički obračun nov općinski većina izglasati jula pokušati ući zgrada preuzeti funkcija tvrditi ikanović organizovati gutić podrška kantonalan tužilaštvo koji kazati imati dobar veza opštinski načelnik gutić pozvati čovjek pred opština pola sat naš dolask izdvojiti 25 čovjek odveti kancelarija oni uputa taj noć pred skup pozvati čovjek preko facebook nered staviti meta čelo kazati ikanović požaliti mup odraditi posao dogovoriti smatrati zaslužan Gutić tamo imati veza gutić odvojiti grupa čovjek učestvovati linču mup šuti objašnjavati srijeda prijaviti gutić devet čovjek pokušaj ubistvo 13 vijećnik izglasati opoziv početkom jula policijski uprava banovići reći htjeti zvati sat vrijeme nazvati evo ovaj trenutak žati ikanović kazati dokaz misliti uložiti facebook status gutić noć napad dva snimka tvrditi davati uputa čovjek udarati smatrati tužilaštvo raditi posao radi ovaj doći tužilaštvo saučesnik ovaj radnja činiti gutić ostati načelnik kraj godina naredni godina moći opozvan pojašnjavati ikanović kazati sutra dogovoriti nov sjednica općinski vijeće koji htjeti odlučiti dalji korak opcija imati nekoliko vidjeti htjeti šta dobar građanin Banović zaključiti ikanović raport erno h</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1108,12 +840,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zagreb, Hina, Hrvatska, OSV, Zagreb, Gospodarsko - socijalnog vijeće, Andrej Plenković, europski socijalan fond plus za razdoblje, hrvatski bratski zajednica 4, Vlada, Branko Bačić, Ivan Celjako, Siska, Žitnoj ulica, nov interan, Opće bolnica, Ivo Pedišić, Ivan Pedišić, ulica Marijan Celjak, Zagreb, konferencija, Socijaldemokrat grad Zagreb, Davor Bernardić, Zagreb, Tomašević, Matija Ljubek, Jarun, gallery Club, Zagreb, konferencija, zajedno - razvoj, Gradsko društvo Crvenog križ, Grado Zagreb, Gradsko društvo Crvenog križ, Ilica, Zagreb, policijski uprava zagrebački, Zagreb, služba prevencija PUZ - a, Velimir Tišma, NR Kina, republika Hrvatska, NJ.E. Qi Qianjin, policijski uprava zagrebački, ulica matica hrvatski 4, Robert Koren, Mario Vrandečić, Đurđa Beraković, hina@hina.hr, Hina</t>
+          <t>Hrvatska, Zagreb, Andrej Plenković, Branko Bačić, socijaldemokrat grad zagreba, Davor Bernardić, Zagreb, Zagreb, Zagreb, velimir tišma, Hrvatska, qianjin, ulica matica, vrandečić, Beraković</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bego Gutić, Banoviać, SDA BANOVIĆI, Općinskog vijeće Banovići, Sifet Ikanović, Raport, policijskoj uprava Banovići, Beg Gutić, općina Banovići, Ikanović, Gutić, Tužilaštva, MUP - a, Gutić, Opština, Facebook, Ikanović, MUP, Gutić, Gutić, MUP, Gutić, policijskoj uprava Banovići, Ikanović, Facebook, Gutić, Tužilaštvo, Gutić, Ikanović, Općinskog vijeće, Banović, Ikanović, Raport, Erna H.</t>
+          <t>Bego Gutić, Banovići, begu gutić, Gutić, ikanović, ikanović, Banović</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1123,29 +855,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava događaja Općeg servisa vijesti Hrvatska (OSV) za utorak, 25. srpnja: 
-	ZAGREB - Održat će se sjednica Gospodarsko-socijalnog vijeća na kojoj će biti i premijer Andrej Plenković. Između ostaloga, prezentirat će se prijedlog zakona o plaćama u državnoj službi i javnim službama te program Europskog socijalnog fonda plus za razdoblje 2021. - 2027. Snimatelji i fotoreporteri mogu snimiti početak sjednice nakon koje su predviđene izjave za medije (10 sati, Nacionalna i sveučilišna knjižnica, Hrvatske bratske zajednice 4).
-SISAK - Potpredsjednik Vlade i ministar prostornog uređenja, graditeljstva i državne imovine Branko Bačić, zajedno sa županom Ivanom Celjakom, posjetit će gradilišta na području Siska. Prvo će obići gradilišta konstrukcijske (samo)obnove višenamjenskih zgrada u Žitnoj ulici (10,15 sati), zatim zgradu Nove interne u krugu Opće bolnice "Dr. Ivo Pedišić" (11 sati, ulaz iz Ulice dr. Ivana Pedišića) koju obnavlja županija. Izjave za medije predviđene su u 11 sati nakon kojih će obići gradilište zamjenske obiteljske kuće (11,45 sati, Ulica Marijana Celjaka 150).
-ZAGREB - Konferencija za novinare Socijaldemokrata Grada Zagreba na kojoj će predsjednik Davor Bernardić sa suradnicima govoriti o prijedlozima za Zagreb bez ambrozije i, kako kaže, novim aferama gradonačelnika Tomaševića. Odgovarat će i na ostala nacionalna politička pitanja (9 sati, Aleja Matije Ljubeka na Jarunu, ispred Gallery Cluba).
-ZAGREB - Konferencija za novinare povodom završetka europskog projekta "Zajedno - razvoj vođen zajednicom" kojeg je zagrebačkog Gradsko društvo Crvenog križa provelo u suradnji s Gradom Zagrebom. Projekt je proveden radi jačanja sustava volonterstva i kapaciteta za pružanje učinkovitog odgovora na potrebe lokalne zajednice u kriznim situacijama te poboljšanja koordiniranog pristupa u rješavanju problema i izlazu iz krize (10 sati, Gradsko društvo Crvenog križa, Ilica 223).
-ZAGREB - Tematska konferencija za medije Policijske uprave zagrebačke povodom provedbe projekta "Sigurna turistička destinacija" na kojoj će biti predstavljen početak rada zajedničkih hrvatsko-korejskih i hrvatsko-kineskih policijskih ophodnji u gradu Zagrebu. Govorit će voditelj Službe prevencije PUZ-a Velimir Tišma i veleposlanik NR Kine u Republici Hrvatskoj NJ.E. Qi Qianjin (10 sati, Policijska uprava zagrebačka, Ulica Matice hrvatske 4).
-Dežurni urednici na desku OSV-a:
-prijepodne - Robert Koren
-poslijepodne - Mario Vrandečić
-navečer - Đurđa Beraković
-telefon: 01/48 08 600
-telefaks: 01/48 08 822
-e-mail: hina@hina.hr
-(Hina) xmhud ybdj
-</t>
+          <t>Zagreb srpanj 2023 hin najava događaj opći servis vijest Hrvatska osvti utorak srpanj Zagreb održati htjeti sjednica vijeće koji htjeti premijer Andrej Plenković između ostali prezentirati htjeti prijedlog zakon plaća državni služba javan služba program europski socijalan fond plus razdoblje 2021 2027 snimatelj fotoreporter moći snimiti početak sjednica predviđen izjava medij 10 sat nacionalan sveučilišni knjižnica hrvatski bratski zajednica 4 sisak potpredsjednik vlada ministar prostoran uređenje graditeljstvo državni imovina Branko Bačić zajedno župan ivan celjaka posjetiti htjeti gradilište područje siski prvo htjeti obići gradilište konstrukcijski obnova višenamjenski zgrada žitnoj ulica sat zatim zgrada nov interni krug opći bolnica Ivo pedišić 11 sat ulaz ulica ivati pedišić obnavljati županija izjava medij predviđen 11 sat koji htjeti obići gradilište zamjenski obiteljski kuća sat ulica marijan celjak 150 Zagreb konferencija novinar socijaldemokrat grad zagreba koji htjeti predsjednik Davor Bernardić suradnik govoriti prijedlozima Zagreb bez ambrozija kazati nov afera gradonačelnik tomaševića odgovarati htjeti ostali nacionalan politički pitanje 9 sat alej matija ljubeak jaruna ispred gallery club Zagreb konferencija novinar povodom završetak europski projekt zajedno razvoj voditi zajednica koji zagrebački gradski društvo crvean križ proveti suradnja grad zagreba projekt provediti radi jačanje sustav volonterstvo kapacitet pružanje učinkovit odgovor potreba lokalan zajednica krizan situacija poboljšanje koordiniran pristup rješavanje problem izlaz kriza 10 sat gradski društvo crvean križ ilica 223 Zagreb tematski konferencija medij policijski uprava zagrebački povodom provedba projekt siguran turistički destinacija koji htjeti predstaviti početak rad zajednički policijski ophodnja grad Zagreb govoriti htjeti voditelj služba prevencija velimir tišma veleposlanik nr kinuti republika Hrvatska qi qianjin 10 sat policijski uprava zagrebački ulica matica hrvatski 4 dežuran urednik deski prijepodne robert koren poslijepodne mariti vrandečić navečer đurđa Beraković telefon 08 600 telefaks 08 822 hin hina xmhud ybdj</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Društvo Ovaj grad je kandidat za Prestonicu kulture 2024. godine Tokom priprema za kandidaturu Zrenjanina za prestonicu kulture Srbije i promovisanja identiteta grada. u sklopu tradicionalne kulturno-zabavne manifestacije Dani piva, koja se po 38. put održava, u utorak 8. avgusta u 20 časova u galeriji Asocijacije likovnih umetnika Zrenjanina, otvara se izložba pod nazivom "Grad- simbol i identitet", na kojoj će biti izloženi radovi likovnih umetnika iz Zrenjanina. Izvor: Novosti/B.Grujić ponedeljak, 7.08.2023. | 15:18 -&gt; 08:23 Zrenjanin Tweet Podeli Foto: BABAROGA/Shutterstock
-"U ozbiljno poodmakloj fazi priprema smo kandidature za srpski prestonicu kulture 2024. godine i pokušavamo da odredimo moguće gradske simbole, ili više njih, koji predstavljaju identitet grada", napominje dr Rastko Stefanović, akademski slikar i predsednik ALUZ-a, uz napomenu da izloženi radovi na predstojećoj izložbi mogu biti odgovor na "zavičajnu" temu i inspiracija i polazište za neka dalja rešenja, prenose Novosti.
-"Svi radovi su asocijacije na Zrenjanin, od intimnih doživljaja do kolektivnih halucinacija, kritični ili idilični pogledi na istoriju i sadašnjost grada, znakovi, simboli suveniri ili antisuveniri", poručuju iz ALUZ-a, uz srdačan poziv ljubiteljima likovne umetnosti, da pogledaju zanimljivu izložbu.
-Pratite nas na našoj Facebook i Instagram stranici, Twitter nalogu i uključite se u našu Viber zajednicu.</t>
+          <t>društvo ovaj grad kandidat prestonica kultura godina tokom pripremati kandidatura zrenjanin prestonica kultura Srbija promovisanje identitet grad sklop tradicionalan manifestacija dan pivo put održavati utorak avgust 20 čas galerija asocijacija likovni umetnik zrenjanin otvarati izložba naziv simbol identitet koji htjeti izložiti rad likovni umetnik zrenjanin izvor Ponedeljak zrenjanin tweet podesti foto ozbiljno poodmakl faza pripremati kandidatura srpski prestonica kultura godina pokušavati odrediti moguć gradski simbol mnogo predstavljati identitet grad napominjati dr rastko stefanović akademski slikar predsednik napomen izložiti rad predstojeći izložba moći odgovor zavičajan tema inspiracija polazište dalje rešenje prenositi novost rad asocijacija zrenjanin intiman doživljaj kolektivan halucinacija kritičan idiličan pogled istorija sadašnjost grad znak simbol suvenir antisuvenir poručovati srdačan poziv ljubiteljima likovan umetnost pogledati zanimljiv izložba pratititi naš facebook instagram stranica twitter nalog uključite naš viber zajednica</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1156,13 +871,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zagreb, Hina, Hrvatska, OSV, Zagreb, Gospodarsko - socijalnog vijeće, Andrej Plenković, europski socijalan fond plus za razdoblje, hrvatski bratski zajednica 4, Vlada, Branko Bačić, Ivan Celjako, Siska, Žitnoj ulica, nov interan, Opće bolnica, Ivo Pedišić, Ivan Pedišić, ulica Marijan Celjak, Zagreb, konferencija, Socijaldemokrat grad Zagreb, Davor Bernardić, Zagreb, Tomašević, Matija Ljubek, Jarun, gallery Club, Zagreb, konferencija, zajedno - razvoj, Gradsko društvo Crvenog križ, Grado Zagreb, Gradsko društvo Crvenog križ, Ilica, Zagreb, policijski uprava zagrebački, Zagreb, služba prevencija PUZ - a, Velimir Tišma, NR Kina, republika Hrvatska, NJ.E. Qi Qianjin, policijski uprava zagrebački, ulica matica hrvatski 4, Robert Koren, Mario Vrandečić, Đurđa Beraković, hina@hina.hr, Hina</t>
+          <t>Hrvatska, Zagreb, Andrej Plenković, Branko Bačić, socijaldemokrat grad zagreba, Davor Bernardić, Zagreb, Zagreb, Zagreb, velimir tišma, Hrvatska, qianjin, ulica matica, vrandečić, Beraković</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Prestonica kultura, Zrenjanin, Srbija, dan pivo, Asocijacija likovni umetnik Zrenjanin, Zrenjanin, Zrenjanin Tweet Podeli Foto, Shutterstock 
-, Rastko Stefanović, ALUZ - a, novosti, Zrenjanin, ALUZ - a, Facebook, Instagram, Twitter, Viber</t>
+          <t>Srbija, Ponedeljak, stefanović akademski slikar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1172,20 +886,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - U kulturi za utorak 25. srpnja nema važnijih događaja za najaviti. 
-	telefon: 01/4808 600
-telefaks: 01/4808 822
-e-mail: kultura@hina.hr
-</t>
+          <t>Zagreb srpanj 2023 hin kultura utorak srpanj važan događaj najaviti telefon 600 telefaks 822 kultura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tekst članka se nastavlja ispod banera
-Upravni odbor Saveza samostalnih sindikata radnika rudnika Federacije Bosne i Hercegovine, zbog stanja u Rudniku mrkog uglja Zenica, donio je odluku o organiziranju prosvjeda koji će biti održan u utorak, 1. kolovoza, ispred zgrade Javnog poduzeća Elektroprivreda BiH u Sarajevu, potvrdio je predsjednik tog sindikata Sinan Husić, a prenosi BHRT.
-Podsjetio je da su zbog neisplaćene plaće za lipanj te naknade za topli obrok za mjesec svibanj, zenički rudari obustavili proizvodnju u utorak, 25. srpnja u drugoj smjeni, kada se grupa od 30 rudara odlučila da ne izađe iz jame''Raspotočje'' u kojoj su proveli dvije noći.
-Husić je nakon jučerašnje sjednice Predsjedništva SSSRRFBiH u Zenici, najavio da će u utorak na prosvjedima u Sarajevu koji će biti organizirani u periodu od 11 do 14 sati, biti 500 radnika iz sedam rudnika Koncerna JP EPBiH.
-"Mi ne tražimo da nas bilo tko prima. Mi dolazimo da iskažemo ogromno nezadovoljstvo naspram svega ovoga što se događa… Želimo kazati da smo ujedinjeni i da nećemo odustati", poručio je ranije Husić.</t>
+          <t>tekst članak nastavljati ispod baner upravni odbor savez samostalan sindikat radnik rudnik federacija Bosna hercegovina zbog stanje rudnik mrki uglj zenica donijeti odluka organiziranje prosvjed htjeti održati utorak kolovoz ispred zgrada javan poduzeće elektroprivreda sarajevu potvrditi predsjednik taj sindikat Sinan husić prenositi bhrt podsjetiti zbog neisplaćen plaća lipanj naknada topli obrok mjesec svibanj zenički rudar obustaviti proizvodnja utorak srpanj drugi smjena grupa 30 rudar odlučiti izaći jama raspotočji koji proveti dva noć husić jučerašnji sjednica predsjedništvo sssrrfbih zenik najaviti htjeti utorak prosvjed sarajevu htjeti organizirati period 11 14 sat 500 radnik sedam rudnik konceran jp epbih tražiti tko primati dolaziti iskazati ogroman nezadovoljstvo naspram sve ovaj što željeti kazati ujediniti htjeti odustati poručiti rano Husić</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1194,14 +900,10 @@
       <c r="D16" t="n">
         <v>0.4540679156780243</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Zagreb, Hina</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>upravni odbor savez samostalan sindikat radnik rudnik federacija Bosna i Hercegovina, Rudnik mrki uglj Zenica, Javan poduzeće elektroprivreda BiH, Sarajevo, Sinan Husić, BHRT, Husić, predsjedništvo SSSRRFBiH u, Zenik, Sarajevo, Koncern JP EPBiH., Husić</t>
+          <t>Bosna hercegovina, Sinan Husić, sssrrfbih zenik, sarajevu, Husić</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1211,19 +913,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - U kulturi za utorak 25. srpnja nema važnijih događaja za najaviti. 
-	telefon: 01/4808 600
-telefaks: 01/4808 822
-e-mail: kultura@hina.hr
-</t>
+          <t>Zagreb srpanj 2023 hin kultura utorak srpanj važan događaj najaviti telefon 600 telefaks 822 kultura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U okviru europskog projekta „Na istoj strani(ci) – Čitanjem do uključivog društva“, u sklopu programa „Neispričane priče“, u Domu za starije i nemoćne osobe Poreč gostovat će Dragan Gortan, pazinski pjesnik. Autor će predstaviti svoju novu zbirku pjesama „Pramjera ljubavi“.
-Ovo je četvrta zbirka poezije kojom se Gortan vraća vječnom izvoru inspiracije – ljubavi, ali ovoga puta u prvom licu. „To je ona ljubav koja mijenja dragulje za trešnje, koja se skriva u jabuci na dnu poštanske torbe, po kojoj se iz šetnje vraća mokrih ramena…“. Ljubav je ono o čemu će naš gost pripovijedati korisnicima Doma te ih pisanom riječi odvesti na putovanje do tajnih simpatija i prvih ljubavi, ukradenih poljubaca i slatkih uspomena.
-Književno druženje održat će se u utorak 25. srpnja 2023. godine u 11 sati u Domu za starije i nemoćne osobe Poreč.
-„Na istoj strani(ci)“, projekt Gradske knjižnice Poreč u partnerstvu s Gradom Porečom – Parenzo, odobren je u okviru europskog natječaja „Čitanjem do uključivog društva“ te se financira u okviru Operativnog programa „Učinkoviti ljudski potencijali“ 2014. – 2020. Europske Unije iz europskog socijalnog fonda: 85 % sredstava osigurano je iz Europskog socijalnog fonda, a 15 % Ministarstva kulture i medija Republike Hrvatske.</t>
+          <t>okvir europski projekt isti strana ci čitanje uključiav društvo sklop program neispričan priča dom star nemoćan osoba poreč gostovati htjeti dragan gortan pazinski pjesnik autor htjeti predstaviti svoj nov zbirka pjesa pramjer ljubav ovaj četvrti zbirka poezija koji gortan vraćati vječan izvor inspiracija ljubav ovaj put prvi lice ljubav mijenjati dragulja trešnja skrivati jabuka dnu poštanski torba koji šetnja vraćati mokar ljubav što htjeti naš gost pripovijedati korisnik doma pisan riječ odvesti putovanje tajni simpatija prvi ljubav ukradean poljubac slatki uspome književan druženje održati htjeti utorak srpanj godina 11 sat dom star nemoćan osoba poreč isti strana ci projekt gradski knjižnica poreč partnerstvo grad poreč parenzo odobriti okvir europski natječaj čitanje uključiav društvo financirati okvir operativan program učinkovit ljudski potencijal 2014 2020 europski unija europski socijalan fond 85 sredstvo osigurati europski socijalan fond 15 ministarstvo kultura medij republika Hrvatska</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1232,14 +927,10 @@
       <c r="D17" t="n">
         <v>0.1545467227697372</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Zagreb, Hina</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neispričane priča, Domu za star i nemoćan osoba, Poreč, Dragan Gortan, pramjer ljubav, Gortan, dom, Domu za star i nemoćan osoba, Poreč, Gradske knjižnica Poreč, Grada Porečom, Parenzo, Operativnog program, europski unija, europski socijalan fond, ministarstvo kultura, republika Hrvatska</t>
+          <t>Dragan gortan, Hrvatska</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1249,28 +940,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - U kulturi za utorak 25. srpnja nema važnijih događaja za najaviti. 
-	telefon: 01/4808 600
-telefaks: 01/4808 822
-e-mail: kultura@hina.hr
-</t>
+          <t>Zagreb srpanj 2023 hin kultura utorak srpanj važan događaj najaviti telefon 600 telefaks 822 kultura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dinamo ima novog igrača, čekanju je kraj: ‘Drago mi je da je konačno sve zaključeno’
-Autor: Ivor Krapac
-Ljetni prijelazni rok u Dinamu donio je potvrdu dolaska novog igrača u momčadi Igora Bišćana. Kako su zagrebački Plavi objavili na službenoj klupskoj stranici, u Maksimir je došao Japanac Takuro Kaneko koji će za pet dana proslaviti 26. rođendan, a po dolasku, uskoro će biti među kandidatima za nastup u novom dresu.
-Od Kaneka se očekuje da će Dinamu pomoći na desnoj strani veznog reda ili na desnom krilu, a do sada, svoju klupsku karijeru gradio je samo u Japanu, gdje mu je posljednja postaja bio Sapporo.
-Japanski nogometaš Takuro Kaneko pojačat će konkurenciju na desnoj strani Dinamove ofenzivne linije 🔥💪🏻✍️
-Dragi Takuro,… Objavljuje GNK Dinamo Zagreb u Utorak, 25. srpnja 2023.
-Japanca čeka novi izazov. Ide putem kakvim je svojedobno prolazio njegov slavni sunarodnjak Kazuyoshi Miura, godinama najveća japanska nogometna zvijezda, u kratkom razdoblju iz 1999. i u dresu Dinama.
-Veseli se dolasku u Europu
-Nakon što je stigao u Europu i pridružio se Dinamu, Takuro Kaneko približio je svoje prve dojmove.
-“Jako sam sretan i zadovoljan dolaskom u ovako respektabilan europski klub. Dugo vremena smo radili na ovom transferu i drago mi je da je konačno sve zaključeno s pozitivnim epilogom, kako za mene, tako i za klub”, opisao je 25-godišnji Japanac.
-“Dinamo predstavlja moj prvi iskorak u europski nogomet, a znam da je klub u Europi već dugi niz godina vrlo konkurentan i da protiv njega nitko ne može unaprijed računati na bodove. Također, znam da je konkurencija u samoj momčadi vrlo snažna, izazovna, no ne bih došao ovdje da ne volim izazove”, nastavio je.
-“Prvi sljedeći za mene osobno bit će dokazati se, kako samom sebi, tako i klupskom vodstvu i navijačima. Siguran sam da ću opravdati povjerenje koje mi je ukazano i da ću na Maksimiru doživjeti mnogo lijepih trenutaka”, dodao je Kaneko za službenu stranicu kluba.
-Welcome Takuro 🇯🇵💙✍️ 🗣️ “Jako sam sretan i zadovoljan dolaskom u ovako respektabilan europski klub. Dugo vremena smo… Objavljuje GNK Dinamo Zagreb u Utorak, 25. srpnja 2023.</t>
+          <t>dinati imati nov igrač čekanje kraj drago konačno zaključiti autor ivor krapac ljetni prijelazni rok dinam donijeti potvrda dolask nov igrač momčad igora bišćanin zagrebački plav objaviti služben klupski stranica maksimir doći japanac takuro kanekoi htjeti pet dan proslaviti rođendan dolazak uskoro htjeti među kandidat nastup nov dres kaneka očekivati htjeti dinam pomoći desni strana vezni red desni kril sada svoj klupski karijera graditi japan gdje posljednji postaja sapporo japanski nogometaš takuro kaneko pojačati htjeti konkurencija desni strana dinamovi ofenzivan linija drag takuro objavljivati gnk dinati Zagreb utorak srpanj 2023 japanco čekati nov izazov ići putem kakav svojedobno prolaziti slavan sunarodnjak Kazuyoshi miur godina velik japanski nogometni zvijezda kratak razdoblje dres dinam veseliti dolazak europa što stići europa pridružiti dinam takuro kaneko približiti prvi dojm jako sretan zadovoljan dolaska ovako respektabilan europski klub dugo vrijeme raditi ovaj transfer drago konačno zaključiti pozitivan epilog klub opisati japanac dinamo predstavljati prvi iskorak europski nogomet znati klub Europa već dug niz godina konkurentan protiv nitko moći unaprijed računati bod također znati konkurencija sam momčad snažan izazovan doći ovdje voljeti izazov nastaviti prvi sljedeći osobno biti htjeti dokazati sam klupski vodstvo navijač siguran htjeti opravdati povjerenje ukazati htjeti maksimir doživjeti mnogo lijep trenutak dodati kaneko služben stranica klub welcome takuro jako sretan zadovoljan dolaska ovako respektabilan europski klub dugo vrijeme objavljivati gnk dinati Zagreb utorak srpanj 2023</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1279,14 +954,10 @@
       <c r="D18" t="n">
         <v>0.5258774161338806</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Zagreb, Hina</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dinamo, Drago ja, Ivor Krapac, Dinam, Igor Bišćan, plav, Maksimir, Japanac, Takuro Kaneko, Kaneka, Dinam, Japan, sapporo, Takuro Kaneko, Dinamova, Dragi Takuro, GNK Dinamo Zagreb, utorak, Japanco, Kazuyoshi Miura, Dinam, Europa, Europa, Dinam, Takuro Kaneko, Japanac, Dinamo, Europa, Maksimir, Kaneko, Welcom Takuro 🇯, GNK Dinamo Zagreb, utorak</t>
+          <t>igora bišćanin, takuro kanekti, Zagreb, japanco, Kazuyoshi miur, kaneko, Europa, welcome takuro, Zagreb</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1296,21 +967,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - U kulturi za utorak 25. srpnja nema važnijih događaja za najaviti. 
-	telefon: 01/4808 600
-telefaks: 01/4808 822
-e-mail: kultura@hina.hr
-</t>
+          <t>Zagreb srpanj 2023 hin kultura utorak srpanj važan događaj najaviti telefon 600 telefaks 822 kultura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Na današnji dan, 25. srpnja 1991. godine izvršen je prvi izravni napad sa teritorija Srbije na Republiku Hrvatsku, točnije na malo mjesto Erdut, u kojem su poginula šestorica pripadnika 1. gardijske brigade Tigrovi
-U prvom izravnom napadu s teritorija Republike Srbije na Republiku Hrvatsku, točnije na Erdut, upravo na današnji dan 1991. godine poginula su šestorica hrvatskih branitelja pripadnika 1. gardijske brigade Tigrovi, a 19 ih je ranjeno.
-Nakon artiljerijskog napada JNA na policijski poligon u Erdutu 25. srpnja 1991. godine, noću u 1,55 sati poginulo je šest i ranjeno osamnaest hrvatskih branitelja.
-U neprijateljskom raketiranju poginuli su Mile Čulina, Anto Grgić, Miroslav Gržan, Josip Knežević, Željko Pavić i Mirko Rožman.
-I dok Dunav protiče, sjećanje na hrvatske heroje koji su u slobodu Domovine utkali ono najvrijednije šta su imali, svoje mlade živote, među narodom polako blijedi, unatoč tome što se žrtva zbog koje smo danas slobodni nikada n zaboraviti nesmije.
-Počivajte u miru hrvatski vitezovi!</t>
+          <t>današnji dan srpanj godina izvršiti prvi izravan napad teritorij Srbija republika hrvatski točno mali mjesto erdut koji poginuti šestorica pripadnik gardijski brigada tigrovi prvi izravan napad teritorij republika Srbija republika hrvatski točno erdut upravo današnji dan godina poginuti šestorica hrvatski branitelj pripadnik gardijski brigada tigrovi 19 ranjeno artiljerijski napad jan policijski poligon erdut srpanj godina noću sat poginuti šest ranjeno osamnaest hrvatski branitelj neprijateljski raketiranje poginuti miti čulina Anto grgić miroslav gržan Josip knežević željko Pavić Mirko rožman dok dunav proticati sjećanje hrvatski heroj sloboda domovina utkati vrijedno šta imati mlad život među narod polako blijediti unatoč što žrtva zbog danas slobodan nikada n zaboraviti nesmije počivati mir hrvatski vitez</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1319,14 +981,10 @@
       <c r="D19" t="n">
         <v>0.3488885462284088</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Zagreb, Hina</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Srbija, republika Hrvatska, Erdut, Tigrov, republika Srbija, republika Hrvatska, Erdut, Tigrov, JNA, Erdut 25, Mile Čulina, Anto Grgić, Miroslav Gržan, Josip Knežević, Željko Pavić, Mirko Rožman, Dunav, domovina</t>
+          <t>Srbija republika, Srbija republika, Anto grgić Miroslav, Josip knežević, željko Pavić Mirko</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1336,25 +994,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - U kulturi za utorak 25. srpnja nema važnijih događaja za najaviti. 
-	telefon: 01/4808 600
-telefaks: 01/4808 822
-e-mail: kultura@hina.hr
-</t>
+          <t>Zagreb srpanj 2023 hin kultura utorak srpanj važan događaj najaviti telefon 600 telefaks 822 kultura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Širi dalje
-Trideset i prva je obljetnica najvećeg ratnog zločina nad Hrvatima u BiH koji se dogodio u selu Briševo kod Prijedora. Između 24. i 25. srpnja 1992. godine u ovom selu ubijeno je 67 mještana, što se smatra najvećim stradanjem Hrvata u jednom danu u proteklom ratu u Bosni i Hercegovini.
-Pokolj u selu Briševu je ratni zločin počinjen početkom rata u BiH 24. i 25. srpnja 1992. nad Hrvatima u župi Stara Rijeka, četiri kilometra južno od Prijedora.
-U selu “izbrisanoga” imena kod Prijedora zvjerski je ubijeno 67 Hrvata tog mjesta. Pokolj u Briševu 1992., hrvatskom selu između Prijedora i Sanskog Mosta počinili su pripadnici 5. Kozaračke brigade i 6. Krajiške brigade iz Sanskog Mosta, što je jedno od najmasovnijih stradanja Hrvata u jednom danu tijekom proteklog rata na području Bosne i Hercegovine
-Smaknute su čitave obitelji Briševa: Matanovića 13, Buzuka 10, Ivandića devetero, Marijana sedmero, Mlinara i Komljena po petero… U pokolju su ubijeni i otac Mladen Matanović, te dva sina: 16- godišnji Ervin i 18-godišnji Johan Matanović. Preživjeli svjedoci tvrde da su zločini strašni i da su u njima stradale cijele obitelji.
-Prije ubojstva gotovo sve žene su silovane, a muškarci masakrirani odsijecanjem noseva, spolnih organa, ušiju…te drugim neopisivim načinima mučenja…
-Najmlađa žrtva bio je 14-godišnji Ervin Matanović, a najstarija 81-godišnji Stipo Dimač i , nažalost, može se slobodno reći kako nitko izvan Briševa nije čuo za te stradalnike i mučenike.
-Danas, 31. godinu poslije, samo jedna činjenica boli skoro jednako kao pokolj nad nevinim ljudima, a to je šutnja javnog mnijenja, a posebice hrvatskih medija i službene hrvatske politike u BiH.
-Proporcionalno gledano koliko medijske pozornosti dobiju drugi zločini u BiH, a posebice pojedini zločini nad Bošnjacima i Srbima, može se slobodno reći da Briševo kao mjesto sjećanja i pijeteta ne postoji.
-RTV HB/Foto: Nedjelja.ba</t>
+          <t>širiti daleko trideset prvi obljetnica velik ratni zločin hrvatima dogoditi selo briševo kod prijedor između srpanj godina ovaj selo ubijiti 67 mještanin što smatrati velik stradanje hrvata jedan dan protekl rat Bosna hercegovini pokolj selo briševi ratni zločin počiniti početkom rat srpanj hrvatima župa star rijeka četiri kilometar južno prijedor selo izbrisanoga ime kod prijedor zvjerski ubijiti 67 hrvat taj mjesto pokolj briševi hrvatski selo između prijedor sanski most počiniti pripadnik 5 kozarački brigada 6 krajiški brigada sanski most što masovan stradanje hrvat jedan dan tijekom protekli rat područje Bosna hercegovina smaknute čitav obitelj briševa matanovića 13 buzuka 10 ivandić devetero marijan sedmero mlinar komljena pokolje ubijeni otac Mladen matanović dva sin godišnji ervin johan matanović preživjeti svjedok tvrditi zločin strašan stradati cijel obitelj ubojstvo gotovo žena silovani muškarac masakrirati odsijecanje nos spolni organ drugi neopisiav način najmlađa žrtva ervin matanović Najstarija stipo dimač nažalost moći slobodno reći nitko izvan briševa čuti stradalnik mučenik danas godina poslije činjenica boliti skoro jednako pokolj nevin čovjek šutnja javan mnijenje posebice hrvatski medij služben hrvatski politika proporcionalno gledati koliko medijski pozornost dobiti drugi zločin posebice pojedini zločin bošnjak srbima moći slobodno reći briševo mjesto sjećanje pijetet postojati rtv</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1363,14 +1008,10 @@
       <c r="D20" t="n">
         <v>0.4490745067596436</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Zagreb, Hina</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hrvaat, BiH, Briševo, prijedor, Hrvat, Bosna i Hercegovina, pokolj, Brišev, BiH, Hrvaat, Stara Rijeka, prijedor, prijedor, Hrvat, pokolj, Brišev, prijedor, Sanski Most, Sanski Most, Hrvat, Bosna i Hercegovina, Briševa, Buzuka, Ivandić Devetero, Marijana sedmero, Mlinar, Komljena, Mladen Matanović, Ervin, Johan Matanović, Ervin Matanović, Stipo Dimač, Briševa, BiH., BiH, Bošnjacima, Srbin, Briševo, RTV HB / Foto</t>
+          <t>hrvatima, Bosna hercegovini, hrvat, hrvat, Bosna hercegovina, briševa matanovića, buzuka 10, ivandić Devetero, Mladen matanović dva, johan matanović, bošnjak srbima</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1380,20 +1021,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - U kulturi za utorak 25. srpnja nema važnijih događaja za najaviti. 
-	telefon: 01/4808 600
-telefaks: 01/4808 822
-e-mail: kultura@hina.hr
-</t>
+          <t>Zagreb srpanj 2023 hin kultura utorak srpanj važan događaj najaviti telefon 600 telefaks 822 kultura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gotovo je!
-U utorak 25. srpnja 2023. godine, nešto iza 14 sati, postavljen je posljednji kamen u pločnik novoobnovljene Nove rive i produženog gata.
-Građevinski radovi na obnovi i rekonstrukcije Obale kralja Petra Krešimira IV. i Liburnske obale tako su praktički došli do samog kraja. Idućih dana slijedi šminkanje, fugiranje i dotjerivanje lanterne koja je nakon gotovo 80 godina vraćena na svoje izvorno mjesto, na vrhu gata.
-Datum za povijest, projektni tim Lučke uprave Zadar i svi izvođači angažirani na radovima odradili su velik i zahtijevan posao, uspjeli su nekoliko mjeseci prije roka (do kraja ove godine), završiti jedan od najopsežnijih infrastrukturnih zahvata u Zadru od završetka Domovinskog rata te rivi vratiti stari sjaj na zadovoljstvo svih Zadranki i Zadrana.
-Prvo testiranje je već u subotu, 29. srpnja, kad se nakon tri godine pauze opet vraća dm-millennium jump.</t>
+          <t>gotovo utorak srpanj godina nešto iza 14 sat postaviti posljednji kamen pločnik novoobnovljen nov riv produžean gat građevinski rad obnova rekonstrukcija obala kralj petar krešimirati iv liburnski obala praktički doći sam kraj idući dan slijediti šminkanje fugiranje dotjerivanje lanteran gotovo 80 godina vraćena izvoran mjesto vrh gat datum povijest projektan tim lučki uprava zadar izvođač angažirati rad odraditi velik zahtijevan posao uspjeti nekoliko mjesec rok kraj ovaj godina završiti jedan opsežan infrastrukturni zahvat zadar završetak domovinski rat riv vratiti star sjaj zadovoljstvo sav zadranka zadrana prvi testiranje već subota srpanj kad tri godina pauza opet vraćati jump</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1402,14 +1035,10 @@
       <c r="D21" t="n">
         <v>0.2596468925476074</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Zagreb, Hina</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>obale kralj Petr Krešimir IV, Liburnske obala, datum, Lučke uprava Zadar, Zadar, domovinski rat, Zadranki, Zadran, Millennium jump</t>
+          <t>kralj petar</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1419,20 +1048,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - U kulturi za utorak 25. srpnja nema važnijih događaja za najaviti. 
-	telefon: 01/4808 600
-telefaks: 01/4808 822
-e-mail: kultura@hina.hr
-</t>
+          <t>Zagreb srpanj 2023 hin kultura utorak srpanj važan događaj najaviti telefon 600 telefaks 822 kultura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gotovo je!
-U utorak 25. srpnja 2023. godine, nešto iza 14 sati, postavljen je posljednji kamen u pločnik novoobnovljene Nove rive i produženog gata.
-Građevinski radovi na obnovi i rekonstrukcije Obale kralja Petra Krešimira IV. i Liburnske obale tako su praktički došli do samog kraja. Idućih dana slijedi šminkanje, fugiranje i dotjerivanje lanterne koja je nakon gotovo 80 godina vraćena na svoje izvorno mjesto, na vrhu gata.
-Datum za povijest, projektni tim Lučke uprave Zadar i svi izvođači angažirani na radovima odradili su velik i zahtijevan posao, uspjeli su nekoliko mjeseci prije roka (do kraja ove godine), završiti jedan od najopsežnijih infrastrukturnih zahvata u Zadru od završetka Domovinskog rata te rivi vratiti stari sjaj na zadovoljstvo svih Zadranki i Zadrana.
-Prvo testiranje je već u subotu, 29. srpnja, kad se nakon tri godine pauze opet vraća dm-millennium jump.</t>
+          <t>gotovo utorak srpanj godina nešto iza 14 sat postaviti posljednji kamen pločnik novoobnovljen nov riv produžean gat građevinski rad obnova rekonstrukcija obala kralj petar krešimirati iv liburnski obala praktički doći sam kraj idući dan slijediti šminkanje fugiranje dotjerivanje lanteran gotovo 80 godina vraćena izvoran mjesto vrh gat datum povijest projektan tim lučki uprava zadar izvođač angažirati rad odraditi velik zahtijevan posao uspjeti nekoliko mjesec rok kraj ovaj godina završiti jedan opsežan infrastrukturni zahvat zadar završetak domovinski rat riv vratiti star sjaj zadovoljstvo sav zadranka zadrana prvi testiranje već subota srpanj kad tri godina pauza opet vraćati jump</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1441,14 +1062,10 @@
       <c r="D22" t="n">
         <v>0.2596468925476074</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Zagreb, Hina</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>obale kralj Petr Krešimir IV, Liburnske obala, datum, Lučke uprava Zadar, Zadar, domovinski rat, Zadranki, Zadran, Millennium jump</t>
+          <t>kralj petar</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1458,18 +1075,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - U kulturi za utorak 25. srpnja nema važnijih događaja za najaviti. 
-	telefon: 01/4808 600
-telefaks: 01/4808 822
-e-mail: kultura@hina.hr
-</t>
+          <t>Zagreb srpanj 2023 hin kultura utorak srpanj važan događaj najaviti telefon 600 telefaks 822 kultura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Večernji đir po gradu 25. srpnja 2023.
-Večernji đir po gradu prepunom tusrista. U prodaji isu akreditacije za 14. d, Millennium Jump pa ako još niste požutite po svoju jer je broj skakača ograničen.
-Izvor: Bojan Bogdanić</t>
+          <t>večernji đir grad srpanj 2023 večernji đir grad prepunom tusrist prodaja isu akreditacija d millennium jump još požututi svoj broj skakač ograničiti izvor bojan Bogdanić</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1478,14 +1089,10 @@
       <c r="D23" t="n">
         <v>0.2923016846179962</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Zagreb, Hina</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Večernji, Millennium Jump, izvor, Bojan Bogdanić</t>
+          <t>Millennium jump, Bogdanić</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1495,19 +1102,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - U kulturi za utorak 25. srpnja nema važnijih događaja za najaviti. 
-	telefon: 01/4808 600
-telefaks: 01/4808 822
-e-mail: kultura@hina.hr
-</t>
+          <t>Zagreb srpanj 2023 hin kultura utorak srpanj važan događaj najaviti telefon 600 telefaks 822 kultura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Svoje su radove izložili Josip Škerlj, Mišo Baričević, Vulko Hajdić, Marija Koprivica, Maro Kriste, Valter Kožul, Anamarija Obradović, Klara Knego, Robert Kralj i Marta Baće
-U utorak, 25. srpnja 2023. u prizemlju Narodne knjižnice Grad otvorena je izložba posvećena 130. obljetnici otkrivanja Gundulićeva spomenika. Deset autora izložilo je svoje radove koristeći različite tehnike. Na otvorenju izložbe sudjelovali su povjesničar umjetnosti Ivan Viđen i knjižničarka Katarina Palinić. Izložba predstavlja vizualni doprinos bogatom programu koji su Dubrovačke knjižnice pripremile kako bi obilježile ovu značajnu obljetnicu.
--Među velikanima starije hrvatske književnosti Đivo Frano Gundulić vjerojatno je najviše puta bio portretiran. Iako se danas ne može sa sigurnošću (u)tvrditi kako je zapravo izgledao, ovaj je dubrovački vlastelin nježnoga nadimka "Mačica" zapravo pravi "celebrity" još od početka 19. stoljeća. Samo od objave "Galerije znamenitih Dubrovčana" 1841. pa do danas svaka je obljetnica povezana uz Gundulića iznjedrila neki novi likovni prikaz njegova lika ili likova iz njegovih djela. Bilo je tako 1838, 1841, 1889., 1893., 1938, 1989., a tako je i ovoga ljeta tijekom kojega obilježavamo 130. godina od podignuća pjesnikova spomenika kojega je izradio kipar Ivan Rendić. Gundulićevoj su se popularnosti u likovnim prikazima u suvremeno doba pridružili vjerojatno još samo Držić i Marulić. Dubrovačke knjižnice važno su mjesto ovogodišnje obljetnice jer je u Znanstvenoj knjižnici postavljena izložba iz fundusa. Međutim, uz razne rukopise i tiskana djela koja se čuvaju u doista bogatome fundusu knjižnice, ova ustanova daje riječ i našim sugrađanima likovnjacima koji ovdje izlažu svoja viđenja pjesnikova lika. Tako mjesto koje čuva pisanu riječ otvara vrata i likovnome jeziku, a taj je spoj i samome Gunduliću često bio vrlo drag motiv (sjetimo se samo opisa poljskoga kraljevskog dvora iz "Osmana"). Ova je mala izložba tako još jedan doprinos Dubrovačkih knjižnica obilježavanju 130. obljetnice podignuća Gundulićeva spomenika u Dubrovniku. - istaknuo je Viđen.
-Izložba ostaje otvorena do 18. kolovoza 2023.</t>
+          <t>rad izložiti Josip škerlj mišo Baričević vulko hajdić Marija koprivica Maro krist valter kožul Anamarija obradović klar knego robert kralj mart baće utorak srpanj prizemlje narodni knjižnica grad otvoriti izložba posvetiti obljetnica otkrivanje gundulić spomenik deset autor izložiti rad koristiti različit tehnika otvorenje izložba sudjelovati povjesničar umjetnost ivan viditi knjižničarka katarina palinić izložba predstavljati vizualan doprinos bogat program dubrovački knjižnica pripremiti obilježiti ovaj značajan obljetnica velikan star hrvatski književnost đivo frano gundulić vjerojatno mnogo put portretirati danas moći sigurnost tvrditi zapravo izgledati ovaj dubrovački vlastelin nježnoga nadimk mačica zapravo prav celebrity još početak stoljeće objava galerija znamenit dubrovčan danas svaki obljetnica povezan gundulića iznjedriti nov likovni prikaz lik lik njegov djelo 1838 1841 1938 ovaj ljeto tijekom koji obilježavati godina podignuće pjesnik spomenik koji izraditi kipar Ivan Rendić gundulićevoj popularnost likovan prikaz suvremen doba pridružiti vjerojatno još držići marulić dubrovački knjižnica važan mjesto ovogodišnji obljetnica znanstveni knjižnica postaviti izložba fundus međutim razni rukopis tiskan djelo čuvati doista bogatom fundus knjižnica ustanova davati riječ naš sugrađaan likovnjac ovdje izlagati viđenje pjesnik lik mjesto čuvati pisati riječ otvarati vrata likovnome jezik spoj samome gundulić često drag motiv sjetiti opis poljski kraljevski dvor osman mali izložba još jedan doprinos dubrovački knjižnica obilježavanje obljetnica podignuće gundulić spomenik dubrovnik istaknuti vidjeti izložba ostajati otvoriti kolovoz 2023</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1516,14 +1116,10 @@
       <c r="D24" t="n">
         <v>0.3767146468162537</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Zagreb, Hina</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Josip Škerlj, Mišo Baričević, Vulko Hajdić, Marija Koprivica, Maro Kriste, Valter Kožul, Anamarija Obradović, Klara Knego, Robert kralj, Marta Baće, narodni knjižnica grad, Gundulićeva, Ivan Viditi, Katarina Palinić, dubrovački knjižnica, Frano Gundulić, Dubrovčana, Gundulić, Ivan Rendić, držić, Marulić, Znanstvenoj knjižnica postaviti izložba, Gundulić, Osman, Gundulićeva, Dubrovnik, Viditi</t>
+          <t>Josip škerlj mišo, Baričević vulko hajdić Marija koprivica Maro, Anamarija obradović klar, knego robert, katarina palinić, frano gundulić, znamenit dubrovčati, Ivan Rendić, samome gundulić</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1533,26 +1129,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - U kulturi za utorak 25. srpnja nema važnijih događaja za najaviti. 
-	telefon: 01/4808 600
-telefaks: 01/4808 822
-e-mail: kultura@hina.hr
-</t>
+          <t>Zagreb srpanj 2023 hin kultura utorak srpanj važan događaj najaviti telefon 600 telefaks 822 kultura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NIJEMCI SU ZGROŽENI SLIKAMA: U evangelističkoj crkvi otvorena pa ubrzo zatvorena izložba slika koje prikazuju pornografiju homoseksualaca
-Nakon brojnih kritika u evangelističkoj crkvi St. Egidien u Nürnbergu je zatvorena izložba pornografskih slika poznate umjetnice, filmske redateljice i Queer aktivistice Rose von Praunheim (80) koja pod nazivom “Isus voli” ( “Jesus liebt” ) prikazuje pornografske slike homoseksualaca.
-Izložba je otvorena u petak, 21. srpnja, a trebala je ostati otvorena do 12. kolovoza. Zatvorena je nakon pet dana zbog brojnih kritika. Neke slike jasno prikazuju gay seksualne odnose, a njemačku mediji pišu kako je takva izložba u evangelističkoj crkvi skandalozina.
-Evangelistička crkva St. Egidien je prije izložbe na svojoj internetskoj stranici objavila kako je Rosa von Praunheim dobro poznata kao gay redateljica i aktivistica u pokretu za emancipaciju homoseksualaca.
-– Malo ljudi zna da ta autorica i slika. CSD Verein e.V. Nürnberg i Kulturkirche St. Egidien prikazuju radove na ovogodišnjim Prideweeksima u kojima se Rosa von Praunheim bavi represivnom religijom, oslobođenom seksualnošću i Isusom koji voli one koji žive na kritičan i otvoren način, napisali su u svojoj objavi.
-Nakon kritika s mnogih strana, crkveno vijeće i odgovorni pastor Thomas Zeitler prekinuli su izložbu u utorak, 25. srpnja 2023.
-Na vratima crkve stoji natpis na kojem je pojašnjeno prijevremeno zatvaranje izložbe.
-– Zbog javnih i internih reakcija na našu izložbu, mi kao zajednica započeli smo raspravu o tome što učiniti dalje. Do tada će crkva ostati zatvorena, piše u objašnjenju kojeg potpisuje pastor Thomas Zeitler.
-No, iako se neki Queer aktivisti zalažu za ponovno otvaranje izložbe, a među njima ima i kritičara te izložbe postavljene u evangelističkoj crkvi. Jedan od njih je i aktivist Ali Utlu, i sam homoseksualac. Bivši musliman je na Twitteru kritizirao otvaranje takve izložbe te napisao kako je gay pornografija u crkvi samo zato jer autor želi biti raznolik.
-Opširnije o izložbi u prilogu na stranici njemačkom portala Citizengo.org na kojoj možete otvoriti i potpisati peticiju protiv te izložbe čije slike još nisu uklonjene iz crkve.
-Fenix-magazin/MD</t>
+          <t>nijemac zgrožiti slika evangelistički crkva otvoriti ubrzo zatvoriti izložba slika prikazivati pornografija homoseksualac brojan kritika evangelistički crkva egidien nürnberg zatvoriti izložba pornografski slika poznat umjetnica filmski redateljica queer aktivistica ros von praunheim 80 naziv isus voljeti jesus liebt prikazivati pornografski slika homoseksualac izložba otvoriti petak srpanj trebati ostati otvoriti kolovoz zatvoriti pet dan zbog brojan kritika neki slika jasno prikazivati gay seksualan odnos njemački medij pisati takav izložba evangelistički crkva skandalozin evangelistički crkva egidien izložba svoj internetski stranica objaviti ros von praunheim dobro poznat gay redateljica aktivistica pokret emancipacija homoseksualac malo čovjek znati autorica slika csd verein Nürnberg kulturkirche egidien prikazivati rad ovogodišnji prideweeks ros von praunheim baviti represivan religija oslobođeni seksualnošću isus voljeti onaj živjeti kritičan otvoren način napisati svoj objava kritika mnogi strana crkven vijeće odgovoran pastor thomas zeitler prekinuti izložba utorak srpanj 2023 vrata crkva stajati natpis koji pojašnjiti prijevremen zatvaranje izložba zbog javan interni reakcija naš izložba zajednica započeti rasprava što učiniti daleko htjeti crkva ostati zatvoriti pisati objašnjenje koji potpisivati pastor thomas zeitler queer aktivist zalagati ponovan otvaranje izložba među imati kritičar izložba postaviti evangelistički crkva jedan aktivist utlo homoseksualac bivši musliman twitter kritizirati otvaranje takav izložba napisati gay pornografija crkva zato autor željeti raznolik opširno izložba prilog stranica njemački portal koji moći otvoriti potpisati peticija protiv izložba čiji slika još uklonjen crkva</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1561,14 +1143,10 @@
       <c r="D25" t="n">
         <v>0.2052842974662781</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Zagreb, Hina</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NIJEMCI, St, Egidien, Nürnberg, Queer aktivistica, Rose von Praunheim, isus, Jesus liebt, Evangelistička crkva St, Egidien, Roso von Praunheim, Verein, V. Nürnberg, Kulturkirche St, Egidien, Prideweeks, Roso von Praunheim, Isus, Thomas Zeitler, Thomas Zeitler, Queer, Ali Utlu, Twitter, Opširnija, Citizengo.org, Fenix - magazin</t>
+          <t>egidien nürnberg, isus, jesus liebt, crkva egidien, verein Nürnberg, isus, zeitler queer</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1578,24 +1156,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - U kulturi za utorak 25. srpnja nema važnijih događaja za najaviti. 
-	telefon: 01/4808 600
-telefaks: 01/4808 822
-e-mail: kultura@hina.hr
-</t>
+          <t>Zagreb srpanj 2023 hin kultura utorak srpanj važan događaj najaviti telefon 600 telefaks 822 kultura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ovih dana svjedočili smo velikoj završnici radova na obnovi zadarske rive, koja se odvija u sklopu EU projekta "Rekonstrukcija i izgradnja lučke infrastrukture Grad Zadar-Poluotok".
-Izvođač radova, zajednica ponuditelja Adriaing d.o.o. sa sjedištem u Kopru, Republika Slovenija i Adriaing d.o.o. Buje, unatoč nesnosnim temperaturama nije posustajao s izvršavanjem radova. Naprotiv, angažirani su i dodatni timovi kako bi se radovi na gatu priveli kraju u najkraćem roku.
-U utorak, 25. srpnja postavljen je posljednji kamen u pločnik novoobnovljene rive, čime je završeno popločavanje gata koje je izvedeno u površini od cca 1200 m2 te obalnog zida u površini od cca 300 m2.
-Ukupna dužina nadograđenog gata iznosi 80 metara, što je 15 metara duže u odnosu na dosadašnje stanje, a u skladu s njegovim povijesnim dimenzijama kakve je imao kada je izgrađen prije stotinjak godina.
-Sva kamena obloga, uključujući opločenje, bankinu, borduru, kamene stube i podesti, izvedena je od kamena vapnenca sedimentnog porijekla bijele boje, a površinska obrada vidljivih ploha je grubo štokana.
-Paralelno s kamenim popločenjem gata, izvodili su se specijalizirani radovi na lanterni koja je nakon gotovo 80 godina vraćena na svoje izvorno mjesto.
-U četvrtak, 27. srpnja završeno je bojanje lanterne, koja je sa svojom impozantnom visinom od gotovo 5 metara već poslužila kao kulisa za fotografije šetača.
-Velik broj angažiranih ljudi od strane izvođača radova podijeljenih u nekoliko timova te odlična koordinacija svih sudionika omogućila je realizaciju zaista velikog obima radova u ovom kratkom periodu. Preostaju još sitni radovi poput ugradnje vrata i rasvjetne konstrukcije lanterne, a koji neće ometati šetače u doživljaju pune ljepote zadarske rive kojoj je vraćen stari sjaj.
-Lučka uprava Zadar koristi ovu priliku da se još jednom zahvali svim građanima, ali i ostalim dionicima na strpljenju kojeg su pokazali kako bi u konačnici svi zajedno mogli uživati u zadarskoj rivi koja je ponos grada.</t>
+          <t>ovaj dan svjedočiti velik završnica rad obnova zadarski riva odvijati sklop EU projekt rekonstrukcija izgradnja lučki infrastruktura grad izvođač rad zajednica ponuditelj adriaing sjedište kopar republik slovenija adriaing bovati unatoč nesnosn temperatura posustajati izvršavanje rad naprotiv angažirati dodatan tim rad gat priveti kraj kralik rok utorak srpanj postaviti posljednji kamen pločnik novoobnovljen riv što završiti popločavanje gat izvedeno površina cca 1200 m2 obalan zid površina cca 300 m2 ukupan dužina nadograđen gat iznositi 80 metar što 15 metar duže odnos dosadašnje stanje sklad njegov povijesni dimenzija kakve imati izgraditi stotinjak godina sav kamen obloga uključivati opločenje bankin bordura kamen stuba podest izvediti kamen vapnenco sedimentan porijeklo bijel boja površinski obrada vidljiv ploha grubo štokan paralelno kamean popločenje gat izvoditi specijaliziran rad lanteran gotovo 80 godina vraćena izvoran mjesto četvrtak srpanj završiti bojanje lanteran svoj impozantan visina gotovo 5 metar već poslužiti kulisa fotografija šetač velik broj angažiran čovjek strana izvođač rad podijeljenih nekoliko tim odličan koordinacija sav sudionik omogućiti realizacija zaista velik ob rad ovaj kratak period preostati još sitan rad poput ugradnja vrata rasvjetan konstrukcija lanteran htjeti ometati šetač doživljati pun ljepota zadarski riva koji vratiti star sjaj lučkati uprava zadar koristiti ovaj prilika još jednom zahvati sav građanin ostali dionik strpljenje koji pokazati konačnik zajedno moći uživati zadarski riv ponos grad</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1604,14 +1170,10 @@
       <c r="D26" t="n">
         <v>0.5150014162063599</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Zagreb, Hina</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>EU, grad Zadar - poluotok, Adriaing d.o.o, kopru, republika Slovenija, Adriaing d.o.o, gat, Lučka uprava Zadar</t>
+          <t>EU, slovenija, Bijel</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1621,24 +1183,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - U kulturi za utorak 25. srpnja nema važnijih događaja za najaviti. 
-	telefon: 01/4808 600
-telefaks: 01/4808 822
-e-mail: kultura@hina.hr
-</t>
+          <t>Zagreb srpanj 2023 hin kultura utorak srpanj važan događaj najaviti telefon 600 telefaks 822 kultura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ovih dana svjedočili smo velikoj završnici radova na obnovi zadarske rive, koja se odvija u sklopu EU projekta "Rekonstrukcija i izgradnja lučke infrastrukture Grad Zadar-Poluotok".
-Izvođač radova, zajednica ponuditelja Adriaing d.o.o. sa sjedištem u Kopru, Republika Slovenija i Adriaing d.o.o. Buje, unatoč nesnosnim temperaturama nije posustajao s izvršavanjem radova. Naprotiv, angažirani su i dodatni timovi kako bi se radovi na gatu priveli kraju u najkraćem roku.
-U utorak, 25. srpnja postavljen je posljednji kamen u pločnik novoobnovljene rive, čime je završeno popločavanje gata koje je izvedeno u površini od cca 1200 m2 te obalnog zida u površini od cca 300 m2.
-Ukupna dužina nadograđenog gata iznosi 80 metara, što je 15 metara duže u odnosu na dosadašnje stanje, a u skladu s njegovim povijesnim dimenzijama kakve je imao kada je izgrađen prije stotinjak godina.
-Sva kamena obloga, uključujući opločenje, bankinu, borduru, kamene stube i podesti, izvedena je od kamena vapnenca sedimentnog porijekla bijele boje, a površinska obrada vidljivih ploha je grubo štokana.
-Paralelno s kamenim popločenjem gata, izvodili su se specijalizirani radovi na lanterni koja je nakon gotovo 80 godina vraćena na svoje izvorno mjesto.
-U četvrtak, 27. srpnja završeno je bojanje lanterne, koja je sa svojom impozantnom visinom od gotovo 5 metara već poslužila kao kulisa za fotografije šetača.
-Velik broj angažiranih ljudi od strane izvođača radova podijeljenih u nekoliko timova te odlična koordinacija svih sudionika omogućila je realizaciju zaista velikog obima radova u ovom kratkom periodu. Preostaju još sitni radovi poput ugradnje vrata i rasvjetne konstrukcije lanterne, a koji neće ometati šetače u doživljaju pune ljepote zadarske rive kojoj je vraćen stari sjaj.
-Lučka uprava Zadar koristi ovu priliku da se još jednom zahvali svim građanima, ali i ostalim dionicima na strpljenju kojeg su pokazali kako bi u konačnici svi zajedno mogli uživati u zadarskoj rivi koja je ponos grada.</t>
+          <t>ovaj dan svjedočiti velik završnica rad obnova zadarski riva odvijati sklop EU projekt rekonstrukcija izgradnja lučki infrastruktura grad izvođač rad zajednica ponuditelj adriaing sjedište kopar republik slovenija adriaing bovati unatoč nesnosn temperatura posustajati izvršavanje rad naprotiv angažirati dodatan tim rad gat priveti kraj kralik rok utorak srpanj postaviti posljednji kamen pločnik novoobnovljen riv što završiti popločavanje gat izvedeno površina cca 1200 m2 obalan zid površina cca 300 m2 ukupan dužina nadograđen gat iznositi 80 metar što 15 metar duže odnos dosadašnje stanje sklad njegov povijesni dimenzija kakve imati izgraditi stotinjak godina sav kamen obloga uključivati opločenje bankin bordura kamen stuba podest izvediti kamen vapnenco sedimentan porijeklo bijel boja površinski obrada vidljiv ploha grubo štokan paralelno kamean popločenje gat izvoditi specijaliziran rad lanteran gotovo 80 godina vraćena izvoran mjesto četvrtak srpanj završiti bojanje lanteran svoj impozantan visina gotovo 5 metar već poslužiti kulisa fotografija šetač velik broj angažiran čovjek strana izvođač rad podijeljenih nekoliko tim odličan koordinacija sav sudionik omogućiti realizacija zaista velik ob rad ovaj kratak period preostati još sitan rad poput ugradnja vrata rasvjetan konstrukcija lanteran htjeti ometati šetač doživljati pun ljepota zadarski riva koji vratiti star sjaj lučkati uprava zadar koristiti ovaj prilika još jednom zahvati sav građanin ostali dionik strpljenje koji pokazati konačnik zajedno moći uživati zadarski riv ponos grad</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1647,14 +1197,10 @@
       <c r="D27" t="n">
         <v>0.5150014162063599</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Zagreb, Hina</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>EU, grad Zadar - poluotok, Adriaing d.o.o, kopru, republika Slovenija, Adriaing d.o.o, gat, Lučka uprava Zadar</t>
+          <t>EU, slovenija, Bijel</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1664,36 +1210,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava važnijih sportskih događaja za utorak, 25. srpnja:
-	FUKUOKA - Nastavak Svjetskog prvenstva u vodenim sportovima, utakmica za poredak od 9. mjesta vaterpolista Hrvatske i Kanade (5 sati)
-SYDNEY - Nastavak Svjetskog prvenstva nogometašica
-ZAGREB - Prvi susret 2. pretkola nogometne Lige prvaka između Dinama i Astane (20.00 sati, stadion Maksimir)
-UMAG - Nastavak ATP teniskog turnira Croatia Open
-HAMBURG - Nastavak ATP i WTA teniskog turnira Hamburg European Open
-ATLANTA - Nastavak ATP teniskog turnira Atlanta Open
-LAUSANNE - Nastavak WTA turnira tenisačica Ladies Open Lausanne 
-VARŠAVA - Nastavak WTA turnira tenisačica Varšava Open
-SPORTSKA REDAKCIJA
-tel: 01/ 4808 671
-fax: 01/ 4808 822
-e-mail: sport@hina.hr
-</t>
+          <t>Zagreb srpanj 2023 hin najava važan sportski događaj utorak srpanj fukuoka nastavak svjetski prvenstvo voden sportov utakmica poredak mjesto vaterpolista hrvatski kanad 5 sat sydney nastavak svjetski prvenstvo nogometašica Zagreb prvi susret pretkol nogometni liga prvak između dina astati sat stadion maksimir umag nastavak atp teniski turnir croatia open hamburg nastavak atp wta teniski turnir hamburg european open atlant nastavak atp teniski turnir atlant open lausanni nastavak wta turnir tenisačica ladies open lausanni varšavati nastavak wta turnir tenisačica varšavati open sportski redakcija tel 4808 671 fax 4808 822 sport</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U Centru Zamet igraju se utakmice skupina E i F, a u kojima se nalaze Danska, Austrija, Kina, Meksiko, Norveška, Crna Gora, Sjeverna Makedonija i Gruzija
-Rijeka je uz Opatiju, Varaždin i Koprivnicu domaćin Svjetskog rukometnog prvenstva do 19 godina, što se održava do 13. kolovoza, a danas je u Salonu Grada Rijeke održan i prijem za predstavnike reprezentacija koje borave i igraju u Rijeci, kao i predstavnike Međunarodne rukometne federacije te Hrvatskog rukometnog saveza.
-U Centru Zamet igraju se utakmice skupina E i F, a u kojima se nalaze Danska, Austrija, Kina, Meksiko, Norveška, Crna Gora, Sjeverna Makedonija i Gruzija.
-Rijeka će biti domaćin i utakmica za poredak od 17. do 24. mjesta, a treninzi ekipa održavaju se u Dvorani mladosti te u dvorani Dinko Lukarić.
-Zamjenica gradonačelnika Sandra Krpan poželjela je sportašima ugodan boravak u Rijeci.
-– Zahvaljujem Međunarodnoj rukometnoj federaciji koja je Rijeku odabrala kao jedan od gradova domaćina ovog natjecanja, a tome je, sigurna sam, doprinijelo i prijašnje iskustvo organizacije velikih natjecanja u našem gradu.
-Pred nama je veliki sportski događaj i ljubitelji sporta i rukometa zasigurno će uživati u vrhunskom sportskom iskustvu – rekla je Sandra Krpan.
-Na ugodnom domaćinstvu Gradu Rijeci zahvalio se i Boris Konjuh, član Upravnog odbora HRS-a, ujedno i predsjednik Rukometnog saveza PGŽ-a. Lidija Bojić Čačić, direktorica natjecanja za Rijeku i Opatiju, dodala je da su igrači zadovoljni uvjetima.
-– Igrači i momčadi imaju odlične uvjete. Nadam se da ćemo imati uspješnu suradnju i u budućnosti – dodala je Lidija Bojić Čačić, dok je predstavnica Međunarodne rukometne federacije naglasila da je infrastruktura na vrhunskoj razini.
-– Infrastruktura i sve što ste nam omogućili je na najvećoj mogućoj razini za ovu kategoriju SP-a. Svima želim sreću, imali smo prilike već vidjeti dobre utakmice, kao i remi Švedske i Irana, što je iznenađenje i znači da svi žele i mogu igrati rukomet.
-Sretna sam što po svijetu svi puno rade u rukometu da bi bili na vrhu – rekla je Narcisa Lecusanu, članica izvršnog odbora Međunarodne rukometne federacije.
-Prijemu su nazočili i predsjednica Gradskog vijeća Grada Rijeke Ana Trošelj, direktor Rijeka sporta Igor Butorac i predsjednica Odbora za sport i tehničku kulturu Gradskog vijeća Grada Rijeke Danijela Bradamante.</t>
+          <t>centar zamet igrati utakmica skupina e f nalaziti danski austrija kino meksiko norveški Crna Gora sjeverni Makedonija gruzija rijeka opat varaždin koprivnica domaćin svjetski rukometan prvenstvo 19 godina što održavati kolovoz danas salon grad rijeka održati prijem predstavnik reprezentacija boraviti igrati rijeka predstavnik međunarodni rukometni federacija hrvatski rukometan savez centar zamet igrati utakmica skupina e f nalaziti danski austrija kino meksiko norveški Crna Gora sjeverni Makedonija gruzija rijeka htjeti domaćin utakmica poredak mjesto treninz ekipa održavati dvoran mladost dvorana dinko Lukarić zamjenica gradonačelnik Sandra Krpan poželjeti sportaš ugodan boravak rijeca zahvaljuj međunarodni rukometni federacija rijeka odabrati jedan grad domaćin ovaj natjecanje siguran doprinijeti prijašnji iskustvo organizacija velik natjecanje naš grad pred velik sportski događaj ljubitelj sport rukomet zasigurno htjeti uživati vrhunski sportski iskustvo reći Sandra krpan ugodan domaćinstvo grad rijeka zahvaliti boris konjuh član upravan odbor ujedno predsjednik rukometan savez lidija bojić čačić direktorica natjecanje rijeka opatija dodati igrač zadovoljan uvjet igrač momčad imati odličan uvjet nadati htjeti imati uspješan suradnja budućnost dodati lidija bojić čačić dok predstavnica međunarodni rukometni federacija naglasiti infrastruktura vrhunski razina infrastruktura što omogućiti najveći moguć razina ovaj kategorija sav željeti sreća imati prilika već vidjeti dobar utakmica remi švedske iran što iznenađenje značiti željeti moći igrati rukomet sretan što svijet puno raditi rukomet vrh reći narcis lecusan članica izvršan odbor međunarodni rukometni federacija prijem nazočiti predsjednica gradski vijeće grad rijeka Ana trošelj direktor rijeka sport Igor butorac predsjednica odbor sport tehnički kultura gradski vijeće grad rijeka danijeti bradamant</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1704,17 +1226,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zagreb, Hina, FUKUOKA - nastavak svjetski prvenstvo, Hrvatska, Kanada, SYDNEY - nastavak svjetski prvenstvo, Zagreb, liga prvak, Dinam, astane, Maksimir, Croatia Open, ATP, WTA, Hamburg European Open 
-, ATLANTA - Nastavak, Atlanta Open 
- LAUSANNE - nastavak WTA, Ladies Open Lausanne 
-, WTA, Varšava Open 
- SPORTSKA, sport@hina.hr 
-</t>
+          <t>svjetski prvenstvo voden sportov utakmica, svjetski prvenstvo nogometašica Zagreb, lausanni, lausanni</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>centar Zamet, E, F, Danska, Austrija, Kina, Meksiko, Norveška, Crna Gora, Sjeverna Makedonija, Gruzija, Rijeka, Opatija, Varaždin, Koprivnica, svjetski rukometan prvenstvo, Salon grad Rijeka, Rijeka, međunarodni rukometni federacija, hrvatski rukometan savez, centar Zamet, E, F, Danska, Austrija, Kina, Meksiko, Norveška, Crna Gora, Sjeverna Makedonija, Gruzija, Rijeka, Dinko Lukarić, Sandra Krpan, Rijeka, Međunarodnoj rukometni federacija, Rijeka, Sandra Krpan, Grad Rijeka, Boris Konjuh, upravan odbor, HRS - a, rukometni savez PGŽ - a., Lidija Bojić Čačić, Rijeka, Opatija, Lidija Bojić Čačić, međunarodni rukometni federacija, SP - a., Švedska, Iran, Narcisa Lecusanu, međunarodni rukometni federacija, gradski vijeće grad Rijeka, Ana Trošelj, Rijeka, Igor Butorac, odbor za sport, gradski vijeće grad Rijeka, Danijela Bradamante</t>
+          <t>Austrija, Crna Gora, Makedonija, savez centar zamet igrati utakmica skupina e f, Austrija, Crna Gora, Makedonija, Lukarić, Sandra Krpan, Sandra, savez lidij, bojić čačić, bojić čačić, Igor butorac</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1724,26 +1241,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAGREB, 25. srpnja 2023. (Hina) - Najava važnijih sportskih događaja za utorak, 25. srpnja:
-	FUKUOKA - Nastavak Svjetskog prvenstva u vodenim sportovima, utakmica za poredak od 9. mjesta vaterpolista Hrvatske i Kanade (5 sati)
-SYDNEY - Nastavak Svjetskog prvenstva nogometašica
-ZAGREB - Prvi susret 2. pretkola nogometne Lige prvaka između Dinama i Astane (20.00 sati, stadion Maksimir)
-UMAG - Nastavak ATP teniskog turnira Croatia Open
-HAMBURG - Nastavak ATP i WTA teniskog turnira Hamburg European Open
-ATLANTA - Nastavak ATP teniskog turnira Atlanta Open
-LAUSANNE - Nastavak WTA turnira tenisačica Ladies Open Lausanne 
-VARŠAVA - Nastavak WTA turnira tenisačica Varšava Open
-SPORTSKA REDAKCIJA
-tel: 01/ 4808 671
-fax: 01/ 4808 822
-e-mail: sport@hina.hr
-</t>
+          <t>Zagreb srpanj 2023 hin najava važan sportski događaj utorak srpanj fukuoka nastavak svjetski prvenstvo voden sportov utakmica poredak mjesto vaterpolista hrvatski kanad 5 sat sydney nastavak svjetski prvenstvo nogometašica Zagreb prvi susret pretkol nogometni liga prvak između dina astati sat stadion maksimir umag nastavak atp teniski turnir croatia open hamburg nastavak atp wta teniski turnir hamburg european open atlant nastavak atp teniski turnir atlant open lausanni nastavak wta turnir tenisačica ladies open lausanni varšavati nastavak wta turnir tenisačica varšavati open sportski redakcija tel 4808 671 fax 4808 822 sport</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UEFA je zabranila gostujuće navijače na utakmici Lige prvaka između AEK-a i Dinama.
-Pročitajte više na Gol.hr</t>
+          <t>uefa zabraniti gostujući navijač utakmica liga prvak između dinam pročitati mnogo</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1754,50 +1257,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zagreb, Hina, FUKUOKA - nastavak svjetski prvenstvo, Hrvatska, Kanada, SYDNEY - nastavak svjetski prvenstvo, Zagreb, liga prvak, Dinam, astane, Maksimir, Croatia Open, ATP, WTA, Hamburg European Open 
-, ATLANTA - Nastavak, Atlanta Open 
- LAUSANNE - nastavak WTA, Ladies Open Lausanne 
-, WTA, Varšava Open 
- SPORTSKA, sport@hina.hr 
-</t>
+          <t>svjetski prvenstvo voden sportov utakmica, svjetski prvenstvo nogometašica Zagreb, lausanni, lausanni</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UEFA, liga prvak, AEK - a, Dinam, Gol.hr</t>
+          <t>uefa</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.09090909090909091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dopredsjednica Udruge hrvatskih sudaca, Tijana Kokić u utorak je komentirala štrajk službenika na sudovima.
-“Ljudi odlaze i mi nemamo s kime raditi. Do ovog štrajka nitko nije razumio da mi bez ovih ljudi ne možemo raditi. Oni su dio tima i ako ih nema, nema ni posla”, istaknula je i osvrnula se na plaće sudaca.
-“Činjenica je da naše sudačke plaće nisu rasle od 2009. To ne izgleda malo naspram prosječne plaće, ali mi se moramo uspoređivati s našim kolegama u EU-u. Ako smo mi rastuće gospodarstvo EU-a i ako nama tako dobro ide onda nema nikakvog razloga da suci nemaju plaće kakve imaju u Portugalu, Španjolskoj, Italiji, Sloveniji Rumunjskoj. Ne uspoređujemo se Nijemcima i Nizozemcima koji imaju veći standard”, rekla je Kokić te dodala:
-“Mi smo štrajkali, ali to nije bio pravi štrajk jer smo i dalje radili, ali tek kad su službenici počeli štrajkati vidjelo se da sustav staje”, napomenula je.
-Sutkinja Kokić stanjem u hrvatskom pravosuđu je zadovoljna.
-“Statistički rezultati pokazuju da nismo loše pravosuđe i nismo sporiji od drugih. Možda je organizacija lošija i ona generira sporost. Nedostatak logistike generira sporost. Veliki sudovi u velikim gradovima, pogotovo u Zagrebu jer je sve centralizirano, su opterećeni. Ostalo je manje i manje. Na jednom sudu sudac ima 100 spisa, a drugi 350. Ta neujednačenost je dovela do loše percepcije”, poručila je dopredsjednica sudačke udruge u svom gostovanju na N1.</t>
+          <t>dopredsjednica udruga hrvatski sudac tijati Kokić utorak komentirati štrajk službenik sud čovjek odlaziti nemati kime raditi ovaj štrajk nitko razumiti bez ovaj čovjek moći raditi dio tim posao istaknuti osvrnuti plaća sudac činjenica naš sudački plaća rasti 2009 izgledati malo naspram prosječan plaća morati uspoređivati naš kolega rastući gospodarstvo dobro ići onda nikakv razlog suci nemati plaća kakav imati portugala španjolski italija Slovenija rumunjski uspoređujemo nijemac nizozemc imati velik standard reći kokić dodati štrajkali prav štrajk daleko raditi tek kad službenik početi štrajkati vidjeti sustav stajati napomenuti sutkinja kokić stanje hrvatski pravosuđe zadovoljan statistički rezultat pokazivati loš pravosuđe spor drugi možda organizacija loš generirati sporost nedostatak logistika generirati sporost velik sud velik grad pogotovo Zagreb centralizirano opterećiti ostalo malo malo jedan sud sudac imati 100 spis drugi 350 neujednačenost dovesti loš percepcija poručiti dopredsjednica sudački udruga gostovanje n1</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1808,12 +1288,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>udruga hrvatski sudac, Tijana Kokić, EU - u., EU - a, Portugala, Španjolska, Italija, Slovenija Rumunjska, Nijemcima, Nizozemk, Kokić, Kokić, Zagreb, N1</t>
+          <t>tijati Kokić, Slovenija, kokić, kokić, Zagreb</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1823,37 +1303,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do ‘breaka‘ došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva ‘breaka‘ prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2</t>
+          <t>marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 break doći početak drugi set čilić spriječiti talijan povesti dva break prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1864,47 +1319,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Martin Landaluce, Špa</t>
+          <t>marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>POVRATAK NA TENISKE TERENE
-Marin Čilić se porazom (6:4, 6:3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3:0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2:2, a po povratku na teren i za 3:3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."</t>
+          <t>povratak teniski teren Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1915,46 +1350,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto</t>
+          <t>Marin čilić, flavija cobollij, stella maris</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do ‘breaka‘ došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva ‘breaka‘ prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."</t>
+          <t>marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 break doći početak drugi set čilić spriječiti talijan povesti dva break prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1965,49 +1381,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto</t>
+          <t>marin čilić, flavija cobollij, stella maris</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hrvatski tenisač vratio se u Umag nakon devet godina, a tenisu se vratio nakon šest mjeseci
-Spustio se zastor nad prvim danom Plava Laguna Croatia Opena u Umagu. Kako se ponedjeljak bližio kraju, tako su se i stvarali sve veći redovi u okolici “Ivaniševića”. Poseban interes plijenio je posljednji meč na stadionu. Razlog? Marin Čilić vratio se u Umag. Ujedno, vratio se i tenisu. Vlasnik US Opena iz 2014. godine proteklih šest mjeseci proveo je na rehabilitaciji nakon ozljede meniskusa, a na istarskim terenima vratio se na posao. Međutim, zaustavljen je na prvoj stepenici umaškog turnira. Flavio Cobolli slavio je sa 6:4, 6:3, te tako osigurao nastavak pohoda u Umagu, nakon što je u glavni ždrijeb dospio kroz dva kola kvalifikacija. Protiv Čilića je, dakle, upisao treću pobjedu u tri dana.
-– Umag je uvijek bio zahtjevan turnir, pogotovo fizički, danas se to isto pokazalo. Bilo je dosta vlažno i nije lagano igrati, pogotovo za ofenzivnije igrače. Pozitivan sam što sam odigrao težak meč i izdržao na dobrom nivou – zadovoljan je Marin, unatoč porazu.
-Da bi mogao imati težak “dan u uredu”, Marin je osjetio na otvaranju meča protiv 21-godišnjeg Talijana. Već u prvom servis gemu morao se suočiti s break loptom suparnika, da bi ipak uskoro popustio. Cobolli mu je uspio oduzeti servis i povesti 3:2, a zatim i privesti prvi set u svoju korist, iako se susreo s Čilićevom break loptom potkraj seta, ali uspješno se obranio njegovim napadima.
-Početak drugog seta ponudio je sličan scenarij. Talijanski predstavnik odmah je izvršio pritisak i oduzeo Čiliću prvi servis gem, čime je zazidao temelje prema konačnoj pobjedi.
-Treba spomenuti kako je početkom drugog seta počela padati kiša, a sudac se u jednom trenu spustio sa stolice kako bi provjerio stanje terena, međutim, u tom trenutku meč je nastavljen. Međutim, samo nakratko. Minutu kasnije, priroda je ubrzavala ritam, a sve jača kiša potjerala je i gledatelje prema što bržem traženju izlaza i obližnjeg zaklona. Uslijedila je pauza od otprilike 25 minuta pri vodstvu Cobollija 3:1, nakon čega su se igrači vratili na teren i ponovno, kao i prije meča, krenuli na zagrijavanje. Po povratku, Marin je ponovno bio blizu breaka, ali suparnik je, praktički, najbolje poene sačuvao za najteže trenutke u meču.
-S obzirom na to kako je Marin zadnji meč odigrao početkom godine u Indiji, izvjesno je kako je duga pauza na njemu ostavila traga, a vjerojatno će biti potrebno još neko vrijeme, što je i normalno nakon višemjesečnih izbivanja u sportu, kako bi u potpunosti vratio osjećaj za igru, koji bi trebao stići u nadolazećim mjesecima.
-– Vidjelo se da mi fali mečeva, imao sam nekoliko prilika, ali to je tako. Cobolli je odigrao dobro u bitnim trenucima, bio je hrabar, ofenzivan. Tražio sam načine, ali nisam uspio pronaći rješenje – rekao je Marin.
-U danima prije turnira zračio je optimizmom, možda i potajno maštajući o epskom povratku tenisu i reprizi uspjeha iz 2012., kada je postao drugi Hrvat s trijumfom u Umagu, nakon Gorana Prpića 1990. Ipak, Marinov “comeback” zasjenila je Cobollijeva dobra predstava. Kako se meč bližio kraju, igrač iz Toskane bio je sve opušteniji, što se i osjetilo u njegovoj igri, piše sportske.jutarnji.hr.
-Mladi tenisač, trenutačno 148. igrač svijeta, upisao je tek petu pobjedu u glavnom dijelu ATP turnira, a trijumf protiv Čilića vjerojatno je i najzvučniji u njegovoj dosadašnjoj karijeri. U osmini finala mogao bi se susresti sa sunarodnjakom Matteom Arnaldijem, godinu starijim igračem, koji u utorak igra prvo kolo protiv Jespera De Jonga, Nizozemca koji je u glavni ždrijeb ušao kroz kvalifikacije.</t>
+          <t>hrvatski tenisač vratiti umag devet godina tenis vratiti šest mjesec spustiti zastor prvi dati plav lagun croatia open umaga ponedjeljak bližiti kraj stvarati velik redov okolica ivanišević poseban interes plijenio posljednji meč stadion razlog Marin čilić vratiti umag ujedno vratiti tenis vlasnik us open godina protekao šest mjesec provesti rehabilitacija ozljeda meniskus istarski teren vratiti posao međutim zaustaviti prvi stepenik umaški turnir flaviti cobolli slaviti osigurati nastavak pohod umaga što glavni ždrijeb dospiti dva kolo kvalifikacija protiv čilić dakle upisati treći pobjeda tri dan umag uvijek zahtjevan turnir pogotovo fizički danas isto pokazati dosta vlažno lagano igrati pogotovo ofenzivan igrač pozitivan što odigrati težak meč izdržati dobar nivo zadovoljan marin unatoč poraz moći imati težak dan ured marin osjetiti otvaranje meč protiv talijan već prvi servis gem morati suočiti break lopta suparnik ipak uskoro popustiti cobolli uspjeti oduzeti servis povesti zatim privesti prvi set svoj korist susreti čilićevo break lopta potkraj set uspješno obraniti njegov napad početak drugi set ponuditi sličan scenarij talijanski predstavnik izvršiti pritisak oduzeti čilić prvi servis gem što zazidati temelj prema konačan pobjeda trebati spomenuti početkom drugi set početi padati kiša sudac jedan tren spustiti stolica provjeriti stanje teren međutim taj trenutak meč nastaviti međutim nakratko minuta kasno priroda ubrzavati ritam jača kiša potjerati gledatelj prema što bržem traženje izlaz obližnjeg zaklon uslijediti pauza otprilike 25 minuta pri vodstvo cobollij što igrač vratiti teren ponovno meč krenuti zagrijavanje povratak marin ponovno blizu break suparnik praktički dobar poen sačuvati najtež trenutak meč obzir Marin zadnji meč odigrati početkom godina indija izvjesno dug pauza ostaviti trag vjerojatno htjeti potreban još neki vrijeme što normalno višemjesečni izbivanje sport potpunost vratiti osjećaj igra trebati stići nadolazeći mjesec vidjeti fati mečev imati nekoliko prilika cobolli odigrati dobro bitan trenutak hrabar ofenzivan tražiti način uspjeti pronaći rješenje reći marin danima turnir zračiti optimizm možda potajno maštajući epski povratak tenis reprizi uspjeh postati drugi hrvat trijumf umaga goran prpić 1990 ipak marinov comeback zasjeniti cobollijev dobar predstava meč bližiti kraj igrač toskan opuštean što osjetiti njegov igra pisati mlad tenisač trenutačno igrač svijet upisati tek peti pobjeda glavni dio atp turnir trijumf protiv čilić vjerojatno najzvučnija njegov dosadašnji karijera osmina finale moći susresti sunarodnjak matteom arnaldijem godina star igrač utorak igrati prvi kolo protiv jesper de jonga nizozemac glavni ždrijeb ući kvalifikacija</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2018,43 +1412,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>umag, Plav Laguna Croatia Open, Umag, Ivanišević, Marin Čilić, umag, US Open, Cobolli, Umag, Čilić, Marin, Marin, Talijan, Cobolli, Čilićevom, Čilić, Cobolli 3:1, Marin, Marin, Indija, Cobolli, Marin, Hrvat, Umag, Goran Prpić, Marinov, comeback, Cobollijeva, Toskane, ATP, Čilić, Matteom Arnaldij, Jesper De Jong, nizozemca</t>
+          <t>Marin čilić, Marin, hrvat, goran prpić, Jonga nizozemac</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."</t>
+          <t>marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2065,52 +1443,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin</t>
+          <t>marin čilić, flavija cobollij, stella maris</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-“Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou”, rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP – 148.) je do ‘breaka’ došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva ‘breaka’ prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-“Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje.”
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-“Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu – nije bilo loše”, zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-“Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto.”
-ATP Umag – 1. kolo
-Flavio Cobolli (Ita) – Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) – Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) – Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) – Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) – Martin Landaluce (Špa) 1-6, 7-5, 6-2</t>
+          <t>marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 break doći početak drugi set čilić spriječiti talijan povesti dva break prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2121,52 +1474,27 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, ATP, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Martin Landaluce, Špa</t>
+          <t>marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.896551724137931</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-“Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou”, rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP – 148.) je do ‘breaka’ došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva ‘breaka’ prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-“Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje.”
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-“Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu – nije bilo loše”, zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-“Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto.”
-ATP Umag – 1. kolo
-Flavio Cobolli (Ita) – Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) – Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) – Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) – Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) – Martin Landaluce (Špa) 1-6, 7-5, 6-2</t>
+          <t>marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 break doći početak drugi set čilić spriječiti talijan povesti dva break prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2177,48 +1505,27 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, ATP, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Martin Landaluce, Špa</t>
+          <t>marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.896551724137931</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>U svom povratničkom meču, a vratio se turnirima nakon stanke od šest mjeseci, Marin Čilić doživio je poraz. U prvom kolu našeg jedinog ATP turnira u Umagu bolji od njega bio je talijanski kvalifikant Flavio Cobolli, 148. tenisač na ATP listi, sa 6:4, 6:3. Poznato je da kvalifikanti znaju biti neugodni za favorizirane igrače (jer su ipak već odigrali nekoliko mečeva na istoj podlozi i u istim uvjetima), ali ne bi Cobolli bio problem za starog Čilića. No, stanka je učinila svoje, Međugorac je samo na trenutke podsjećao na pobjednika US Opena i bivšeg broja tri svjetskog tenisa. No, ono što je najvažnije - vratio se!
-- Koljeno je izdržalo jako dobro i to je prilično pozitivna stvar. Umag je uvijek bio prilično težak turnir, pogotovo u tjelesnom smislu. To se i danas pokazalo. Bilo je vlažno i uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije, bili su prilično nepovoljni. Cobolli je bio jako dobar na nogama, prilično dobro posložen je atletski i nije mi nudio puno. Pozitivan sam zbog toga što sam odigrao fizički prilično težak meč i izdržao ga na dobroj razini - kazao je Čilić, pobjednik tog turnira iz 2012. godine.
-GALERIJA Ekskluzivne fotografije Novaka Đokovića u Dubrovniku. Srpski as uživa u Hrvatskoj
-Nije Marinu pomogao ni 20-minutni prekid u drugom setu, do kojeg je došlo zbog kiše, iako se u jednom trenutku učinilo da se može vratiti u meč (propustio je priliku za izjednačenje na 3:3).
-- Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi nedostaje mečeva. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine, ali završio je meč a ja nisam uspio pronaći rješenje. No, nadam se da će u sljedećim mečevima moja igra ići na bolje - poželio je Čilić, otkrivši da bi nakon svega taj meč radije odigrao u nekom drugom terminu.
-VEZANI ČLANCI:
-- Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je nekoliko situacija hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet-šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih pogrešaka, pa i strateških. No, prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše - zaključio je Marin, najavivši sljedeće akcije:
-- Volio bih odigrati još jedan turnir na zemlji prije betonske sezone. Kitzbühel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto i ondje započeti američku turneju.
-VIDEO Trening Dinama uoči utakmice 2. pretkola Lige prvaka protiv Astane</t>
+          <t>povratnički meč vratiti turnirima stanka šest mjesec marin čilić doživiti poraz prvi kolo naš jedin atp turnir umaga dobar talijanski kvalifikant flaviti cobolli tenisač atp list poznato kvalifikant znati neugodan favoriziran igrač ipak već odigrati nekoliko mečeva isti podloza isti uvjet cobolli problem star čilić stanka učiniti međugorac trenutak podsjećati pobjednik us open bivši broj tri svjetski tenis što važan vratiti koljeno izdržati jako dobro prilično pozitivan stvar umag uvijek prilično težak turnir pogotovo tjelesan smisao danas pokazati vlažno uvjet igrač što igrati malo ofenzivno prilično nepovoljan coboll jako dobar noga prilično dobro posložiti atletski nuditi puno pozitivan zbog taj što odigrati fizički prilično težak meč izdržati dobar razina kazati čilić pobjednik taj turnir godina galerija ekskluzivan fotografija novak đokovića dubrovnik srpski as uživati hrvatskoj marina pomoći prekid drugi set koji doći zbog kiša jednom trenutak učiniti moći vratiti meč propustiti prilika izjednačenje šansa vidjeti taj neki situacija nedostajati mečev morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način završiti meč uspjeti pronaći rješenje nadati htjeti sljedeći mečev igrati ići dobro poželiti čilić otkriti svega meč rado odigrati neki drugi termin vezan članak igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak nekoliko situacija hoću vratiti prelomilo njegov strana zadnji gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički pogreška strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin najaviti sljedeći akcija voliti odigrati još jedan turnir zemlja betonski sezona kitzbühel opcija tamo glavni turnir uspjeti ići htjeti toronto ondje započeti američki turneja video trening dina uoči utakmica pretkol liga prvak protiv astati</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2229,45 +1536,27 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Marin Čilić, ATP, Umag, Flaviti Cobolli, Cobolli, Čilić, Međugorac, US Open, Cobolli, Čilić, Novak Đoković, Dubrovnik, Hrvatska, Marina, Čilić, Marin, Kitzbühel, Toronto, Dinam, liga prvak, astane</t>
+          <t>marin čilić, đokovića dubrovnik</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Prošlo je već neko vrijeme od službenog dogovora meča između Francisa Ngannoua i Tysona Furyja, ali reakcije javnosti ne prestaju. Dosta često fanovi ili beskompromisno podržavaju ili najstrože osuđuju ovaj meč, ali se u jednoj stvari većina ipak slaže; a to je da ovaj meč nema nikakvu sportsku vrijednost.
-Bez obzira na to, zasigurno će biti zanimljivo gledati sve ono što nam oko tog meča slijedi, a na kraju i sam meč. Legendarni Mike Tyson je rekao kako je spreman pomoći Ngannou u pripremama za Furyja, a izgleda da ni Francis ne bi imao apsolutno ništa protiv:
-‘‘Fury je rekao puno stvari, ali bolje bi mu bilo da se priprema za 28.10. jer ako me ne shvati ozbiljno, to bi mu mogla biti najveća životna greška. Mislim da bi mi nekoliko savjeta Mikea Tysona koristilo, ali također možda i Lennoxa Lewisa. Volim taj stil boksa, jako je jednostavan ali efikasan. Jedan ili dva udarca, klasik ali jako dobar‘‘, rekao je ranije Ngannou.
-To je sve došlo i do Tysona koji je otvoren za ovu suradnju:
-‘‘Volio bih to učiniti, bilo bi cool. Volio bih to, da, volio bih. Fury je dugi udarač, tako da mu morate ući unutra s jakim udarcima. Kada on počne bacati, budite spremni. Bum, jak udarac u tijelo‘‘, rekao je Mike.
-Hoće li se od ovoga išta i obistiniti, vidjet ćemo u sljedećih nekoliko mjeseci. Ngannnou je zasigurno već u debelim pripremama za Furyja sa svojim timom, no savjet od velikog Tysona nitko ne bi odbio.</t>
+          <t>proći već neki vrijeme služben dogovor meč između Francis ngannoua tyson Furyj reakcija javnost prestati dosta često fan beskompromisno podržavati najstrože osuđivati ovaj meč jedan stvar većina ipak slagati ovaj meč nikakav sportski vrijednost bez obzir zasigurno htjeti zanimljiv gledati što oko taj meč slijediti kraj meč legendaran mika tyson reći spreman pomoći ngannou priprema furyja izgledati francis imati apsolutno ništa protiv fury reći puno stvar dobro pripremati shvati ozbiljno moći velik životan greška misliti nekoliko savjet Mike tysono koristiti također možda lennox lewis voljeti stil bokse jako jednostavan efikasan jedan dva udarac klasik jako dobar reći rano ngannou doći tyson otvoriti ovaj suradnja voliti učiniti Cool voliti voliti fury dug udarač morati ući unutra jaak udarc početi bacati budite spreman Bum jak udarac tijelo reći mika htjeti ovaj išta obistiniti vidjeti htjeti sljedeći nekoliko mjesec ngannnou zasigurno već debel priprema furyja svoj tim savjet velik tyson nitko odbiti</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2278,12 +1567,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Francisa Ngannou, Tyson Furyj, Mike Tyson, Ngannou, Fury, Francis, fury, Mike Tyson, Lennox Lewis, Ngannou, Tyson, Bum, Mike, ngannnou, Fury, Tyson</t>
+          <t>Francis, Furyj, mika Tyson, francis, Mike tysono, lennox lewis, Bum</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2293,30 +1582,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kći bivšeg hrvatskog premijera Tihomira Oreškovića, Ella Orešković (24) odmara se od studentskih obaveza i uživa u ljetnim radostima. Glazbenica i studentica psihologije objavila je fotografiju u ljetnom izdanju na kojoj je iznad kupaćeg kostima nosila prozirnu ljetnu haljinu koja je istaknula njezinu vitku liniju i od pratitelja je dobila komplimente za svoj izgled i ljetni outfit.
-Ellu je javnost upoznala kada se prije dvije godine prvi put prijavila na Doru gdje je imala svoj pjevački debi s pjesmom "Come this Way", koju je sama napisala, a odlazak na Euroviziju pokušala je izboriti i prošle godine, s još jednom autorskom pjesmom "If you go away". Kada je u jednom intervju govorila o tome smeta li joj što ju često oslovljavaju kao kći bivšeg premijera.
-- Moj je tata bio premijer u određenom trenutku našeg života. Ljudima će to uvijek biti zanimljivo, tako da mi, moram priznati, to ne smeta - objasnila je za Story.hr. Dodala je i da otac podržava njezinu karijeru, ali od nje traži ozbiljnost prema drugim obavezama i fakultetu. Kazala je i da je on uvijek spreman za razgovor te da otvoreno govori što misli o njezinu pjevanju.
-Ella studira psihologiju, a pjevati je počela s 10 godina, dok je s obitelji još živjela u Kanadi, u glazbu se u potpunosti zaljubila nakon dolaska u Hrvatsku. U Zagrebu je pohađala Američku međunarodnu školu u kojoj je u sklopu obveznog glazbenog predmeta počela brusiti svoj glazbeni talent.
-– Počela sam pjevati svaki dan, a imala sam i profesoricu pjevanja. U glazbi sam se skroz pronašla i tada sam shvatila da se njome želim baviti ozbiljno – rekla je jednom prilikom Ella. Ipak, unatoč želji za uspjehom u estradnom svijetu oduvijek je bila svjesna da glazbenu karijeru nije lako ostvariti pa je nakon završetka srednje škole upisala studij psihologije u španjolskom gradu Murcia. – Mislim da je uvijek dobro imati nešto sa strane u slučaju da glazbena karijera ne uspije - kaže.
-VIDEO Joško Lokas otkriva dobro čuvanu tajnu omiljenih kvizova ‘Potjera’ i ‘Superpotjera’</t>
+          <t>kći bivši hrvatski premijer tihomir oreškovića ella orešković 24 odmar studentski obaveza uživati ljetni radost glazbenica studentica psihologija objaviti fotografija ljetan izdanje koji iznad kupaći kost nositi proziran ljetni haljina istaknuti njezin vitak linija pratitelj dobiti kompliment izgled ljetni outfit ell javnost upoznati dva godina prvi put prijaviti dora gdje imati pjevački debi pjesma com this way sam napisati odlazak eurovizija pokušati izboriti prošli godina još jedan autorski pjesma if you go away jednom intervju govoriti smetati što često oslovljavati kći bivši premijer tata premijer određen trenutak naš život čovjek htjeti uvijek zanimljiv morati priznati smetati objasniti dodati otac podržavati njezin karijera on tražiti ozbiljnost prema drugi obaveza fakultet kazati uvijek spreman razgovor otvoreno govoriti što misliti njezin pjevanje ell studirati psihologija pjevati početi 10 godina dok obitelj još živjeti kanadi glazba potpunost zaljubiti dolazak hrvatski Zagreb pohađati američki međunarodni škola koji sklop obvezan glazbeni predmet početi brusiti glazben talent početi pjevati svaki dan imati profesorica pjevanje glazba skroz pronaći shvatiti njome željeti baviti ozbiljno reći jedan prilika ella ipak unatoč želji uspjeh estradan svijet oduvijek svjesan glazben karijera lako ostvariti završetak srednji škola upisati studij psihologija španjolski grad murcia misliti uvijek dobro imati nešto strana slučaj glazben karijera uspjeti kazati video joško Lokas otkrivati dobro čuvati tajna omiljean kviz potjera superpotjer</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2327,12 +1598,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tihomir Orešković, Ella Orešković, Ella, Dora, Come this Way, Eurovizija, If you go away, story.hr, Ella, Kanada, Hrvatska, Zagreb, Američki međunarodni škola u, Ella, Murcia, Joško Lokas, potjer, superpotjera</t>
+          <t>tihomir oreškovića ella orešković, Zagreb, ella, lokas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2342,30 +1613,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Noćas je emitirana deveta epizoda ‘‘The Ultimate Fightera‘‘, a na rasporedu su bila polufinala u lakoj kategoriji. Održala se borba između dvojice boraca iz Chandlerovog tima, odnosno Austina Hubbarda i Roosevelta Robertsa, a Dana White nije bio impresioniran ni borbom ni sudačkom odlukom.
-Obojica su borbu otvorila podosta rezervirano te je djelovalo kao da imaju previše poštovanja jedan prema drugome. Roosevelt je pogađao solidne udarce nogom, dok je Hubbard svoju priliku vidio u udarcima u tijelo. Iako nije imao svog borca u kavezu, McGregora to nije spriječilo da borcima daje upute tokom meča. Roberts je u jednom trenutku odlično pogodio koljeno, a nakon njega je dobio udarac u međunožje.
-U drugoj rundi je sudac Robertsa upozorio da pripazi na prste, nakon čega ga je Roosevelt srušio. Roberts je uhvatio ‘‘giljotinu‘‘, no Hubbard nije bio ozbiljnije ugrožen te je nastavio raditi u parteru, ali su rundu ipak završili na nogama. U posljednjoj je rundi Roberts bio nešto agresivniji, a Roberts je počeo inicirati klinč na žici. Pobjedu je odnio Austin Hubbard podijeljenom sudačkom odlukom.
-Dana nije oduševljen onime što je vidio:
-‘‘Bez obzira na ovu sudačku odluku, nisam impresioniran. Mi u UFC-u želimo tipove koji preuzimaju kontrolu i završavaju borbe. Bili su tu, ali nisu bili agresivni. Tko god da je pobijedio, nadam se da će bolje izgledati u finalu‘‘, rekao je Dana.
-Sljedećeg tjedna je na rasporedu polufinale u bantam kategoriji, a nastupit će Brad Katona ispred tima McGregor, dok će Chandlera i njegov tim predstavljati Timur Valiev.</t>
+          <t>noćas emitirati deveti epizoda the ultimati fighter raspored polufinal laki kategorija održati borba između dvojica borac chandlerov tim odnosno austin hubbard roosevelt roberts dan whitjeti impresioniran borba sudački odluka obojica borba otvoriti podosta rezerviran djelovati imati previše poštovanje jedan prema drugi roosevelt pogađao solidan udarac nog dok hubbard svoj prilika vidjeti udarc tijelo imati borac kavezu mcgregora spriječiti bork davati uputa tokom meč roberts jedan trenutak odlično pogoditi koljeno dobiti udarac međunožje drugi runda sudac roberts upozoriti pripaziti prst što roosevelt srušiti roberts uhvatiti giljotina hubbard ozbiljno ugrožen nastaviti raditi parter runda ipak završiti noga posljednji runda roberts nešto agresivan roberts početi inicirati klinč žica pobjeda odniti austin hubbard podijeljen sudački odluka dan oduševljiti onime što vidjeti bez obzir ovaj sudački odluka impresioniran željeti tipov preuzimati kontrola završavati borba agresivan tko god pobijediti nadati htjeti dobro izgledati finale reći dan sljedeći tjedan raspored polufinale Bantam kategorija nastupiti htjeti brad katon ispred tim mcgregor dok htjeti chandlera taj predstavljati timur valiev</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2376,12 +1629,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>the Ultimati Fighter, Chandlerovog, Austin, Hubbard, Roosevelta Roberts, dan White, Roosevelt, Hubbard, McGregor, Roberts, Robertsa, Roosevelt, Roberts, Hubbard, Roberts, Roberts, Austin Hubbard, UFC - u, dan, Bantam kategorija, Brad Katon, McGregor, Chandler, Timur Valiev</t>
+          <t>austin hubbard roosevelt, giljotina hubbard, austin hubbard, Bantam, brad katon</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2391,33 +1644,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ako ste imali slično iskustvo podijelite ga s nama putem maila [email protected]
-Nakon objave članka o neugodnom iskustvu jedne Zagrepčanke na pregledu kod ginekologa, javila nam se još jedna čitateljica.
-Trudnica došla na prvi pregled u Zagrebu pa doživjela šok: ‘Gospođo znate li vi da su žene prije rađale štihajući na polju?’
-“Želim podijeliti svoje neugodno iskustvo na pregledu i neposredno prije pregleda u trudnoći. Dakle, poznato je da su osobni podaci zaštićeni GDPR uredbama, u čekaonici i ordinacijama ginekologije je nepoštivanje uredbe posebno istaknuto. No, sestra me je prozvala ispred desetak ljudi sa ‘ajmo trudnica’ iako sam bila samo sedam tjedana trudna, ništa se nije vidjelo i nije bilo naznaka trudnoće.
-Ordinacija je bila u kvartu gdje sam poznavala neke osobe koje su bile u čekaonicu, pa sam morala ranije od planiranog priopćiti svojim bližnjima da sam trudna jer su neki od susjeda očito to već znali. Trudnoća je bila visoko rizična i željela sam zadržati za sebe saznanje o trudnoći, no sestra u domu zdravlja je ipak odlučila umjesto mene”, ispričala nam je svoje neugodno iskustvo jedna čitateljica te nastavila.
-Neugodno iskustvo s naručivanjem kod doktora: ‘Još ti bahato i bezobrazno zalupe vratima pred nosom’
-“Na prvom pregledu ginekologinja mi je na zahtjev da pogledam pokrete bebice koji se vide na ultrazvuku rekla da nemam što vidjeti i što ću to gledati, na što sam zašutjela zbunjeno. Također, nisam mogla dobiti isprintan papir s ultrazvuka jer se taj papir štedi, tako da sam partneru i bližnjima opisivala kako moja bebica izgleda. Štedjeli su se i papirnati ručnici, pa sam gel koji se koristi prilikom pregleda ultrazvukom brisala o svoju majicu”, zaključila je ogorčena Zagrepčanka.
-1 euro = 7,53450 kuna
-Komentari</t>
+          <t>imati sličan iskustvo podijeliti putem mail email protected objava članak neugodan iskustvo zagrepčanka pregled kod ginekolog javiti još čitateljica trudnica doći prvi pregled Zagreb doživjeti šok gospođo znati žena rađati štihajući polje željeti podijeliti neugodan iskustvo pregled neposredno pregled trudnoć dakle poznato osoban podatak zaštićiti gdpr uredba čekaonik ordinacija ginekologija nepoštivanje uredba posebno istaknuti sestra prozvati ispred desetak čovjek ajti trudnica sedam tjedan trudan ništa vidjeti naznaka trudnoća ordinacija kvart gdje poznavati neki osoba biti čekaonica moral rano planirati priopćiti svoj bližnjima trudn susjed očito već znati trudnoća visoko rizičan željeti zadržati saznanje trudnoć sestra dom zdravlje ipak odlučiti umjesto ispričati neugodan iskustvo čitateljica nastaviti neugodan iskustvo naručivanje kod doktor još bahato bezobrazno zalupa vrata pred nos prvi pregled ginekologinje zahtjev pogledati pokret bebica vidjeti ultrazvuka reći nemati što vidjeti što htjeti gledati što zašutjeti zbunjeno također moći dobiti isprintan papir ultrazvuk papir štediti partner bližnjima opisivati bebica izgledati štedjeti papirnati ručnik gel koristiti prilikom pregled ultrazvuak brisati svoj majica zaključiti ogorčen zagrepčanka 1 euro kuna komentar</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2428,12 +1660,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zagrepčanka, Zagreb, GDPR, Zagrepčanka</t>
+          <t>Zagreb</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2443,37 +1675,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Marin Čilić vratio se u tinejdžerske dane. Osim što je prošli ponedjeljak, prvi put nakon gotovo 16 godina, za dlaku ispao iz društva najboljih sto igrača na ATP ljestvici, tenisač iz Međugorja u Umagu je reprizirao rezultat iz doba dok je još bio maloljetan. Drugi put u karijeri, osvajač US Opena iz 2014. zapeo je na prvoj stepenici turnira, što mu se dogodilo jedino 2005. Bio je tada na pragu punoljetnosti, a tadašnji poraz u prvom kolu od Belgijca Kristofa Vliegena pamtit će po premijeri na ATP razini.
-Iako se oprostio od pohoda na drugi naslov u Umagu, nakon što je turnir pokorio 2012. kao jedini Hrvat u povijesti uz Gorana Prpića, treba uzeti u obzir kako mu je ovogodišnji nastup u Istri ujedno bio i povratak tenisu nakon šestomjesečne pauze zbog ozljede koljena, zbog koje je morao obaviti operaciju meniskusa.
-- Koljeno je dobro izdržalo, s tim sam pozitivan. Odigrao sam fizički težak meč i izdržao na dobrom nivou. Vidjelo se da mi nedostaje mečeva da iskoristim neke prilike koje mi je suparnik nudio - pričao je Marin nakon povratka, nakon što je posljednji meč odigrao u Indiji u siječnju, naglašujući usput i dobru igru 21-godišnjeg Flavija Cobollija, koji je upisao petu ATP pobjedu u karijeri.
-Dugi izostanci
-Da povratak sportu nakon dužeg izbivanja nije lagan, najbolje dokazuje i ostatak koncentracije Grand Slam pobjednika koja se ovih dana okupila u Umagu. I Stan Wawrinka i Dominic Thiem prethodnih su godina prošli kalvariju s ozljedama, što se u konačnici, kao i kod Marina, odrazilo na njihovom plasmanu na ljestvici. Baš kao Čilić, i Švicarac i Austrijanac vrhunac karijere, osim po velikim titulama, pamtit će po trećem mjestu na ATP listi. No ozljede su donijele i valovite trendove u nastavku njihovih karijera.
-Iako se niti jedan sport ne dopušta život na staroj slavi, u tenisu je to posebno uočljivo. Bodovi se hvataju iz tjedan u tjedan, a velika imena, uslijed ozljeda, suočavaju se sa sve rednim brojevima kraj imena, dok su vrijednosti bodova sve manje.
-Tako se Wawrinka, kojemu jedino Wimbledon nedostaje za "poker" Grand Slamova, početkom kolovoza prošle godine našao na na 322. mjestu. S druge strane, Thiem je trenutačno 112. igrač svijeta, iako je i to plasman na koji nas nije navikao kroz karijeru, ali uzme li se u obzir kako je u lipnju prošle godine bio 352., koketiranje sa statusom sto najboljih upućuje na zaključak o očiglednom napretku u njegovoj igri u posljednjih godinu dana.
-- Nije jednostavno, došao sam tu s dobrim temeljima, ali meč je nešto drugačije od treninga. Nadam se da će od ovoga sve dalje ići prema boljem. Kad podvučem crtu, nije bilo loše - ponovio je Marin, i sam svjestan kako su kroz slične scenarije prolazili i njegovi kolege, ali i da ga do potencijalnog povratka među najbolje mora odraditi još puno dobrih turnira.
-Kitzbühel ili Toronto?
-Nastavno, izvjesno je kako Marina čekaju i nešto slabiji turniri, dok bi se na nekima mogao oslanjati na pozivnice i zaštićeni renking.
-- Kamo ću dalje? Nisam siguran, volio bih igrati barem još jedan turnir na zemlji. Kitzbühel je jedna od opcija, međutim tamo nisam u glavnom turniru, a nisam siguran kakva će biti situacija s pozivnicama, moram vidjeti. Ako to ne uspije, ići ću u Toronto - zaključio je Marin prije odlaska iz Umaga.
-U tekući tjedan zakoračio je kao točno stoti igrač svijeta, no sasvim je moguće da se spusti za koje mjesto do idućeg ponedjeljka, ako njegovi pratitelji odrade dobar ostatak tjedna. Koncem rujna proslavit će 35. rođendan, a dva njegova jedina vršnjaka u top 30, Roberto Bautista Agut (25.) i Adrian Mannarino (27.), pokazuju kako u društvu najboljih još uvijek ima prostora i za nešto "stariju gardu".
-Dobar primjer je i godinu stariji Andy Murray, koji u posljednje vrijeme kuca na vrata 30 najboljih, dok Novak Đoković, još jedan igrač godinu stariji od Marina, odolijeva ozljedama i dalje igra na najvišoj mogućoj razini. Najstariji igrač u društvu najboljih 50 je Richard Gasquet, dobro poznati, 37-godišnji francuski "jednoručni bekhend".</t>
+          <t>marin čilić vratiti tinejdžerski dan osim što proći ponedjeljak prvi put gotovo 16 godina dlaka ispati društvo dobar sto igrač atp ljestvica tenisač međugorja umaga reprizirati rezultat doba dok još maloljetan drugi put karijera osvajač us open zapeti prvi stepenik turnir što dogoditi jedino 2005 prag punoljetnost tadašnji poraz prvi kolo Belgijc kristof vliegen pamtiti htjeti premijera atp razina oprostiti pohod drugi naslov umaga što turnir pokoriti jedini hrvat povijest goran prpić trebati uzeti obzir ovogodišnji nastup istra ujedno povratak tenis šestomjesečan pauza zbog ozljeda koljen zbog morati obaviti operacija meniskus koljeni dobro izdržati taj pozitivan odigrati fizički težak meč izdržati dobar nivo vidjeti nedostaj mečev iskoristiti neki prilika suparnik nuditi pričati marin povratak što posljednji meč odigrati indija siječanj naglašuti usput dobar igra flavija cobollija upisati peti atp pobjeda karijer dug izostanac povratak sport dužeg izbivanje lagan dobro dokazivati ostatak koncentracija grand slam pobjednik ovaj dan okupiti umaga stan wawrinka Dominic thi prethodan godina proći kalvarija ozljeda što konačnica kod marin odraziti njihov plasman ljestvica baš čilić švicarac austrijanac vrhunac karijera osim velik titula pamtiti htjeti treći mjesto atp list ozljeda donijeti valovit trend nastavka njihov karijera niti jedan sport dopuštati život star slaviti tenis posebno uočljivo bodov hvatati tjedan tjedan velik ime uslijed ozljeda suočavati redan brojevima kraj ime dok vrijednost bod malo wawrinka koji jedino wimbledon nedostajati poker grand slam početkom kolovoz prošli godina naći mjesto drugi strana thi trenutačno igrač svijet plasman navići karijera uzeti obzir lipanj prošli godina koketiranje status sto najboljih upućivati zaključak očigledn napredak njegov igra posljednji godina dan jednostavno doći dobar temelj meč nešto drugačije trening nadati htjeti ovaj daleko ići prema boljem kad podvučem crta loše ponoviti marin svjestan sličan scenarija prolaziti njegov kolega potencijalan povratak među dobro morati odraditi još puno dobar turnir Kitzbühel toronto nastavno izvjesno marina čekati nešto slab turnir dok neki moći oslanjati pozivnica zaštićeni renking kamo htjeti daleko siguran voliti igrati barem još jedan turnir zemlja kitzbühel opcija međutim tamo glavni turnir siguran kakav htjeti situacija pozivnica morati vidjeti uspjeti ići htjeti toronto zaključiti marin odlazak umaga tekući tjedan zakoračiti točno stoti igrač svijet sasvim moguć spustiti mjesto idući ponedjeljak njegov pratitelj odraditi dobar ostatak tjedan koncem rujan proslaviti htjeti rođendan dva jedini vršnjak top 30 roberto bautist agut 25 adrian mannarino 27 pokazivati društvo dobar još uvijek imati prostor nešto star garda dobar primjer godina star andy Murray posljednji vrijeme kuca vrata 30 dobar dok novak đoković još jedan igrač godina star marina odolijevati ozljeda daleko igrati visok moguć razina star igrač društvo dobar 50 richard gasquet dobro poznat francuski jednoručni bekhend</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2484,51 +1691,27 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Marin Čilić, Međugorje, Umag, US Open, Belgijca, Kristofa Vliegen, ATP, Umag, Hrvat, Goran Prpić, Istra, Marin, Indija, Flavija Cobollij, Grand Slam pobjednik, Umag, Stan Wawrinka, Dominic Thiem, Marina, Čilić, Švicarac, Austrijanac, Wawrinka, Wimbledon, Grand slamov, Thi, Marin, Kitzbühel, Toronto, Marina, Toronto, Marin, Umaga, Roberto Bautista Agut, Adrian Mannarino, Andy Murray, Novak Đoković, Marina, Richard Gasquet</t>
+          <t>marin čilić, Belgijc, hrvat, goran prpić, Dominic, švicarac Austrijanac, Kitzbühel, roberto bautist, Adrian Mannarino, Murray, richard gasquet</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.1320754716981132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Imaju obraza reći da je Hrvatska skupa: ‘Ne mogu vjerovati što sam platio 15 eura’
-Autor: Ivana Jurišić
-Visoke cijene na Jadranu gotovo su svakodnevna tema hrvatskih medija. Sladoledi za tri, pivo za šest, pizza i ćevapi za 10 do 15 eura postale su sasvim normalne cijene u našim turističkim destinacijama. Dok domaći izbjegavaju restorane, stranci se žale na društvenim mrežama kako će Hrvatska svojim cijenama uskoro dostići već tradicionalno skupu Azurnu obalu.
-Iako Hrvatska nije jeftina, računi iz drugih dijelova svijeta pokazuju kako u usporedbi s nekim drugim turističkim destinacijama ipak nismo toliko skupi, osobito kada se gleda kvaliteta hrane. Odnosno, nismo skupi za turiste, jer domaći sa svojim prosječnim hrvatskim plaćama su već posve druga priča.
-Dva računa iz New Orleansa
-Jedan naš čitatelj koji trenutačno boravi u New Orleansu u američkoj državi Louisiana poslao nam je dva računa za jelo koje je pojeo u toj popularnoj američkoj turističkoj destinaciji.
-Tako je porciju kozica u umaku od povrća platio 10,45 USD (9,53 EUR).
-Iako se u svijetu masovno pišu pohvale kreolskoj kuhinji, naš čitatelj kaže kako usprkos visokoj cijeni uopće nije bio oduševljen jelom.
-“Bilo je kao da jedem začinjenu skušu s povrćem iz konzerve”, kaže naš čitatelj.
-Drugo jelo je platio dosta skuplje, ali je bio i nešto zadovoljniji. Riječ je o sendviču dugom osam inča (20 cm) s pohanim kozicama koje je platio 16,56 USD (15,11 EUR).
-“Nije bilo loše, iako svaka naša pekarnica ima bolji kruh. Barem ne nisu gnjavili s napojnicama”, komentirao je naš čitatelj američku uslugu.
-</t>
+          <t>imati obraz reći Hrvatska skupa moći vjerovati što platiti 15 euro autor Ivana jurišić visok cijena jadrana gotovo svakodnevan tema hrvatski medij sladoledi tri pivo šest pizza ćevapi 10 15 euro postati sasvim normalan cijena naš turistički destinacija dok domaći izbjegavati restoran stranka žaliti društven mreža htjeti hrvatski svoj cijena uskoro dostići već tradicionalno skup azurni obala hrvatski jeftina račun drugi dio svijet pokazivati usporedba neki drugi turistički destinacija ipak toliko skup osobito gledati kvaliteta hrana odnosno skup turist domaći svoj prosječan hrvatski plaća već posve drugi priča dva račun new orleans jedan naš čitatelj trenutačno boraviti New orleans američki država louisian poslati dva račun jelo pojeo popularan američki turistički destinacija porcija kozica umak povrće platiti usd eur svijet masovno pišu pohvati kreolski kuhinja naš čitatelj kazati usprkos visok cijena uopće oduševliti jel jedem začinjen skuša povrći konzervi kazati naš čitatelj drugi jelo platiti dosta skuplje nešto zadovoljan riječ sendvič dug osam inč 20 cm pohan kozica platiti usd eur loše svaki naš pekarnica imati dobar kruh barem gnjaviti napojnica komentirati naš čitatelj američki usluga</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2539,12 +1722,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hrvatska, Ivana Jurišić, Jadran, Hrvatska, Azurnu obala, Hrvatska, New Orleans, New Orleansu, Louisian, EUR, EUR</t>
+          <t>Hrvatska, Ivana jurišić, New orleans, new orleans, Louisian, pohan kozica</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2554,37 +1737,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AMERIKANAC Todd Raymond je ranije ovog mjeseca sa svojom obitelji boravio na hrvatskoj obali. Posjetio je nekoliko gradova, a svoje iskustvo u Hrvatskoj podijelio je u Facebook grupi Split Croatia Travel 2023.
-Pohvalio je mnoge destinacije na Jadranu, no Todd priznaje kako mu se jedan grad ipak nije svidio. Riječ je o Splitu.
-"Uživali smo u našem putovanju kroz Hrvatsku. No, kao i kod svakog putovanja, bilo je i pozitivnih i negativnih strana. Prije svega, ljudi u Hrvatskoj su divni. Učine sve što mogu da se turisti osjećaju dobrodošlima. Izvrsno.
-Oduševili smo se Rovinjem, Pulom i Trogirom. Najveće razočaranje bilo je Split. Smatrali smo ga prepunim, prljavim i prilično nezanimljivim. Muzeji su u najboljem slučaju prosječni, a hrana precijenjena", napisao je Todd.
-"Split ima problem - uništili su ga turisti. Smatram da je jedini razlog za posjetiti Split - odlazak na otoke. Vis nam je bio najdraži. No moja objava nije bila omalovažavajuća prema dobrim ljudima Splita. Nadam se da će ovaj grad vratiti svoju slavu", dodao je.
-Objava izazvala puno komentara
-U komentarima ispod Toddove objave javili su se mnogi Hrvati koji su mu poručili da se slažu s njim.
-Tekst se nastavlja ispod oglasa
-"Tužno, ali istinito. Moram priznati kako su turisti u Splitu najgori", "Nažalost, to je surova stvarnost Splita, gužve su sve veće", "Sada zamisli nas koji živimo i radimo ovdje, cijelu godinu", neki su od komentara.
-No bilo je i onih koji se s Amerikancem nisu složili. Oglasio se jedan turist koji je dolaskom u Split, čini se, bio jako zadovoljan.
-"Krajem rujna i prvog dijela listopada vidio sam drugačiji Split. To je bio točan razlog (prenatrpanost) zbog kojeg smo rezervirali naše putovanje izvan vrhunca sezone. Mnogi misle da će dolaskom u Hrvatsku proći jeftinije. Ljudi moraju znati Hrvatska (više) nije zemlja trećeg svijeta.
-Jedina primjedba su bili promet i parking, ali imamo iste probleme u mnogim gradovima u SAD-u koji se oslanjaju na turizam. Mislite o Splitu što hoćete, ali meni je to bilo jedno od najljepših mjesta na svijetu.
-Bio sam u nekim velikim gradovima poput Rima, Barcelone, Atene, Cannesa, ali meni ih Split nadilazi. Moj prijedlog onima koji se žale, ne vraćajte se, nađite drugo mjesto za odmor. Jedna stvar s kojom se slažem je ta da su ljudi u Hrvatskoj divni", napisao je.</t>
+          <t>amerikanac todd raymond rano ovaj mjesec svoj obitelj boraviti hrvatski obala posjetiti nekoliko grad iskustvo Hrvatska podijeliti facebook grupa Split croatia travel 2023 pohvaliti mnogi destinacija jadran todd priznavati jedan grad ipak sviditi riječ splitu uživati naš putovanje hrvatski kod svaki putovanje pozitivan negativan strana sve čovjek Hrvatska divan učiniti što moći turist osjećati dobrodošl izvrsno oduševiti rovinje pul trogir velik razočaranje split smatrati prepuni prljav prilično nezanimljiav muzej dobar slučaj prosječan hrana precijenjen napisati todd Split imati problem uništiti turist smatrati jedini razlog posjetiti split odlazak otoka vis najdraži objava omalovažavajuać prema dobar čovjek splita nadati htjeti ovaj grad vratiti svoj slava dodati objava izazvati puno komentar komentar ispod toddov objava javiti mnogi hrvat poručiti slagati tekst nastavljati ispod oglas tužno istinit morati priznati turist splitu najgori nažalost sur stvarnost split gužva velik sada zamisliti živjeti raditi ovdje cijel godina komentar onaj amerikancem složiti oglasiti jedan turist dolasak split činiti jako zadovoljan krajem rujan prvi dio listopad vidjeti drugačiji Split točan razlog prenatrpanost zbog koji rezervirati naš putovanje izvan vrhunac sezona mnogi misliti htjeti dolazak hrvatski proći jeftian čovjek morati znati hrvatski mnogo zemlja treći svijet jedini primjedba promet parking imati isti problem mnogi grad oslanjati turizam misliti splitu što hoćete najljepših mjesto svijet neki velik grad poput ri barcelona atene cannesa Split nadilaziti prijedlog onaj žaliti vraćati naći drugi mjesto odmor stvar koji slažem čovjek Hrvatska divan napisati</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2595,12 +1753,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AMERIKANAC, Todd Raymond, Hrvatska, Facebook, Split Croatia Travel, Jadran, Todd, Split, Hrvatska, Hrvatska, Rovinjem, Pula, Split, Todd, Split, Split, Vis, Split, Toddov, Hrvat, Split, Split, Amerikancem, Split, Split, Hrvatska, Hrvatska, SAD - u, Split, Rim, Barcelone, Atena, Cannesa, Split, Hrvatska</t>
+          <t>todd raymond, Hrvatska, Split, travel, splitu, Hrvatska, split, Split, splita, hrvat, splitu, Split gužva, dolasak Split, Split, splitu, Split, Hrvatska</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2610,50 +1768,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jedna je žena ispričala kako rado dopušta svom mužu da izlazi s drugim ženama, jer to više koristi njezinom načinu života nego kad su bili u tradicionalnom braku. Tjerajući ga da izlazi na spojeve, ona uživa sve pogodnosti samačkog života, ali naposljetku dobiva mjesto gdje će živjeti besplatno sa svim plaćenim računima i može uzeti slobodnu noć od toga 'majčinskog posla' kad god poželi, piše Mirror.
-Objašnjavajući kako par ima trogodišnje djevojčice blizanke, njezin je suprug dugo forsirao poliamorni brak, na što je ona naposljetku pristala iako nije imala interesa pronaći novog supruga. Mama je priznala da joj zapravo nije stalo da nađe nekoga drugoga, samo uživa u blagodatima samohrane majke dok ima lagodan život.
-VEZANI ČLANCI:
-Anonimno dijeleći svoju jedinstvenu situaciju na Redditu, napisala je: "Pet smo godina u braku s trogodišnjim djevojčicama blizankama. Nakon djevojčica, on se zalagao za poligamnu vezu i isprva sam bila protiv toga. Nastavio je navaljivati ​​i konačno sam rekla da. U početku kad bi bio vani s nekom drugom ja bih plakala. Neko sam vrijeme raspravljala o razvodu. Nakon što sam isplakala i sve obradila u glavi, shvatila sam koliko sam ga preboljela. Također sam shvatila da bi me ostavljanje njega dovelo u užasnu poziciju i da bi djevojke morale živjeti cijeli život seleći se svaki drugi tjedan. Onda, dok sam odlučivala što učiniti, shvatila sam povlastice.
-On radi puno radno vrijeme, a ona pola radnog vremena predaje nekoliko satova joge ujutro. Dobiva odlično osiguranje kroz njegov posao, odlično mjesto za život i jedva plaćam račune. Tvrdi da je on radio od kuće većinu dana, ali ga je polako uvjerila da ode u ured nakon što se vrati kući s jutarnjih satova joge (oko 9 ujutro). "Tada sam ga tjerala da izlazi na više spojeva, a ja bih radila što god sam htjela s blizankama. Družimo se s drugom djecom i njihovim mamama, gledamo filmove, idemo u parkove i radimo što god želimo. U ovom trenutku ga gotovo nikad nema jer ide na više spojeva s više žena. Ja biram što želim gledati svaku večer nakon što djevojke odu spavati. Rijetko moram čistiti za njim jer ga nema cijelo vrijeme. Uglavnom plaćeni su mi svi računi. Dobivam besplatno mjesto za život. Ako želim slobodnu noć, samo kažem mužu da imam spoj, a on će se brinuti o djevojčicama ili ih odvesti kod svojih roditelja. Obično nemam spojeve, samo idem u kupovinu, jedem sama na nekom mjestu, čitam knjigu u Starbucksu", rekla je.
-VEZANI ČLANCI:
-Tvrdi da je bila na nekoliko spojeva, ali da joj baš i nije do toga da izlazi. "Naša je veza zapravo gotova, ali sada uživam u njezinim povlasticama." Nakon što su mnogi ljudi pokazali zabrinutost zbog njezina načina života, kasnije je dodala svojoj objavi: "Stvarno cijenim vašu zabrinutost. Nisam siromašna ni slomljena. Imam neko nasljedstvo od očeve smrti i mogla bih raditi sate joge puno radno vrijeme i ne moram brinuti o mjestu stanovanja ili slično.Trenutno mi se sviđa ovako jer neću morati viđati svoje djevojke samo svaki drugi tjedan. Neće morati dijeliti svoje stvari između dvije kuće. On uvijek stigne kući do 4:30 ujutro kako bi bio s djevojkama dok ja idem podučavati satove joge. Također sam rekla da postoji šansa da ću upoznati nekoga. Mogućnost da odlučim da sam gotova. Mislim, koja je razlika između odluke o razvodu sada ili kasnije 5 godina, ili 10 godina ili kad god se dogodi? Barem ću znati da sam svojim djevojčicama pokušala pružiti stabilnost u njihovim mladim godinama", dodala je.
-Ali drugi korisnici Redditora nisu bili baš sigurni, pa je jedan komentirao: "Razumijem povlastice o kojima govorite. Ali činjenica je da ovisite o nekom drugom. Nikada to ne biste trebali učiniti." "Otvorene veze kada imate djecu suluda su ideja. Poligamija bi bila jedno, ali ovo nije poligamija", napisao je drugi. "Oni nisu dobro. To 100% nije zdrav odnos između dvoje ljudi. I nije zdrav za tu djecu", komentirala je treća korisnica.
-No, neki su mislili da je to dobra ideja i podržali su ženine odluke. "Zvuči kao da to prilično dobro funkcionira. Čestitam vam oboma. Nadam se da će komunikacija i međusobno razumijevanje ostati kao/ako se stvari razviju i promjene", glasio je jedan komentar. "Pa, hej, ako vam odgovara - onda samo naprijed i budite sretni. Ali ako nađete nekoga, nemojte sebe lišiti sreće", savjetovao joj je drugi.
-Žena živi s mužem i s dečkom: "Hejteri kažu da sam sebična, a ja samo mislim da sam sretnica!"</t>
+          <t>žena ispričati rado dopuštati mužu izlaziti drugi žena mnogo koristiti njezin način život kad tradicionalan brak tjerati izlaziti spoj uživati pogodnost samački život naposljetku dobivati mjesto gdje htjeti živjeti besplatno sav plaćen račun moći uzeti slobodan noć taj posao kad god poželi pisati mirror objašnjavajući par imati trogodišnji djevojčica blizanka suprug dugo forsirati poliamoran brak što naposljetku pristati imati interes pronaći nov suprug mama priznati zapravo stati naći neki drugi uživati blagodat samohran majka dok imati lagodan život vezan članak anonimno dijeliti svoj jedinstven situacija reddit napisati pet godina brak trogodišnj djevojčica blizanka djevojčica zalaći poligaman veza isprva protiv taj nastaviti navaljivati konačno reći početak kad vani neki drugi plakati neki vrijeme raspravljati razvod što isplakati obraditi glava shvatiti koliko preboljeti također shvatiti ostavljanje dovesti užasan pozicija djevojka morati živjeti cijel život seliti svaki drugi tjedan onda dok odlučivati što učiniti shvatiti povlastica raditi pun radni vrijeme pola radni vrijeme predavati nekoliko sat joga ujutro dobivati odličan osiguranje posao odličan mjesto život jedva plaćati račun tvrditi raditi kuća većina dan polako uvjeriti odeti ured što vratiti kuća jutarnji sat joga oko 9 ujutro tjerati izlaziti mnogo spoj raditi što god htjeti blizanka družiti drugi djecom njihov mama gledati film idemo park raditi što god željeti ovaj trenutak gotovo nikad ići mnogo spojev mnogo žena birati što željeti gledati svaki večer što djevojka odu spavati rijetko morati čistiti cijel vrijeme uglavnom plaćen račun dobivati besplatan mjesto život željeti slobodan noć kažem muž imati spoj htjeti brinuti djevojčica odvesti kod svoj roditelj obično nemati spoj idem kupovina jedem sam neki mjesto čitam knjiga starbucksi reći vezan članak tvrditi nekoliko spoj baš taj izlaziti naš veza zapravo gotov sada uživati njezin povlastica što mnogi čovjek pokazati zabrinutost zbog način život kasno dodati svoj objava stvarno cijeniti vaš zabrinutost siromašn slomljena imati neki nasljedstvo očevi smrt moći raditi sat joga pun radni vrijeme moram brinuti mjesto stanovanje sviđati ovako htjeti morati viđati djevojka svaki drugi tjedan htjeti morati dijeliti stvar između dva kuća uvijek stignuti kuća ujutro djevojka dok idem podučavati sat joga također reći postojati šansa htjeti upoznati neki mogućnost odlučiti gotov misliti razlika između odluka razvod sada kasno 5 godina 10 godina kad god dogoditi barem htjeti znati svoj djevojčica pokušati pružiti stabilnost njihov mlad godina dodati drugi korisnik redditor baš siguran jedan komentirati razumijem povlastica govorititi činjenica ovisiti neki drugi nikada trebati učiniti otvoriti veza imati dijete sulud ideja poligamija ovaj poligamija napisati drugi dobro 100 zdrav odnos između dvoje čovjek zdrav djeca komentirati treći korisnica misliti dobar ideja podržati ženin odluka zvučiti prilično dobro funkcionirati čestitam oboma nadati htjeti komunikacija međusoban razumijevanje ostati stvar razviju promjena glasiti jedan komentar hej odgovarati onda naprijed budite sretan nađete neki nemojte lišiti sreća savjetovati drugi žena živjeti mužem dečk hejter kazati sebičan misliti sretnica</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>0.1238278560650126</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>-0.03747363388538361</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mirror, Redditu, Starbucksu, Redditora, hej</t>
+          <t>hej</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2663,35 +1799,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Američki turist ocrnio Split kao malo tko do sad: ‘Veliko razočaranje, taj grad ima jedan problem’
-Autor: H.B.
-Američki turist Todd Raymond posjetio je Hrvatsku ovoga mjeseca i bio je u nekoliko velikih obalnih gradova, to jest, top destinacija za ljetovanje. Svoje je iskustvo podijelio u Facebook grupi Split Croatia Travel 2023.
-Todd je uglavnom imao samo riječi hvale za mjesta koja je posjetio, ali jedan mu se grad nije svidio. Raymond nije bio zadovoljan onime što je vidio u Splitu.
-“Uživali smo u našem putovanju kroz Hrvatsku, ali kao i kod svakog putovanja, bilo je i pozitivnih i negativnih strana. Prije svega, ljudi u Hrvatskoj su divni. Učine sve što mogu da se turisti osjećaju dobrodošlima. To je sjajno. Oduševili smo se Rovinjem, Pulom i Trogirom”, započeo je i potom nastavio govoriti o Splitu.
-“Najveće razočaranje bilo je Split. Smatrali smo ga prepunim, prljavim i prilično nezanimljivim. Muzeji su u najboljem slučaju prosječni, a hrana precijenjena. Split ima problem, uništili su ga turisti. Smatram da je jedini razlog za posjetiti Split, odlazak na otoke. Vis nam je bio najdraži”, rekao je Todd i potom napomenuo da nije imao namjeru vrijeđati.
-“Moja objava nije bila omalovažavajuća prema dobrim ljudima Splita. Nadam se da će ovaj grad vratiti svoju slavu. No, čini se da je Split u neredu. Nekada je to bila top destinacija, i nadam se da će lokalni lideri i stanovništvo poduzeti nešto da mu vrate stari sjaj”, poručio je Todd.
-‘To je surova stvarnost’
-U komentarima mu se pak javilo dosta Hrvata i uglavnom su se složili s njim. “Istinito je i tužno. Turisti u Splitu su najgori”, “To je surova stvarnost Splita, gužve su sve veće”, “Slažem se 100 posto, bili smo u Splitu nedavno i točno je tako”, “Split je čaroban, ali samo kada nije sezona”, “Kao stanovnik Splita, mogu potvrditi sve što je ovaj čovjek rekao, ja ne idem u grad u razdoblju od lipnja do rujna”, samo su neki od komentara.
-Isto tako bilo je i onih koji su bili zadovoljni posjetom Splitu i nemaju ovakvih primjedbi. “Koncem rujna i početkom listopada vidio sam drugačiji Split. Razlog je prenatrpanost u sezoni i zato smo rezervirali putovanje izvan sezone. Ljudi misle da će proći jeftinije ako ljetuju u Hrvatskoj, ali Hrvatska više nije zemlja trećeg svijeta. Jedinu zamjerku imamo na parking i promet, ali tako je i u SAD-u. Mislite si vi o Splitu što želite, ali to je jedno od najljepših mjesta na svijetu. Bio sam u Rimu, Barceloni, Ateni, Cannesu, ali Split ih nadmašuje. Ako vam se ne sviđa, ne vraćajte se ovamo, nađite drugo mjesto za odmor”, poručio mu je jedan Amerikanac.
-</t>
+          <t>američki turist ocrniti Split malo tko sad velik razočaranje grad imati jedan problem autor američki turist todd raymond posjetiti hrvatski ovaj mjesec nekoliko velik obalni grad top destinacija ljetovanje iskustvo podijeliti facebook grupa Split croatia travel 2023 todd uglavnom imati riječ hvati mjesto posjetiti jedan grad sviditi raymond zadovoljan onime što vidjeti split uživati naš putovanje hrvatski kod svaki putovanje pozitivan negativan strana sve čovjek Hrvatska divan učiniti što moći turist osjećati dobrodošl sjajno oduševiti rovinje pul trogir započeti potom nastaviti govoriti split velik razočaranje split smatrati prepuni prljav prilično nezanimljiav muzej dobar slučaj prosječan hrana precijeniti Split imati problem uništiti turist smatrati jedini razlog posjetiti split odlazak otoka vis najdraži reći todd potom napomenuti imati namjera vrijeđati objava omalovažavajuać prema dobar čovjek splita nadati htjeti ovaj grad vratiti svoj slava činiti Split nered nekada top destinacija nadati htjeti lokalan lider stanovništvo poduzeti nešto vratiti star sjaj poručiti todd sur stvarnost komentar javiti dosta hrvat uglavnom složiti istinito tužno turist splitu najgori surov stvarnost split gužva velik slažem 100 posto splitu nedavno točno Split čaroban sezona stanovnik split moći potvrditi što ovaj čovjek reći idem grad razdoblje lipanj rujan komentar isto onaj zadovoljan posjet splitu nemati ovakav primjedba koncem rujan početkom listopad vidjeti drugačiji Split razlog prenatrpanost sezona zato rezervirati putovanje izvan sezona čovjek misliti htjeti proći jeftinije ljetuju Hrvatska hrvatski mnogo zemlja treći svijet jedini zamjerka imati parking promet misliti splitu što željeti najljepših mjesto svijet rima barcelona ateni cannesu Split nadmašivati sviđati vraćati ovamo nađiti drugi mjesto odmor poručiti jedan amerikanac</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2702,12 +1815,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Split, H.B., Todd Raymond, Hrvatska, Facebook, Split Croatia Travel, Todd, Raymond, Split, Hrvatska, Hrvatska, Rovinjem, Pula, Split, Split, Split, Split, Vis, Todd, Split, Split, Todd, Hrvat, Split, Split, Split, Split, Split, Split, Split, Hrvatska, Hrvatska, SAD - u., Split, Rim, Barceloni, Atena, Cannesu, Split, Amerikanac</t>
+          <t>Split, todd raymond, Split, travel, Hrvatska, split, split, Split, splita, Split, hrvat, splitu, Split gužva, splitu, Split, split, splitu, Split, Hrvatska, splitu, Split</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2717,43 +1830,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bečarević: "Mentor i vlasnik iz sjene Sarajevogasa je Marjanović, dobit kompanije ste smanjili na 70.000 KM"
-FOTO: PRESS KS
-Bečarević sumnja da se namješta pozicija direktora Sarajevogasa, optužio Marjanovića da je zaposlio četiri radnika. NO Sarajevogasa najavljuje krivičnu prijavu protiv ministra Bečarevića. Bečarević prijavio Sarajevogas Uredu za borbu protiv korupcije: Je li Marjanović dostavio ime direktora?
-Zahvaljujem na odgovoru koji ste uputili javno kako sam isti i tražio. Nadam se da ste primjerak dostavili Uredu za korupciju KS? Također se nadam da će te krivičnu prijavu protiv ovog ministra dostaviti u što kraćem roku u kantonalno tužilaštvo.
-Zašto sam tražio javni odgovor?
-Kako sam dio vas upoznao preko Damira Marjanovića ( predsjedavajućeg Skupštine Sarajevogasa) u prostorijama ministarstva bio sam ubijeđen da ćete u svom odgovoru stati u zaštitu gospodina Damira Marjanovića, mentora i vlasnika iz sjene Sarajevogasa. Dostavljeni dopis dovoljno govori o vašoj potrebi za zaštitu g. Marjanovića, a ne o suštini mojih pitanja i stoga da upoznam Ured za korupciju i javnost o sljedećem:
-U svom odgovoru navodite: “Direktor preduzeća prije svega treba da je menadžer sa širinom i vizijom upravljanja preduzećem, da zna raditi s ljudima.”
-Ovdje se radi o najznaćajnijoj energetskoj kompaniji u KS, a ne o kompaniji kojom treba upravljati psiholog ili psihijatar ili pedagog zbog slomljenih i narušenih odnosa među ljudima.
-Na vaše direktno pitanje, a kao što je sa tim upoznata i javnost KS, Ja, Almir Bečarević, sam ministar cijelog resora i ministar Sarajevogasa. Vlada KS može to potvrditi, a na web stranici vlade imate gotovo sve aktivnosti mene kao ministra kao i dnevne redove vlade KS, na kojima nije bilo sjednice, a da na istoj nisam predložio bar jednu tačku dnevnog reda. Najznačajnija je pokretanje procedure za formiranje energetskog haba putem kojeg će Sarajevogas manje isporučivati ruskog gasa prema Toplanama Sarajevo.
-Razlog zbog kojeg se bavim preduzećem Sarajevogas, je taj što ste uspjeli da po zvaničnom bilansu uspjeha smanjite dobit ove kompanije sa 1,2 mil. KM na 70.000 KM. Nekad je dobit Sarajevogasa bila i 2,0 mil. KM.
-Sto se tiče zdravstvenog stanja direktora nisam znao da se bavite i analizom medicinske dokumentacije, te stoga razumijem da sada želite da spojite psihologiju i opću medicinu u Sarajevogasu.
-Za vašu informaciju, a i za informaciju javnosti dogovorna ostavka u ovoj političkoj korupciji je da aktuelni direktor g. Baković nakon ostavke bude pripravan za poziciju izvršnog direktora BH-Gasa, a u kojem bi direktor trebao biti g. Vjekoslav Bevanda. Pratit cemo put g. Bakovića da li će isti popravljati svoje zdravstveno stanje (ovu temu ste vi otvorili) ili ići na novu funkciju.
-Idemo dalje, kažete da ste vodili računa o kompetencijama novog V.D. Direktora, a ne kažete ko vam je to ime dostavio. Moje pitanje je upravo to bilo i ja nemam problem sa protokolom jer sam upravo ukazao na to da nisam konsultovan, niti vlada KS, o tim kompetencijama, već jedan od dva poslanika g. Marjanović ili g. Lemezan. Možda vaš kandidat ima 8 godina u struci, ali u struci koja je povezana sa Terapijskom zajednicom Kampus i moram provjeriti da li je ista bar koristila prirodni gas, kako bih našao poveznicu sa osnovnom djelatnošću Sarajevogasa.
-Tačno je da sam poništio 31 saglasnost za prijem radnika na određeno i neodređeno vrijeme i koja se nisu realizovala u posljednjih godinu dana. Razlog za poništenje je navod direktora da nije obezbjedio finansijska sredstva za ove prijeme u radni odnos.
-O finansijskom utjecaju ovih prijema analizirajte sa aspekta dobiti i troška od milion KM. Postavljeni ste da nadzirete rad preduzeća, a ne da kukate o prijemima zaposlenika koji svakako završe na Facebook grupi “Raja sa biroa”.
-Ovaj ministar nije ništa reducirao po pitanju prijema radnika već je to g. Marjanovic izdiktirao i zahtjevan iz razloga što mu “gori” u Sarajevogasu, a gorilo mu je npr. mjesto administratora u Sarajevogasu.
-NO Sarajevogasa je priopćio javnosti da sam desetkovao Sarajevogas u kadrovskom smislu što moram priznati da je uspjeh, a NO je uspio od desetina odobrenja za zapošljavanje zaposliti radnika na poziciju novinara, inače prijatelja g. Marjanovica. Sada Sarajevogas ima službu (brojno stanje) informisanja koju ni predsjednik države nema.
-Sada bih želio, da zaključim ovu raspravu putem medija i da se svi preselimo u Ured za korupciju pa da tamo analiziramo ko je dostavio ime za V.D. Direktora, ko je obavio razgovor sa kandidatom i na čiji nagovor, kako se to dijele direktorska mjesta u “tranziciji” vlasti, kako g. Marjanović u ime Sarajevogasa određuje koja su to prioritetna mjesta za zapošljavanje? Također da svi dostavite listinge mobitela, da vidimo i utvrdimo da li ste u kontaktu sa zastupnikom Marjanovićem kao neformalnim vlasnikom Sarajevogasa. Niti na jedno moje pitanje nije jasno odgovoreno, a moj modus operandi je prijaviti političku korupciju u kojoj učestvujete, dragi moji, zimzeleni, članovi NO, stoji u saopćenju ministra Bečarevića.
-(Erna H.)</t>
+          <t>Bečarević mentor vlasnik sjena sarajevogasa Marjanović dobit kompanija smanjiti km foto press ks bečarević sumnja namještati pozicija direktor sarajevogasa optužiti marjanovića zaposliti četiri radnik sarajevogasa najavljivati krivičan prijava protiv ministar Bečarević Bečarević prijaviti sarajevogas ured borba protiv korupcija Marjanović dostaviti ime direktor zahvaljivati odgovor uputiti javno isti tražiti nadam primjerak dostaviti ured korupcija ks također nadati htjeti krivičan prijava protiv ovaj ministar dostaviti što kraćem rok kantonalan tužilaštvo zašto tražiti javan odgovor dio upoznati preko damira marjanović predsjedavajući skupština sarajevogas prostorija ministarstvo ubijediti htjeti odgovor stati zaštita gospodin damira marjanović mentor vlasnik sjena sarajevogasa dostaviti dopis dovoljno govoriti vaši potreba zaštita marjanović suština moj pitanje stoga upoznati ured korupcija javnost sljedeći odgovor navoditi direktor preduzeće sve trebati menadžer širin vizija upravljanje preduzeće znati raditi ovdje raditi najznaćajniji energetski kompanija ks kompanija koji trebati upravljati psiholog psihijatar pedagog zbog slomljean narušen odnos među čovjek vaš direktan pitanje što taj upoznati javnost ks almir Bečarević ministar cijel resor ministar sarajevogas vlada ks moći potvrditi web stranica vlada imati gotovo aktivnost ministar dnevni redov vlada ks sjednica isti predložiti bar jedan tačka dnevan red najznačajnija pokretanje procedura formiranje energetski haba putem koji htjeti sarajevogas malo isporučivati ruski gas prema toplana sarajevo razlog zbog koji baviti preduzeće sarajevogas što uspjeti zvaničan bilansa uspjeh smanjiti dobit ovaj kompanija mil km km nekad dobit sarajevogasa mil km sto ticati zdravstven stanje direktor znati baviti analiza medicinski dokumentacija stoga razumijem sada željeti spojite psihologija opći medicina sarajevogas vaš informacija informacija javnost dogovoran ostavka ovaj politički korupcija aktuelan direktor baković ostavka biti pripravan pozicija izvršan direktor koji direktor trebati vjekoslav bevanda pratiti cemo put Baković htjeti isti popravljati zdravstven stanje ovaj tema otvoriti ići nov funkcija idemo daleko kažete voditi račun kompetencija nov direktor kažuti ko ime dostaviti pitanje upravo nemati problem protokol upravo ukazati konsultovan niti vlada ks taj kompetencija već jedan dva poslanik Marjanović lemezan možda vaš kandidat imati 8 godina struka struka povezan terapijski zajednica kampus morati provjeriti isti bar koristiti prirodan gas naći poveznica osnovan djelatnošću sarajevogasa tačno poništiti 31 saglasnost prijem radnik određen neodređen vrijeme realizovati posljednji godina dan razlog poništenje navod direktor obezbjediti finansijski sredstvo ovaj prijeme radni odnos finansijski utjecaj ovaj prijema analizirati aspekt dobiti trošk milion km postavljiti nadzirete rad preduzeće kukata prijem zaposlenik svakako završiti facebook grupa raj biro ovaj ministar ništa reducirati pitanje prijema radnik već marjanovic izdiktirati zahtjevan razlog što goriti sarajevogasa goriti npr mjesto administrator sarajevogasu sarajevogasa priopćiti javnost desetkovati sarajevogas kadrovski smisao što morati priznati uspjeh uspjeti desetina odobrenje zapošljavanje zaposliti radnik pozicija novinar inače prijatelj marjanovica sada sarajevogas imati služba brojan stanje informisanje predsjednik država sada željeti zaključiti ovaj rasprava putem medij preseliti ured korupcija tamo analizirati ko dostaviti ime direktor ko obaviti razgovor kandidat čiji nagovor dijeliti direktorski mjesto tranzicija vlast Marjanović ime Sarajevogasa određivati prioritetan mjesto zapošljavanje također dostaviti listinga mobitelo vidjeti utvrditi kontakt zastupnik marjanović neformalan vlasnik sarajevogasa niti pitanje jasno odgovoreno modus operandi prijaviti politički korupcija koji učestvujete drag moj zimzelen član stajati saopćenje ministar bečarević ern h</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2764,13 +1846,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bečarević, Sarajevogasa, Marjanović, KS 
- Bečarević, Sarajevogasa, Marjanović, Sarajevogasa, Bečarević, Bečarević, Sarajevogas Ured, Marjanović, Ured za korupcija KS, Damir Marjanović, skupština Sarajevogasa, Damir Marjanović, Sarajevogasa, Marjanović, ured za korupcija i javnost, Almir Bečarević, Sarajevogasa, KS, Sarajevogas, Toplanama Sarajevo, Sarajevogas, Sarajevogasa, sarajevogasu, Baković, BH - Gasa, Vjekoslav Bevanda, Bakovića, V.D. direktor, KS, Marjanović, Kampus, Sarajevogasa, Facebook, Raj, Marjanovic, sarajevogasu, sarajevogasu, Sarajevogasa, Sarajevogas, marjanovica, Sarajevogas, ured za korupcija, V.D. direktor, Marjanović, Sarajevogasa, Marjanović, Sarajevogasa, Bečarević, Erna H.</t>
+          <t>Bečarević, sjena sarajevogasa Marjanović, Bečarević, sarajevogasa, sarajevogasa, Bečarević Bečarević, ured borba protiv korupcija, Marjanović, damirati Marjanović, damirati Marjanović, sjena sarajevogasa, Marjanović, slomljean, almir Bečarević, Baković, Baković, Marjanović, sarajevogas sarajevogas, Marjanović, Sarajevogasa, Marjanović, sarajevogasa, Bečarević ern</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2780,30 +1861,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vijesti
-Mandić nedvosmisleno: "Iza mog opoziva stoji ekipa iz NiP-a, koja je nekada bila u SDA odijelima!"
-Srđan Mandić ekskluzivno: Nećete me smijeniti, bit ću opet kandidat! Neće biti dobro ako progovorim!
-Načelnik Općine Centar, Srđan Mandić, otvoren dokraja: "Upozoravali su me da je 'žurba šejtanski posao', a onda su pogriješili! Jasmin Ademović je inicijator mog opoziva! Poručujem mu: mlad si, tek ti je trideset! Ne možeš još biti načelnik Centra! (...)"
-"(...) Sve sam rekao Konakoviću; neka zna da oko njega ima kukolja! Jesu u NiP-u, ali džaba – to je SDA DNK, geni su im mutirani! 2024. ću se opet kandidovati! Ne da me narod!"
-Općina Centar je uvijek u fokusu; jeste “usijana”, ali dovest ćemo ovo stanje na “normalnu temperaturu”! Teško mi ovo pada, jer sam s ovim ljudima bio u kampanji! Iskreno, svi smo od jučer šokirani! Slično se spremalo prije godinu – to smo znali odmah! Imali su i tad ambicije za ovo, ali ovo jučer što se desilo je potpuni šok! Nismo se znali postaviti; da li napustiti sjednicu ili ne… Bilo je i povišenih tonova! Sugestije su uvijek poželjne, da se razumijemo! Kad je Ćosić otvorio sjednicu, bilo je par “uobičajenih” tački… i onda inicijativa za moj opoziv! Jasmin Ademović iz NiP-a je bio glavni inicijator! Napustio sam sjednicu jer je bila mučna. Nije važno kako se ja osjećam; odaslana je loša poruka. Ovo će se odraziti na moj rad, iako sam po zakonu još uvijek načelnik. Mora se uključiti CIK, pa organizirati referendum, koji je zakazan za 17. septembra. Vijećnik iz NiP-a me htio “upozoriti”, kazavši da je “brzina šejtanski posao”, a mi smo im danas sve dokazali! Uložili smo prigovor jer nisu ispunjene neke zakonitosti i Vijeće se sada mora očitovati, a mogu i povući ovu inicijativu. Referendum u Starom Gradu je koštao 150.000 KM. Procjenjujem da bi ova glupost koju su jučer napravili mogla koštati pola miliona KM, a mi nemamo taj novac! Hoćemo li smanjiti socijalne naknade, naknade porodiljama, djeci?! Pozivam ih da se, do kraja mandata, odreknu svojih paušala umjesto smanjivanja naknada ugroženim. Novi načelnik bi mogao stupiti na dužnost tek u januaru. Neobjašnjivo je i šokirajuće ovo što su uradili. Ohrabren sam podrškom Naše stranke, SDP-a, a i neki članovi NiP-a pružili su ruku! Podržao me Konaković! Vidjeli smo se danas; došao je kod mene i počašćen sam. Njega poznajem i sarađujem s njim, evo, već četiri godine; moj je saborac! Neće dozvoliti da zbog ličnih interesa ova priča eskalira. Rekao mi je da će ovo spriječiti! Ademović ima ambicije da zauzme moje mjesto! Imaju još uvijek šansu ispraviti ovu grešku, ali neka znaju da su samo ojačali Našu stranku. Član sam Glavnog odbora Naše stranke. U izbornoj sam noći rekao da želim biti načelnik svih građana i građanki, a možda sam zbog tog htijenja i zanemario stranačko djelovanje… Zahvalan sam Forti i svim odborima što su stali iza mene, pogotovo ako dođe do referenduma. Opet ću se kandidovati za načelnika 2024. godine! Postoje vijećnici koji imaju privatne sportske biznise, pa predlažu budžetiranje, a ja to ne dozvoljavam! Nema mjesta za lične interese i zato me ne vole! Sve je transparentno; sjednice se snimaju, a nekad nisu postojali ni stenografi! Kod mene ne pali “daj mi ovo ili ono”: prvo javni poziv, ispunjavanje uvjeta, pa onda može! Jasmine Ademoviću, tek ti je trideset godina; rano ti je za poziciju načelnika! Polako, ima vremena. Žurba je šejtanski posao. Ova je odluka došla iz malog kruga ostrašćenih ljudi, koji žele mene smijeniti. Sve je zbog pozicije, ali neće uspjeti! Želim dovršiti ovaj mandat i iznijeti sve što smo dosad uradili, i to transparentno! Kajem se samo što sam prešutio neke stvari. Ovo sve je napravila ekipa iz NiP-a koja je nekad bila u odijelima SDA! To je DNK SDA, mutirani su im geni! Moguće je da smijene i Tanovića. Muzur ima većinu, pa sumnjam da njega mogu “skloniti”. NiP je kvalitetna stranka, ali ima kukolja! Konaković će morati to riješiti! Učinit ću sve, spreman sam opet pružiti ruku, samo da dovedemo ovaj mandat do kraja. Nemam ličnih interesa! Možda bi me oni smijenili, ali narod neće dati! Podići ćemo spomen-ploču Bošku i Admiri – to im dugujemo! Ploča će biti kraj OHR-a. Mogao bih se zamisliti na sastanku s Dodikom! Sjećam se da je nekad na FACE-u, kod Senada Hadžifejzovića, govorio o ekonomskim problemima s kojima se suočava Banja Luka… S njim bih mogao govoriti samo o ekonomiji! Nezgodan je, znam! Kad bismo uspjeli nametnuti ekonomske teme u ovom društvu, bilo bi nam svima bolje! Tako bismo i Dodika pobijedili!</t>
+          <t>vijest mandić nedvosmisleno iza moj opoziv stajati ekipa nekada sdati odijel srđan mandić ekskluzivno nećete smijeniti biti htjeti opet kandidat htjeti dobro progovorimti načelnik općina centar srđan mandić otvoriti dokraja upozoravati šejtanski posao onda pogriješiti jasmin Ademović inicijator moj opozivati poručovati mlad tek trideset moći još načelnik centar reći konaković znati oko imati kukolja džaba sda dnk gen oni mutiran htjeti opet kandidovati narod općina centar uvijek fokus usijan dovesti htjeti ovaj stanje normalan temperatura teško ovaj padati ovaj čovjek kampanja iskreno jučer šokirati slično spremati godina znati imati tad ambicija ovaj ovaj jučer što desiti potpuni šok znati postaviti napustiti sjednica povišean toan sugestija uvijek poželjan razumijemo kad ćosić otvoriti sjednica par uobičajen onda inicijativa opoziv jasmin ademović glavni inicijator napustiti sjednica mučan važan osjećati odaslati loš poruka ovaj htjeti odraziti rad zakon još uvijek načelnik morati uključiti cik organizirati referendum zakazati septembri vijećnik htjeti upozoriti kazati brzina šejtanski posao oni danas dokazati uložiti prigovor ispunjiti neki zakonitost vijeće sada morati očitovati moći povući ovaj inicijativa referendum star grad koštati km procjenjovati glupost jučer napraviti moći koštati pola milion km nemati novac hoćemo smanjiti socijalan naknada naknada porodilja djeca pozivati kraj mandat odreknu svoj paušati umjesto smanjivanje naknada ugrožen nov načelnik moći stupiti dužnost tek januar neobjašnjiv šokirajući ovaj što uraditi ohrabren podrška naš stranka član pružiti ruka podržati konaković vidjeti danas doći kod počašćen poznajem sarađujem evo već četiri godina saborac htjeti dozvoliti zbog ličan interes priča eskalirati reći htjeti ovaj spriječiti ademović imati ambicija zauzeti mjesto imati još uvijek šansa ispraviti ovaj greška znati ojačati naš stranka član glavni odbor naš stranka izborni noć reći željeti načelnik sav građanin građanka možda zbog taj htijenje zanemariti stranački zahvalan forta sav odbor što stati iza pogotovo doći referendum opet htjeti kandidovati načelnik godina postojati vijećnik imati privatan sportski biznis predlagati budžetiranje dozvoljavam mjesto ličan interes zato voljeti transparentno sjednica snimati nekad postojati stenograf kod pati dati ovaj prvo javan poziv ispunjavanje uvjet onda moći jasmina ademović tek trideset godina rano pozicija načelnik polako imati vrijeme žurba šejtanski posao odluka doći mali krug ostrašćeni čovjek željeti smijeniti zbog pozicija htjeti uspjeti željeti dovršiti ovaj mandat iznijeti što dosad uraditi transparentno kaje što prešutiti neki stvar ovaj napraviti ekipa nekad odijelo sda dnk sda mutiran oni gen moguć smijeniti tanovića muzur imati većina sumnjati moći skloniti nip kvalitetan stranka imati kukolja Konaković htjeti morati riješiti učiniti htjeti spreman opet pružiti ruka dovedemo ovaj mandat kraj nemati ličan interes možda smijeniti narod htjeti dati podići htjeti boški admiri oni dugivati ploča htjeti kraj moći zamisliti sastanak dodika sjećati nekad kod senad hadžifejzović govoriti ekonomski problem suočavati banja moći govoriti ekonomija nezgodan znati kad uspjeti nametnuti ekonomski tema ovaj društvo sav dobro dodik pobijediti</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2814,12 +1877,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>vijest, Mandić, NiP - a, SDA, Srđan Mandić, općina centar, Srđan Mandić, Jasmin Ademović, centar !, Konaković, NiP - u, SDA, općina centar, Ćosić, Jasmin Ademović, NiP - a, CIK, NiP - a, vijeće, Star Grad, SDP - a, NiP - a, Konaković, Ademović, glavni odbor naš stranka, Forti, Jasmina Ademović, Kaj, NiP - a, SDA, SDA, Tanović, Muzur, NiP, Konaković, Boška, admiri, OHR - a., Dodiko, FACE - u, Senada Hadžifejzović, Banja Luka, Dodik</t>
+          <t>vijest mandić, srđan mandić, srđan mandić, jasmin Ademović, jasmin ademović, ademović, jasmina ademović, Konaković, senad hadžifejzović</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2829,33 +1892,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Večeras na Teatru uz more HNK Šibenik i Ivo Pattiera održali su posebno rođendansko izdanje "Arsenovog ferala" povodom 85. rođendana velikog Arsena Dedića.
-﻿
-Posebno emotivna večer razgalila je splitsku publiku koja je dugim aplauzom nagradila umjetnike ali i odala štovanje velikom majstoru glazbe i stiha, neponovljivom Arsenu.
-Posebno emotivan bio je i susret Ive Pattiere s publikom koja je u glas pjevala i njegove i Arsenove pjesme.
-"Arsen je veličina u tri dimenzije a kao osoba predivan. Bila mi je čast večeras njemu u spomen stati pred splitsku publiku i podijeliti sjećanje na našeg Arsena." - Ivo Pattiera
-I dok su ovih dana ususret rođendanu mnogi njegovi suradnici prisjećali se njegova lika i djela večeras je o Arsenu rekla publika:
-"Divna večer i maestralni Arsen. Zaista je umjetnik koji je neponovljiv i koji zaslužuje veliko štovanje" - Maja S.
-"Sigurna sam da su njegovi suradnici posebno emotivni dok izvode njegova djela, ali itekako smo emotivni i mi u publici koji smo odrastali i živjeli uz njegove pjesme. Nadam se da će ovakve večeri postati tradicionalne jer naš Arsen zaslužuje i mnogo više. " - Ana R.
-"Arsena slušam od svoje mladosti i moram priznati da kako sam starija sve se više nalazim u mnogim životnim stihovima i još uvijek učim iz njih. Arsen je bio i ostao genijalac kakvi se rode jednom u tisuću godina. " - Tea M.</t>
+          <t>večeras teatar more hnk šibenik Ivo pattiera održati posebno rođendanski izdanje arsenovi ferati povodom rođendan velik arsen dedić posebno emotivan večer razgaliti splitski publika dug aplauz nagraditi umjetnik odati štovanje velik majstor glazba stiah neponovljiv arsen posebno emotivan susret iv pattier publika glas pjevati njegov arsenov pjesma arsen veličina tri dimenzija osoba predivan čast večeras spomen stati pred splitski publika podijeliti sjećanje naš arsen ivo pattier dok ovaj dan ususret rođendan mnogi njegov suradnik prisjećati lik djelo večeras arsen reći publika divan večer maestralan arsen zaista umjetnik neponovljiv zasluživati velik štovanje maj siguran njegov suradnik posebno emotivan dok izvoditi djelo itekako emotivan publik odrastati živjeti njegov pjesma nadati htjeti ovakav večer postati tradicionalan naš arsen zasluživati mnogo an arsen slušati mladost morati priznati star mnogo nalaziti mnogi životan stih još uvijek učiti arsen ostati genijalac kakav roditi jednom tisuća te m</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -2866,12 +1908,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>teatru uz more HNK Šibenik, Ivo Pattier, Arsen Dedić, Arsen, Ivo Pattiere, Arsenove, Arsen biti veličina, Arsen, Ivo Pattier, Arsen, Arsen, Maja S., Arsen, Ana R., Arsen</t>
+          <t>šibenik Ivo pattier, arsen dedić</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2881,43 +1923,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bečarević opet odgovara Marjanoviću: "Mentor i vlasnik iz sjene Saraevogasa, dobit kompanije ste smanjili na 70.000 KM"
-FOTO: PRESS KS
-Bečarević sumnja da se namješta pozicija direktora Sarajevogasa, optužio Marjanovića da je zaposlio četiri radnika. NO Sarajevogasa najavljuje krivičnu prijavu protiv ministra Bečarevića. Bečarević prijavio Sarajevogas Uredu za borbu protiv korupcije: Je li Marjanović dostavio ime direktora?
-Zahvaljujem na odgovoru koji ste uputili javno kako sam isti i tražio. Nadam se da ste primjerak dostavili Uredu za korupciju KS? Također se nadam da će te krivičnu prijavu protiv ovog ministra dostaviti u što kraćem roku u kantonalno tužilaštvo.
-Zašto sam tražio javni odgovor?
-Kako sam dio vas upoznao preko Damira Marjanovića ( predsjedavajućeg Skupštine Sarajevogasa) u prostorijama ministarstva bio sam ubijeđen da ćete u svom odgovoru stati u zaštitu gospodina Damira Marjanovića, mentora i vlasnika iz sjene Sarajevogasa. Dostavljeni dopis dovoljno govori o vašoj potrebi za zaštitu g. Marjanovića, a ne o suštini mojih pitanja i stoga da upoznam Ured za korupciju i javnost o sljedećem:
-U svom odgovoru navodite: “Direktor preduzeća prije svega treba da je menadžer sa širinom i vizijom upravljanja preduzećem, da zna raditi s ljudima.”
-Ovdje se radi o najznaćajnijoj energetskoj kompaniji u KS, a ne o kompaniji kojom treba upravljati psiholog ili psihijatar ili pedagog zbog slomljenih i narušenih odnosa među ljudima.
-Na vaše direktno pitanje, a kao što je sa tim upoznata i javnost KS, Ja, Almir Bečarević, sam ministar cijelog resora i ministar Sarajevogasa. Vlada KS može to potvrditi, a na web stranici vlade imate gotovo sve aktivnosti mene kao ministra kao i dnevne redove vlade KS, na kojima nije bilo sjednice, a da na istoj nisam predložio bar jednu tačku dnevnog reda. Najznačajnija je pokretanje procedure za formiranje energetskog haba putem kojeg će Sarajevogas manje isporučivati ruskog gasa prema Toplanama Sarajevo.
-Razlog zbog kojeg se bavim preduzećem Sarajevogas, je taj što ste uspjeli da po zvaničnom bilansu uspjeha smanjite dobit ove kompanije sa 1,2 mil. KM na 70.000 KM. Nekad je dobit Sarajevogasa bila i 2,0 mil. KM.
-Sto se tiče zdravstvenog stanja direktora nisam znao da se bavite i analizom medicinske dokumentacije, te stoga razumijem da sada želite da spojite psihologiju i opću medicinu u Sarajevogasu.
-Za vašu informaciju, a i za informaciju javnosti dogovorna ostavka u ovoj političkoj korupciji je da aktuelni direktor g. Baković nakon ostavke bude pripravan za poziciju izvršnog direktora BH-Gasa, a u kojem bi direktor trebao biti g. Vjekoslav Bevanda. Pratit cemo put g. Bakovića da li će isti popravljati svoje zdravstveno stanje (ovu temu ste vi otvorili) ili ići na novu funkciju.
-Idemo dalje, kažete da ste vodili računa o kompetencijama novog V.D. Direktora, a ne kažete ko vam je to ime dostavio. Moje pitanje je upravo to bilo i ja nemam problem sa protokolom jer sam upravo ukazao na to da nisam konsultovan, niti vlada KS, o tim kompetencijama, već jedan od dva poslanika g. Marjanović ili g. Lemezan. Možda vaš kandidat ima 8 godina u struci, ali u struci koja je povezana sa Terapijskom zajednicom Kampus i moram provjeriti da li je ista bar koristila prirodni gas, kako bih našao poveznicu sa osnovnom djelatnošću Sarajevogasa.
-Tačno je da sam poništio 31 saglasnost za prijem radnika na određeno i neodređeno vrijeme i koja se nisu realizovala u posljednjih godinu dana. Razlog za poništenje je navod direktora da nije obezbjedio finansijska sredstva za ove prijeme u radni odnos.
-O finansijskom utjecaju ovih prijema analizirajte sa aspekta dobiti i troška od milion KM. Postavljeni ste da nadzirete rad preduzeća, a ne da kukate o prijemima zaposlenika koji svakako završe na Facebook grupi “Raja sa biroa”.
-Ovaj ministar nije ništa reducirao po pitanju prijema radnika već je to g. Marjanovic izdiktirao i zahtjevan iz razloga što mu “gori” u Sarajevogasu, a gorilo mu je npr. mjesto administratora u Sarajevogasu.
-NO Sarajevogasa je priopćio javnosti da sam desetkovao Sarajevogas u kadrovskom smislu što moram priznati da je uspjeh, a NO je uspio od desetina odobrenja za zapošljavanje zaposliti radnika na poziciju novinara, inače prijatelja g. Marjanovica. Sada Sarajevogas ima službu (brojno stanje) informisanja koju ni predsjednik države nema.
-Sada bih želio, da zaključim ovu raspravu putem medija i da se svi preselimo u Ured za korupciju pa da tamo analiziramo ko je dostavio ime za V.D. Direktora, ko je obavio razgovor sa kandidatom i na čiji nagovor, kako se to dijele direktorska mjesta u “tranziciji” vlasti, kako g. Marjanović u ime Sarajevogasa određuje koja su to prioritetna mjesta za zapošljavanje? Također da svi dostavite listinge mobitela, da vidimo i utvrdimo da li ste u kontaktu sa zastupnikom Marjanovićem kao neformalnim vlasnikom Sarajevogasa. Niti na jedno moje pitanje nije jasno odgovoreno, a moj modus operandi je prijaviti političku korupciju u kojoj učestvujete, dragi moji, zimzeleni, članovi NO, stoji u saopćenju ministra Bečarevića.
-(Erna H.)</t>
+          <t>Bečarević opet odgovarati marjanović mentor vlasnik sjena saraevogas dobit kompanija smanjiti km foto press ks bečarević sumnja namještati pozicija direktor sarajevogasa optužiti marjanovića zaposliti četiri radnik sarajevogasa najavljivati krivičan prijava protiv ministar Bečarević Bečarević prijaviti sarajevogas ured borba protiv korupcija Marjanović dostaviti ime direktor zahvaljivati odgovor uputiti javno isti tražiti nadam primjerak dostaviti ured korupcija ks također nadati htjeti krivičan prijava protiv ovaj ministar dostaviti što kraćem rok kantonalan tužilaštvo zašto tražiti javan odgovor dio upoznati preko damira marjanović predsjedavajući skupština sarajevogas prostorija ministarstvo ubijediti htjeti odgovor stati zaštita gospodin damira marjanović mentor vlasnik sjena sarajevogasa dostaviti dopis dovoljno govoriti vaši potreba zaštita marjanović suština moj pitanje stoga upoznati ured korupcija javnost sljedeći odgovor navoditi direktor preduzeće sve trebati menadžer širin vizija upravljanje preduzeće znati raditi ovdje raditi najznaćajniji energetski kompanija ks kompanija koji trebati upravljati psiholog psihijatar pedagog zbog slomljean narušen odnos među čovjek vaš direktan pitanje što taj upoznati javnost ks almir Bečarević ministar cijel resor ministar sarajevogas vlada ks moći potvrditi web stranica vlada imati gotovo aktivnost ministar dnevni redov vlada ks sjednica isti predložiti bar jedan tačka dnevan red najznačajnija pokretanje procedura formiranje energetski haba putem koji htjeti sarajevogas malo isporučivati ruski gas prema toplana sarajevo razlog zbog koji baviti preduzeće sarajevogas što uspjeti zvaničan bilansa uspjeh smanjiti dobit ovaj kompanija mil km km nekad dobit sarajevogasa mil km sto ticati zdravstven stanje direktor znati baviti analiza medicinski dokumentacija stoga razumijem sada željeti spojite psihologija opći medicina sarajevogas vaš informacija informacija javnost dogovoran ostavka ovaj politički korupcija aktuelan direktor baković ostavka biti pripravan pozicija izvršan direktor koji direktor trebati vjekoslav bevanda pratiti cemo put Baković htjeti isti popravljati zdravstven stanje ovaj tema otvoriti ići nov funkcija idemo daleko kažete voditi račun kompetencija nov direktor kažuti ko ime dostaviti pitanje upravo nemati problem protokol upravo ukazati konsultovan niti vlada ks taj kompetencija već jedan dva poslanik Marjanović lemezan možda vaš kandidat imati 8 godina struka struka povezan terapijski zajednica kampus morati provjeriti isti bar koristiti prirodan gas naći poveznica osnovan djelatnošću sarajevogasa tačno poništiti 31 saglasnost prijem radnik određen neodređen vrijeme realizovati posljednji godina dan razlog poništenje navod direktor obezbjediti finansijski sredstvo ovaj prijeme radni odnos finansijski utjecaj ovaj prijema analizirati aspekt dobiti trošk milion km postavljiti nadzirete rad preduzeće kukata prijem zaposlenik svakako završiti facebook grupa raj biro ovaj ministar ništa reducirati pitanje prijema radnik već marjanovic izdiktirati zahtjevan razlog što goriti sarajevogasa goriti npr mjesto administrator sarajevogasu sarajevogasa priopćiti javnost desetkovati sarajevogas kadrovski smisao što morati priznati uspjeh uspjeti desetina odobrenje zapošljavanje zaposliti radnik pozicija novinar inače prijatelj marjanovica sada sarajevogas imati služba brojan stanje informisanje predsjednik država sada željeti zaključiti ovaj rasprava putem medij preseliti ured korupcija tamo analizirati ko dostaviti ime direktor ko obaviti razgovor kandidat čiji nagovor dijeliti direktorski mjesto tranzicija vlast Marjanović ime Sarajevogasa određivati prioritetan mjesto zapošljavanje također dostaviti listinga mobitelo vidjeti utvrditi kontakt zastupnik marjanović neformalan vlasnik sarajevogasa niti pitanje jasno odgovoreno modus operandi prijaviti politički korupcija koji učestvujete drag moj zimzelen član stajati saopćenje ministar bečarević ern h</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -2928,13 +1939,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bečarević, Marjanović, Saraevogasa, KS 
- Bečarević, Sarajevogasa, Marjanović, Sarajevogasa, Bečarević, Bečarević, Sarajevogas Ured, Marjanović, Ured za korupcija KS, Damir Marjanović, skupština Sarajevogasa, Damir Marjanović, Sarajevogasa, Marjanović, ured za korupcija i javnost, Almir Bečarević, Sarajevogasa, KS, Sarajevogas, Toplanama Sarajevo, Sarajevogas, Sarajevogasa, sarajevogasu, Baković, BH - Gasa, Vjekoslav Bevanda, Bakovića, V.D. direktor, KS, Marjanović, Kampus, Sarajevogasa, Facebook, Raj, Marjanovic, sarajevogasu, sarajevogasu, Sarajevogasa, Sarajevogas, marjanovica, Sarajevogas, ured za korupcija, V.D. direktor, Marjanović, Sarajevogasa, Marjanović, Sarajevogasa, Bečarević, Erna H.</t>
+          <t>Bečarević, Marjanović, sjena saraevogas, Bečarević, sarajevogasa, sarajevogasa, Bečarević Bečarević, ured borba protiv korupcija, Marjanović, damirati Marjanović, damirati Marjanović, sjena sarajevogasa, Marjanović, slomljean, almir Bečarević, Baković, Baković, Marjanović, sarajevogas sarajevogas, Marjanović, Sarajevogasa, Marjanović, sarajevogasa, Bečarević ern</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2944,43 +1954,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bečarević: "Mentor i vlasnik iz sjene Sarajevogasa, dobit kompanije ste smanjili na 70.000 KM"
-FOTO: PRESS KS
-Bečarević sumnja da se namješta pozicija direktora Sarajevogasa, optužio Marjanovića da je zaposlio četiri radnika. NO Sarajevogasa najavljuje krivičnu prijavu protiv ministra Bečarevića. Bečarević prijavio Sarajevogas Uredu za borbu protiv korupcije: Je li Marjanović dostavio ime direktora?
-Zahvaljujem na odgovoru koji ste uputili javno kako sam isti i tražio. Nadam se da ste primjerak dostavili Uredu za korupciju KS? Također se nadam da će te krivičnu prijavu protiv ovog ministra dostaviti u što kraćem roku u kantonalno tužilaštvo.
-Zašto sam tražio javni odgovor?
-Kako sam dio vas upoznao preko Damira Marjanovića ( predsjedavajućeg Skupštine Sarajevogasa) u prostorijama ministarstva bio sam ubijeđen da ćete u svom odgovoru stati u zaštitu gospodina Damira Marjanovića, mentora i vlasnika iz sjene Sarajevogasa. Dostavljeni dopis dovoljno govori o vašoj potrebi za zaštitu g. Marjanovića, a ne o suštini mojih pitanja i stoga da upoznam Ured za korupciju i javnost o sljedećem:
-U svom odgovoru navodite: “Direktor preduzeća prije svega treba da je menadžer sa širinom i vizijom upravljanja preduzećem, da zna raditi s ljudima.”
-Ovdje se radi o najznaćajnijoj energetskoj kompaniji u KS, a ne o kompaniji kojom treba upravljati psiholog ili psihijatar ili pedagog zbog slomljenih i narušenih odnosa među ljudima.
-Na vaše direktno pitanje, a kao što je sa tim upoznata i javnost KS, Ja, Almir Bečarević, sam ministar cijelog resora i ministar Sarajevogasa. Vlada KS može to potvrditi, a na web stranici vlade imate gotovo sve aktivnosti mene kao ministra kao i dnevne redove vlade KS, na kojima nije bilo sjednice, a da na istoj nisam predložio bar jednu tačku dnevnog reda. Najznačajnija je pokretanje procedure za formiranje energetskog haba putem kojeg će Sarajevogas manje isporučivati ruskog gasa prema Toplanama Sarajevo.
-Razlog zbog kojeg se bavim preduzećem Sarajevogas, je taj što ste uspjeli da po zvaničnom bilansu uspjeha smanjite dobit ove kompanije sa 1,2 mil. KM na 70.000 KM. Nekad je dobit Sarajevogasa bila i 2,0 mil. KM.
-Sto se tiče zdravstvenog stanja direktora nisam znao da se bavite i analizom medicinske dokumentacije, te stoga razumijem da sada želite da spojite psihologiju i opću medicinu u Sarajevogasu.
-Za vašu informaciju, a i za informaciju javnosti dogovorna ostavka u ovoj političkoj korupciji je da aktuelni direktor g. Baković nakon ostavke bude pripravan za poziciju izvršnog direktora BH-Gasa, a u kojem bi direktor trebao biti g. Vjekoslav Bevanda. Pratit cemo put g. Bakovića da li će isti popravljati svoje zdravstveno stanje (ovu temu ste vi otvorili) ili ići na novu funkciju.
-Idemo dalje, kažete da ste vodili računa o kompetencijama novog V.D. Direktora, a ne kažete ko vam je to ime dostavio. Moje pitanje je upravo to bilo i ja nemam problem sa protokolom jer sam upravo ukazao na to da nisam konsultovan, niti vlada KS, o tim kompetencijama, već jedan od dva poslanika g. Marjanović ili g. Lemezan. Možda vaš kandidat ima 8 godina u struci, ali u struci koja je povezana sa Terapijskom zajednicom Kampus i moram provjeriti da li je ista bar koristila prirodni gas, kako bih našao poveznicu sa osnovnom djelatnošću Sarajevogasa.
-Tačno je da sam poništio 31 saglasnost za prijem radnika na određeno i neodređeno vrijeme i koja se nisu realizovala u posljednjih godinu dana. Razlog za poništenje je navod direktora da nije obezbjedio finansijska sredstva za ove prijeme u radni odnos.
-O finansijskom utjecaju ovih prijema analizirajte sa aspekta dobiti i troška od milion KM. Postavljeni ste da nadzirete rad preduzeća, a ne da kukate o prijemima zaposlenika koji svakako završe na Facebook grupi “Raja sa biroa”.
-Ovaj ministar nije ništa reducirao po pitanju prijema radnika već je to g. Marjanovic izdiktirao i zahtjevan iz razloga što mu “gori” u Sarajevogasu, a gorilo mu je npr. mjesto administratora u Sarajevogasu.
-NO Sarajevogasa je priopćio javnosti da sam desetkovao Sarajevogas u kadrovskom smislu što moram priznati da je uspjeh, a NO je uspio od desetina odobrenja za zapošljavanje zaposliti radnika na poziciju novinara, inače prijatelja g. Marjanovica. Sada Sarajevogas ima službu (brojno stanje) informisanja koju ni predsjednik države nema.
-Sada bih želio, da zaključim ovu raspravu putem medija i da se svi preselimo u Ured za korupciju pa da tamo analiziramo ko je dostavio ime za V.D. Direktora, ko je obavio razgovor sa kandidatom i na čiji nagovor, kako se to dijele direktorska mjesta u “tranziciji” vlasti, kako g. Marjanović u ime Sarajevogasa određuje koja su to prioritetna mjesta za zapošljavanje? Također da svi dostavite listinge mobitela, da vidimo i utvrdimo da li ste u kontaktu sa zastupnikom Marjanovićem kao neformalnim vlasnikom Sarajevogasa. Niti na jedno moje pitanje nije jasno odgovoreno, a moj modus operandi je prijaviti političku korupciju u kojoj učestvujete, dragi moji, zimzeleni, članovi NO, stoji u saopćenju ministra Bečarevića.
-(Erna H.)</t>
+          <t>Bečarević mentor vlasnik sjena sarajevogasa dobit kompanija smanjiti km foto press ks bečarević sumnja namještati pozicija direktor sarajevogasa optužiti marjanovića zaposliti četiri radnik sarajevogasa najavljivati krivičan prijava protiv ministar Bečarević Bečarević prijaviti sarajevogas ured borba protiv korupcija Marjanović dostaviti ime direktor zahvaljivati odgovor uputiti javno isti tražiti nadam primjerak dostaviti ured korupcija ks također nadati htjeti krivičan prijava protiv ovaj ministar dostaviti što kraćem rok kantonalan tužilaštvo zašto tražiti javan odgovor dio upoznati preko damira marjanović predsjedavajući skupština sarajevogas prostorija ministarstvo ubijediti htjeti odgovor stati zaštita gospodin damira marjanović mentor vlasnik sjena sarajevogasa dostaviti dopis dovoljno govoriti vaši potreba zaštita marjanović suština moj pitanje stoga upoznati ured korupcija javnost sljedeći odgovor navoditi direktor preduzeće sve trebati menadžer širin vizija upravljanje preduzeće znati raditi ovdje raditi najznaćajniji energetski kompanija ks kompanija koji trebati upravljati psiholog psihijatar pedagog zbog slomljean narušen odnos među čovjek vaš direktan pitanje što taj upoznati javnost ks almir Bečarević ministar cijel resor ministar sarajevogas vlada ks moći potvrditi web stranica vlada imati gotovo aktivnost ministar dnevni redov vlada ks sjednica isti predložiti bar jedan tačka dnevan red najznačajnija pokretanje procedura formiranje energetski haba putem koji htjeti sarajevogas malo isporučivati ruski gas prema toplana sarajevo razlog zbog koji baviti preduzeće sarajevogas što uspjeti zvaničan bilansa uspjeh smanjiti dobit ovaj kompanija mil km km nekad dobit sarajevogasa mil km sto ticati zdravstven stanje direktor znati baviti analiza medicinski dokumentacija stoga razumijem sada željeti spojite psihologija opći medicina sarajevogas vaš informacija informacija javnost dogovoran ostavka ovaj politički korupcija aktuelan direktor baković ostavka biti pripravan pozicija izvršan direktor koji direktor trebati vjekoslav bevanda pratiti cemo put Baković htjeti isti popravljati zdravstven stanje ovaj tema otvoriti ići nov funkcija idemo daleko kažete voditi račun kompetencija nov direktor kažuti ko ime dostaviti pitanje upravo nemati problem protokol upravo ukazati konsultovan niti vlada ks taj kompetencija već jedan dva poslanik Marjanović lemezan možda vaš kandidat imati 8 godina struka struka povezan terapijski zajednica kampus morati provjeriti isti bar koristiti prirodan gas naći poveznica osnovan djelatnošću sarajevogasa tačno poništiti 31 saglasnost prijem radnik određen neodređen vrijeme realizovati posljednji godina dan razlog poništenje navod direktor obezbjediti finansijski sredstvo ovaj prijeme radni odnos finansijski utjecaj ovaj prijema analizirati aspekt dobiti trošk milion km postavljiti nadzirete rad preduzeće kukata prijem zaposlenik svakako završiti facebook grupa raj biro ovaj ministar ništa reducirati pitanje prijema radnik već marjanovic izdiktirati zahtjevan razlog što goriti sarajevogasa goriti npr mjesto administrator sarajevogasu sarajevogasa priopćiti javnost desetkovati sarajevogas kadrovski smisao što morati priznati uspjeh uspjeti desetina odobrenje zapošljavanje zaposliti radnik pozicija novinar inače prijatelj marjanovica sada sarajevogas imati služba brojan stanje informisanje predsjednik država sada željeti zaključiti ovaj rasprava putem medij preseliti ured korupcija tamo analizirati ko dostaviti ime direktor ko obaviti razgovor kandidat čiji nagovor dijeliti direktorski mjesto tranzicija vlast Marjanović ime Sarajevogasa određivati prioritetan mjesto zapošljavanje također dostaviti listinga mobitelo vidjeti utvrditi kontakt zastupnik marjanović neformalan vlasnik sarajevogasa niti pitanje jasno odgovoreno modus operandi prijaviti politički korupcija koji učestvujete drag moj zimzelen član stajati saopćenje ministar bečarević ern h</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -2991,13 +1970,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bečarević, Sarajevogasa, KS 
- Bečarević, Sarajevogasa, Marjanović, Sarajevogasa, Bečarević, Bečarević, Sarajevogas Ured, Marjanović, Ured za korupcija KS, Damir Marjanović, skupština Sarajevogasa, Damir Marjanović, Sarajevogasa, Marjanović, ured za korupcija i javnost, Almir Bečarević, Sarajevogasa, KS, Sarajevogas, Toplanama Sarajevo, Sarajevogas, Sarajevogasa, sarajevogasu, Baković, BH - Gasa, Vjekoslav Bevanda, Bakovića, V.D. direktor, KS, Marjanović, Kampus, Sarajevogasa, Facebook, Raj, Marjanovic, sarajevogasu, sarajevogasu, Sarajevogasa, Sarajevogas, marjanovica, Sarajevogas, ured za korupcija, V.D. direktor, Marjanović, Sarajevogasa, Marjanović, Sarajevogasa, Bečarević, Erna H.</t>
+          <t>Bečarević, sjena sarajevogasa, Bečarević, sarajevogasa, sarajevogasa, Bečarević Bečarević, ured borba protiv korupcija, Marjanović, damirati Marjanović, damirati Marjanović, sjena sarajevogasa, Marjanović, slomljean, almir Bečarević, Baković, Baković, Marjanović, sarajevogas sarajevogas, Marjanović, Sarajevogasa, Marjanović, sarajevogasa, Bečarević ern</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3007,44 +1985,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Podijeli :
-N1
-"Zahvaljujem na odgovoru koji ste uputili javno kako sam isti i tražio. Nadam se da ste primjerak dostavili Uredu za korupciju KS? Također se nadam da ćete krivičnu prijavu protiv ovog ministra dostaviti u što kraćem roku u kantonalno tužilaštvo", navodi se u odgovoru ministra komunalne privrede, infrastrukture, prostornog uređenja, građenja i zaštite okoliša Kantona Sarajevo Almira Bečarevića na navode koje je iznio Nadzorni odbor Sarajevogasa.
-“Zašto sam tražio javni odgovor?
-Kako sam dio vas upoznao preko Damira Marjanovića (predsjedavajućeg Skupštine Sarajevogasa) u prostorijama ministarstva bio sam ubijeđen da ćete u svom odgovoru stati u zaštitu gospodina Damira Marjanovića, mentora i vlasnika iz sjene Sarajevogasa. Dostavljeni dopis dovoljno govori o vašoj potrebi za zaštitu g. Marjanovića, a ne o suštini mojih pitanja i stoga da upoznam Ured za korupciju i javnost o sljedećem”, navodi Bečarević i dodaje:
-“U svom odgovoru navodite: “Direktor preduzeća prije svega treba da je menadžer sa širinom i vizijom upravljanja preduzećem, da zna raditi s ljudima.”
-Ovdje se radi o najznaćajnijoj energetskoj kompaniji u KS, a ne o kompaniji kojom treba upravljati psiholog ili psihijatar ili pedagog zbog slomljenih i narušenih odnosa među ljudima”.
-“Na vaše direktno pitanje, a kao što je sa tim upoznata i javnost KS, Ja, Almir Bečarević, sam ministar cijelog resora i ministar Sarajevogasa. Vlada KS može to potvrditi, a na web stranici vlade imate gotovo sve aktivnosti mene kao ministra kao i dnevne redove vlade KS, na kojima nije bilo sjednice, a da na istoj nisam predložio bar jednu tačku dnevnog reda. Najznačajnija je pokretanje procedure za formiranje energetskog haba putem kojeg će Sarajevogas manje isporučivati ruskog gasa prema Toplanama Sarajevo.
-Razlog zbog kojeg se bavim preduzećem Sarajevogas, je taj što ste uspjeli da po zvaničnom bilansu uspjeha smanjite dobit ove kompanije sa 1,2 mil. KM na 70.000 KM. Nekad je dobit Sarajevogasa bila i 2,0 mil. KM.
-Sto se tiče zdravstvenog stanja direktora nisam znao da se bavite i analizom medicinske dokumentacije, te stoga razumijem da sada želite da spojite psihologiju i opću medicinu u Sarajevogasu”, poručio je Bečarević.
-U daljem odgovoru, Bečarević se referiše na činjenicu da je poništio 31 saglasnost na prijem radnika na određeno i neodređeno vrijeme.
-“Za vašu informaciju, a i za informaciju javnosti dogovorna ostavka u ovoj političkoj korupciji je da aktuelni direktor g. Baković nakon ostavke bude pripravan za poziciju izvršnog direktora BH-Gasa, a u kojem bi direktor trebao biti g. Vjekoslav Bevanda. Pratit cemo put g. Bakovića da li će isti popravljati svoje zdravstveno stanje (ovu temu ste vi otvorili) ili ići na novu funkciju.
-Idemo dalje, kažete da ste vodili računa o kompetencijama novog V.D. Direktora, a ne kažete ko vam je to ime dostavio. Moje pitanje je upravo to bilo i ja nemam problem sa protokolom jer sam upravo ukazao na to da nisam konsultovan, niti vlada KS, o tim kompetencijama, već jedan od dva poslanika g. Marjanović ili g. Lemezan. Možda vaš kandidat ima 8 godina u struci, ali u struci koja je povezana sa Terapijskom zajednicom Kampus i moram provjeriti da li je ista bar koristila prirodni gas, kako bih našao poveznicu sa osnovnom djelatnošću Sarajevogasa.
-Tačno je da sam poništio 31 saglasnost za prijem radnika na određeno i neodređeno vrijeme i koja se nisu realizovala u posljednjih godinu dana. Razlog za poništenje je navod direktora da nije obezbjedio finansijska sredstva za ove prijeme u radni odnos”.
-Bečarević je još dao komentar na navode da je on “desetkovao Sarajevogas”.
-“O finansijskom utjecaju ovih prijema analizirajte sa aspekta dobiti i troška od milion KM. Postavljeni ste da nadzirete rad preduzeća, a ne da kukate o prijemima zaposlenika koji svakako završe na Facebook grupi “Raja sa biroa”.
-Ovaj ministar nije ništa reducirao po pitanju prijema radnika već je to g. Marjanović izdiktirao i zahtjevan iz razloga što mu “gori” u Sarajevogasu, a gorilo mu je npr. mjesto administratora u Sarajevogasu.
-NO Sarajevogasa je priopćio javnosti da sam desetkovao Sarajevogas u kadrovskom smislu što moram priznati da je uspjeh, a NO je uspio od desetina odobrenja za zapošljavanje zaposliti radnika na poziciju novinara, inače prijatelja g. Marjanovica. Sada Sarajevogas ima službu (brojno stanje) informisanja koju ni predsjednik države nema.
-Sada bih želio, da zaključim ovu raspravu putem medija i da se svi preselimo u Ured za korupciju pa da tamo analiziramo ko je dostavio ime za V.D. Direktora, ko je obavio razgovor sa kandidatom i na čiji nagovor, kako se to dijele direktorska mjesta u “tranziciji” vlasti, kako g. Marjanović u ime Sarajevogasa određuje koja su to prioritetna mjesta za zapošljavanje? Također da svi dostavite listinge mobitela, da vidimo i utvrdimo da li ste u kontaktu sa zastupnikom Marjanovićem kao neformalnim vlasnikom Sarajevogasa. Niti na jedno moje pitanje nije jasno odgovoreno, a moj modus operandi je prijaviti političku korupciju u kojoj učestvujete, dragi moji, zimzeleni, članovi NO”, poručio je Bečarević.
-Program N1 televizije možete pratiti UŽIVO na ovom linku kao i putem aplikacija za Android|iPhone/iPad</t>
+          <t>podijeliti n1 zahvaljuj odgovor uputiti javno isti tražiti nadam primjerak dostaviti ured korupcija ks također nadati htjeti krivičan prijava protiv ovaj ministar dostaviti što kraćem rok kantonalan tužilaštvo navoditi odgovor ministar komunalan privreda infrastruktura prostoran uređenje građenje zaštita okoliš kanton sarajevo almirati bečarevića navoditi iznijeti nadzoran odbor sarajevogas zašto tražiti javan odgovor dio upoznati preko damira marjanović predsjedavajući skupština sarajevogas prostorija ministarstvo ubijediti htjeti odgovor stati zaštita gospodin damira marjanović mentor vlasnik sjena sarajevogasa dostaviti dopis dovoljno govoriti vaši potreba zaštita marjanović suština moj pitanje stoga upoznati ured korupcija javnost sljedeći navoditi Bečarević dodavati odgovor navodite direktor preduzeće sve trebati menadžer širin vizija upravljanje preduzeće znati raditi ovdje raditi najznaćajniji energetski kompanija ks kompanija koji trebati upravljati psiholog psihijatar pedagog zbog slomljean narušen odnos među čovjek vaš direktan pitanje što taj upoznati javnost ks almir Bečarević ministar cijel resor ministar sarajevogas vlada ks moći potvrditi web stranica vlada imati gotovo aktivnost ministar dnevni redov vlada ks sjednica isti predložiti bar jedan tačka dnevan red najznačajnija pokretanje procedura formiranje energetski haba putem koji htjeti sarajevogas malo isporučivati ruski gas prema toplana sarajevo razlog zbog koji baviti preduzeće sarajevogas što uspjeti zvaničan bilansa uspjeh smanjiti dobit ovaj kompanija mil km km nekad dobit sarajevogasa mil km sto ticati zdravstven stanje direktor znati baviti analiza medicinski dokumentacija stoga razumijem sada željeti spojite psihologija opći medicina sarajevogasu poručiti Bečarević daljem odgovor Bečarević referiši činjenica poništiti 31 saglasnost prijem radnik određen neodređen vrijeme vaš informacija informacija javnost dogovoran ostavka ovaj politički korupcija aktuelan direktor baković ostavka biti pripravan pozicija izvršan direktor koji direktor trebati vjekoslav bevanda pratiti cemo put Baković htjeti isti popravljati zdravstven stanje ovaj tema otvoriti ići nov funkcija idemo daleko kažete voditi račun kompetencija nov direktor kažuti ko ime dostaviti pitanje upravo nemati problem protokol upravo ukazati konsultovan niti vlada ks taj kompetencija već jedan dva poslanik Marjanović lemezan možda vaš kandidat imati 8 godina struka struka povezan terapijski zajednica kampus morati provjeriti isti bar koristiti prirodan gas naći poveznica osnovan djelatnošću sarajevogasa tačno poništiti 31 saglasnost prijem radnik određen neodređen vrijeme realizovati posljednji godina dan razlog poništenje navod direktor obezbjediti finansijski sredstvo ovaj prijeme radni odnos Bečarević još dati komentar navoditi desetkovati sarajevogas finansijski utjecaj ovaj prijema analizirati aspekt dobiti trošk milion km postavljiti nadzirete rad preduzeće kukata prijem zaposlenik svakako završiti facebook grupa raj biro ovaj ministar ništa reducirati pitanje prijema radnik već marjanović izdiktirati zahtjevan razlog što goriti sarajevogasa goriti npr mjesto administrator sarajevogasu sarajevogasa priopćiti javnost desetkovati sarajevogas kadrovski smisao što morati priznati uspjeh uspjeti desetina odobrenje zapošljavanje zaposliti radnik pozicija novinar inače prijatelj marjanovica sada sarajevogas imati služba brojan stanje informisanje predsjednik država sada željeti zaključiti ovaj rasprava putem medij preseliti ured korupcija tamo analizirati ko dostaviti ime direktor ko obaviti razgovor kandidat čiji nagovor dijeliti direktorski mjesto tranzicija vlast Marjanović ime Sarajevogasa određivati prioritetan mjesto zapošljavanje također dostaviti listinga mobitelo vidjeti utvrditi kontakt zastupnik marjanović neformalan vlasnik sarajevogasa niti pitanje jasno odgovoreno modus operandi prijaviti politički korupcija koji učestvujete drag moj zimzelen član poručiti bečarević program n1 televizija moći pratiti uživo ovaj link putem aplikacija</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3055,12 +2001,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>N1, Ured za korupcija KS, Sarajevo, Almir Bečarević, nadzorni odbor Sarajevogasa, Damir Marjanović, skupština Sarajevogasa, Damir Marjanović, Sarajevogasa, Marjanović, ured za korupcija i javnost, Bečarević, Almir Bečarević, Sarajevogasa, KS, Sarajevogas, Toplanama Sarajevo, Sarajevogas, Sarajevogasa, sarajevogasu, Bečarević, Bečarević, Baković, BH - Gasa, Vjekoslav Bevanda, Bakovića, V.D. direktor, KS, Marjanović, Kampus, Sarajevogasa, Bečarević, Sarajevogas, Facebook, Raj, Marjanović, sarajevogasu, sarajevogasu, Sarajevogasa, Sarajevogas, marjanovica, Sarajevogas, ured za korupcija, V.D. direktor, Marjanović, Sarajevogasa, Marjanović, Sarajevogasa, Bečarević, program N1 televizija, Android|iPhone, iPad</t>
+          <t>sarajevo, almirati bečarević, damirati Marjanović, damirati Marjanović, sjena sarajevogasa, Marjanović, Bečarević, slomljean, almir Bečarević, Bečarević, Bečarević, Baković, Baković, Marjanović, Bečarević, Marjanović, sarajevogas sarajevogas, Marjanović, Sarajevogasa, Marjanović, sarajevogasa, Bečarević</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3070,41 +2016,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ministar komunalne privrede Kantona Sarajevo Almir Bečarević uputio je javni odgovor Nadzornom odboru Sarajevogasa. Podsjećamo, tokom jučerašnjeg dana bilo je više saopćenja s obje strane oko ostavke direktora Edisa Bakovića.
-"Poštovani,
-Zahvaljujem na odgovoru koji ste uputili javno kako sam isti i tražio. Nadam se da ste primjerak dostavili Uredu za borbu protiv korupcije KS? Također se nadam da ćete krivičnu prijavu protiv ovog ministra dostaviti u što kraćem roku u Kantonalno tužilaštvo.
-Zašto sam tražio javni odgovor?
-Kako sam dio vas upoznao preko Damira Marjanovića (predsjedavajućeg Skupštine Sarajevogasa) u prostorijama ministarstva bio sam ubijeđen da ćete u svom odgovoru stati u zaštitu gospodina Damira Marjanovića, mentora i vlasnika iz sjene Sarajevogasa. Dostavljeni dopis dovoljno govori o vašoj potrebi za zaštitu g. Marjanovića, a ne o suštini mojih pitanja i stoga da upoznam Ured za borbu protiv korupcije i javnost o sljedećem:
-U svom odgovoru navodite: "Direktor preduzeća prije svega treba da je menadžer sa širinom i vizijom upravljanja preduzećem, da zna raditi s ljudima."
-Ovdje se radi o najznačajnijoj energetskoj kompaniji u KS, a ne o kompaniji kojom treba upravljati psiholog ili psihijatar ili pedagog zbog slomljenih i narušenih odnosa među ljudima.
-Na vaše direktno pitanje, a kao što je sa tim upoznata i javnost KS, ja, Almir Bečarević, sam ministar cijelog resora i ministar Sarajevogasa. Vlada KS može to potvrditi, a na web stranici vlade imate gotovo sve aktivnosti mene kao ministra kao i dnevne redove vlade KS, na kojima nije bilo sjednice, a da na istoj nisam predložio bar jednu tačku dnevnog reda. Najznačajnija je pokretanje procedure za formiranje energetskog haba putem kojeg će Sarajevogas manje isporučivati ruskog gasa prema Toplanama Sarajevo.
-Razlog zbog kojeg se bavim preduzećem Sarajevogas, je taj što ste uspjeli da po zvaničnom bilansu uspjeha smanjite dobit ove kompanije sa 1,2 mil. KM na 70.000 KM. Nekad je dobit Sarajevogasa bila i 2,0 mil. KM.
-Što se tiče zdravstvenog stanja direktora nisam znao da se bavite i analizom medicinske dokumentacije, te stoga razumijem da sada želite da spojite psihologiju i opću medicinu u Sarajevogasu.
-Za vašu informaciju, a i za informaciju javnosti dogovorena ostavka u ovoj političkoj korupciji je da aktuelni direktor g. Baković nakon ostavke bude pripravan za poziciju izvršnog direktora BH-Gasa, a u kojem bi direktor trebao biti g. Vjekoslav Bevanda. Pratit ćemo put g. Bakovića da li će isti popravljati svoje zdravstveno stanje (ovu temu ste vi otvorili) ili ići na novu funkciju.
-Idemo dalje, kažete da ste vodili računa o kompetencijama novog V.D. direktora, a ne kažete ko vam je to ime dostavio. Moje pitanje je upravo to bilo i ja nemam problem sa protokolom jer sam upravo ukazao na to da nisam konsultovan, niti vlada KS, o tim kompetencijama, već jedan od dva poslanika g. Marjanović ili g. Lemezan. Možda vaš kandidat ima 8 godina u struci, ali u struci koja je povezana sa Terapijskom zajednicom Kampus i moram provjeriti da li je ista bar koristila prirodni gas, kako bih našao poveznicu sa osnovnom djelatnošću Sarajevogasa.
-Tačno je da sam poništio 31 saglasnost za prijem radnika na određeno i neodređeno vrijeme i koja se nisu realizovala u posljednjih godinu dana. Razlog za poništenje je navod direktora da nije obezbijedio finansijska sredstva za ove prijeme u radni odnos.
-O finansijskom utjecaju ovih prijema analizirajte sa aspekta dobiti i troška od milion KM. Postavljeni ste da nadzirete rad preduzeća, a ne da kukate o prijemima zaposlenika koji svakako završe na Facebook grupi "Raja sa biroa".
-Ovaj ministar nije ništa reducirao po pitanju prijema radnika već je to g. Marjanovic izdiktirao i zahtijevao iz razloga što mu "gori" u Sarajevogasu, a gorilo mu je npr. mjesto administratora u Sarajevogasu.
-NO Sarajevogasa je priopćio javnosti da sam desetkovao Sarajevogas u kadrovskom smislu što moram priznati da je uspjeh, a NO je uspio od desetina odobrenja za zapošljavanje zaposliti radnika na poziciju novinara, inače prijatelja g. Marjanovica. Sada Sarajevogas ima službu (brojno stanje) informisanja koju ni predsjednik države nema.
-Sada bih želio, da zaključim ovu raspravu putem medija i da se svi preselimo u Ured za borbu protiv korupcije pa da tamo analiziramo ko je dostavio ime za V.D. direktora, ko je obavio razgovor sa kandidatom i na čiji nagovor, kako se to dijele direktorska mjesta u "tranziciji" vlasti, kako g. Marjanović u ime Sarajevogasa određuje koja su to prioritetna mjesta za zapošljavanje? Također da svi dostavite listinge mobitela, da vidimo i utvrdimo da li ste u kontaktu sa zastupnikom Marjanovićem kao neformalnim vlasnikom Sarajevogasa. Niti na jedno moje pitanje nije jasno odgovoreno, a moj modus operandi je prijaviti političku korupciju u kojoj učestvujete, dragi moji, zimzeleni, članovi NO", navodi se u odgovoru Bečarevića.</t>
+          <t>ministar komunalan privreda kanton sarajevo almir Bečarević uputiti javan odgovor nadzoran odbor sarajevogasa podsjećati tokom jučerašnji dan mnogo saopćenje oba strana oko ostavka direktor edisa bakovića poštovati zahvaljuj odgovor uputiti javno isti tražiti nadam primjerak dostaviti ured borba protiv korupcija ks također nadati htjeti krivičan prijava protiv ovaj ministar dostaviti što kraćem rok kantonalan tužilaštvo zašto tražiti javan odgovor dio upoznati preko damira marjanović predsjedavajući skupština sarajevogas prostorija ministarstvo ubijediti htjeti odgovor stati zaštita gospodin damira marjanović mentor vlasnik sjena sarajevogasa dostaviti dopis dovoljno govoriti vaši potreba zaštita marjanović suština moj pitanje stoga upoznati ured borba protiv korupcija javnost sljedeći odgovor navoditi direktor preduzeće sve trebati menadžer širin vizija upravljanje preduzeće znati raditi čovjek ovdje raditi najznačajnijoj energetski kompanija ks kompanija koji trebati upravljati psiholog psihijatar pedagog zbog slomljean narušen odnos među čovjek vaš direktan pitanje što taj upoznati javnost ks almir Bečarević ministar cijel resor ministar sarajevogas vlada ks moći potvrditi web stranica vlada imati gotovo aktivnost ministar dnevni redov vlada ks sjednica isti predložiti bar jedan tačka dnevan red najznačajnija pokretanje procedura formiranje energetski haba putem koji htjeti sarajevogas malo isporučivati ruski gas prema toplana sarajevo razlog zbog koji baviti preduzeće sarajevogas što uspjeti zvaničan bilansa uspjeh smanjiti dobit ovaj kompanija mil km km nekad dobit sarajevogasa mil km što ticati zdravstven stanje direktor znati baviti analiza medicinski dokumentacija stoga razumijem sada željeti spojite psihologija opći medicina sarajevogas vaš informacija informacija javnost dogovoriti ostavka ovaj politički korupcija aktuelan direktor baković ostavka biti pripravan pozicija izvršan direktor koji direktor trebati vjekoslav bevanda pratiti htjeti put Baković htjeti isti popravljati zdravstven stanje ovaj tema otvoriti ići nov funkcija idemo daleko kažete voditi račun kompetencija nov direktor kažuti ko ime dostaviti pitanje upravo nemati problem protokol upravo ukazati konsultovan niti vlada ks taj kompetencija već jedan dva poslanik Marjanović lemezan možda vaš kandidat imati 8 godina struka struka povezan terapijski zajednica kampus morati provjeriti isti bar koristiti prirodan gas naći poveznica osnovan djelatnošću sarajevogasa tačno poništiti 31 saglasnost prijem radnik određen neodređen vrijeme realizovati posljednji godina dan razlog poništenje navod direktor obezbijediti finansijski sredstvo ovaj prijeme radni odnos finansijski utjecaj ovaj prijema analizirati aspekt dobiti trošk milion km postavljiti nadzirete rad preduzeće kukata prijem zaposlenik svakako završiti facebook grupa raj biro ovaj ministar ništa reducirati pitanje prijema radnik već marjanovic izdiktirati zahtijevati razlog što goriti sarajevogasa goriti npr mjesto administrator sarajevogasu sarajevogasa priopćiti javnost desetkovati sarajevogas kadrovski smisao što morati priznati uspjeh uspjeti desetina odobrenje zapošljavanje zaposliti radnik pozicija novinar inače prijatelj marjanovica sada sarajevogas imati služba brojan stanje informisanje predsjednik država sada željeti zaključiti ovaj rasprava putem medij preseliti ured borba protiv korupcija tamo analizirati ko dostaviti ime direktor ko obaviti razgovor kandidat čiji nagovor dijeliti direktorski mjesto tranzicija vlast Marjanović ime Sarajevogasa određivati prioritetan mjesto zapošljavanje također dostaviti listinga mobitelo vidjeti utvrditi kontakt zastupnik marjanović neformalan vlasnik sarajevogasa niti pitanje jasno odgovoreno modus operandi prijaviti politički korupcija koji učestvujete drag moj zimzelen član navoditi odgovor bečarević</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3115,12 +2032,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sarajevo, Almir Bečarević, nadzornom odbor Sarajevogasa, Edis Bakovića, Ured za borba protiv korupcija KS, Kantonalno tužilaštvo, Damir Marjanović, skupština Sarajevogasa, Damir Marjanović, Sarajevogasa, Marjanović, ured za borba protiv korupcija i javnost, Almir Bečarević, Sarajevogasa, KS, Sarajevogas, Toplanama Sarajevo, Sarajevogas, Sarajevogasa, sarajevogasu, Baković, BH - Gasa, Vjekoslav Bevanda, Bakovića, KS, Marjanović, Kampus, Sarajevogasa, Facebook, Raj, Marjanovic, sarajevogasu, sarajevogasu, Sarajevogasa, Sarajevogas, marjanovica, Sarajevogas, ured za borba protiv korupcija pa, Marjanović, Sarajevogasa, Marjanović, Sarajevogasa, Bečarević</t>
+          <t>sarajevo, almir Bečarević, edisa Baković, ured borba protiv korupcija, damirati Marjanović, damirati Marjanović, sjena sarajevogasa, Marjanović, ured borba protiv korupcija javnost, slomljean, almir Bečarević, Baković, Baković, Marjanović, sarajevogas sarajevogas, ured borba protiv korupcija, Marjanović, Sarajevogasa, Marjanović, sarajevogasa, Bečarević</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3130,27 +2047,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S23 FE bi mogao imati i bežično punjenje?
-Racunalo.com prije 5 sati
-Smartfon se ovih dana nalazi na raznim certifikacijskim postupcima odakle dolaze podaci o nekim zanimljivim karakteristikama. Samsung Galaxy S23 FE je smartfon za fanove (Fan Edition), koji je uvijek bio vrlo popularan jer za osjetno nižu cijenu nudi brojne karakteristike flagship modela. Prošli model je bio S21 FE, preskočena je serija S22 tako da se […]</t>
+          <t>samsung galaxy s23 fe moći imati bežičan punjenje 5 sat smartfon ovaj dan nalaziti razni certifikacijski postupak odakle dolaziti podatak neki zanimljiav karakteristika samsung galaxy s23 fe smartfon fanov fan edition uvijek popularan osjetno nižu cijena nuditi brojan karakteristika flagship model proći model s21 fe preskočiti serija s22</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3161,12 +2063,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Samsung Galaxy, FE, Racunalo.com, Samsung Galaxy, FE, Fan Edition, S21 FE, S22</t>
+          <t>s21 fe, s22</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3176,33 +2078,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sin Alke Vuice progovorio o odnosu s Ellom Dvornik i otkrio: ‘Veliki sam lover boy’
-Autor: Dnevno.hr/ T.Š.
-Glasine o razvodu Elle Dvornik-Pierce i Charlesa Piercea pojavile su se u travnju nakon što je influencerica objavila prvi album, čiji je producent Arian Vuica, sin naše hitmejkerice Alke Vuice.
-“Znamo se cijeli život i odlično se razumijemo i slažemo. Slušala sam njegove savjete jer je on profesionalac i majstor svoga posla, ali na kraju je uvijek bitno da sam ja zadovoljna finalnim proizvodom jer je to moje autorsko djelo. Zahvalna sam Arianu što mi je dao potpunu slobodu i nije me ograničavao”, rekla je Ella za Story nakon izlaska albuma ‘Teška vremena za sanjare’ i dodala kako je Alka bila tu kako bi njoj i Arianu dala pokoji savjet ili pitala jesu li gladni, jer se Arianov studio nalazi u podrumu obiteljske kuće Alke Vuice.
-Pogledajte ovu objavu na Instagramu. Objavu dijeli Ella Dvornik-Pearce (@elladvornik)
-Prije godinu dana Arian Vuica je za Story govorio o tome kako je sretno zaljubljen, ali i da je uvijek imao uspjeha kod djevojaka. “Ona je mlađa sestra jednog od mojih najboljih prijatelja. Moram priznati da je na početku bio malo rezerviran zbog te ideje na početku naše veze, ali se opustio sad nakon četiri godine”, ispričao je Arian i otkrio:
-“Neću lagati, moram priznati da sam uvijek imao sreće sa ženama, ali sam i veliki lover boy. Uvijek sam bio u dugim vezama jer imam sreće pa naletim na divne žene u svakom smislu i rijetko kad sam imao traumatičan prekid”, rekao je.
-Usprkos javnoj potvrdi ljubavne veze, šuškanja o njegovom dubljem odnosu s Ellom Dvornik su se nastavila pa se sada ponovno oglasio Arian Vuica koji je u razgovoru za 24sata otkrio kako između njega i Elle ‘nema ništa’.
-</t>
+          <t>sin alka vuica progovoriti odnos ell dvornik otkriti velik lover boy autor glasina razvod ella charlesa pierce pojaviti travanj što influencerica objaviti prvi album čiji producent Arian vuica sin naš hitmejkerica alka vuice znati cijel život odlično razumijemo slažemo slušati njegov savjet profesionalac majstor svoj posao kraj uvijek bitno zadovoljan finalan proizvod autorski djelo zahvalan arianu što dati potpun sloboda ograničavati reći ella Story izlazak album težak vrijeme sanjar dodati alka arianu dati pokoji savjet pitati gladan Arianov studio nalaziti podrum obiteljski kuća alka vuica pogledati ovaj objava instagram objava dijeliti ella elladvornik godina dan Arian Vuica Story govoriti sretno zaljubliti uvijek imati uspjeh kod djevojka mlađa sestra jedan mojih najboljih prijatelj morati priznati početak malo rezervirati zbog ideja početak naš veza opustiti sad četiri godina ispričati Arian otkriti htjeti lagati morati priznati uvijek imati sreća žena velik lover Boy uvijek dug veza imati sreća naletiti divan žena svaki smisao rijetko kad imati traumatičan prekid reći usprkos javan potvrda ljubavan veza šuškanje njegov dubljem odnos ell dvornik nastaviti sada ponovno oglasiti Arian vuica razgovor 24sata otkriti između elle ništa</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3213,12 +2094,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ell dvornik, boy, T.Š., Elle Dvornik, Charles Pierce, Arian Vuica, Alka Vuica, Arian, Ella, Story, Alka, Arian, Arianov, Alka Vuica, Instagram, Ella Dvornik, Arian Vuica, Story, Arian, boy, Ell dvornik, Arian Vuica, Elle</t>
+          <t>alka vuica, boy, ella charles, Arian vuica, arian, ella Story, alka arian, Arianov, ella elladvornik, Arian Vuica Story, Arian, Boy, Arian</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3228,33 +2109,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sin Alke Vuice progovorio o odnosu s Ellom Dvornik, otkrio: ‘Veliki sam lover boy’
-Autor: Dnevno.hr/ T.Š.
-Glasine o razvodu Elle Dvornik-Pierce i Charlesa Piercea pojavile su se u travnju nakon što je influencerica objavila prvi album, čiji je producent Arian Vuica, sin naše hitmejkerice Alke Vuice.
-“Znamo se cijeli život i odlično se razumijemo i slažemo. Slušala sam njegove savjete jer je on profesionalac i majstor svoga posla, ali na kraju je uvijek bitno da sam ja zadovoljna finalnim proizvodom jer je to moje autorsko djelo. Zahvalna sam Arianu što mi je dao potpunu slobodu i nije me ograničavao”, rekla je Ella za Story nakon izlaska albuma ‘Teška vremena za sanjare’ i dodala kako je Alka bila tu kako bi njoj i Arianu dala pokoji savjet ili pitala jesu li gladni, jer se Arianov studio nalazi u podrumu obiteljske kuće Alke Vuice.
-Pogledajte ovu objavu na Instagramu. Objavu dijeli Ella Dvornik-Pearce (@elladvornik)
-Prije godinu dana Arian Vuica je za Story govorio o tome kako je sretno zaljubljen, ali i da je uvijek imao uspjeha kod djevojaka. “Ona je mlađa sestra jednog od mojih najboljih prijatelja. Moram priznati da je na početku bio malo rezerviran zbog te ideje na početku naše veze, ali se opustio sad nakon četiri godine”, ispričao je Arian i otkrio:
-“Neću lagati, moram priznati da sam uvijek imao sreće sa ženama, ali sam i veliki lover boy. Uvijek sam bio u dugim vezama jer imam sreće pa naletim na divne žene u svakom smislu i rijetko kad sam imao traumatičan prekid”, rekao je.
-Usprkos javnoj potvrdi ljubavne veze, šuškanja o njegovom dubljem odnosu s Ellom Dvornik su se nastavila pa se sada ponovno oglasio Arian Vuica koji je u razgovoru za 24sata otkrio kako između njega i Elle ‘nema ništa’.
-</t>
+          <t>sin alka vuica progovoriti odnos ell dvornik otkriti velik lover boy autor glasina razvod ella charlesa pierce pojaviti travanj što influencerica objaviti prvi album čiji producent Arian vuica sin naš hitmejkerica alka vuice znati cijel život odlično razumijemo slažemo slušati njegov savjet profesionalac majstor svoj posao kraj uvijek bitno zadovoljan finalan proizvod autorski djelo zahvalan arianu što dati potpun sloboda ograničavati reći ella Story izlazak album težak vrijeme sanjar dodati alka arianu dati pokoji savjet pitati gladan Arianov studio nalaziti podrum obiteljski kuća alka vuica pogledati ovaj objava instagram objava dijeliti ella elladvornik godina dan Arian Vuica Story govoriti sretno zaljubliti uvijek imati uspjeh kod djevojka mlađa sestra jedan mojih najboljih prijatelj morati priznati početak malo rezervirati zbog ideja početak naš veza opustiti sad četiri godina ispričati Arian otkriti htjeti lagati morati priznati uvijek imati sreća žena velik lover Boy uvijek dug veza imati sreća naletiti divan žena svaki smisao rijetko kad imati traumatičan prekid reći usprkos javan potvrda ljubavan veza šuškanje njegov dubljem odnos ell dvornik nastaviti sada ponovno oglasiti Arian vuica razgovor 24sata otkriti između elle ništa</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3265,12 +2125,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ell dvornik, boy, T.Š., Elle Dvornik, Charles Pierce, Arian Vuica, Alka Vuica, Arian, Ella, Story, Alka, Arian, Arianov, Alka Vuica, Instagram, Ella Dvornik, Arian Vuica, Story, Arian, boy, Ell dvornik, Arian Vuica, Elle</t>
+          <t>alka vuica, boy, ella charles, Arian vuica, arian, ella Story, alka arian, Arianov, ella elladvornik, Arian Vuica Story, Arian, Boy, Arian</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3280,35 +2140,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bivša RTL-ova voditeljica i jedna od najljepših Hrvatica, Antonija Stupar Jurkin (41), zadnjih se godina povukla iz javnog života, no i dalje je vrlo aktivna na Instagramu, gdje je prati više od 40 tisuća ljudi. Antonija često dijeli svoje fotografije,a sada je oduševila pratitelje novom fotografijom s plaže.
-Bivša voditeljica pozirala je na stijeni pokraj mora, a preplanuli ten i atraktivna figura došli su do izražaja u ružičastom bikiniju koji je nosila.
-''Dnevna doza sunca i mora'', dodala je u opisu fotografija. Osim fotografija podijelila je i videozapis koji sadrži još mnoštvo fotografija.
-"Prelijepo", "Prelijepa i prekrasna žena", "Boginja", neki su od komplimenata koje je dobila.
-Antonija je inače mama dvoje djece, kćeri Paole i sina Ivana, koje je dobila sa suprugom Ivanom.
-VEZANI ČLANCI
-Poznato je kako Antonija svoju figuru održava redovitim treninzima. U teretani provodi dosta vremena, a rezultati su itekako vidljivi.
-Inače, bivša voditeljica se sredinom 2019. godine oprostila od RTL-a. Tada nam je rekla kako je želja za novim znanjima, za koje nije imala vremena dok je bila u radnom odnosu, prevagnula i zato je odlučila oprostiti se od televizije. Nakon što je napustila RTL, imala je više vremena pa se posvetila svom starom hobiju – uređivanju starih komada namještaja. Sve je počelo prije više od desetak godina kada je novo ruho dala stolcima u blagovaonici i nakon toga počela je uređivati i druge komade namještaja.
-– Ne mislim da bi mi ovaj hobi jednog dana mogao prerasti u posao jer tada to više ne bi bio hobi, no voljela bih da mi ovaj gušt postane obveza. Ovo radim kad hoću i kad imam vremena i tako me veseli – otkrila je Antonija i dodala kako inspiraciju pronalazi na internetu. Kaže kako joj ne nedostaje rad pred TV kamerama i kako ima dojam da sada istinski uživa i ima vremena za sve.
-– Moram priznati da mi uopće ne nedostaju kamere. Nakon 15 godina prvi put u životu guštam i uživam u novim izazovima. Posvetila sam se učenju pa sam tako na poslovnom učilištu u jednoj godini uspjela završiti dva smjera, marketing i event manager – pohvalila se Stupar Jurkin.
-VIDEO Joško Lokas o neuspjehu emisije Marka Tolje: Mislim da je to i prije bilo osuđeno na propast</t>
+          <t>bivši voditeljica najljepših hrvatica antonio Stupar Jurkin 41 zadnji godina povući javan život daleko aktivan instagram gdje pratiti mnogo 40 tisuća čovjek antonija često dijeliti fotografija sada oduševiti pratitelj nov fotografija plaža bivši voditeljica pozirati stijeni pokraj morati preplanuti ten atraktivan figura doći izražaj ružičast bikiniju nositi dnevni doza sunce more dodati opis fotografija osim fotografija podijeliti videozapis sadržati još mnoštvo fotografija prelijepo prelijep prekrasan žena boginja komplimenat dobiti antonija inače mama dvoje dijete kćera paole sin ivati dobiti supruga ivan vezan članak poznat antonija svoj figura održavati redoviat treninz teretan provoditi dosta vrijeme rezultat itekako vidljiv inače bivši voditeljica sredinom godina oprostiti reći želja nov znanje imati vrijeme dok radni odnos prevagnuti zato odlučiti oprostiti televizija što napustiti rtl imati mnogo vrijeme posvetiti star hobij uređivanje star komad namještaj početi mnogo desetak godina nov ruho dati stolc blagovaonica taj početi uređivati drugi komada namještaj misliti ovaj hobi jedan dan moći prerasti posao mnogo hobi voljeti ovaj gušt postati obveza ovaj raditi kad hoću kad imati vrijeme vesela otkriti antonija dodati inspiracija pronalaziti internet kazati nedostajati rad pred tv kamera imati dojam sada istinski uživati imati vrijeme morati priznati uopće nedostati kamera 15 godina prvi put život guštati uživati nov izazov posvetiti učenje poslovan učilište jedan godina uspjeti završiti dva smjer marketing event manager pohvaliti stupar Jurkin video joško lokas neuspjeah emisija marka tolje misliti osuđeno propast</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3319,12 +2156,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>RTL - ova, Hrvatica, Antonija Stupar Jurkin, Instagram, Antoni, boginja, Antoni, Paola, Ivan, Ivan, Antoni, RTL - a., RTL, Antoni, Stupar Jurkin, Joško Lokas, Marko Tolja</t>
+          <t>hrvatica, Antonio Stupar Jurkin, Jurkin, Joško Lokas</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3334,28 +2171,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>"Trenutačno stanje je dobro, ali zaista je nevjerojatna brzina i količina padalina koje su pale u ovom periodu. Mi kada smo došli ovdje u Kamnik ograda je bila čitava, a sad je nastalo oštećenje na njoj koja je to količina bujice bila. Dvorište je potopljeno, voda se slijeva. Mi kada smo došli ovdje prije tri-četiri sata, malo više sve bilo potopljeno kao i jedno križanje. Ovdje su bili vatrogasci, vojska. Bilo je baš dramatično stanje", izvijestio je reporter Dnevnika Nove TV, Ivan Čorkalo.
-"Nešto ovako nismo doživjeli. Bilo je ponekad, ali nikad ovako. Imali smo već cijeli podrum poplavljen, samo nikad nije bilo više od ovog što je asfaltirano", rekao je Joža Košir, stanovnik Kamnika.
-"To je došlo za 15-20 minuta, ona nije brza, samo se razvija, drugačije je nego da dođe dolje s brda. Trebat će sanirati, treba isprazniti, očistiti", poručio je Košir i dodao: "Imam 55 godina i nikad nije bilo ovako, bilo je oko 60 centimetara."
-"Očito se vremenske prilike mijenjaju, nadamo se samo da neće biti gore od ovoga što smo doživjeli danas u Sloveniji", zaključio je Čorkalo.</t>
+          <t>trenutačan stanje dobro zaista nevjerojatan brzina količina padalin pati ovaj period doći ovdje kamnik ograda čitavi sad nastati oštećenje količina bujica dvorište potopiti voda slijevati doći ovdje sat malo mnogo potopljen križanje ovdje vatrogasciti vojska baš dramatičan stanje izvijestiti reporter dnevnik nov tv ivan čorkati nešto ovako doživjeti ponekad nikad ovako imati već cijel podrum poplavliti nikad mnogo ovaj što asfaltirati reći joža košir stanovnik kamnik doći minuta brz razvijati drugačije doći dolje brdo trebati htjeti sanirati trebati isprazniti očistiti poručiti košir dodati imati 55 godina nikad ovako oko 60 centimetar očito vremenski prilika mijenjati nadati htjeti gore ovaj što doživjeti danas Slovenija zaključiti čorkati</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -3366,12 +2187,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kamnik ograda, dnevnik, nov TV, Ivan Čorkalo, Joža Košir, Kamnik, Košir, Slovenija, čorkalo</t>
+          <t>joža, Slovenija</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3381,44 +2202,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lovačkim žargonom, zrakoplov i tenk trofejna su divljač u ratu. Ova je priča upravo o jednom tenku – onome oznake 4720 koji je na današnji dan u jutarnjim satima prvi ušao u Knin. Njime je upravljala posada mehanizirane bojne 7. gardijske brigade “Pume”, poznati model T-55 i danas se čuva u petrinjskoj vojarni, piše HRT.
-Prije 28 godina kretali su se preko Crvene zemlje kroz Sivi put, pa do sela Kovačić odakle su u koloni ušli Knin – danas u petrinjskoj vojarni stara 55-ica budi emocije, vraća sjećanja.
-– Pokojni vozač Ivica Delić, poslužitelj Kristijan Vajcek iz Brista, on je bio iz južne Hrvatske, ciljač je bio Mario Gerić i moja malenkost – zapovjednik tenka. Poznam ga po cijevi. U okršaju je bio i pogođen po cijevi od gelera, pa kad bi ga mogli otvoriti, vjerujem da bi malo teže upalio. Vjerujem da unutra, što se tiče topa i strojnica, sve radi, rekao je Vladimir Miljenović Bronx, zapovjednik 2. tenkovskog voda 2. tenkovske satnije, 7. gardijska brigada “Pume”.
-A takva je bila i sama akcija Oluja, čekić i nakovanj – sve je gorjelo! Prije svega od ljubavi prema domovini, želji za oslobođenje okupiranog teritorija, trebalo je povezati sve dijelove Hrvatske ponovno.
-– Preko noći je došla zapovijed da će se ići prema Kninu. Prvo smo ostali zatečeni, onda nakon nekoliko trenutaka, krenula je euforija. Jednostavno, ne možeš ni vjerovati da ćemo sutra biti u Kninu iz kojeg je sve počelo, naglasio je satnik Dubravko Jurinić Jura, zapovjednik 2. tenkovske satnije Oklopno-mehanizirane bojne, 7. gardijska brigada “Pume”.
-“Mnogo je još neispričanih priča”
-I bili su, prvi su u jutarnjim satima ušli u kraljevski grad – kažu mnogo je još neispričanih priča, a u tenku oznake 2470 nisu samo prvi ušli samo u Knin nego i u Bosansko Grahovo.
-Zapravo nema bojišta i oslobođenog mjesta u kojemu tenk i njegova posada nisu imali važnu ulogu.
-– Neke svoje najbolje mladenačke godine sam proveo u tom tenku. Od početka do kraja rata i to je bio naš dom. Vezali smo se uz tu tehniku, navikli smo se na nju i tu smo spavali, jeli i boravili tih 5 godina. To je kao kad puž svoju kućicu nađe, ne pušta je dok god nije bilo potrebe da se ostavi, rekao je Jurinić.
-Veliko srce
-Jer taj je tenk u vihoru rata tada golobradim mladićima, ali ipak vrlo dobro uigranoj posadi, značio sigurnost. Kažu – imali su osjećaj da su neuništivi, a o njihovoj snazi dovoljno govori podatak da ih je čak i NATO u akcijama morao zaustavljati.
-– Moram priznati da smo imali i dozu sreće u svom tom onom ludom vremenu, dodao je.
-– Samo veliko srce i to je u stvari taj nekakvi pokretač. Automatski si puno jači i hrabriji, odvažniji. Srce je u stvari najbitnije, istaknuo je Robert Puja, natporučnik u miru, predsjednik Udruge veterana 7. gardijske brigade “Pume”.
-Uz to veliko srce, čista glava i stečeno ratno iskustvo, priznaju, bili su dobitna kombinacija.
-Izravni okršaj s protivnikom
-No uza sve morali su biti i snalažljivi, zbunjivali su neprijatelja, tenkovima se noću vozili, mijenjali položaje. Pričaju – dok su se približavali Crvenoj zemlji, neprijatelj ih gotovo nije ni primijetio, no na kraju je ipak došlo do izravnog okršaja s protivnikom.
-– Bio sam na prednjem nagibu, a on je bio skriven dolje u žbunju. Jedino što ga je odavalo – pucao je s pancirnim streljivom. On ima traser, tako da se vidi crveno svjetlo. Onda smo se dodavali, malo on mene, malo ja njega. Mislim da sam 7 ili 8 komada ispalio. Prva je bila trenutna, ostale su bile pancirne. Vjerujem da sam ga pogodio jer zadnje zrno koje je išlo, to je na 3-4 kilometara, vidjelo se da se zasvijetlilo. Znači da smo pogodili nešto željezno, rekao je Miljenović Bronx.
-Kakav je pogodak bio, nisu mogli provjeriti jer moralo se nastaviti, efekt iznenađenja bio je presudan jer nitko nije vjerovao da se kroz Crvenu zemlju tenkovima može ući u grad niti je to neprijatelj očekivao, a onda su se našli tik pred toliko željenim Kninom.
-– Kad smo došli do ploče Knin, skrenuli smo desno i pratili situaciju, čekamo da se javi neprijatelj. Nije bilo neprijatelja. Mi smo se malo požurili, pa su i oni bili iznenađeni, a i neki su pobjegli kroz noć, tako da do centra nismo imali nikakvih problema, rekao je Miljenović Bronx.
-Emocije su morali staviti u drugi plan, kažu, jer zadaću je trebalo izvršiti do kraja – za pobjedničku Hrvatsku vojsku tada ništa nije bilo nemoguće. Tenk oznake 2470 zauvijek će ostati dijelom vojne povijesti. Posljednja akcija bila mu je “Južni potez”, piše HRT.</t>
+          <t>lovački žargon zrakoplov tenk trofejan divljač rat pričati upravo jedan tenk onaj oznaka 4720 današnji dan jutarnji sat prvi ući knin on upravljati posada mehanizirati bojan gardijski brigada pume poznat model danas čuvati petrinjski vojarna pisati hrt 28 godina kretati preko crven zemlja siv put selo kovačić odakle kolon ući knin danas petrinjski vojarna star buditi emocija vraćati sjećanje pokojan vozač ivica delić poslužitelj kristijan vajcek brist južan hrvatski ciljač mariti gerić malenkost zapovjednik tenak poznati cijev okršaj pogođen cijev geler kad moći otvoriti vjerovati malo teško upaliti vjerovati unutra što ticati top strojnica raditi reći vladimir miljenović bronx zapovjednik tenkovski voda tenkovski satnija gardijski brigada puma takav sam akcija oluja čekić nakovanj gorjelo sve ljubav prema domovina želja oslobođenje okupiran teritorij trebati povezati dio hrvatski ponovno preko noć doći zapovijed htjeti ići prema knina prvo ostali zatečeni onda nekoliko trenutak krenuti euforija jednostavno moći vjerovati htjeti sutra knina koji početi naglasiti satnik Dubravko jurinić jura zapovjednik tenkovski satnija bojan gardijski brigada puma mnogo još neispričaan priča prvi jutarnji sat ući kraljevski grad kazati mnogo još neispričaan priča tenk oznaka 2470 prvi ući knin bosanski grahov zapravo bojišta oslobođen mjesto koji tenk posada imati važan uloga neki dobar mladenački godina provesti taj tenk početak kraj rat naš dom vezati tehnika navići spavati jeti boraviti taj 5 godina kad puž svoj kućica naći puštati dok god potreba ostaviti reći Jurinić velik srce tenk vihor rat golobrad mladićima ipak dobro uigraan posada značiti sigurnost kazati imati osjećaj neuništiva njihov snaga dovoljno govoriti podatak čak nato akcija morati zaustavljati morati priznati imati doza sreća taj onaj luda vremene dodati velik srce stvar nekakav pokretač automatski puno jači hrabr odvažn srce stvar najbitno istaknuti robert puja natporučnik mir predsjednik udruga veteran gardijski brigada pume velik srce čist glava stečen ratni iskustvo priznati dobitni kombinacija izravan okršaj protivnik uz morati snalažljiv zbunjivati neprijatelj tenkovima noću voziti mijenjati položaj pričati dok približavati crven zemlja neprijatelj gotovo primijetiti kraj ipak doći izravan okršaj protivniko prednje nagibu skriven dolje žbunja jedino što odavati pucati panciran streljivom imati traser vidjeti crven svjetlo onda dodavati malo malo misliti 7 8 komad ispaliti prvi trenutan ostali biti pancirne vjerovati pogoditi zadnji zrno ići kilometar vidjeti zasvijetlilo značiti pogoditi nešto željezno reći miljenović bronx kakav pogodak moći provjeriti morati nastaviti efekt iznenađenje presudan nitko vjerovati crven zemlja tenkovima moći ući grad niti neprijatelj očekivati onda naći tik pred toliko željen knin kad doći ploča knin skrenuti desno pratiti situacija čekati javiti neprijatelj neprijatelj malo požuriti iznenaditi pobjeći noć centar imati nikakav problem reći miljenović bronx emocija morati staviti drugi plan kazati zadaća trebati izvršiti kraj pobjednički hrvatski vojska ništa nemoguće tenk oznaka 2470 zauvijek htjeti ostati dio vojni povijest posljednji akcija južni potez pisati hrt</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -3429,12 +2218,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knin, T-55, HRT, Crvene zemlja, sivi put, Kovačić, Knin, Ivica Delić, Kristijan Vajcek, Brist, Hrvatska, Mario Gerić, Vladimir Miljenović Bronx, oluja, Hrvatska, Knina, Knina, Dubravko Jurinić Jura, Oklopno - mehanizirane bojne, Knin, Bosanski Grahovo, Jurinić, NATO, Robert Puja, udruga veteran 7, Crvenoj zemlja, Miljenović Bronx, Crvenu zemlja, Knin, Knin, Miljenović Bronx, Hrvatska, Južni potez, HRT</t>
+          <t>kovačić, Ivica delić, kristijan vajcek, Vladimir Miljenović, Dubravko jurinić, Jurinić, Miljenović, Miljenović</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3444,46 +2233,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Prvi dio Svjetskog prvenstva mlađih juniora (U-19) koje se igra u četiri hrvatska grada - Varaždinu, Rijeci, Opatiji i Koprivnici završen je u subotu utakmicama posljednjeg kola u svih osam skupina. Nedjelja je bila slobodni dan na SP, a u ponedjeljak i utorak su na rasporedu utakmice drugog kruga za 16 reprezentacija koje su prošle u “glavnu rundu” natjecanja te susreti President’s Cupa za preostalih 16 koje će se do kraja SP boriti za plasman od 17. do 32. mjesta.
-Hrvatska je svoj posao u prvom krugu obavila bez greške. Alžir i Ruanda nisu nikakvo mjerilo, ali su naši igrači te dvije utakmice odradili baš kao što je trebalo. Ozbiljno, angažirano, napravili velike razlike i podijelili minutažu između sebe. Portugal je bio puno ozbiljniji test, ali izabranici Kreše Ivankovića su vrlo brzo i u tom susretu preuzeli konce igre potpuno u svoje ruke i ostavili Portugalce bez ikakve šanse što će i potvrditi +7 na poluvremenu i +11 na kraju.
-Drugi krug u skupini I Hrvatska počinje s dva boda na svom kontu, kao i Mađarska, dok su Slovenija i Portugal na nuli, a to znači da bi nam pobjeda protiv Slovenije u ponedjeljak u Varaždinu već donijela plasman u četvrtfinale.
-Nismo potpuno zadovoljni
-Jeste li potpuno zadovoljni onim što je naša reprezentacija pokazala u prvom krugu?
-- Nismo potpuno zadovoljni, ali jesmo zadovoljni s ostvarenim prvim ciljem, a to je da smo prošli skupinu i prenijeli dva boda. Sigurno da prve dvije utakmice nisu bile nikakvo mjerilo, ali bilo je to dobro zagrijavanje za malo finale skupine protiv Portugala - kaže izbornik Krešo Ivanković kojeg smo u nedjelju prijepodne prekinuli taman usred analize utakmice protiv Portugala.
-- Otvaranje je opet bilo malo teško za nas, nismo se baš dobro snašli u tih prvih 10-tak minuta, ali kad smo promijenili obranu iz 6-0 u 5-1 počeli smo igrati puno otvorenije i agresivnije.
-S čime to niste potpuno zadovoljni u prvom krugu?
-- Ima tu još prostora za bolje, prvenstveno u 6-0 obrani. Moramo poboljšati još malo taj središnji blok, malo više izlaziti na igrače i raditi još više prekida, biti agresivniji... Ima još nekih sitnica i u tranziciji i napadu na koje ćemo upozoriti igrače kako bi bili spremni za utakmicu protiv Slovenije.
-Ulog u toj utakmici bit će veliki jer bi nam pobjeda već osigurala četvrtfinale.
-- Ulog je u svakoj utakmici veliki, bio je protiv Portugala, bit će protiv Slovenije, pa protiv Mađarske, a ako Bog da i kasnije. Mi idemo utakmicu po utakmicu, prva sljedeća je najbitnija, o ostalima se ne razmišlja jer se ni nema vremena razmišljati unaprijed. Niti se to smije jer onaj koji razmišlja unaprijed, taj je već u debelom minusu.
-Ako su Alžir i Ruanda bile nepoznanice, doduše lako rješive, Slovenija nam je jako dobro poznata.
-- Oni su dobra, borbena ekipa, imaju dobrih pojedinaca koji su dosta jaki i čvrsti u igri jedan na jedan. Istina je da se međusobno jako dobro poznajemo i bit će to sigurno dobra utakmica.
-Slovenci i Mađari 20-30% bolji
-Dobro poznajemo i našeg drugog suparnika u drugom krugu - Mađarsku. Zanimljivo, ova generacija je s njima igrala i prošle godine na Europskom prvenstvu U18 u skupini drugog kruga. Tada smo ih pobijedili 28:25, ali Mađari su iz prvog kruga donijeli pobjedu protiv Njemačke i u drugom svladali Portugal te kao prvi u skupini prošli u borbu za medalje, a mi smo kao četvrti završili u razigravanju od 5. do 8. mjesta. U polufinalu je od Mađara bila bolja Švedska, a u susretu za broncu Njemačka im je uzvratila za poraz u prvom krugu.
-- I s Mađarima se jako dobro poznajemo. Igrali smo i prijateljske utakmice prošle godine s njima, bili smo u prosincu kod njih. Obje naše utakmice drugog kruga bit će zasigurno jako zanimljive i teške, ali na muci se poznaju junaci.
-Koliko su Slovenija i Mađarska bolje od Portugala?
-- Mislim da su sigurno bolje 20-30 posto tako da će trebati još više ozbiljnosti i još čvršće i jače igrati. Kako turnir odmiče tako dolaze sve teže utakmice, to je jednostavno tako i moraš biti sve bolji ako želiš doći do nekog rezultata.
-Ono što je dobro, u prve tri utakmice vidjeli smo na terenu sve naše igrače i rezultat nije padao kad biste promijenili startnu postavu.
-- To nam je i bio cilj od početka jer na velikim natjecanjima ne možeš igrati sa sedam igrača. U kratkom periodu imaš puno utakmica i nemoguće je da jedan igrač igra sve utakmice, a da mu se ne dogodi pad u igri. Kad bi to bilo moguće svi bi igrali u Barceloni. Snaga ekipe je u širini, pogotovo u turnirskom sustavu i mi to za sada dobro koristimo.
-Kao i sve, i našeg izbornika je iznenadio rasplet u skupini H u kojoj su u drugi krug prošli Iran i Farski otoci, a Švedska je ispala u President’s Cup.
-- Apsolutno, to je jako, jako veliko iznenađenje. Mi smo se baš šalili kako je Šveđanima očito lijepo u Opatiji pa su odlučili ostati i dalje tamo. Šalu na stranu, ali oni su doista najveće neugodno iznenađenje, a ugodno su Česi i Iranci koji igraju jako lijepi rukomet.</t>
+          <t>prvi dio svjetski prvenstvo mlad junior igrati četiri hrvatski grad varaždin rijeka opatija koprivnik završiti subota utakmica posljednji kolo sav osam skupina nedjelja slobodan dan sp ponedjeljak utorak raspored utakmica drugi krug 16 reprezentacija prošli glavni runda natjecanje susret president cup preostao 16 htjeti kraj sp boriti plasman mjesto Hrvatska posao prvi krug obaviti bez greška alžir ruanda nikakav mjerilo naš igrač dva utakmica odraditi baš što trebati ozbiljno angažirano napraviti velik razlika podijeliti minutaža između portugal puno ozbiljan test izabranik krešiti ivankovića brzo taj susret preuzeti konac igra potpuno ruka ostaviti portugalac bez ikakav šansa što htjeti potvrditi poluvremenu kraj drugi krug skupina Hrvatska počinjati dva bod kont mađarski dok slovenija portugal nuti značiti pobjeda protiv slovenija ponedjeljak varaždina već donijeti plasman četvrtfinale potpuno zadovoljan potpuno zadovoljan onaj što naš reprezentacija pokazati prvi krug potpuno zadovoljan zadovoljan ostvariti prvi cilj proći skupina prenijeti dva bod sigurno prvi dva utakmica biti nikakav mjerilo dobar zagrijavanje malo finale skupina protiv portugal kazati izbornik krešo ivanković koji nedjelja prijepodne prekinuti taman usred analiza utakmica protiv portugal otvaranje opet malo teško baš dobro snaći taj prvi minuta kad promijeniti obrana početi igrati puno otvoreno agresivn što potpuno zadovoljan prvi krug imati još prostor dobro prvenstveno obrana morati poboljšati još malo središnji blok malo mnogo izlaziti igrač raditi još mnogo prekid agresivn imati još neki sitnica tranzicija napad htjeti upozoriti igrač spreman utakmica protiv slovenija ulog utakmica biti htjeti velik pobjeda već osigurati četvrtfinale ulog svaki utakmica velik protiv portugal biti htjeti protiv slovenija protiv mađarski bog kasno idemo utakmica utakmica prvi sljedeći bitan ostali razmišljati vrijeme razmišljati unaprijed niti smjeti onaj razmišljati unaprijed već debel minus alžir ruanda biti nepoznanica doduše lako rješiv slovenija jako dobro poznat dobar borben ekipa imati dobar pojedinac dosta jak čvrst igra jedan jedan istina međusobno jako dobro poznajemo biti htjeti sigurno dobar utakmica slovenac mađar dobar dobro poznajemo naš drugi suparnik drugi krug mađarski zanimljiv generacija igrati prošli godina europski prvenstvo u18 skupina drugi krug pobijediti mađari prvi krug donijeti pobjeda protiv njemački drugi svladati portugal prvi skupina proći borba medalja četvrti završiti razigravanje mjesto polufinale mađar dobar švedski susret broncu Njemačka oni uzvratiti poraz prvi krug mađarima jako dobro poznajemo igrati prijateljski utakmica prošli godina prosinac kod oba naš utakmica drugi krug biti htjeti zasigurno jako zanimljiv težak muci poznati junak koliko slovenija mađarski dobro portugal misliti sigurno dobro posto htjeti trebati još mnogo ozbiljnost još čvršće jače igrati turnir odmicati dolaziti teža utakmica jednostavno moraš dobar želiti doći rezultat što dobro prvi tri utakmica vidjeti teren naš igrač rezultat padati kad promijeniti startan postava cilj početak velik natjecanje moći igrati sedam igrač kratak period imaš puno utakmica nemoguće jedan igrač igrati utakmica dogoditi pad igra kad moguć igrati barceloni snaga ekipa širina pogotovo turnirski sustav sada dobro koristiti naš izbornik iznenaditi rasplet skupina h koji drugi krug proći iran farski otoci švedski ispati president cup apsolutno jako jako velik iznenađenje baš šaliti šveđan očito lijepo opatija odlučiti ostati daleko tamo šala strana doista velik neugodno iznenađenje ugodno čes iranac igrati jako lijep rukomet</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -3494,12 +2249,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>svjetski prvenstvo, Varaždin, Rijeka, Opatija, Koprivnik, SP, President ’s Cupa, Hrvatska, Alžir, Ruanda, Portugal, Kreša Ivanković, portugalce, +11, Hrvatska, Mađarska, Slovenija, Portugal, Slovenija, Varaždin, Portugal, Krešo Ivanković, Portugal, Slovenija, Portugal, Slovenija, Mađarska, bog, Alžir, Ruanda, Slovenija, Slovenac, Mađar, Mađarska, europski prvenstvo, U18, Mađar, Njemačka, Portugal, Mađar, Švedska, Njemačka, Mađaar, Slovenija, Mađarska, Portugal, Barceloni, H, Iran, Farski otoci, Švedska, president ’s Cup, Šveđanima, Opatija, Česa, Iranac</t>
+          <t>Hrvatska, portugal, Hrvatska, slovenija, slovenija, krešo ivanković, portugal, slovenija, Bog, slovenija, slovenac Mađar, u18, portugal, bronca Njemačka, slovenija, portugal</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -3509,33 +2264,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Vojo mu je rekao da je pas neurotičan, a baba zločesta i škrta. Čekala ga je ispred zgrade, otresajući muštiklu.
-– Kasnite – rekla je i pružila mu povodac. – Ovuda ravno, preko mosta u park. Četrdeset pet minuta i natrag.
-Pas, neka sasvim minijaturna vrsta, krenuo je s nestrpljenjem iz kojeg se vidjelo da je šetače navikao doživljavati kao poslugu. Mrzovoljno je krenuo za njim. Dok nije došao u Pariz, nije ni znao da postoji takvo zanimanje. Kerovođa, kako bi rekao Vojo. A i taj sitni crnogorski kombinator išao mu je sve više na živce, mogao mu je naprosto reći "Vrati mi pare", a ne da ga neprestano ucjenjuje protuuslugama, sve jedna gora od druge. Nije se bojao posla, znao je kad je dolazio da ovdje neće biti odbora za doček, prao je tanjure po restoranima, odrađivao noćne smjene na recepcijama štunden-hotela, radio po autopraonicama, u dostavi… Kad bi ga, u svojim lošijim trenucima, Madelaine upitala zašto nije uspio zadržati ni jedan posao, odgovarao bi: "Zato što onda ne bih upoznao tebe." Ali, pravi odgovor je, naravno, bio složeniji: ono po što je došao bila je jedinstvena energija grada koju je, kao i toliki prije njega, htio pretočiti u vlastiti kreativni uzgon i da nije bio spreman platiti ulaznicu, svaku ulaznicu, ostao bi zauvijek u rodnome vilajetu, povrh starog Griča brda. Usred one matoševske svakidašnje glupe perspektive, među nižerazrednim primjercima vlastite branše koji bi ga, da mogu, utopili u čaši vode.
-Bio je iscrpljen i mamuran. Već druga neprospavana noć, slabe popodnevne nadoknade, alkohol, nemir i kronična, zamorna besparica… I sad još ova karikatura od psa koja ga vuče u park, gdje ih čekaju iste takve karikature pasa i njihovih vlasnika.
-Nije to bio onaj Pariz iz njegovih studentskih ekskurzija, otvoreni grad s još vidljivim tragovima Mitterrandove ere. Ali kad je došao, to mu nije smetalo, dapače. Uspio se bez problema naviknuti na Global South, na mješavinu boja, rasa, jezika; na koncu, ne samo da je očekivao kozmopolitsku gungulu, nego je došao baš zato da se naglavačke baci u tu babilonsku pjenu u kojoj je tražio lijek ne samo za vlastite kreativne blokade, nego i za cjelokupnu sklerozu Zapada. Ali Bugari su ga baš zatekli; bilo ih je posvuda. Jordanku je već vidio one večeri kod Eliasa, došla je s tim malim mulatom, gitaristom iz Henryjevog studija, kepecom koji bi svaki čas ljubomorno iskrsnuo između njih, a na kraju samo što joj nije zasjeo u krilo. Ni muško ni žensko, ni crn ni bijel, ni dijete ni odrastao; čudesna je lakoća kojom takvi poluproizvodi stječu žensko povjerenje. Ona, pak, nije bila previsoka, građena klasično u najboljem smislu, s pomalo semitskim crtama lica – nije mu poznata lokalna trakijska tipologija, ali bila je više nego zanimljiva, čovjek je teško skidao oči s nje. Pjevala je izvanredno, čak i za bugarske standarde, i neodređeno se smiješila i na komplimente i na primjedbe, kao da baš ne razumije jezik. Chanson de la Seine. Sinoć kad je ponovila tu pjesmu i kad je njena interpretacija, tako dosljedna u svojoj unutarnjoj logici, izazvala oduševljenje među studentarijom za šankom, ipak je u njihovom raspoloženju naslutio jedan nekritički ton zbog kojeg je neke stvari morao staviti na svoje mjesto. Čim netko kaže da su mu lektira Prévert ili Jesenjin, odmah postaje jasno da taj za druge pjesnike nije ni čuo. Za Saint-John Persea ili Michauxa, na primjer. Ili Bjelog. Slični tipovi priproste idolatrije postoje u svim umjetnostima. Prévert je jednostavno banalan, to malo simpatije, ma kako iskrene, prema socijalizmu i antiklerikalizmu ipak ne može sakriti izvorno malograđansku prirodu njegove inspiracije: trivijalna melodrama koja običnim riječima dira obična srca, poezija upravo vulgarno nediskurzivna. Chanson? Dječja brojalica koju je u ovoj prilici izvukla samo njena jedinstvena interpretacija. I sam pojam "talenta" – na tu je temu u Zagrebu vodio nebrojene bitke – duboko je malograđanski, jeftino romantičarski mišljen. Ponekad izravno antiintelektualan. Htio je (za njeno dobro) izvesti analizu od početka do kraja, u punoj dedukciji, ali onda se pojavio taj Thierry, producent, kustos, izdavač, sponzor, što li već, ukratko bourgeois s lovom – i s nekoliko boca čileanskog chardonnaya – pa se nevoljko zaputio za njima do Henryja. Tamo je pokušao nastaviti razgovor, ali su ga naprosto ignorirali. Jordanka je otpjevala nekoliko pjesama Françoise Hardy, zatim neku bugarsku narodnu i nešto od Jobima, gnom je pikao po gitari i sisao joint. Elias se, naravno, odmah ustrčao oko mecene… Ali, ako su očekivali da će se skanjivati, morao ih je razočarati. Natakao si je kao da toči iz vlastitog vinograda, da je pri ruci bilo mineralne, smućkao bi si jedan demonstrativni gemišt. Uostalom, što da radi? Stvari su mu ionako ostale kod Madelaine, ukoliko ih već nije pobacala kroz prozor, a tip s kojim je dijelio sobu, neki Vojkov kamerad sa Žabljaka, znao je razgovarati samo o getribama. Pred zoru, kad se društvance razišlo (Jordanka mu je na odlasku ipak dobacila jedan utješni pogled) odlučio je naći neki bistro na Quayu i popiti kavu prije nego se zaputi prema toj babi u Rue Beautreillis.
-Došli su do mosta, jednog od onih s beskrajnim balustradama, a pseto je, čini se, kanilo zapišati svaki stupić. Rijeka je ispod njih tekla neprozirna pod oštrim jutarnjim suncem, baš kao na kičastim reprodukcijama što ih je Madelaine lijepila na zid iznad kreveta. Pokušao je životinju odvući prema sredini mosta i tako se povodcem upetljao u čopor djece u svijetlom kaftanu i zamalo srušio njihovu majku. Ili što se već nalazilo u tom basetnom zamotuljku. Zagraktali su puni neprijateljstva. Iskustvo ga je poučilo da ne reagira. Taman kad smo se počeli rješavati religije, te apšisale srednjovjekovne aveti, eto ti još oporije i primitivnije varijante. I to gdje? U samoj metropoli sekularizma. Mašala! Treba otići iz ovog provincijalnog spektakla, još uvijek punog narcističke samouvjerenosti "centra zbivanja", iz ove operetne Lutecije koju više ne opravdava nikakva avangarda. Bude li se ikad igdje ponovila šansa iz šezdeset i osme, to se sasvim sigurno neće desiti u Parizu. Uska varoš, uski ljudi. I histerični psi. Postoji li još neko mjesto pod suncem gdje se umjetnička praksa može oteti iz kandži buržoaskog konformizma, gdje umjetnost još igra neku ulogu u društvenoj transformaciji, na putu prema onome čemu se nekad klicalo po ovim istim bulevarima? Liberté! Egalité!... Treba otići u London, New York, možda na Kubu. Jer pusta zemlja Evrope, jalovo tkivo Rima, Amsterdama, Barcelone, svjedoči da su pokondireni prekupci poput Thierryja već isisali svaku artističku supstanciju, ostaviviši iza sebe muzeje, galerije i slične mrtvačnice. Berlin možda izdrži još koju godinu... Da mu je samo Jordanku dobiti sat-dva nasamo, iščupati je iz tog mediokritetskog ansambla. Djelovala je tako uravnoteženo, kao da nema oluje koju ne bi mogao smiriti njen tamni, nujni alt. Mir! Da, morao je oko sebe najprije stvoriti sklad da bi uopće bio u stanju stvoriti išta drugo…
-U tom času pseto ga ponovo trzne prema žardinjeri, tako da je jedva ostao na nogama. Skratio je povodac i visoko ispružio ruku, pseto je pokušalo protestirati, ali već iduće sekunde vitlao ga je iznad sebe, jedan, drugi, treći krug, a zatim, uhvativši punu rotaciju, pustio da zajedno s povodcem u visokom luku odleti preko balustrade. Nije se ni obazro kad je taj vrtolet pljusnuo u Seinu i kad je malo pjene na površini nestalo pod mostom.
-O autoru
-Ratko Cvetnić rođen je 1957. godine, objavio je pet proznih naslova, od kojih su neki dobili ugledne nagrade. Priča "Zima u provinciji" uvrštena je u Večernjakovu antologiju "50 godina, 50 priča" 2015., a priča "Carpaccio" dobila je treću nagradu u Večernjakovu natječaju za kratku priču "Ranko Marinković" 2020. godine.</t>
+          <t>vojo reći pas neurotičan baba zločest škrta čekati ispred zgrada otresati muštikla kasniti reći pružiti povodac ovud ravno preko most park četrdeset pet minuta natrag pas sasvim minijaturan vrsta krenuti nestrpljenje koji vidjeti šetač navići doživljavati posluga mrzovoljno krenuti dok doći pariz znati postojati takav zanimanje kerovođa reći vojo sitan crnogorski kombinator ići mnogo živca moći naprosto reći vratiti para neprestano ucjenjivati protuusluga gora drugi bojati posao znati kad dolaziti ovdje htjeti odbor doček prati tanjura restoran odrađivati noćni smjena recepcija raditi autopraonicam kad svoj loš trenutak madelaina upitati zašto uspjeti zadržati jedan posao odgovarati zato što onda upoznati prav odgovor naravno složen što doći jedinstven energija grad tolik htjeti pretočiti vlastit kreativan uzgon spreman platiti ulaznica svaki ulaznica ostati zauvijek rodnome vilajet povrh star grič brdo usred onaj matoševski svakidašnji glup perspektiva među nižerazredan primjerc vlastit branša moći utopiti čaš voditi iscrpljiti mamuran već drugi neprospavan noć slab popodnevan nadoknada alkohol nemir kroničan zamoran sad još karikatura pas vući park gdje čekati isti takav karikatura pas njihov vlasnik onaj pariz njegov studentski ekskurzija otvoren grad još vidljiv trag mitterrandov era kad doći smetati dapače uspjeti bez problem naviknuti global south mješavina boja rasa jezik konac očekivati kozmopolitski gungula doći baš zato naglavačke baciti babilonski pjena koji tražiti lijek vlastit kreativan blokada cjelokupan skleroza zapad bugari baš zateći posvuda jordanka već vidjeti onaj večer kod elias doći taj mali mulat gitarist henryjevi studij kepecom svaki čas ljubomorno iskrsnuti između kraj što zasjesti krilo muški ženski crn bijel dijete odrastati čudesan lakoća koji takav poluproizvod stjecati ženski povjerenje previsok graditi klasično dobar smisao pomalo semitski crta lice poznat lokalan trakijski tipologija mnogo zanimljiv čovjek teško skidati oči on pjevati izvanredno čak bugarski standard neodređeno smiješiti kompliment primjedba baš razumjeti jezik chanson de la seini sinoć kad ponoviti pjesma kad njen interpretacija dosljedan svoj unutarnj logica izazvati oduševljenje među studentariji šank ipak njihov raspoloženje naslutiti jedan nekritički ton zbog koji neki stvar morati staviti mjesto čim kazati lektirati prévert jesenjin postajati jasno drugi pjesnik čuti persea michauxa primjer bjel sličan tip priprost idolatrija postojati sav umjetnost prévert jednostavno banalan malo simpatija ma iskren prema socijalizam antiklerikalizam ipak moći sakriti izvorno malograđanski priroda njegov inspiracija trivijalan melodra običan riječ dirati obični srce poezija upravo vulgaran nediskurzivan chanson dječji brojalica ovaj prilica izvući njen jedinstven interpretacija pojam talent tema Zagreb voditi nebrojen bitka duboko malograđanski jeftin romantičarski mišljen ponekad izravno antiintelektualan htjeti njen dobro izvesti analiza početak kraj pun dedukcija onda pojaviti thierry producent kustos izdavač sponzor što već ukratko bourgeois lov nekoliko boca čileanski chardonnay nevoljko zaputiti henryja tamo pokušati nastaviti razgovor naprosto ignorirati jordanka otpjevati nekoliko pjesma françoise hardy zatim bugarski narodni nešto job gna pikati gitara sisati joint elias naravno ustrčati oko očekivati htjeti skanjivati morati razočarati nataći točiti vlastit vinograd pri ruka mineralan smućći jedan demonstrativan gemišt uostalom što raditi stvar ionako ostali kod madelaina ukoliko već pobacati prozor tip koji dijeliti soba Vojkov kamerad žabljakati znati razgovarati getriba pred zora kad društvanac razići jordanka odlazak ipak dobaciti jedan utješan pogled odlučiti naći bistro quay popiti kava zaputiti prema baba rue Beautreillis doći most jedan onaj beskrajan balustradam pseto činiti kaniti zapišati svaki stupić rijeka ispod teći neproziran oštar jutarnji sunce baš kičastim reprodukcija što madelaina lijepiti zid iznad krevet pokušati životinja odvući prema sredina most povodcem upetljati čopor dijete svijetl kaftan zamalo srušiti njihov majka što već nalaziti taj basetan zamotuljka zagraktati pun neprijateljstvo iskustvo poučiti reagirati taman kad početi rješavati religija apšisati srednjovjekovni avet eto još opor primitivan varijanta gdje sam metropoli sekularizam mašati trebati otići ovaj provincijalan spektaći još uvijek pun narcistički samouvjerenost centar zbivanje ovaj operetni lutecija mnogo opravdavati nikakav avangard biti ikad igdje ponoviti šansa šezdeset osme sasvim sigurno htjeti desiti parizu uski varoš uski čovjek histeričan ps postojati još neki mjesto sunce gdje umjetnički praksa moći oteti kandži buržoaski konformizam gdje umjetnost još igrati uloga društven transformacija put prema onaj što nekad klicati ovaj isti bulevar Liberté egalité trebati otići London New york možda kub pust zemlja evropa jalov tkivo ri amsterda barcelona svjedočiti pokondiren prekupac poput thierryja već isisati svaki artistički supstancija ostaviviši iza muzej galerija sličan mrtvačnica Berlin možda izdržiti još godina jordanka dobiti nasamo iščupati taj mediokritetski ansambal djelovati uravnoteženo oluja moći smiriti njen taman nujan alt mir morati oko najprije stvoriti sklad uopće stanje stvoriti išta taj času pseto ponovo trznuti prema žardinjer jedva ostati noga skratiti povodac visoko ispružiti ruka pseto pokušati protestirati već idući sekunda vitlati iznad jedan drugi treći krug zatim uhvatiti pun rotacija pustiti zajedno povodcem visokom luka odletiti preko balustrada obazro kad vrtolet pljusnuti seina kad malo pjena površina nestati most autor ratko cvetnić roditi godina objaviti pet prozan naslov koji dobiti ugledan nagrada priča zima provincija uvrštena večernjakov antologija 50 godina 50 priča priča carpaccio dobiti treći nagrada večernjakovu natječaj kratak priča ranko marinković godina</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -3546,12 +2280,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>baba zločest, pas, Pariz, Kerovođa, Vojo, Madelaina, Griča brdo, Pariz, Mitterrandove, Global South, Zapad, Bugari, Jordanka, Elias, Henryjev, Bijel, Chanson de la Seine, Prévert, jesenjin, Saint - John Persea, Michauxa, Bjel, Prévert, Chanson, Zagreb, Thierry, Henry, Jordanka, Françoise Hardy, Jobima, Elias, Madelaina, Vojkov, Jordanka, Quay, Rue Beautreillis, pseto, Rijeka, Madelaina, kaftan, Lutecija, Pariz, Uska varoš, London, New York, Kuba, Evropa, jalovo, Rim, Amsterdama, Barcelone, Thierry, Berlin, Jordanka, nujan, Sein, Ratko Cvetnić, Večernjakov antologija, Carpaccio, Večernjakovo, Ranko Marinković</t>
+          <t>henryjevi studij, chanson de la, Zagreb, françoise hardy, Vojkov, Beautreillis, balustradam pseto, Avangard, parizu, varoš, London New, thierryja, Berlin, cvetnić, Carpaccio, ranko Marinković</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3561,31 +2295,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kandidatkinja prošle sezone 'Braka na prvu' Hedviga Tandara podijelila je na svom Instagramu podijelila je jednu fotografiju s mora i napisala kako je u svim životnim periodima bila najsretnija u srpnju i kolovozu.
-- Ja ne znam u čemu je stvar s ovim krajem sedmog i početkom osmog mjeseca, ali sam redovno baš tada, evo već godinama najsretnija. Vrtjela sam kalendar ima nekoliko godina unazad i najljepše uspomene su mi baš iz ovog perioda. Smijem se baš onako da mi zubići izlaze dok se prisjećam kako sam neke sretne trenutke pokušala sakriti jer nisam mogla vjerovati da su istiniti i da razbijaju moj začarani krug poznatih i ustaljenih načina ponašanja u međusobnim odnosima, a neki su bili bas ispred nosa i samo sam trebala dozvoliti ljudima da mi pokažu kako je lijepo biti autohtona Ti i da, premda tvoj tijek svijesti malo tko može pratiti, nećeš nikada biti ono nešto što se prodaje velikoj masi. Nije da to ne možeš. - napisala je i nastavila:
-VEZANI ČLANCI
-- To je tako jednostavno i plitko i površno i stane u jednu riječ. Nedorečeno. Radije ćeš pisati tekst sjedeći na istrošenim sandalama, dok ti čempres bode leđa, dok sakrivaš koljeno laktom, da ti bedro dere kamen, da ti pete traže masnu kremu prije spavanja, da desna lopatica sagorijeva, da ti se vlasi ni ne trude biti počešljane, a pojedeni ruž ima okus grožđa kojeg nosiš gdje te nitko neće naći. A probala si biti oni. Ipak si rođena da budeš slana i da ne budeš dio njih. Takva si i limitirano si izdanje. Koje je posebno sretno s prelaskom srpnja na kolovoz.
-Nedavno je pričala i o svom zdravlju i dijagnozi epilepsije te je terapiji zbog koje mora donijeti teške životne odluke i rekla je kako se loše osjeća. - Loše. Najiskrenije, odgovor je jako loše. Prvotni plan je bio da mi novu terapiju uvedemo do 23. kolovoza. Postoje teme o kojima mi je lakše pričati i one o kojima mi je dosta teže. Nemam problema govoriti o svom stanju - epilepsiji. Kad pokušamo uvesti novu terapiju da bi mi bilo bolje, ne ide na bolje. Osjećam kako mi je teže, kako mi se grlo steže - ispričala je Hedviga u razgovoru za RTL.
-Otkrila je kako se morala suočiti s dosta težom terapijom koja nije preporučljiva za žene u reproduktivnoj dobi. - Morala sam se suočiti s time ako koristim tu novu terapiju da ću se stvarno morati pozdraviti s tom idejom da ću imati djecu, da to poglavlje zatvaram u potpunosti kao opciju koliko god sam godinama govorila da to ne dolazi u obzir za mene. Ovo je baš točka na i. Moram birati hoću li napraviti nešto za svoje zdravlje ili hoću li jednog dana biti u mogućnosti roditi donekle zdravo dijete. Nažalost, morala sam donijeti tu odluku. Bilo bi mi lakše odlučiti se između lijekova i operacije nego ovoga. Na neki način spašavam sebe - rekla je Hedviga.
-VIDEO Joško Lokas o neuspjehu emisije Marka Tolje: Mislim da je to i prije bilo osuđeno na propast</t>
+          <t>kandidatkinja prošli sezona prvi hedvig tandar podijeliti instagram podijeliti jedan fotografija morati napisati sav životan periode sretan srpanj kolovoz znati što stvar ovaj krajem sedmi početkom osmog mjesec redovno baš evo već godina sretan vrtjeti kalendar imati nekoliko godina unazad najljepše uspomen baš ovaj period smijem baš onako zubić izlaziti dok prisjećati neki sretan trenutka pokušati sakriti moći vjerovati istiniti razbijati začaran krug poznat ustaljeni način ponašanje međusoban odnos bas ispred nos trebati dozvoliti čovjek pokazati lijepo autohton premda tijek svijest malo tko moći pratiti nećeš nikada nešto što prodavati velik masa moći napisati nastaviti vezan članak jednostavno plitko površno stati jedan riječ nedorečeno rado ćeš pisati tekst sjedeći istrošen sandala dok čempres boditi leđa dok sakrivati koljeno lakt bedro dera kamen peta tražiti masan krema spavanje desni lopatica sagorijevati vlas truditi počešljati pojeden ruž imati okus grožđ koji nosišti gdje nitko htjeti naći probala ipak roditi budeš slan budeš dio takav limitiran izdanje posebno sretno prelasak srpanj kolovoz nedavno pričati zdravlje dijagnoza epilepsija terapija zbog morati donijeti težak životan odluka reći loše osjećati loše najiskrean odgovor jako loše prvotan plan nov terapija uvedemo kolovoz postojati tema lako pričati onaj dosta teško nemati problem govoriti stanje epilepsija kad pokušati uvesti nov terapija dobro ići dobro osjećati težiti grlo stežati ispričati hedviga razgovor rtl otkriti moral suočiti dosta težom terapija preporučljiv žena reproduktivni dob morati suočiti taj koristiti nov terapija htjeti stvarno morati pozdraviti taj ideja htjeti imati dijete poglavlje zatvarati potpunost opcija koliko god godina govoriti dolaziti obzir ovaj baš točka morati birati hoću napraviti nešto zdravlje hoću jedan dan mogućnost roditi donekle zdrav dijete nažalost morati donijeti odluka lako odlučiti između lijek operacija ovaj način spašavati reći hedviga video joško lokas neuspjeah emisija marka tolje misliti osuđeno propast</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -3596,12 +2311,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hedviga Tandara, Instagram, Hedviga, RTL, Hedviga, Joško Lokas, Marko Tolja</t>
+          <t>Joško Lokas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3611,50 +2326,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMAG, 25. srpnja 2023. (Hina) - Marin Čilić se porazom (6-4, 6-3) od talijanskog kvalifikanta Flavija Cobollija u prvom kolu Plava Laguna Croatia Opena, vratio na ATP Tour nakon šestomjesečnog izbivanja zbog ozljede koljena, a unatoč porazu nije bio nezadovoljan onime što mu je ovaj meč donio.
-	"Koljeno je izdržalo jako dobro i to je dosta pozitivno. Umag je uvijek bio dosta težak turnir, pogotovo fizički. To se i danas pokazalo. Bilo je vlažno, dosta teški uvjeti za igrače kao što sam ja, koji igraju malo ofenzivnije. Cobolli je bio dosta dobar na nogama, dosta dobro posložen atletski i nije davao puno. Pozitivan sam što sam odigrao fizički dosta težak meč i izdržao ga na dobrom nivou", rekao je povratnik u Stella Maris, umaški pobjednik iz 2012.
-Jedan izgubljen servis koštao ga je gubitka prvog seta, a Cobolli (ATP - 148.) je do 'breaka' došao i na početku drugog seta. Čilić je spriječio da Talijan povede 3-0 s dva 'breaka' prednosti, a onda je nastupio 20-minutni kišni prekid. Talijan nije popustio i nakon jednog sata i 55 minuta igre stigao je do najveće pobjede u karijeri. Imao je Marin prilike za izjednačenje na 2-2, a po povratku na teren i za 3-3, ali su sve ostale neiskorištene.
-"Bilo je šansi, ali se vidjelo u tim nekim situacijama da mi fali mečeva, da ih iskoristim. Moram priznati da je on odigrao jako dobro u bitnim trenucima. Bio je hrabar, ofenzivan, vidjelo se da su mu uvjeti išli na ruku. Odigrao je veoma solidno od početka do kraja. Tražio sam načine. Isteklo je vrijeme, a nisam uspio pronaći rješenje. Nadam se da će od ovoga sve ići na bolje."
-Kad bi mogao ponovno odigrati taj meč, Marin bi izabrao drugačiji termin.
-"Igrao bih po danu, jer su ipak malo življi uvjeti, bilo bi mi lakše. Mislim da sam u drugom setu malo više pustio ruku. No, bio sam u rezultatskom zaostatku. Bilo je par situacija, hoću li se vratiti ili ne, a prelomilo se na njegovu stranu. Zadnjih pet, šest gemova je bila borba, i psihička i fizička, tako da sam s tim zadovoljan. U prvom setu sam napravio nekoliko taktičkih grešaka, strateških. Prvi je meč, moram i sebi dati prostora za pogrešku, ali na kraju, kad podvučem crtu - nije bilo loše", zaključio je Marin na odlasku iz Umaga i prema novim izazovima.
-"Volio bih igrati još jedan turnir na zemlji. Kitzbuehel je jedna opcija, ali tamo nisam u glavnom turniru. Ako to ne uspije, ići ću u Toronto."
-ATP Umag - 1. kolo
-Flavio Cobolli (Ita) - Marin Čilić (Hrv) 6-4, 6-3
-Dino Prižmić (Hrv) - Duje Ajduković (Hrv) 6-1, 6-2
-Alexei Popyrin (Aus) - Benjamin Bonzi (Fra) 6-4, 7-5
-Dominic Thiem (Aut) - Facundo Bagnis (Arg) 6-4, 7-5
-Taro Daniel (Jap) - Martin Landaluce (Špa) 1-6, 7-5, 6-2
-</t>
+          <t>umag srpanj 2023 hin Marin čilić poraz talijanski kvalifikant flavija cobollij prvi kolo plav lagun croatia open vratiti atp tour šestomjesečan izbivanje zbog ozljeda koljen unatoč poraz nezadovoljan onime što ovaj meč doniti koljeno izdržati jako dobro dosta pozitivan umag uvijek dosta težak turnir pogotovo fizički danas pokazati vlažno dosta tešak uvjet igrač što igrati malo ofenzivno cobolli dosta dobar noga dosta dobro posložiti atletski davati puno pozitivan što odigrati fizički dosta težak meč izdržati dobar nivo reći povratnik stella maris umaški pobjednik 2012 jedan izgubliti servis koštati gubitak prvi set cobolli atp 148 doći početak drugi set čilić spriječiti talijan povesti dva prednost onda nastupiti kišni prekid talijan popustiti jedan sat 55 minuta igra stići velik pobjeda karijera imati marin prilika izjednačenje povratak teren ostali neiskorišten šansa vidjeti taj neki situacija fati mečeva iskoristiti morati priznati odigrati jako dobro bitan trenutak hrabar ofenzivan vidjeti uvjet ići ruka odigrati veoma solidno početak kraj tražiti način istekli vrijeme uspjeti pronaći rješenje nadati htjeti ovaj ići dobro kad moći ponovno odigrati meč marin izabrati drugačiji termin igrati dan ipak malo življ uvjet lako misliti drugi set malo mnogo pustiti ruka rezultatski zaostatak par situacija hoću vratiti prelomilo njegov strana zadnji pet šest gem borba psihički fizički tim zadovoljan prvi set napraviti nekoliko taktički grešak strateški prvi meč morati dati prostor pogreška kraj kad podvučem crta loše zaključiti marin odlazak umaga prema nov izazov voliti igrati još jedan turnir zemlja kitzbuehel opcija tamo glavni turnir uspjeti ići htjeti toronto atp umag kolo flaviti cobolli ito Marin čilić hrv dini prižmić hrv divati ajduković hrv Alexei popyrin Aus Benjamin bonzi fra dominic thiem aut facundo Bagnis Arg taro daniel jap martin landaluce špa</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Prikupljeni uzorci će nam reći priču o geološkom razvoju istraživanog područja, ali i da li je možda bilo života na Marsu, kaže Tanja Bosak, profesorica geobiologije na prestižnom MIT-u u Bostonu.
-Spoznaja da je Zemlja jedina planeta za koju znamo sa životom utjecala je na to da se dr. Tanja Bosak, profesorica geobiologije na prestižnom Massachusetts Institute of Technology (MIT) u Bostonu (Sjedinjene Američke Države), počne baviti ovom interdisciplinarnom naukom. Sada je i dio znanstvenog tima Američke svemirske agencije (NASA) u misiji Mars 2020 kojem je zadatak prikupiti uzorke s te planete, a koje će znanstvena zajednica analizirati po povratku rovera Perseverance na Zemlju.
-„Ta prisutnost i rasprostranjenost života na Zemlji je jedna od osnovnih karakteristika koje mi koristimo kada opisujemo kakva je to Zemlja. Reći da je Zemlja Zemlja, bez života, to jednostavno nije isti planet“, govori Bosak.
-Dodaje da se danas mnogo toga zna o nastanku planete Zemlje i cijelog Sunčevog sistema.
-„Znamo kada se to desilo, u osnovnim crtama kako se to desilo, zašto su planeti nastali. Naravno, ima nekih pitanja o nastanku velikih planeta kao što je Jupiter, da li su nastale tu gdje su danas ili možda malo dalje od Sunca, ali mi zapravo znamo jako puno iz raznih uzoraka koji su došli, na primjer meteorita, biokemijskih istraživanja. Tako da sam postanak Sunčevog sustava koji uključuje planetu, znamo puno. Ono što ne znamo je kako i kada je nastao život na Zemlji“, kaže sagovornica.
-Govoreći o Zemljinoj površini, objašnjava da se Zemlja mijenja sve brže i to obično zbog ljudskog utjecaja te da je jedno od osnovnih pitanja u geobiologiji kako je život utjecao na Zemlju i kako procesi koji se odvijaju na raznim planetima mogu utjecati na evoluciju života.
-„Na primjer, kako vulkani, količina vode na Zemlji, klima, kisik utječu na dalji razvoj života. Mi u nekim najstarijim stijenama koje imamo sa Zemlje koje su oko 3,5 milijarde godina stare vidimo tragove ranog života. Znamo da se život počeo dosta rano razvijati, ali ne znamo koliko je tom životu trebalo da postane rasprostranjen. I ono što isto ne znamo, nemamo nikakve tragove života na Zemlji od prije 3,5 milijarde godina zato što nema sedimentnih stijena koje su toliko stare. Jednostavno, na Zemlji se sve odroni ili ode pod tektonske ploče tako da mi nemamo zapis više.“
-Prve stijene s Marsa
-Kako je sada uključena u NASA-inu misiju Mars 2020 navodi da je njena uloga vezana za rover Perseverance kojim se skupljaju uzorci raznih stijena i tla s Marsa, a koji će znanstvena zajednica koristiti da traži tragove života na toj planeti.
-„Kada se rover vrati na Zemlju, ti uzorci će biti korišteni za istraživanje procesa na Marsu, za istraživanje Marsa kao planete koja se može nastaniti jer su neke od tih stijena bile stvorene u prisutnosti vode, kad je davno bilo vode na Marsu. To su stijene koje potječu iz okoliša koji bi danas na Zemlji definitivno mogli podržavati život. I ti uzorci kada se donesu na Zemlju, što će se desiti za više od deset godina, u njima će se, između ostalog, tražiti tragovi života na Marsu. Pričamo o stijenama koje su starije od 3,5 milijarde godina, dakle puno starije od velike većine onih koje imamo na Zemlji. Mars nam pruža priliku da tražimo život koji je raniji od bilo čega što možemo naći u tragovima na Zemlji“, priča Bosak.
-NASA raspolaže svim informacijama za Perseverance rover, koliko je prešao kilometara, odnosno koliko je udaljen od početne tačke, što se može i pratiti.
-„Instrumenti na Perseverance roveru svi rade jako dobro i već smo skupili dosta uzoraka stijena, uključujući prve stijene s Marsa koje su bile položene u prisutnosti vode, što do sada nismo nikad imali i što nam zbilja jednog dana može dati uvid u vrijeme kada je voda tekla površinom Marsa, kada nije bio toliko suh i negostoljubiv. Do sada smo skupili neke stijene koje su jako uzbudljive velikom dijelu znanstvene zajednice“, kaže sagovornica.
-Ističe kako Perseverance rover nastavlja svoju misiju te je sletio u krater Jezero u kojem je nekad bilo jezero, pa je baš zbog toga izabran kao mjesto slijetanja.
-„Sada se rover polako miče prema rubu tog kratera i dolazi do jednih zanimljivih stijena koje su nastale u prisutnosti vode i koje bi mogle imati puno karbonata koji su slični vapnencu na Zemlji. Onda će se maknuti do ruba tog kratera, izaći iz njega i nastaviti se kretati po terenu koji je još stariji od samog kratera koji sadrži neke tipove stijena koje do sada nikad nismo ni vidjeli.“
-Puno interesa za ljudski let na Mars
-Prema njenim riječima, do sada prikupljeni uzorci su otprilike veličine olovke, a to opet zavisi uzorka, tipa stijene koja se izuzima jer neke stijene se raspadnu, dok su neke onako čvršće.
-„Dužine uzoraka su od šest do osam centimetara, a široki su malo više od jednog centimetra. Do sada smo uzimali po dva uzorka jer smo neke od tih duplikata već položili na površinu Marsa, prije nego što smo se počeli kretati po delti, odnosno sedimentnim stijenama koje su nam zapravo i rekle da je tu nekoć bila voda. Pola tih uzoraka je ostalo tamo i mi smo se uspeli uz deltu i prikupili još više uzoraka. Imamo puno uzoraka vulkanskih stijena, sedimentnih stijena i nastavljamo ih skupljati. Grupno, ti uzorci će nam reći priču o geološkom razvoju cijelog tog područja. Sedimentni uzorci pogotovo će nam moći reći da li je možda bilo života na Marsu“, napominje Bosak.
-Naglašava da su uzorci s Marsa stariji od bilo čega što mi imamo na Zemlji.
-„Kada mi gledamo stare stijene na Zemlji, koje su recimo od 3,5 milijarde godina, one su prerađene, one su bile ukopane ispod kilometara drugih stijena, izložene velikim temperaturama i tlakovima, one su bile odronjene i razne tekućine su prolazile kroz njih. Tako da je jako teško tražiti tragove života iz sve te povijesti koje su te zemaljske stijene iskusile. A na Marsu nema toliko vode, nije bilo te stalne erozije, nema tektonskih ploča, tako da je utjecaj tih naknadnih procesa tamo puno blaži pa stoga imamo puno veću šansu naći nešto u njima ako je nečega bilo. Znači, ako je bilo života na Marsu i ostaju tragovi, ti tragovi nemaju istu šansu biti izbrisani kao tragovi života na Zemlji“, obrazlaže sagovornica.
-Poručuje da ljudski let na Mars jako zavisi o misiji Perseverance rovera, i cijele kampanje povratka uzoraka s te planete.
-„Jedan od osnovnih problema koje treba savladati je kako donijeti uzorke, kako donijeti materijal s nekog drugog planeta, koji je zapravo jako velik i puno košta energetski da se nešto lansira s Marsa i onda dovede na Zemlju. Sve to moramo prevladati, da bi mi ljude mogli slati na Mars i onda ih vratiti na Zemlju. Prije nego što ne donesemo uzorke s Marsa, sigurno neće biti ljudskog leta. Zanimljivo, ima puno interesa za ljudski let na Mars tako da se ne bi čudila da se u sljedećih par decenija tako nešto i desi, ako nas klimatske promjene sve ne pogaze.“
-Nemamo dobar način predviđanja
-Priznaje i da klimatske promjene jako utječu na život na Zemlji, te da je vrlo velik ljudski utjecaj na raznolikost života na Zemlji i stabilnost ekosistema.
-„Kada gledamo tragove prošlog života, recimo u posljednjih 500 milijuna godina od kada imamo životinje, oni nam mogu puno reći o nekim vremenima kada su bile nagle klimatske promjene. Tako da paleontolozi i gledaju na promjenu na tim fosilnim ekosistemima, te traže razne uzroke zašto su i kada promjene desile i kako nam to može pomoći u predviđanju što će se desiti na Zemlji. No, naše klimatske promjene su toliko brze da mi nemamo dobar način predviđanja, nismo dovoljno opremljeni da znamo što će se desiti, a puno toga je i u politici. Nije do znanosti, nego do politike“, tvrdi Bosak.
-Zaključuje kako pseudoznanost otežava posao iskusnim znanstvenicima što je očito jedan globalni fenomen.
-„Svi mi koji smo znanstvenici, bavimo se znanošću zato što želimo naći najbolje objašnjenje za nešto što nas zanima i za nešto što je ljudsko iskustvo, iskustvo dobrog planeta i zapravo želimo znati kako stvari rade. A kad postoji pseudoznanost i ljudi koji ne znaju ili ih ne zanima da imaju dobre izvore informacija, ili da ih dobro interpretiraju, ljudi koji ne znaju kako povezati A i B da bi donosili dobre zaključke i kada to utječe na politiku, ekonomiju i ponašanje društva, sve je jako korozivno jer umanjuje riječ razuma i stručnosti“, smatra Bosak.</t>
+          <t>prikupljiti uzorak htjeti reći priča geološki razvoj istraživan područje možda život marsu kazati tanje bosak profesorica geobiologija prestižni boston spoznaj zemlja jedini planet znati život utjecati tanje bosak profesorica geobiologija prestižna massachusetts instituta of technology mit bostonu sjedinjen američki država početi baviti ovaj interdisciplinaran nauki sada dio znanstven tim američki svemirski agencija nas misija mars 2020 koji zadatak prikupiti uzorak planeta htjeti znanstven zajednica analizirati povratak rover perseveranac zemlja prisutnost rasprostranjenost život zemlja osnovan karakteristik koristiti opisujemo kakav zemlja reći zemlja zemlja bez život jednostavno isti planet govoriti Bosak dodavati danas mnogo taj znati nastanak planet zemlja cijel sunčev sistem znati desiti osnovan crta desiti zašto planeta nastati naravno imati neki pitanje nastanak velik planet što jupiter nastati gdje danas možda malo daleko sunce zapravo znati jako puno razni uzorak doći primjer meteorit biokemijski istraživanje postanak sunčeav sustav uključivati planet znati puno što znati nastati život zemlja kazati sagovornica govoriti zemljian površina objašnjavati zemlja mijenjati brzo obično zbog ljudski utjecaj osnovan pitanje geobiologija život utjecati zemlja proces odvijati razni planetima moći utjecati evolucija život primjer vulkan količina voditi zemlja klima kisik utjecati dalj razvoj život neki najstariaj stijena imati zemlja oko milijarda godina star vidjeti trag raan život znati život početi dosta rano razvijati znati koliko taj život trebati postati rasprostranjiti što isto znati nemati nikakav trag život zemlja milijarda godina zato što sedimentn stijena toliko star jednostavno zemlja odroni oći tektonski ploča nemati zapis prvi stijena marsa sada uključiti misija mars 2020 navoditi njen uloga vezan rover perseveranac koji skupljati uzorak razni stijena tlo marsa htjeti znanstven zajednica koristiti tražiti trag život planeta rover vratiti zemlja uzorac htjeti korišteni istraživanje proces marsu istraživanje marsa planeta moći nastaniti neki taj stijena biti stvoren prisutnost voditi kad davno voditi marsu stijena potjecati okoliš danas zemlja definitivno moći podržavati život uzorac donesu zemlja što htjeti desiti mnogo deset godina htjeti između ostali tražiti trag život marsu pričati stijena star milijarda godina dakle puno star velik većina onaj imati zemlja mars pružati prilika tražiti život ran što što moći naći tragov zemlja priča bosak nas raspolazati sav informacija perseveranac rover koliko preći kilometar odnosno koliko udaljiti početni tačka što moći pratiti instrument perseveranac rover raditi jako dobro već skupiti dosta uzorak stijena uključivati prvi stijena marsa biti položene prisutnost voditi što sada nikad imati što zbilja jedan dan moći dati uvid vrijeme voda tekla površina marsa toliko suh negostoljubiv sada skupiti neki stijena jako uzbudljiv velik dio znanstven zajednica kazati sagovornica isticati perseveranac rover nastavljati svoj misija sletiti krater jezero koji nekad jezero baš zbog taj izabrati mjesto slijetanje sada rover polako micati prema rub taj krater dolaziti jedan zanimljiv stijena nastati prisutnost voda moći imati puno karbonat sličan vapnenac zemlja onda htjeti maknuti rub taj krater izaći nastaviti kretati teren još star sam krater sadržati neki tip stijena sada nikad puno interes ljudski let mars prema njen riječ sada prikupljiti uzorak otprilike veličina olovka opet zavisiti uzorak tip stijena izuzimati neki stijena raspadnu dok neki onako čvršće dužina uzorak šest osam centimetar široki malo mnogo jedan centimetar sada uzimati dva uzorak neki taj duplikat već položiti površina mars što početi kretati delti odnosno sedimentn stijena zapravo rekti nekoć voda pola taj uzorak ostati tamo uspeti delta prikupiti još mnogo uzorak imati puno uzorak vulkanski stijena sedimentn stijena nastavljati skupljati grupno uzorac htjeti reći priča geološki razvoj cijel taj područje sedimentan uzorac pogotovo htjeti moći reći možda život marsu napominjati bosak naglašavati uzorac marsa star što što imati zemlja gledati star stijena zemlja recimo milijarda godina onaj preraditi onaj biti ukopati ispod kilometar drugi stijena izložiti velik temperatura tlakov onaj biti odronjen razni tekućina prolaziti jako teško tražiti trag život povijest zemaljski stijena iskusiti marsu toliko voditi stalan erozija tektonski ploča utjecaj taj naknadni proces tamo puno blaži stoga imati puno velik šansa naći nešto neče značiti život marsu ostajati trag trag nemati isti šansa izbrisati trag život zemlja obrazlazati sagovornica poručivati ljudski let mars jako zavisiti misija perseveranac rover cijel kampanja povratak uzorak planet jedan osnovan problem trebati savladati donijeti uzorak donijeti materijal drugi planet zapravo jako velik puno koštati energetski nešto lansirati marsa onda dovesti zemlja morati prevladati čovjek moći slati mars onda vratiti zemlja što donesemo uzorke marsa sigurno htjeti ljudski let zanimljiv imati puno interes ljudski let mars čuditi sljedeći par decenija nešto desi klimatski promjena nemati dobar način predviđanje priznavati klimatski promjena jako utjecati život zemlja velik ljudski utjecaj raznolikost život zemlja stabilnost ekosistem gledati trag prošli život reći posljednji 500 milijun godina imati životinja moći puno reći neki vrijeme biti nagl klimatski promjena paleontolog gledati promjena taj fosilan ekosistem tražiti razni uzrok zašto promjena desiti moći pomoći predviđanje što htjeti desiti zemlja naš klimatski promjena toliko brz nemati dobar način predviđanje dovoljno opremljen znati što htjeti desiti puno taj politika znanost politika tvrditi Bosak zaključivati pseudoznanost otežavati posao iskusn znanstvenik što očito jedan globalan fenomen znanstvenik baviti znanost zato što željeti naći dobar objašnjenje nešto što zanimati nešto što ljudski iskustvo iskustvo dobar planet zapravo željeti znati stvar raditi kad postojati pseudoznanost čovjek znati zanimati imati dobar izvor informacija dobro interpretirati čovjek znati povezati b donositi dobar zaključak utjecati politika ekonomija ponašanje društvo jako korozivno umanjivati riječ razum stručnost smatrati Bosak</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -3665,12 +2342,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hina, Marin Čilić, Flavija Cobollij, Plav Laguna Croatia Open, ATP Tour, Cobolli, Stella Maris, Cobolli, Čilić, Talijan, Talijan, Marin, Marin, Marin, Umaga, Toronto, ATP Umag, Flaviti Cobolli, Ita, Marin Čilić, hrv, Dino Prižmić, hrv, Duje Ajduković, hrv, Alexei Popyrin, Aus, Benjamin Bonzi, Fra, Dominic Thiem, Facundo Bagnis, Arg, Taro Daniel, Martin Landaluce, Špa</t>
+          <t>Marin čilić, flavija cobollij, stella maris, Marin čilić, ditan prižmić, divati Ajduković, Alexei popyrin Aus Benjamin bonzi fra dominic thiem, Bagnis Arg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Marsu, Tanja Bosak, MIT - u, Boston, zemlja, Tanja Bosak, Massachusetts Instituta of Technology, MIT, Boston, sjedinjen američki država, američki svemirski agencija, NASA, Mars, Perseverance, zemlju, zemlja zemlja, Bosak, zemlja, Sunčevog, Jupiter, Sunce, Sunčevog, Zemljinoj, zemlju, zemlja, zemlja, Marsa, NASA - inu, Mars, Perseverance, Marsa, zemlju, Marsu, Marsa, Marsu, zemlja, zemlju, Marsu, zemlja, Mars, Bosak, NASA, perseverance rover, Perseverance, Marsa, Marsa, Perseverance, Jezero, zemlja, Mars, Marsa, Marsu, Bosak, Marsa, zemlja, zemlja, Marsu, Marsu, Mars, Perseverance, Marsa, zemlju, Mars, zemlju, Marsa, Mars, zemlja, zemlja, Bosak, B, Bosak</t>
+          <t>Massachusetts institut of technology, Bosak, marsa, marsa, marsa, delta, marsa, marsa, marsa, Bosak, Bosak</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3680,31 +2357,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUITO, 25.srpnja (Hina/Reuters) - Ekvadorski predsjednik Guillermo Lasso u ponedjeljak je proglasio izvanredno stanje i policijski sat u tri pokrajine, nakon što je osmero ljudi proteklog vikenda izgubilo život u nasilnim neredima u toj južnoameričkoj zemlji.
-	Izvanredno stanje Lasso je proglasio u pokrajinama Manabi i Los Rios te u gradu Duran, u blizini drugog najvećeg grada u zemlji Guayaquil, dan nakon što je ubijen gradonačelnik obalnog grada Manta Agustin Intriago. 
-Predsjednikov potez također je i odgovor na nerede u zatvoru Penitenciaria del Litoral u Guayaquilu koji uključuju obračune između članova bandi u zatvoru.
-Lasso je u više navrata posezao za proglašavanjem izvanrednog stanja, s obzirom da su nemiri u zatvorima i valovi nasilja česte pojave u Ekvadoru.
-"Ne možemo poreći da je organizirani kriminal prožeo državu, političke organizacije i društvo, to je problem koji nas muči mnogo dulje od jednog desetljeća", izjavio je Lasso nakon sastanka svog kabineta. 
-Izvanredno će stanje biti na snazi 60 dana, dok će se trajanje policijskog sata mijenjati tijekom navedenog razdoblja. 
-U međuvremenu, policija istražuje ubojstvo gradonačelnika Mante, rekao je predsjednik države.
-Najmanje šestero zatvorenika smrtno je stradalo, a njih 11 je ozlijeđeno nakon nedjeljnih nereda, prema podacima upravitelja zatvora u Guayaquilu
-Uz to, zatvorenici u zatvorima Cotopaxi, Azuay, Cañar, El Oro i Napo drže 96 čuvara kao taoce te nastavljaju štrajku glađu koji su započeli 13.srpnja, ne otkrivajući razloge štrajka.
-Zatvorski se sustav u Ekvadoru suočava s brojnim strukturnim problemima već desetljećima, a stopa nasilja je porasla od 2021.godine, od kada je oko 400 osoba ubijeno u svakodnevnim obračunima, što je izazvalo zabrinutost Ujedinjenih naroda .
-</t>
+          <t>quito ekvadorski predsjednik guillermo lasso ponedjeljak proglasiti izvanredan stanje policijski sat tri pokrajina što osmero čovjek protekli vikend izgubiti život nasilan nered južnoamerički zemlja izvanredan stanje Lasso proglasiti pokrajina manaba los rios grad duran blizina drugi velik grad zemlja guayaquil dan što ubiti gradonačelnik obalan grad Manta agustin intriago predsjednikov potez također odgovor nered zatvor penitenciaria Del litoral guayaquilu uključivati obračun između član banda zatvor Lasso mnogo navrat posezati proglašavanje izvanredan stanje obzir nemir zatvor val nasilje čest pojava ekvador moći poreći organiziran kriminal prožeo država politički organizacija društvo problem mučiti mnogo dugo jedan desetljeće izjaviti lasso sastanak kabinet izvanredno htjeti stanje snaga 60 dan dok htjeti trajanje policijski sat mijenjati tijekom naveden razdoblje međuvrijeme policija istraživati ubojstvo gradonačelnik manta reći predsjednik država malo šestero zatvorenik smrtno stradati 11 ozlijeđen nedjeljan nered prema podatak upravitelj zatvor guayaquilu zatvorenik zatvorima cotopaxi azuay cañar el oro napo držati 96 čuvar taoce nastavljati štrajku glađu započeti otkrivati razlog štrajka zatvorski sustav ekvador suočavati brojan strukturan problem već desetljeće stopa nasilje porasti oko 400 osoba ubijiti svakodnevan obračun što izazvati zabrinutost ujedinjen narod</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ekvadorski predsjednik Guillermo Lasso u ponedjeljak je proglasio izvanredno stanje i policijski sat u tri pokrajine, nakon što je osmero ljudi proteklog vikenda izgubilo život u nasilnim neredima u toj južnoameričkoj zemlji.
-Izvanredno stanje Lasso je proglasio u pokrajinama Manabi i Los Rios te u gradu Duran, u blizini drugog najvećeg grada u zemlji Guayaquil, dan nakon što je ubijen gradonačelnik obalnog grada Manta Agustin Intriago.
-Predsjednikov potez također je i odgovor na nerede u zatvoru Penitenciaria del Litoral u Guayaquilu koji uključuju obračune između članova bandi u zatvoru.
-Lasso je u više navrata posezao za proglašavanjem izvanrednog stanja, s obzirom da su nemiri u zatvorima i valovi nasilja česte pojave u Ekvadoru.
-"Ne možemo poreći da je organizirani kriminal prožeo državu, političke organizacije i društvo, to je problem koji nas muči mnogo dulje od jednog desetljeća", izjavio je Lasso nakon sastanka svog kabineta.
-Izvanredno će stanje biti na snazi 60 dana, dok će se trajanje policijskog sata mijenjati tijekom navedenog razdoblja.
-U međuvremenu, policija istražuje ubojstvo gradonačelnika Mante, rekao je predsjednik države.
-Najmanje šestero zatvorenika smrtno je stradalo, a njih 11 je ozlijeđeno nakon nedjeljnih nereda, prema podacima upravitelja zatvora u Guayaquilu
-Uz to, zatvorenici u zatvorima Cotopaxi, Azuay, Cañar, El Oro i Napo drže 96 čuvara kao taoce te nastavljaju štrajku glađu koji su započeli 13.srpnja, ne otkrivajući razloge štrajka.
-Zatvorski se sustav u Ekvadoru suočava s brojnim strukturnim problemima već desetljećima, a stopa nasilja je porasla od 2021.godine, od kada je oko 400 osoba ubijeno u svakodnevnim obračunima, što je izazvalo zabrinutost Ujedinjenih naroda .</t>
+          <t>ekvadorski predsjednik guillermo lasso ponedjeljak proglasiti izvanredan stanje policijski sat tri pokrajina što osmero čovjek protekli vikend izgubiti život nasilan nered južnoamerički zemlja izvanredan stanje Lasso proglasiti pokrajina manaba los rios grad duran blizina drugi velik grad zemlja guayaquil dan što ubiti gradonačelnik obalan grad Manta agustin intriago predsjednikov potez također odgovor nered zatvor penitenciaria Del litoral guayaquilu uključivati obračun između član banda zatvor Lasso mnogo navrat posezati proglašavanje izvanredan stanje obzir nemir zatvor val nasilje čest pojava ekvador moći poreći organiziran kriminal prožeo država politički organizacija društvo problem mučiti mnogo dugo jedan desetljeće izjaviti lasso sastanak kabinet izvanredno htjeti stanje snaga 60 dan dok htjeti trajanje policijski sat mijenjati tijekom naveden razdoblje međuvrijeme policija istraživati ubojstvo gradonačelnik manta reći predsjednik država malo šestero zatvorenik smrtno stradati 11 ozlijeđen nedjeljan nered prema podatak upravitelj zatvor guayaquilu zatvorenik zatvorima cotopaxi azuay cañar el oro napo držati 96 čuvar taoce nastavljati štrajku glađu započeti otkrivati razlog štrajka zatvorski sustav ekvador suočavati brojan strukturan problem već desetljeće stopa nasilje porasti oko 400 osoba ubijiti svakodnevan obračun što izazvati zabrinutost ujedinjen narod</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -3715,45 +2373,27 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>QUITO, Hina, Reuters, Guillermo Lasso, Lasso, Manabi, Los Rios, Duran, guayaquil, Agustin Intriago, Penitenciaria del litoral, Guayaquilu, Lasso, Ekvador, Lasso, Mante, Guayaquilu, Cotopaxi, Azuay, Cañar, El Oro, napo, Ekvador, Ujedinjenih narod</t>
+          <t>guillermo Lasso, Lasso, los rios, Manta agustin intriago predsjednikov, penitenciaria Del, Lasso, ekvador, Lasso, manta, zatvor guayaquilu, cañar el oro, ekvador</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Guillermo Lasso, Lasso, Manabi, Los Rios, Duran, guayaquil, Agustin Intriago, Penitenciaria del litoral, Guayaquilu, Lasso, Ekvador, Lasso, Mante, Guayaquilu, Cotopaxi, Azuay, Cañar, El Oro, napo, Ekvador, Ujedinjenih narod</t>
+          <t>guillermo Lasso, Lasso, los rios, Manta agustin intriago predsjednikov, penitenciaria Del, Lasso, ekvador, Lasso, manta, zatvor guayaquilu, cañar el oro, ekvador</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUITO, 25.srpnja (Hina/Reuters) - Ekvadorski predsjednik Guillermo Lasso u ponedjeljak je proglasio izvanredno stanje i policijski sat u tri pokrajine, nakon što je osmero ljudi proteklog vikenda izgubilo život u nasilnim neredima u toj južnoameričkoj zemlji.
-	Izvanredno stanje Lasso je proglasio u pokrajinama Manabi i Los Rios te u gradu Duran, u blizini drugog najvećeg grada u zemlji Guayaquil, dan nakon što je ubijen gradonačelnik obalnog grada Manta Agustin Intriago. 
-Predsjednikov potez također je i odgovor na nerede u zatvoru Penitenciaria del Litoral u Guayaquilu koji uključuju obračune između članova bandi u zatvoru.
-Lasso je u više navrata posezao za proglašavanjem izvanrednog stanja, s obzirom da su nemiri u zatvorima i valovi nasilja česte pojave u Ekvadoru.
-"Ne možemo poreći da je organizirani kriminal prožeo državu, političke organizacije i društvo, to je problem koji nas muči mnogo dulje od jednog desetljeća", izjavio je Lasso nakon sastanka svog kabineta. 
-Izvanredno će stanje biti na snazi 60 dana, dok će se trajanje policijskog sata mijenjati tijekom navedenog razdoblja. 
-U međuvremenu, policija istražuje ubojstvo gradonačelnika Mante, rekao je predsjednik države.
-Najmanje šestero zatvorenika smrtno je stradalo, a njih 11 je ozlijeđeno nakon nedjeljnih nereda, prema podacima upravitelja zatvora u Guayaquilu
-Uz to, zatvorenici u zatvorima Cotopaxi, Azuay, Cañar, El Oro i Napo drže 96 čuvara kao taoce te nastavljaju štrajku glađu koji su započeli 13.srpnja, ne otkrivajući razloge štrajka.
-Zatvorski se sustav u Ekvadoru suočava s brojnim strukturnim problemima već desetljećima, a stopa nasilja je porasla od 2021.godine, od kada je oko 400 osoba ubijeno u svakodnevnim obračunima, što je izazvalo zabrinutost Ujedinjenih naroda .
-</t>
+          <t>quito ekvadorski predsjednik guillermo lasso ponedjeljak proglasiti izvanredan stanje policijski sat tri pokrajina što osmero čovjek protekli vikend izgubiti život nasilan nered južnoamerički zemlja izvanredan stanje Lasso proglasiti pokrajina manaba los rios grad duran blizina drugi velik grad zemlja guayaquil dan što ubiti gradonačelnik obalan grad Manta agustin intriago predsjednikov potez također odgovor nered zatvor penitenciaria Del litoral guayaquilu uključivati obračun između član banda zatvor Lasso mnogo navrat posezati proglašavanje izvanredan stanje obzir nemir zatvor val nasilje čest pojava ekvador moći poreći organiziran kriminal prožeo država politički organizacija društvo problem mučiti mnogo dugo jedan desetljeće izjaviti lasso sastanak kabinet izvanredno htjeti stanje snaga 60 dan dok htjeti trajanje policijski sat mijenjati tijekom naveden razdoblje međuvrijeme policija istraživati ubojstvo gradonačelnik manta reći predsjednik država malo šestero zatvorenik smrtno stradati 11 ozlijeđen nedjeljan nered prema podatak upravitelj zatvor guayaquilu zatvorenik zatvorima cotopaxi azuay cañar el oro napo držati 96 čuvar taoce nastavljati štrajku glađu započeti otkrivati razlog štrajka zatvorski sustav ekvador suočavati brojan strukturan problem već desetljeće stopa nasilje porasti oko 400 osoba ubijiti svakodnevan obračun što izazvati zabrinutost ujedinjen narod</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Izvanredno stanje Lasso je proglasio u pokrajinama Manabi i Los Rios te u gradu Duran, u blizini drugog najvećeg grada u zemlji Guayaquil, dan nakon što je ubijen gradonačelnik obalnog grada Manta Agustin Intriago.
-Predsjednikov potez također je i odgovor na nerede u zatvoru Penitenciaria del Litoral u Guayaquilu koji uključuju obračune između članova bandi u zatvoru.
-Lasso je u više navrata posezao za proglašavanjem izvanrednog stanja, s obzirom da su nemiri u zatvorima i valovi nasilja česte pojave u Ekvadoru.
-"Ne možemo poreći da je organizirani kriminal prožeo državu, političke organizacije i društvo, to je problem koji nas muči mnogo dulje od jednog desetljeća", izjavio je Lasso nakon sastanka svog kabineta.
-Izvanredno će stanje biti na snazi 60 dana, dok će se trajanje policijskog sata mijenjati tijekom navedenog razdoblja.
-U međuvremenu, policija istražuje ubojstvo gradonačelnika Mante, rekao je predsjednik države.
-Najmanje šestero zatvorenika smrtno je stradalo, a njih 11 je ozlijeđeno nakon nedjeljnih nereda, prema podacima upravitelja zatvora u Guayaquilu
-Uz to, zatvorenici u zatvorima Cotopaxi, Azuay, Cañar, El Oro i Napo drže 96 čuvara kao taoce te nastavljaju štrajku glađu koji su započeli 13.srpnja, ne otkrivajući razloge štrajka.
-Zatvorski se sustav u Ekvadoru suočava s brojnim strukturnim problemima već desetljećima, a stopa nasilja je porasla od 2021. godine, od kada je oko 400 osoba ubijeno u svakodnevnim obračunima, što je izazvalo zabrinutost Ujedinjenih naroda.</t>
+          <t>izvanredan stanje Lasso proglasiti pokrajina manaba los rios grad duran blizina drugi velik grad zemlja guayaquil dan što ubiti gradonačelnik obalan grad Manta agustin intriago predsjednikov potez također odgovor nered zatvor penitenciaria Del litoral guayaquilu uključivati obračun između član banda zatvor Lasso mnogo navrat posezati proglašavanje izvanredan stanje obzir nemir zatvor val nasilje čest pojava ekvador moći poreći organiziran kriminal prožeo država politički organizacija društvo problem mučiti mnogo dugo jedan desetljeće izjaviti lasso sastanak kabinet izvanredno htjeti stanje snaga 60 dan dok htjeti trajanje policijski sat mijenjati tijekom naveden razdoblje međuvrijeme policija istraživati ubojstvo gradonačelnik manta reći predsjednik država malo šestero zatvorenik smrtno stradati 11 ozlijeđen nedjeljan nered prema podatak upravitelj zatvor guayaquilu zatvorenik zatvorima cotopaxi azuay cañar el oro napo držati 96 čuvar taoce nastavljati štrajku glađu započeti otkrivati razlog štrajka zatvorski sustav ekvador suočavati brojan strukturan problem već desetljeće stopa nasilje porasti godina oko 400 osoba ubijiti svakodnevan obračun što izazvati zabrinutost ujedinjen narod</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -3764,48 +2404,27 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>QUITO, Hina, Reuters, Guillermo Lasso, Lasso, Manabi, Los Rios, Duran, guayaquil, Agustin Intriago, Penitenciaria del litoral, Guayaquilu, Lasso, Ekvador, Lasso, Mante, Guayaquilu, Cotopaxi, Azuay, Cañar, El Oro, napo, Ekvador, Ujedinjenih narod</t>
+          <t>guillermo Lasso, Lasso, los rios, Manta agustin intriago predsjednikov, penitenciaria Del, Lasso, ekvador, Lasso, manta, zatvor guayaquilu, cañar el oro, ekvador</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lasso, Manabi, Los Rios, Duran, guayaquil, Agustin Intriago, Penitenciaria del litoral, Guayaquilu, Lasso, Ekvador, Lasso, Mante, Guayaquilu, Cotopaxi, Azuay, Cañar, El Oro, napo, Ekvador, Ujedinjenih narod</t>
+          <t>Lasso, los rios, Manta agustin intriago predsjednikov, penitenciaria Del, Lasso, ekvador, Lasso, manta, zatvor guayaquilu, cañar el oro, ekvador</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.8</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUITO, 25.srpnja (Hina/Reuters) - Ekvadorski predsjednik Guillermo Lasso u ponedjeljak je proglasio izvanredno stanje i policijski sat u tri pokrajine, nakon što je osmero ljudi proteklog vikenda izgubilo život u nasilnim neredima u toj južnoameričkoj zemlji.
-	Izvanredno stanje Lasso je proglasio u pokrajinama Manabi i Los Rios te u gradu Duran, u blizini drugog najvećeg grada u zemlji Guayaquil, dan nakon što je ubijen gradonačelnik obalnog grada Manta Agustin Intriago. 
-Predsjednikov potez također je i odgovor na nerede u zatvoru Penitenciaria del Litoral u Guayaquilu koji uključuju obračune između članova bandi u zatvoru.
-Lasso je u više navrata posezao za proglašavanjem izvanrednog stanja, s obzirom da su nemiri u zatvorima i valovi nasilja česte pojave u Ekvadoru.
-"Ne možemo poreći da je organizirani kriminal prožeo državu, političke organizacije i društvo, to je problem koji nas muči mnogo dulje od jednog desetljeća", izjavio je Lasso nakon sastanka svog kabineta. 
-Izvanredno će stanje biti na snazi 60 dana, dok će se trajanje policijskog sata mijenjati tijekom navedenog razdoblja. 
-U međuvremenu, policija istražuje ubojstvo gradonačelnika Mante, rekao je predsjednik države.
-Najmanje šestero zatvorenika smrtno je stradalo, a njih 11 je ozlijeđeno nakon nedjeljnih nereda, prema podacima upravitelja zatvora u Guayaquilu
-Uz to, zatvorenici u zatvorima Cotopaxi, Azuay, Cañar, El Oro i Napo drže 96 čuvara kao taoce te nastavljaju štrajku glađu koji su započeli 13.srpnja, ne otkrivajući razloge štrajka.
-Zatvorski se sustav u Ekvadoru suočava s brojnim strukturnim problemima već desetljećima, a stopa nasilja je porasla od 2021.godine, od kada je oko 400 osoba ubijeno u svakodnevnim obračunima, što je izazvalo zabrinutost Ujedinjenih naroda .
-</t>
+          <t>quito ekvadorski predsjednik guillermo lasso ponedjeljak proglasiti izvanredan stanje policijski sat tri pokrajina što osmero čovjek protekli vikend izgubiti život nasilan nered južnoamerički zemlja izvanredan stanje Lasso proglasiti pokrajina manaba los rios grad duran blizina drugi velik grad zemlja guayaquil dan što ubiti gradonačelnik obalan grad Manta agustin intriago predsjednikov potez također odgovor nered zatvor penitenciaria Del litoral guayaquilu uključivati obračun između član banda zatvor Lasso mnogo navrat posezati proglašavanje izvanredan stanje obzir nemir zatvor val nasilje čest pojava ekvador moći poreći organiziran kriminal prožeo država politički organizacija društvo problem mučiti mnogo dugo jedan desetljeće izjaviti lasso sastanak kabinet izvanredno htjeti stanje snaga 60 dan dok htjeti trajanje policijski sat mijenjati tijekom naveden razdoblje međuvrijeme policija istraživati ubojstvo gradonačelnik manta reći predsjednik država malo šestero zatvorenik smrtno stradati 11 ozlijeđen nedjeljan nered prema podatak upravitelj zatvor guayaquilu zatvorenik zatvorima cotopaxi azuay cañar el oro napo držati 96 čuvar taoce nastavljati štrajku glađu započeti otkrivati razlog štrajka zatvorski sustav ekvador suočavati brojan strukturan problem već desetljeće stopa nasilje porasti oko 400 osoba ubijiti svakodnevan obračun što izazvati zabrinutost ujedinjen narod</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EKVADORSKI predsjednik Guillermo Lasso jučer je proglasio izvanredno stanje i policijski sat u tri pokrajine, nakon što je osmero ljudi proteklog vikenda izgubilo život u nasilnim neredima u toj južnoameričkoj zemlji.
-Izvanredno stanje Lasso je proglasio u pokrajinama Manabi i Los Rios te u gradu Duran, u blizini drugog najvećeg grada u zemlji Guayaquil, dan nakon što je ubijen gradonačelnik obalnog grada Manta Agustin Intriago.
-Predsjednikov potez također je i odgovor na nerede u zatvoru Penitenciaria del Litoral u Guayaquilu koji uključuju obračune između članova bandi u zatvoru.
-Predsjednik: Organizirani kriminal prožeo je državu, političke organizacije i društvo
-Lasso je u više navrata posezao za proglašavanjem izvanrednog stanja, s obzirom da su nemiri u zatvorima i valovi nasilja česte pojave u Ekvadoru.
-"Ne možemo poreći da je organizirani kriminal prožeo državu, političke organizacije i društvo, to je problem koji nas muči mnogo dulje od jednog desetljeća", izjavio je Lasso nakon sastanka svog kabineta.
-Tekst se nastavlja ispod oglasa
-Izvanredno će stanje biti na snazi 60 dana, dok će se trajanje policijskog sata mijenjati tijekom navedenog razdoblja. U međuvremenu, policija istražuje ubojstvo gradonačelnika Mante, rekao je predsjednik države.
-Čuvari su taoci u četiri zatvora
-Najmanje šestero zatvorenika smrtno je stradalo, a njih 11 je ozlijeđeno nakon nedjeljnih nereda, prema podacima upravitelja zatvora u Guayaquilu
-Uz to, zatvorenici u zatvorima Cotopaxi, Azuay, Cañar, El Oro i Napo drže 96 čuvara kao taoce te nastavljaju štrajku glađu koji su započeli 13.srpnja, ne otkrivajući razloge štrajka.
-Zatvorski se sustav u Ekvadoru suočava s brojnim strukturnim problemima već desetljećima, a stopa nasilja je porasla od 2021.godine, od kada je oko 400 osoba ubijeno u svakodnevnim obračunima, što je izazvalo zabrinutost Ujedinjenih naroda .</t>
+          <t>ekvadorski predsjednik guillermo lasso jučer proglasiti izvanredan stanje policijski sat tri pokrajina što osmero čovjek protekli vikend izgubiti život nasilan nered južnoamerički zemlja izvanredan stanje Lasso proglasiti pokrajina manaba los rios grad duran blizina drugi velik grad zemlja guayaquil dan što ubiti gradonačelnik obalan grad Manta agustin intriago predsjednikov potez također odgovor nered zatvor penitenciaria Del litoral guayaquilu uključivati obračun između član banda zatvor predsjednik organiziran kriminal prožeo država politički organizacija društvo Lasso mnogo navrat posezati proglašavanje izvanredan stanje obzir nemir zatvor val nasilje čest pojava ekvador moći poreći organiziran kriminal prožeo država politički organizacija društvo problem mučiti mnogo dugo jedan desetljeće izjaviti lasso sastanak kabinet tekst nastavljati ispod oglas izvanredno htjeti stanje snaga 60 dan dok htjeti trajanje policijski sat mijenjati tijekom naveden razdoblje međuvrijeme policija istraživati ubojstvo gradonačelnik manta reći predsjednik država čuvar taoci četiri zatvor malo šestero zatvorenik smrtno stradati 11 ozlijeđen nedjeljan nered prema podatak upravitelj zatvor guayaquilu zatvorenik zatvorima cotopaxi azuay cañar el oro napo držati 96 čuvar taoce nastavljati štrajku glađu započeti otkrivati razlog štrajka zatvorski sustav ekvador suočavati brojan strukturan problem već desetljeće stopa nasilje porasti oko 400 osoba ubijiti svakodnevan obračun što izazvati zabrinutost ujedinjen narod</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -3816,47 +2435,27 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>QUITO, Hina, Reuters, Guillermo Lasso, Lasso, Manabi, Los Rios, Duran, guayaquil, Agustin Intriago, Penitenciaria del litoral, Guayaquilu, Lasso, Ekvador, Lasso, Mante, Guayaquilu, Cotopaxi, Azuay, Cañar, El Oro, napo, Ekvador, Ujedinjenih narod</t>
+          <t>guillermo Lasso, Lasso, los rios, Manta agustin intriago predsjednikov, penitenciaria Del, Lasso, ekvador, Lasso, manta, zatvor guayaquilu, cañar el oro, ekvador</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Guillermo Lasso, Lasso, Manabi, Los Rios, Duran, guayaquil, Agustin Intriago, Penitenciaria del litoral, Guayaquilu, Lasso, Ekvador, Lasso, Mante, Guayaquilu, Cotopaxi, Azuay, Cañar, El Oro, napo, Ekvador, Ujedinjenih narod</t>
+          <t>guillermo Lasso, Lasso, los rios, Manta agustin intriago predsjednikov, penitenciaria Del, Lasso, ekvador, Lasso, manta, zatvor guayaquilu, cañar el oro, ekvador</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUITO, 25.srpnja (Hina/Reuters) - Ekvadorski predsjednik Guillermo Lasso u ponedjeljak je proglasio izvanredno stanje i policijski sat u tri pokrajine, nakon što je osmero ljudi proteklog vikenda izgubilo život u nasilnim neredima u toj južnoameričkoj zemlji.
-	Izvanredno stanje Lasso je proglasio u pokrajinama Manabi i Los Rios te u gradu Duran, u blizini drugog najvećeg grada u zemlji Guayaquil, dan nakon što je ubijen gradonačelnik obalnog grada Manta Agustin Intriago. 
-Predsjednikov potez također je i odgovor na nerede u zatvoru Penitenciaria del Litoral u Guayaquilu koji uključuju obračune između članova bandi u zatvoru.
-Lasso je u više navrata posezao za proglašavanjem izvanrednog stanja, s obzirom da su nemiri u zatvorima i valovi nasilja česte pojave u Ekvadoru.
-"Ne možemo poreći da je organizirani kriminal prožeo državu, političke organizacije i društvo, to je problem koji nas muči mnogo dulje od jednog desetljeća", izjavio je Lasso nakon sastanka svog kabineta. 
-Izvanredno će stanje biti na snazi 60 dana, dok će se trajanje policijskog sata mijenjati tijekom navedenog razdoblja. 
-U međuvremenu, policija istražuje ubojstvo gradonačelnika Mante, rekao je predsjednik države.
-Najmanje šestero zatvorenika smrtno je stradalo, a njih 11 je ozlijeđeno nakon nedjeljnih nereda, prema podacima upravitelja zatvora u Guayaquilu
-Uz to, zatvorenici u zatvorima Cotopaxi, Azuay, Cañar, El Oro i Napo drže 96 čuvara kao taoce te nastavljaju štrajku glađu koji su započeli 13.srpnja, ne otkrivajući razloge štrajka.
-Zatvorski se sustav u Ekvadoru suočava s brojnim strukturnim problemima već desetljećima, a stopa nasilja je porasla od 2021.godine, od kada je oko 400 osoba ubijeno u svakodnevnim obračunima, što je izazvalo zabrinutost Ujedinjenih naroda .
-</t>
+          <t>quito ekvadorski predsjednik guillermo lasso ponedjeljak proglasiti izvanredan stanje policijski sat tri pokrajina što osmero čovjek protekli vikend izgubiti život nasilan nered južnoamerički zemlja izvanredan stanje Lasso proglasiti pokrajina manaba los rios grad duran blizina drugi velik grad zemlja guayaquil dan što ubiti gradonačelnik obalan grad Manta agustin intriago predsjednikov potez također odgovor nered zatvor penitenciaria Del litoral guayaquilu uključivati obračun između član banda zatvor Lasso mnogo navrat posezati proglašavanje izvanredan stanje obzir nemir zatvor val nasilje čest pojava ekvador moći poreći organiziran kriminal prožeo država politički organizacija društvo problem mučiti mnogo dugo jedan desetljeće izjaviti lasso sastanak kabinet izvanredno htjeti stanje snaga 60 dan dok htjeti trajanje policijski sat mijenjati tijekom naveden razdoblje međuvrijeme policija istraživati ubojstvo gradonačelnik manta reći predsjednik država malo šestero zatvorenik smrtno stradati 11 ozlijeđen nedjeljan nered prema podatak upravitelj zatvor guayaquilu zatvorenik zatvorima cotopaxi azuay cañar el oro napo držati 96 čuvar taoce nastavljati štrajku glađu započeti otkrivati razlog štrajka zatvorski sustav ekvador suočavati brojan strukturan problem već desetljeće stopa nasilje porasti oko 400 osoba ubijiti svakodnevan obračun što izazvati zabrinutost ujedinjen narod</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>UVEDEN I POLICIJSKI SAT
-Ekvadorski predsjednik Guillermo Lasso u ponedjeljak je proglasio izvanredno stanje i policijski sat u tri pokrajine, nakon što je osmero ljudi proteklog vikenda izgubilo život u nasilnim neredima u toj južnoameričkoj zemlji.
-Izvanredno stanje Lasso je proglasio u pokrajinama Manabi i Los Rios te u gradu Duran, u blizini drugog najvećeg grada u zemlji Guayaquil, dan nakon što je ubijen gradonačelnik obalnog grada Manta Agustin Intriago.
-Predsjednikov potez također je i odgovor na nerede u zatvoru Penitenciaria del Litoral u Guayaquilu koji uključuju obračune između članova bandi u zatvoru.
-Lasso je u više navrata posezao za proglašavanjem izvanrednog stanja, s obzirom da su nemiri u zatvorima i valovi nasilja česte pojave u Ekvadoru.
-"Ne možemo poreći da je organizirani kriminal prožeo državu, političke organizacije i društvo, to je problem koji nas muči mnogo dulje od jednog desetljeća", izjavio je Lasso nakon sastanka svog kabineta.
-Izvanredno će stanje biti na snazi 60 dana, dok će se trajanje policijskog sata mijenjati tijekom navedenog razdoblja.
-U međuvremenu, policija istražuje ubojstvo gradonačelnika Mante, rekao je predsjednik države.
-Najmanje šestero zatvorenika smrtno je stradalo, a njih 11 je ozlijeđeno nakon nedjeljnih nereda, prema podacima upravitelja zatvora u Guayaquilu
-Uz to, zatvorenici u zatvorima Cotopaxi, Azuay, Cañar, El Oro i Napo drže 96 čuvara kao taoce te nastavljaju štrajku glađu koji su započeli 13.srpnja, ne otkrivajući razloge štrajka.
-Zatvorski se sustav u Ekvadoru suočava s brojnim strukturnim problemima već desetljećima, a stopa nasilja je porasla od 2021.godine, od kada je oko 400 osoba ubijeno u svakodnevnim obračunima, što je izazvalo zabrinutost Ujedinjenih naroda .</t>
+          <t>uvesti policijski sat ekvadorski predsjednik guillermo lasso ponedjeljak proglasiti izvanredan stanje policijski sat tri pokrajina što osmero čovjek protekli vikend izgubiti život nasilan nered južnoamerički zemlja izvanredan stanje Lasso proglasiti pokrajina manaba los rios grad duran blizina drugi velik grad zemlja guayaquil dan što ubiti gradonačelnik obalan grad Manta agustin intriago predsjednikov potez također odgovor nered zatvor penitenciaria Del litoral guayaquilu uključivati obračun između član banda zatvor Lasso mnogo navrat posezati proglašavanje izvanredan stanje obzir nemir zatvor val nasilje čest pojava ekvador moći poreći organiziran kriminal prožeo država politički organizacija društvo problem mučiti mnogo dugo jedan desetljeće izjaviti lasso sastanak kabinet izvanredno htjeti stanje snaga 60 dan dok htjeti trajanje policijski sat mijenjati tijekom naveden razdoblje međuvrijeme policija istraživati ubojstvo gradonačelnik manta reći predsjednik država malo šestero zatvorenik smrtno stradati 11 ozlijeđen nedjeljan nered prema podatak upravitelj zatvor guayaquilu zatvorenik zatvorima cotopaxi azuay cañar el oro napo držati 96 čuvar taoce nastavljati štrajku glađu započeti otkrivati razlog štrajka zatvorski sustav ekvador suočavati brojan strukturan problem već desetljeće stopa nasilje porasti oko 400 osoba ubijiti svakodnevan obračun što izazvati zabrinutost ujedinjen narod</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -3867,47 +2466,27 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>QUITO, Hina, Reuters, Guillermo Lasso, Lasso, Manabi, Los Rios, Duran, guayaquil, Agustin Intriago, Penitenciaria del litoral, Guayaquilu, Lasso, Ekvador, Lasso, Mante, Guayaquilu, Cotopaxi, Azuay, Cañar, El Oro, napo, Ekvador, Ujedinjenih narod</t>
+          <t>guillermo Lasso, Lasso, los rios, Manta agustin intriago predsjednikov, penitenciaria Del, Lasso, ekvador, Lasso, manta, zatvor guayaquilu, cañar el oro, ekvador</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UVEDEN, Guillermo Lasso, Lasso, Manabi, Los Rios, Duran, guayaquil, Agustin Intriago, Penitenciaria del litoral, Guayaquilu, Lasso, Ekvador, Lasso, Mante, Guayaquilu, Cotopaxi, Azuay, Cañar, El Oro, napo, Ekvador, Ujedinjenih narod</t>
+          <t>guillermo Lasso, Lasso, los rios, Manta agustin intriago predsjednikov, penitenciaria Del, Lasso, ekvador, Lasso, manta, zatvor guayaquilu, cañar el oro, ekvador</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.8095238095238095</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUITO, 25.srpnja (Hina/Reuters) - Ekvadorski predsjednik Guillermo Lasso u ponedjeljak je proglasio izvanredno stanje i policijski sat u tri pokrajine, nakon što je osmero ljudi proteklog vikenda izgubilo život u nasilnim neredima u toj južnoameričkoj zemlji.
-	Izvanredno stanje Lasso je proglasio u pokrajinama Manabi i Los Rios te u gradu Duran, u blizini drugog najvećeg grada u zemlji Guayaquil, dan nakon što je ubijen gradonačelnik obalnog grada Manta Agustin Intriago. 
-Predsjednikov potez također je i odgovor na nerede u zatvoru Penitenciaria del Litoral u Guayaquilu koji uključuju obračune između članova bandi u zatvoru.
-Lasso je u više navrata posezao za proglašavanjem izvanrednog stanja, s obzirom da su nemiri u zatvorima i valovi nasilja česte pojave u Ekvadoru.
-"Ne možemo poreći da je organizirani kriminal prožeo državu, političke organizacije i društvo, to je problem koji nas muči mnogo dulje od jednog desetljeća", izjavio je Lasso nakon sastanka svog kabineta. 
-Izvanredno će stanje biti na snazi 60 dana, dok će se trajanje policijskog sata mijenjati tijekom navedenog razdoblja. 
-U međuvremenu, policija istražuje ubojstvo gradonačelnika Mante, rekao je predsjednik države.
-Najmanje šestero zatvorenika smrtno je stradalo, a njih 11 je ozlijeđeno nakon nedjeljnih nereda, prema podacima upravitelja zatvora u Guayaquilu
-Uz to, zatvorenici u zatvorima Cotopaxi, Azuay, Cañar, El Oro i Napo drže 96 čuvara kao taoce te nastavljaju štrajku glađu koji su započeli 13.srpnja, ne otkrivajući razloge štrajka.
-Zatvorski se sustav u Ekvadoru suočava s brojnim strukturnim problemima već desetljećima, a stopa nasilja je porasla od 2021.godine, od kada je oko 400 osoba ubijeno u svakodnevnim obračunima, što je izazvalo zabrinutost Ujedinjenih naroda .
-</t>
+          <t>quito ekvadorski predsjednik guillermo lasso ponedjeljak proglasiti izvanredan stanje policijski sat tri pokrajina što osmero čovjek protekli vikend izgubiti život nasilan nered južnoamerički zemlja izvanredan stanje Lasso proglasiti pokrajina manaba los rios grad duran blizina drugi velik grad zemlja guayaquil dan što ubiti gradonačelnik obalan grad Manta agustin intriago predsjednikov potez također odgovor nered zatvor penitenciaria Del litoral guayaquilu uključivati obračun između član banda zatvor Lasso mnogo navrat posezati proglašavanje izvanredan stanje obzir nemir zatvor val nasilje čest pojava ekvador moći poreći organiziran kriminal prožeo država politički organizacija društvo problem mučiti mnogo dugo jedan desetljeće izjaviti lasso sastanak kabinet izvanredno htjeti stanje snaga 60 dan dok htjeti trajanje policijski sat mijenjati tijekom naveden razdoblje međuvrijeme policija istraživati ubojstvo gradonačelnik manta reći predsjednik država malo šestero zatvorenik smrtno stradati 11 ozlijeđen nedjeljan nered prema podatak upravitelj zatvor guayaquilu zatvorenik zatvorima cotopaxi azuay cañar el oro napo držati 96 čuvar taoce nastavljati štrajku glađu započeti otkrivati razlog štrajka zatvorski sustav ekvador suočavati brojan strukturan problem već desetljeće stopa nasilje porasti oko 400 osoba ubijiti svakodnevan obračun što izazvati zabrinutost ujedinjen narod</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ekvadorski predsjednik Guillermo Lasso proglasio je vanredno stanje i policijski sat u tri pokrajine, nakon što je osam osoba proteklog vikenda izgubilo život u nasilnim neredima u toj južnoameričkoj zemlji, prenosi Hina pozivajući se na Reuters.
-Vanredno stanje Lasso je proglasio u pokrajinama Manabi i Los Rios te u gradu Duran, u blizini drugog najvećeg grada u zemlji Guayaquil, dan nakon što je ubijen gradonačelnik obalnog grada Manta Agustin Intriago.
-Predsjednikov potez također je i odgovor na nerede u zatvoru Penitenciaria del Litoral u Guayaquilu koji uključuju obračune između članova bandi u zatvoru.
-Lasso je u više navrata posezao za proglašavanjem vanrednog stanja, s obzirom da su nemiri u zatvorima i valovi nasilja česte pojave u Ekvadoru.
-“Ne možemo poreći da je organizirani kriminal prožeo državu, političke organizacije i društvo, to je problem koji nas muči mnogo duže od jednog desetljeća”, izjavio je Lasso nakon sastanka svog kabineta.
-Ubistvo gradonačelnika Mante
-Vanredno će stanje biti na snazi 60 dana, dok će se trajanje policijskog sata mijenjati tokom navedenog razdoblja.
-U međuvremenu, policija istražuje ubistvo gradonačelnika Mante, rekao je predsjednik države.
-Najmanje šest zatvorenika smrtno je stradalo, a njih 11 je povrijeđeno nakon nedjeljnih nereda, prema podacima upravitelja zatvora u Guayaquilu.
-Uz to, zatvorenici u zatvorima Cotopaxi, Azuay, Cañar, El Oro i Napo drže 96 čuvara kao taoce te nastavljaju štrajku glađu koji su započeli 13. jula, ne otkrivajući razloge štrajka.
-Zatvorski se sistem u Ekvadoru suočava s brojnim strukturnim problemima već desetljećima, a stopa nasilja je porasla od 2021. od kada je oko 400 osoba ubijeno u svakodnevnim obračunima, što je izazvalo zabrinutost Ujedinjenih naroda.</t>
+          <t>ekvadorski predsjednik guillermo lasso proglasiti vanredan stanje policijski sat tri pokrajina što osam osoba protekli vikend izgubiti život nasilan nered južnoamerički zemlja prenositi hin pozivati reuters vanredan stanje Lasso proglasiti pokrajina manaba los rios grad duran blizina drugi velik grad zemlja guayaquil dan što ubiti gradonačelnik obalan grad Manta agustin intriago predsjednikov potez također odgovor nered zatvor penitenciaria Del litoral guayaquilu uključivati obračun između član banda zatvor Lasso mnogo navrat posezati proglašavanje vanredan stanje obzir nemir zatvor val nasilje čest pojava ekvador moći poreći organiziran kriminal prožeo država politički organizacija društvo problem mučiti mnogo duže jedan desetljeće izjaviti lasso sastanak kabinet ubistvo gradonačelnik manta vanredno htjeti stanje snaga 60 dan dok htjeti trajanje policijski sat mijenjati tokom naveden razdoblje međuvrijeme policija istraživati ubistvo gradonačelnik manta reći predsjednik država malo šest zatvorenik smrtno stradati 11 povrijeđeno nedjeljan nered prema podatak upravitelj zatvor guayaquilu zatvorenik zatvorima cotopaxi azuay cañar el oro napo držati 96 čuvar taoce nastavljati štrajku glađu započeti jula otkrivati razlog štrajka zatvorski sistem ekvador suočavati brojan strukturan problem već desetljeće stopa nasilje porasti oko 400 osoba ubijiti svakodnevan obračun što izazvati zabrinutost ujedinjen narod</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -3918,46 +2497,27 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>QUITO, Hina, Reuters, Guillermo Lasso, Lasso, Manabi, Los Rios, Duran, guayaquil, Agustin Intriago, Penitenciaria del litoral, Guayaquilu, Lasso, Ekvador, Lasso, Mante, Guayaquilu, Cotopaxi, Azuay, Cañar, El Oro, napo, Ekvador, Ujedinjenih narod</t>
+          <t>guillermo Lasso, Lasso, los rios, Manta agustin intriago predsjednikov, penitenciaria Del, Lasso, ekvador, Lasso, manta, zatvor guayaquilu, cañar el oro, ekvador</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Guillermo Lasso, Hina, Reuters, vanredno, Lasso, Manabi, Los Rios, Duran, guayaquil, Agustin Intriago, Penitenciaria del litoral, Guayaquilu, Lasso, Ekvador, Lasso, Mante, vanredno, Mante, Guayaquilu, Cotopaxi, Azuay, Cañar, El Oro, napo, Ekvador, Ujedinjenih narod</t>
+          <t>guillermo Lasso, Reuters, Lasso, los rios, Manta agustin intriago predsjednikov, penitenciaria Del, Lasso, ekvador, Lasso, Manta vanredno, manta, zatvor guayaquilu, cañar el oro</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUITO, 25.srpnja (Hina/Reuters) - Ekvadorski predsjednik Guillermo Lasso u ponedjeljak je proglasio izvanredno stanje i policijski sat u tri pokrajine, nakon što je osmero ljudi proteklog vikenda izgubilo život u nasilnim neredima u toj južnoameričkoj zemlji.
-	Izvanredno stanje Lasso je proglasio u pokrajinama Manabi i Los Rios te u gradu Duran, u blizini drugog najvećeg grada u zemlji Guayaquil, dan nakon što je ubijen gradonačelnik obalnog grada Manta Agustin Intriago. 
-Predsjednikov potez također je i odgovor na nerede u zatvoru Penitenciaria del Litoral u Guayaquilu koji uključuju obračune između članova bandi u zatvoru.
-Lasso je u više navrata posezao za proglašavanjem izvanrednog stanja, s obzirom da su nemiri u zatvorima i valovi nasilja česte pojave u Ekvadoru.
-"Ne možemo poreći da je organizirani kriminal prožeo državu, političke organizacije i društvo, to je problem koji nas muči mnogo dulje od jednog desetljeća", izjavio je Lasso nakon sastanka svog kabineta. 
-Izvanredno će stanje biti na snazi 60 dana, dok će se trajanje policijskog sata mijenjati tijekom navedenog razdoblja. 
-U međuvremenu, policija istražuje ubojstvo gradonačelnika Mante, rekao je predsjednik države.
-Najmanje šestero zatvorenika smrtno je stradalo, a njih 11 je ozlijeđeno nakon nedjeljnih nereda, prema podacima upravitelja zatvora u Guayaquilu
-Uz to, zatvorenici u zatvorima Cotopaxi, Azuay, Cañar, El Oro i Napo drže 96 čuvara kao taoce te nastavljaju štrajku glađu koji su započeli 13.srpnja, ne otkrivajući razloge štrajka.
-Zatvorski se sustav u Ekvadoru suočava s brojnim strukturnim problemima već desetljećima, a stopa nasilja je porasla od 2021.godine, od kada je oko 400 osoba ubijeno u svakodnevnim obračunima, što je izazvalo zabrinutost Ujedinjenih naroda .
-</t>
+          <t>quito ekvadorski predsjednik guillermo lasso ponedjeljak proglasiti izvanredan stanje policijski sat tri pokrajina što osmero čovjek protekli vikend izgubiti život nasilan nered južnoamerički zemlja izvanredan stanje Lasso proglasiti pokrajina manaba los rios grad duran blizina drugi velik grad zemlja guayaquil dan što ubiti gradonačelnik obalan grad Manta agustin intriago predsjednikov potez također odgovor nered zatvor penitenciaria Del litoral guayaquilu uključivati obračun između član banda zatvor Lasso mnogo navrat posezati proglašavanje izvanredan stanje obzir nemir zatvor val nasilje čest pojava ekvador moći poreći organiziran kriminal prožeo država politički organizacija društvo problem mučiti mnogo dugo jedan desetljeće izjaviti lasso sastanak kabinet izvanredno htjeti stanje snaga 60 dan dok htjeti trajanje policijski sat mijenjati tijekom naveden razdoblje međuvrijeme policija istraživati ubojstvo gradonačelnik manta reći predsjednik država malo šestero zatvorenik smrtno stradati 11 ozlijeđen nedjeljan nered prema podatak upravitelj zatvor guayaquilu zatvorenik zatvorima cotopaxi azuay cañar el oro napo držati 96 čuvar taoce nastavljati štrajku glađu započeti otkrivati razlog štrajka zatvorski sustav ekvador suočavati brojan strukturan problem već desetljeće stopa nasilje porasti oko 400 osoba ubijiti svakodnevan obračun što izazvati zabrinutost ujedinjen narod</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ekvadorski predsjednik Guillermo Lasso u ponedjeljak je proglasio izvanredno stanje i policijski sat u tri pokrajine, nakon što je osmero ljudi proteklog vikenda izgubilo život u nasilnim neredima u toj južnoameričkoj zemlji.
-Izvanredno stanje Lasso je proglasio u pokrajinama Manabi i Los Rios te u gradu Duran, u blizini drugog najvećeg grada u zemlji Guayaquil, dan nakon što je ubijen gradonačelnik obalnog grada Manta Agustin Intriago.
-Predsjednikov potez također je i odgovor na nerede u zatvoru Penitenciaria del Litoral u Guayaquilu koji uključuju obračune između članova bandi u zatvoru.
-Lasso je u više navrata posezao za proglašavanjem izvanrednog stanja, s obzirom da su nemiri u zatvorima i valovi nasilja česte pojave u Ekvadoru.
-“Ne možemo poreći da je organizirani kriminal prožeo državu, političke organizacije i društvo, to je problem koji nas muči mnogo dulje od jednog desetljeća”, izjavio je Lasso nakon sastanka svog kabineta.
-Izvanredno će stanje biti na snazi 60 dana, dok će se trajanje policijskog sata mijenjati tijekom navedenog razdoblja.
-U međuvremenu, policija istražuje ubojstvo gradonačelnika Mante, rekao je predsjednik države.
-Najmanje šestero zatvorenika smrtno je stradalo, a njih 11 je ozlijeđeno nakon nedjeljnih nereda, prema podacima upravitelja zatvora u Guayaquilu
-Uz to, zatvorenici u zatvorima Cotopaxi, Azuay, Cañar, El Oro i Napo drže 96 čuvara kao taoce te nastavljaju štrajku glađu koji su započeli 13.srpnja, ne otkrivajući razloge štrajka.
-Zatvorski se sustav u Ekvadoru suočava s brojnim strukturnim problemima već desetljećima, a stopa nasilja je porasla od 2021.godine, od kada je oko 400 osoba ubijeno u svakodnevnim obračunima, što je izazvalo zabrinutost Ujedinjenih naroda .</t>
+          <t>ekvadorski predsjednik guillermo lasso ponedjeljak proglasiti izvanredan stanje policijski sat tri pokrajina što osmero čovjek protekli vikend izgubiti život nasilan nered južnoamerički zemlja izvanredan stanje Lasso proglasiti pokrajina manaba los rios grad duran blizina drugi velik grad zemlja guayaquil dan što ubiti gradonačelnik obalan grad Manta agustin intriago predsjednikov potez također odgovor nered zatvor penitenciaria Del litoral guayaquilu uključivati obračun između član banda zatvor Lasso mnogo navrat posezati proglašavanje izvanredan stanje obzir nemir zatvor val nasilje čest pojava ekvador moći poreći organiziran kriminal prožeo država politički organizacija društvo problem mučiti mnogo dugo jedan desetljeće izjaviti lasso sastanak kabinet izvanredno htjeti stanje snaga 60 dan dok htjeti trajanje policijski sat mijenjati tijekom naveden razdoblje međuvrijeme policija istraživati ubojstvo gradonačelnik manta reći predsjednik država malo šestero zatvorenik smrtno stradati 11 ozlijeđen nedjeljan nered prema podatak upravitelj zatvor guayaquilu zatvorenik zatvorima cotopaxi azuay cañar el oro napo držati 96 čuvar taoce nastavljati štrajku glađu započeti otkrivati razlog štrajka zatvorski sustav ekvador suočavati brojan strukturan problem već desetljeće stopa nasilje porasti oko 400 osoba ubijiti svakodnevan obračun što izazvati zabrinutost ujedinjen narod</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -3968,38 +2528,27 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>QUITO, Hina, Reuters, Guillermo Lasso, Lasso, Manabi, Los Rios, Duran, guayaquil, Agustin Intriago, Penitenciaria del litoral, Guayaquilu, Lasso, Ekvador, Lasso, Mante, Guayaquilu, Cotopaxi, Azuay, Cañar, El Oro, napo, Ekvador, Ujedinjenih narod</t>
+          <t>guillermo Lasso, Lasso, los rios, Manta agustin intriago predsjednikov, penitenciaria Del, Lasso, ekvador, Lasso, manta, zatvor guayaquilu, cañar el oro, ekvador</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Guillermo Lasso, Lasso, Manabi, Los Rios, Duran, guayaquil, Agustin Intriago, Penitenciaria del litoral, Guayaquilu, Lasso, Ekvador, Lasso, Mante, Guayaquilu, Cotopaxi, Azuay, Cañar, El Oro, napo, Ekvador, Ujedinjenih narod</t>
+          <t>guillermo Lasso, Lasso, los rios, Manta agustin intriago predsjednikov, penitenciaria Del, Lasso, ekvador, Lasso, manta, zatvor guayaquilu, cañar el oro, ekvador</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUITO, 25.srpnja (Hina/Reuters) - Ekvadorski predsjednik Guillermo Lasso u ponedjeljak je proglasio izvanredno stanje i policijski sat u tri pokrajine, nakon što je osmero ljudi proteklog vikenda izgubilo život u nasilnim neredima u toj južnoameričkoj zemlji.
-	Izvanredno stanje Lasso je proglasio u pokrajinama Manabi i Los Rios te u gradu Duran, u blizini drugog najvećeg grada u zemlji Guayaquil, dan nakon što je ubijen gradonačelnik obalnog grada Manta Agustin Intriago. 
-Predsjednikov potez također je i odgovor na nerede u zatvoru Penitenciaria del Litoral u Guayaquilu koji uključuju obračune između članova bandi u zatvoru.
-Lasso je u više navrata posezao za proglašavanjem izvanrednog stanja, s obzirom da su nemiri u zatvorima i valovi nasilja česte pojave u Ekvadoru.
-"Ne možemo poreći da je organizirani kriminal prožeo državu, političke organizacije i društvo, to je problem koji nas muči mnogo dulje od jednog desetljeća", izjavio je Lasso nakon sastanka svog kabineta. 
-Izvanredno će stanje biti na snazi 60 dana, dok će se trajanje policijskog sata mijenjati tijekom navedenog razdoblja. 
-U međuvremenu, policija istražuje ubojstvo gradonačelnika Mante, rekao je predsjednik države.
-Najmanje šestero zatvorenika smrtno je stradalo, a njih 11 je ozlijeđeno nakon nedjeljnih nereda, prema podacima upravitelja zatvora u Guayaquilu
-Uz to, zatvorenici u zatvorima Cotopaxi, Azuay, Cañar, El Oro i Napo drže 96 čuvara kao taoce te nastavljaju štrajku glađu koji su započeli 13.srpnja, ne otkrivajući razloge štrajka.
-Zatvorski se sustav u Ekvadoru suočava s brojnim strukturnim problemima već desetljećima, a stopa nasilja je porasla od 2021.godine, od kada je oko 400 osoba ubijeno u svakodnevnim obračunima, što je izazvalo zabrinutost Ujedinjenih naroda .
-</t>
+          <t>quito ekvadorski predsjednik guillermo lasso ponedjeljak proglasiti izvanredan stanje policijski sat tri pokrajina što osmero čovjek protekli vikend izgubiti život nasilan nered južnoamerički zemlja izvanredan stanje Lasso proglasiti pokrajina manaba los rios grad duran blizina drugi velik grad zemlja guayaquil dan što ubiti gradonačelnik obalan grad Manta agustin intriago predsjednikov potez također odgovor nered zatvor penitenciaria Del litoral guayaquilu uključivati obračun između član banda zatvor Lasso mnogo navrat posezati proglašavanje izvanredan stanje obzir nemir zatvor val nasilje čest pojava ekvador moći poreći organiziran kriminal prožeo država politički organizacija društvo problem mučiti mnogo dugo jedan desetljeće izjaviti lasso sastanak kabinet izvanredno htjeti stanje snaga 60 dan dok htjeti trajanje policijski sat mijenjati tijekom naveden razdoblje međuvrijeme policija istraživati ubojstvo gradonačelnik manta reći predsjednik država malo šestero zatvorenik smrtno stradati 11 ozlijeđen nedjeljan nered prema podatak upravitelj zatvor guayaquilu zatvorenik zatvorima cotopaxi azuay cañar el oro napo držati 96 čuvar taoce nastavljati štrajku glađu započeti otkrivati razlog štrajka zatvorski sustav ekvador suočavati brojan strukturan problem već desetljeće stopa nasilje porasti oko 400 osoba ubijiti svakodnevan obračun što izazvati zabrinutost ujedinjen narod</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dugotrajnom toplotnom talasu, koji nas prati već nedeljama, konačno je došao kraj. Pročitaj više
-Vaš komentar Ime</t>
+          <t>dugotrajan toplotan talas pratiti već nedelja konačno doći kraj pročitaj mnogo vaš komentar ime</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -4010,7 +2559,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>QUITO, Hina, Reuters, Guillermo Lasso, Lasso, Manabi, Los Rios, Duran, guayaquil, Agustin Intriago, Penitenciaria del litoral, Guayaquilu, Lasso, Ekvador, Lasso, Mante, Guayaquilu, Cotopaxi, Azuay, Cañar, El Oro, napo, Ekvador, Ujedinjenih narod</t>
+          <t>guillermo Lasso, Lasso, los rios, Manta agustin intriago predsjednikov, penitenciaria Del, Lasso, ekvador, Lasso, manta, zatvor guayaquilu, cañar el oro, ekvador</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -4021,33 +2570,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUITO, 25.srpnja (Hina/Reuters) - Ekvadorski predsjednik Guillermo Lasso u ponedjeljak je proglasio izvanredno stanje i policijski sat u tri pokrajine, nakon što je osmero ljudi proteklog vikenda izgubilo život u nasilnim neredima u toj južnoameričkoj zemlji.
-	Izvanredno stanje Lasso je proglasio u pokrajinama Manabi i Los Rios te u gradu Duran, u blizini drugog najvećeg grada u zemlji Guayaquil, dan nakon što je ubijen gradonačelnik obalnog grada Manta Agustin Intriago. 
-Predsjednikov potez također je i odgovor na nerede u zatvoru Penitenciaria del Litoral u Guayaquilu koji uključuju obračune između članova bandi u zatvoru.
-Lasso je u više navrata posezao za proglašavanjem izvanrednog stanja, s obzirom da su nemiri u zatvorima i valovi nasilja česte pojave u Ekvadoru.
-"Ne možemo poreći da je organizirani kriminal prožeo državu, političke organizacije i društvo, to je problem koji nas muči mnogo dulje od jednog desetljeća", izjavio je Lasso nakon sastanka svog kabineta. 
-Izvanredno će stanje biti na snazi 60 dana, dok će se trajanje policijskog sata mijenjati tijekom navedenog razdoblja. 
-U međuvremenu, policija istražuje ubojstvo gradonačelnika Mante, rekao je predsjednik države.
-Najmanje šestero zatvorenika smrtno je stradalo, a njih 11 je ozlijeđeno nakon nedjeljnih nereda, prema podacima upravitelja zatvora u Guayaquilu
-Uz to, zatvorenici u zatvorima Cotopaxi, Azuay, Cañar, El Oro i Napo drže 96 čuvara kao taoce te nastavljaju štrajku glađu koji su započeli 13.srpnja, ne otkrivajući razloge štrajka.
-Zatvorski se sustav u Ekvadoru suočava s brojnim strukturnim problemima već desetljećima, a stopa nasilja je porasla od 2021.godine, od kada je oko 400 osoba ubijeno u svakodnevnim obračunima, što je izazvalo zabrinutost Ujedinjenih naroda .
-</t>
+          <t>quito ekvadorski predsjednik guillermo lasso ponedjeljak proglasiti izvanredan stanje policijski sat tri pokrajina što osmero čovjek protekli vikend izgubiti život nasilan nered južnoamerički zemlja izvanredan stanje Lasso proglasiti pokrajina manaba los rios grad duran blizina drugi velik grad zemlja guayaquil dan što ubiti gradonačelnik obalan grad Manta agustin intriago predsjednikov potez također odgovor nered zatvor penitenciaria Del litoral guayaquilu uključivati obračun između član banda zatvor Lasso mnogo navrat posezati proglašavanje izvanredan stanje obzir nemir zatvor val nasilje čest pojava ekvador moći poreći organiziran kriminal prožeo država politički organizacija društvo problem mučiti mnogo dugo jedan desetljeće izjaviti lasso sastanak kabinet izvanredno htjeti stanje snaga 60 dan dok htjeti trajanje policijski sat mijenjati tijekom naveden razdoblje međuvrijeme policija istraživati ubojstvo gradonačelnik manta reći predsjednik država malo šestero zatvorenik smrtno stradati 11 ozlijeđen nedjeljan nered prema podatak upravitelj zatvor guayaquilu zatvorenik zatvorima cotopaxi azuay cañar el oro napo držati 96 čuvar taoce nastavljati štrajku glađu započeti otkrivati razlog štrajka zatvorski sustav ekvador suočavati brojan strukturan problem već desetljeće stopa nasilje porasti oko 400 osoba ubijiti svakodnevan obračun što izazvati zabrinutost ujedinjen narod</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Strani radnici spašavaju sezonuRaditi u Hrvatsku već godinama se dolazi ne samo iz susjednih zemalja, nego i s drugih kontinenata. Dobrodošli su svi koji žele raditi. Ne veseli činjenica što radne snage, doznali smo u Supetru, ne nedostaje samo u turizmu.
-Velika supetarska hotelska tvrtka puna je zaposlenika iz inozemstva. Strani radnici doslovce spašavaju sezonu. Nazarenu su u posjet Hrvatskoj doveli hrvatski korijeni, a zadržao ju je bolji život.
-- Iskreno, situacija u Argentini je komplicirana. Vidim da se ovdje može bolje živjeti i planirati budućnost. Mogu raditi, štedjeti, putovati. Nažalost, to u Argentini nije moguće, rekla je Nazarena Mendoza za HRT.
-Mlada recepcionerka dosad nije radila u turizmu, iako dolazi iz turističke zemlje, no posao je brzo naučila.
-- Moja je zemlja također vrlo skupa, pa kada dođem ovamo i zaradim, mogu si mnogo toga priuštiti u Mađarskoj. Ovdje imam smještaj, hranu i dobre prijatelje, rekla je.
-Radnu snagu iz Europe, Latinske Amerike i Azije u Supetru dovode uz pomnu pripremu. Nema mjesta iznenađenju.
-- Posla ima puno i stvarno dobro dođe. Organizirani su, znaju raditi i komunicirat, kazao je Petar Krneta, voditelj restorana.
-- Već sada kroz ovo ljeto pogotovo s radnom snagom razgovaramo i dogovaramo iduću sezonu, tako da ovi kada dođu kući pričaju sa svojom rodbinom, poznanicima i prijateljima tako da i njima dajemo priliku da dođu ovdje raditi, izjavio je Pero Maričić, savjetnik Uprave hotelske tvrtke u Supetru.
-Iznenađenje je da su stranci zaposleni i u supetarskoj komunalnoj tvrtki.
-- Znate, Bangladeš je siromašna zemlja, ima velike gospodarske probleme i ja sam došao ovamo raditi i pomoći obitelji, izjavio je Abdur Rohim.
-- Ove godine pokrenuli smo 4 nove radne dozvole koje smo ishodili, ali ove godine je problem s ishođenjem viza koje nešto duže traje, tako da smo kroz ovu godinu nam je stigao tek jedan od 4 tražena djelatnika, objasnila je Marijana Šemanović, direktorica Komunalnog društva "Grad" d.o.o. Supetar.
-Poslodavci sve potrebnijih stranih radnika zadovoljni su time što je država omogućila njihovo nesmetano zapošljavanje. No, sporo rješavanje za to potrebne administracije, svi ponavljaju, velik je problem koji treba što prije riješiti</t>
+          <t>stran radnik spašavati sezonuraditi hrvatski već godina dolaziti susjedni zemlja drugi kontinent dobrodoći željeti raditi veseli činjenica što radni snaga doznati supetar nedostajati turizam velik supetarski hotelski tvrtka pun zaposlenik inozemstvo strana radnik doslovce spašavati sezona nazaren posjet Hrvatska dovesti hrvatski korijen zadržati dobar život iskreno situacija argentina kompliciran vidjeti ovdje moći dobro živjeti planirati budućnost moći raditi štedjeti putovati nažalost argentina moguć reći nazaren mendoza hrt mlad recepcionerka dosad raditi turizam dolaziti turistički zemlja posao brzo naučiti zemlja također skup dođeti ovamo zaraditi moći mnogo taj priuštiti mađarskoj ovdje imati smještaj hrana dobar prijatelj reći radni snaga Europa latinski amerika azija supetar dovoditi poman priprema mjesto iznenađenje posao imati puno stvarno dobro doći organiziran znati raditi komunicirat kazati petar krnet voditelj restoran već sada ovaj ljeto pogotovo radni snaga razgovarati dogovarati idući sezona ovaj dođu kuća pričati svoj rodbina poznanik prijatelj dati prilika dođu ovdje raditi izjaviti pero maričić savjetnik uprava hotelski tvrtka supetar iznenađenje stranac zaposlen supetarski komunalni tvrtka znati bangladeš siromašn zemlja imati velik gospodarski problem doći ovamo raditi pomoći obitelj izjaviti Abdur rohim ovaj godina pokrenuti 4 nov radni dozvola ishoditi ovaj godina problem ishođenje viza nešto duže trajati ovaj godina stići tek jedan 4 tražen djelatnik objasniti marijana šemanović direktorica komunalan društvo grad supetar poslodavac potrebniji stran radnik zadovoljan taj što država omogućiti nesmetan zapošljavanje spor rješavanje potreban administracija ponavljati velik problem trebati što riješiti</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -4058,12 +2586,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>QUITO, Hina, Reuters, Guillermo Lasso, Lasso, Manabi, Los Rios, Duran, guayaquil, Agustin Intriago, Penitenciaria del litoral, Guayaquilu, Lasso, Ekvador, Lasso, Mante, Guayaquilu, Cotopaxi, Azuay, Cañar, El Oro, napo, Ekvador, Ujedinjenih narod</t>
+          <t>guillermo Lasso, Lasso, los rios, Manta agustin intriago predsjednikov, penitenciaria Del, Lasso, ekvador, Lasso, manta, zatvor guayaquilu, cañar el oro, ekvador</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hrvatska, Supetr, Nazaren, Hrvatska, Argentina, Argentina, Nazaren Mendoza, HRT, Mađarska, Europa, Latinski Amerika, Azija, Supetr, Petar Krnet, Pero Maričić, uprava hotelski tvrtka, Supetr, Bangladeš, Abdur Rohim, Marijana Šemanović, Komunalnog društvo</t>
+          <t>Hrvatska, argentina, mađarskoj, Europa, Amerika, Petar krnet, pero Maričić, Abdur rohim</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -4073,24 +2601,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUITO, 25.srpnja (Hina/Reuters) - Ekvadorski predsjednik Guillermo Lasso u ponedjeljak je proglasio izvanredno stanje i policijski sat u tri pokrajine, nakon što je osmero ljudi proteklog vikenda izgubilo život u nasilnim neredima u toj južnoameričkoj zemlji.
-	Izvanredno stanje Lasso je proglasio u pokrajinama Manabi i Los Rios te u gradu Duran, u blizini drugog najvećeg grada u zemlji Guayaquil, dan nakon što je ubijen gradonačelnik obalnog grada Manta Agustin Intriago. 
-Predsjednikov potez također je i odgovor na nerede u zatvoru Penitenciaria del Litoral u Guayaquilu koji uključuju obračune između članova bandi u zatvoru.
-Lasso je u više navrata posezao za proglašavanjem izvanrednog stanja, s obzirom da su nemiri u zatvorima i valovi nasilja česte pojave u Ekvadoru.
-"Ne možemo poreći da je organizirani kriminal prožeo državu, političke organizacije i društvo, to je problem koji nas muči mnogo dulje od jednog desetljeća", izjavio je Lasso nakon sastanka svog kabineta. 
-Izvanredno će stanje biti na snazi 60 dana, dok će se trajanje policijskog sata mijenjati tijekom navedenog razdoblja. 
-U međuvremenu, policija istražuje ubojstvo gradonačelnika Mante, rekao je predsjednik države.
-Najmanje šestero zatvorenika smrtno je stradalo, a njih 11 je ozlijeđeno nakon nedjeljnih nereda, prema podacima upravitelja zatvora u Guayaquilu
-Uz to, zatvorenici u zatvorima Cotopaxi, Azuay, Cañar, El Oro i Napo drže 96 čuvara kao taoce te nastavljaju štrajku glađu koji su započeli 13.srpnja, ne otkrivajući razloge štrajka.
-Zatvorski se sustav u Ekvadoru suočava s brojnim strukturnim problemima već desetljećima, a stopa nasilja je porasla od 2021.godine, od kada je oko 400 osoba ubijeno u svakodnevnim obračunima, što je izazvalo zabrinutost Ujedinjenih naroda .
-</t>
+          <t>quito ekvadorski predsjednik guillermo lasso ponedjeljak proglasiti izvanredan stanje policijski sat tri pokrajina što osmero čovjek protekli vikend izgubiti život nasilan nered južnoamerički zemlja izvanredan stanje Lasso proglasiti pokrajina manaba los rios grad duran blizina drugi velik grad zemlja guayaquil dan što ubiti gradonačelnik obalan grad Manta agustin intriago predsjednikov potez također odgovor nered zatvor penitenciaria Del litoral guayaquilu uključivati obračun između član banda zatvor Lasso mnogo navrat posezati proglašavanje izvanredan stanje obzir nemir zatvor val nasilje čest pojava ekvador moći poreći organiziran kriminal prožeo država politički organizacija društvo problem mučiti mnogo dugo jedan desetljeće izjaviti lasso sastanak kabinet izvanredno htjeti stanje snaga 60 dan dok htjeti trajanje policijski sat mijenjati tijekom naveden razdoblje međuvrijeme policija istraživati ubojstvo gradonačelnik manta reći predsjednik država malo šestero zatvorenik smrtno stradati 11 ozlijeđen nedjeljan nered prema podatak upravitelj zatvor guayaquilu zatvorenik zatvorima cotopaxi azuay cañar el oro napo držati 96 čuvar taoce nastavljati štrajku glađu započeti otkrivati razlog štrajka zatvorski sustav ekvador suočavati brojan strukturan problem već desetljeće stopa nasilje porasti oko 400 osoba ubijiti svakodnevan obračun što izazvati zabrinutost ujedinjen narod</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3.8.2023. 22:06 Podijeli na: Komentari: 0
-Sada su stvari jasnije: Pojavio se snimak na kojem muškarci maltretiraju kornjaču. Čupali je za peraja i oklop
-Proteklih dana, brojni građani u okolini Trogira, Hrvatska, tvrdili su da su ih kornjače napale, što je izazvalo zabrinutost i nelagodu među lokalnim stanovništvom. Međutim, novi snimci objavljeni od strane Hrvatske radiotelevizije (HRT) otkrivaju sasvim drugačiju istinu i stvaraju novi pogled na ovu situaciju.</t>
+          <t>podijeti komentar 0 sada stvar jasno pojaviti snimak koji muškarac maltretirati kornjača čupati peraja oklop protekao dan brojan građanin okolina trogirati Hrvatska tvrditi kornjač napati što izazvati zabrinutost nelagoda među lokalan stanovništvo međutim nov snimak objaviti strana hrvatski radiotelevizija hrt otkrivati sasvim drugačiji istina stvarati nov pogled ovaj situacija</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -4101,12 +2617,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>QUITO, Hina, Reuters, Guillermo Lasso, Lasso, Manabi, Los Rios, Duran, guayaquil, Agustin Intriago, Penitenciaria del litoral, Guayaquilu, Lasso, Ekvador, Lasso, Mante, Guayaquilu, Cotopaxi, Azuay, Cañar, El Oro, napo, Ekvador, Ujedinjenih narod</t>
+          <t>guillermo Lasso, Lasso, los rios, Manta agustin intriago predsjednikov, penitenciaria Del, Lasso, ekvador, Lasso, manta, zatvor guayaquilu, cañar el oro, ekvador</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trogir, Hrvatska, hrvatski radiotelevizija, HRT</t>
+          <t>Hrvatska</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -4116,17 +2632,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Na magistrali malo iza skretanja za Bosanku prema Župi dubrovačkoj, oko 11 i 30 sati došlo je do prometne nezgode u kojoj su sudjelovali osobno vozilo i motociklist. Na sreću nema ozlijeđenih, pričinjena je materijalna šteta. Promet se odvija nesmetano, čeka se dolazak policije, javljaju iz Operativno-komunikacijskog centra PU dubrovačko-neretvanske.</t>
+          <t>magistral malo iza skretanje bosanak prema župa dubrovačkoj oko 11 30 sat doći prometan nezgoda koji sudjelovati osoban vozilo motociklist sreća ozlijeđen pričiniti materijalan šteta promet odvijati nesmetano čekati dolazak policija javljati centar pu</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -4137,14 +2648,10 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Bosanka, pU dubrovačko - neretvanske</t>
-        </is>
-      </c>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
         <v>0</v>
       </c>
@@ -4152,23 +2659,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TEŠKA PROMETNA NESREĆA U HRVATSKOJ: Poginulo je dvoje ljudi, ozlijeđeno je još troje
-Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod Nove Gradiške, u kojoj je sudjelovalo teretno i osobno vozilo, a ozlijeđene su još tri osobe, javljaju iz PU Brodsko-posavske.
-Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške.
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-Fenix-magazin/MD/Hina</t>
+          <t>težak prometan nesreća Hrvatska poginuti dvoje čovjek ozlijediti još troje dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osoban vozilo ozlijediti još tri osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -4179,37 +2675,27 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>pROMETNA NESREĆA, HRVATSKOJ, nov gradiška, pU Brodsko - posavske, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod, Fenix - magazin, Hina</t>
+          <t>Hrvatska, a3</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3
-Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod Nove Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđene su još tri osobe, javljaju iz PU Brodsko-posavske.
-Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške.
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju uviđaja.</t>
+          <t>pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još tri osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje uviđaj</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -4220,36 +2706,27 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>A3, nov gradiška, pU Brodsko - posavske, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3, a3</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod Nove Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske.
-Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške.
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.</t>
+          <t>dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -4260,37 +2737,27 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>nov gradiška, pU Brodsko - posavske, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strašna prometnoj nesreći dogodila se u ponedjeljak kasno navečer, izvijestila je brodsko-posavska policija.
-Policija je javila kako je u 23:32 sati u Operativno-komunikacijskom centru Policijske uprave brodsko-posavske, zaprimljena dojava da je na južnoj kolničkoj traci autoceste A3, kod 163 km u smjeru Lipovca (nedaleko od Nove Gradiške), došlo do prometne nesreće u kojoj su sudjelovali teretno i osobno vozilo i u kojoj su dvije osobe smrtno stradale, dok su tri ozlijeđene i prevezene u OB Nova Gradiška radi ukazivanja liječničke pomoći.
-Angažirani su pripadnici HMP i vatrogasci radi izvlačenja ozlijeđenih osoba iz vozila, priopćila je Policijska uprava brodsko-posavska.
-Policijski službenici na mjesto događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-U tijeku je očevid kako bi se utvrdile okolnosti prometne nesreće.
-</t>
+          <t>strašan prometni nesreća dogoditi ponedjeljak kasno navečer izvijestiti policija policija javiti sat centar policijski uprava zaprimiti dojava južan kolnički traka autocesta a3 kod 163 km smjer lipovac nedaleko nov gradiška doći prometan nesreća koji sudjelovati teretni osoban vozilo koji dva osoba smrtno stradati dok tri ozlijediti prevezene ob nov gradiška radi ukazivanje liječnički pomoć angažiran pripadnik hmp vatrogascin radi izvlačenje ozlijeđen osoba vozilo priopćiti policijski uprava policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka tijek očevid utvrditi okolnost prometan nesreća</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -4301,36 +2768,23 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>policijski uprava brodsko - posavske, A3, Lipovca, nov gradiška, OB Nova Gradiška, HMP, Policijski uprava brodsko - posavska</t>
-        </is>
-      </c>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod Nove Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske.
-Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške.
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.</t>
+          <t>dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -4341,35 +2795,27 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>nov gradiška, pU Brodsko - posavske, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške.
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.</t>
+          <t>pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -4380,39 +2826,23 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
-        </is>
-      </c>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Podijeli :
-PU splitsko-dalmatinska / Ilustracija
-U ponedjeljak kasno navečer na autocesti A3 u Hrvatskoj došlo je do teške nesreće u kojoj su sudjelovali teretno i osobno vozilo. Dvije su osobe poginule, a tri ozlijeđene.
-U ponedjeljak oko 23:30 došlo je do teške prometne nesreće na južnoj kolničkoj traci autoceste A3, kod 163 km (u blizini Nove Gradiške) u kojoj su sudjelovali teretno i osobno vozilo.
-Dvije osobe smrtno su stradale, dok su tri ozlijeđene i prevezene na ukazivanje liječničke pomoći novogradišku bolnicu.
-Angažirani su pripadnici Hitne medicinske pomoći i vatrogasci radi izvlačenja ozlijeđenih osoba iz vozila.
-Policijski službenici na mjesto događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake. Očevid je u tijeku, izvijestili su iz policije.
-Program N1 televizije možete pratiti UŽIVO na ovom linku kao i putem aplikacija za Android|iPhone/iPad</t>
+          <t>podijeti pu ilustracija ponedjeljak kasno navečer autocest a3 Hrvatska doći težak nesreća koji sudjelovati teretni osoban vozilo dva osoba poginuti tri ozlijediti ponedjeljak oko doći težak prometan nesreća južni kolnički traka autocesta a3 kod 163 km blizina nov gradiška koji sudjelovati teretni osoban vozilo dva osoba smrtno stradati dok tri ozlijeđene prevezen ukazivanje liječnički pomoć novogradišku bolnica angažiran pripadnik hitan medicinski pomoć vatrogask radi izvlačenje ozlijeđen osoba vozilo policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka očevid tijek izvijestiti policija program n1 televizija moći pratiti uživo ovaj link putem aplikacija</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -4423,37 +2853,27 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>pU splitsko - dalmatinska, A3, Hrvatska, A3, nov gradiška, Hitne medicinski pomoć i vatrogask, program N1 televizija, Android|iPhone, iPad</t>
+          <t>a3 Hrvatska</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HITNA I VATROGASCI IZVLAČILI OZLIJEĐENE IZ VOZILA
-Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod Nove Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske.
-Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške.
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.</t>
+          <t>hitan vatrogascin izvlačiti ozlijeđene vozilo dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -4464,35 +2884,27 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>nov gradiška, pU Brodsko - posavske, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske.
-Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške.
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.</t>
+          <t>dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -4503,39 +2915,27 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>gradiške, pU Brodsko - posavske, A3, nov gradiška, opću bolnica Nova Gradiška</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Podijeli :
-PU splitsko-dalmatinska / Ilustracija
-Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske.
-Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške.
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-N1 pratite putem aplikacija za Android | iPhone/iPad i mreža Twitter | Facebook | Instagram | TikTok.</t>
+          <t>podijeti pu ilustracija dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid n1 pratite putem aplikacija Android mreža twitter facebook instagram tiktok</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -4546,33 +2946,27 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>pU splitsko - dalmatinska, gradiške, pU Brodsko - posavske, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod, N1, Android, iPhone, iPad, Twitter, Facebook</t>
+          <t>a3, Android</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. Pročitaj više
-Vaš komentar Ime</t>
+          <t>dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pročitaji mnogo vaš komentar ime</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -4583,36 +2977,27 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>gradiške, pU Brodsko - posavske</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod Nove Gradiške, u kojoj su sudjelovali teretno i osobno vozilo, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske, prenosi Jutarnji list.
-Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške.
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.</t>
+          <t>dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osoban vozilo ozlijediti još troje osoba javljati pu prenositi jutarnji list pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -4623,45 +3008,27 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>nov gradiška, pU Brodsko - posavske, Jutarnji list, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.5454545454545454</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ljudi poginuli na autocesti, više završilo u bolnici: Ogromna tragedija kod Nove Gradiške
-Autor: I.G.
-U Splitu se u utorak ujutro dogodila teška prometna nesreća u kojoj je poginula jedna osoba.
-“Jutros, 25. srpnja 2023.godine, oko 06:12 sati u Splitu na križanju ulica Mažuranićevo šetalište i ulice Slobode, došlo je prometne nesreće, sudara dva kombi vozila. Jedna osoba je preminula na mjestu događaja, dok je druga osoba prevezena na pružanje liječničke pomoći. O događaju obaviješteno nadležno državno odvjetništvo.
-Zamjenica općinskog državnog odvjetništva će rukovoditi očevidom”, izvijestila je policija.
-Cesta je na mjestu prometne nesreće zatvorena za sav promet. Policijski službenici na obližnja tri raskrižja preusmjeravaju promet i to na križanjima Mažuranićevo šetalište- Dubrovačka, ulica Slobode- Vukovarska i ulica Slobode Velebitska).
-“U cilju utvrđivanja svih činjenica i okolnosti koje su prethodile nastanku prometne nesreće, pozivamo svjedoke/ očevidce, kao i sve osobe koje imaju korisnih saznanja o nastanku navedene prometne nesreće da se jave u Postaju prometne policije Split na brojeve telefona 021 504-010, 021 504-036, ili pristupe osobno u postaju na adresi Plokita 81”, pozvala je policija.
-Prometna kod Trogira
-Još jedan stravičan incident dogodio se u noći s ponedjeljka na utorak. Kako poručuju iz Policije, na cesti D8, u Trogiru dogodila se prometna nesreća sudar osobnog vozila i motocikla. Vozač motocikla prevezen je u bolnicu na pružanje liječničke pomoći, ali je tijekom noći nažalost preminuo.
-O prometnoj nesreći je obavješteno nadležno državno odvjetništvo i na mjestu događaja je obavljen očevid.
-Nesreća i kod Nove Gradiške
-“Dana 24.07.2023.g. u 23,32 sati, u Operativno-komunikacijskom centru Policijske uprave brodsko-posavske, zaprimljena je dojava da je na južnoj kolničkoj traci autoceste A3, kod 163 km (u blizini N. Gradiške), došlo do prometne nesreće u kojoj su sudjelovali teretno i osobno vozilo i u kojoj su dvije osobe smrtno stradale, dok su 3 ozlijeđene i prevezene na ukazivanje liječničke pomoći u OB u N. Gradišku”, poručili su iz PU brodsko-posavske.
-Kako poručuju, angažirani su pripadnici HMP i vatrogasci radi izvlačenja ozlijeđenih osoba iz vozila.
-“Policijski službenici na mjesto događaja osiguravaju protočnost prometa, te u zajedničkoj suradnji sa ODO Slav. Brod nastavljaju daljnji rad i obavljanje očevida”, poručili su.</t>
+          <t>čovjek poginuti autocest mnogo završiti bolnica ogroman tragedija kod nov gradiška autor splitu utorak ujutro dogoditi tešak prometan nesreća koji poginuti osoba jutros srpanj oko sat splitu križanje ulica mažuranićevo šetalište ulica sloboda doći prometan nesreća sudar dva kombi vozilo osoba preminuti mjesto događaj dok drugi osoba prevezena pružanje liječnički pomoć događaj obaviješteno nadležno državni odvjetništvo zamjenica općinski državni odvjetništvo htjeti rukovoditi očevid izvijestiti policija cesta mjesto prometan nesreća zatvoriti sav promet policijski službenik obližnje tri raskrižje preusmjeravati promet križanj mažuranićevo dubrovački ulica vukovarski ulica sloboda velebitski cilj utvrđivanje sav činjenica okolnost prethoditi nastanak prometan nesreća pozivati očevidce osoba imati korisan saznanje nastanak naveden prometan nesreća javiti postaja prometan policija Split broj telefon 021 021 pristupe osobno postati adresa plokitati 81 pozvati policija prometan kod trogirati još jedan stravičan incident dogoditi noć ponedjeljak utorak poručivati policija cesta d8 trogir dogoditi prometan nesreća sudar osoban vozilo motocići vozač motocikao prevezen bolnica pružanje liječnički pomoć tijekom noć nažalost preminuti prometni nesreća obavještiti nadležn državni odvjetništvo mjesto događaj obaviti očevid nesreća kod nov gradiška dan sat centar policijski uprava zaprimiti dojava južan kolnički traka autocesta a3 kod 163 km blizina gradiška doći prometan nesreća koji sudjelovati teretni osoban vozilo koji dva osoba smrtno stradati dok 3 ozlijeđene prevezen ukazivanje liječnički pomoć ob gradišku poručiti pu poručivati angažiran pripadnik hmp vatrogascin radi izvlačenje ozlijeđen osoba vozilo policijski službenik mjesto događaj osiguravati protočnost promet zajednički suradnja odo slav brod nastavljati daljnji rad obavljanje očevid poručiti</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -4672,37 +3039,27 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>nov gradiška, I.G. 
- u, Split, Split, Sloboda, Mažuranićevo šetalište- Dubrovačka, ulica Slobode- Vukovarsko, Sloboda Velebitsko, Split, plokita, Trogir, Trogir, nov gradiška, policijski uprava brodsko - posavske, A3, N. Gradiška, Gradišku, pU brodsko - posavske, HMP, oDO Slav</t>
+          <t>splitu, Split</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod Nove Gradiške, u kojoj su sudjelovali teretno i osobno vozilo, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske, prenosi Jutarnji list.
-Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške.
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.</t>
+          <t>dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osoban vozilo ozlijediti još troje osoba javljati pu prenositi jutarnji list pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -4713,36 +3070,27 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>nov gradiška, pU Brodsko - posavske, Jutarnji list, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.5454545454545454</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>POLICIJA je jutros izvijestila kako je u sinoćnjoj prometnoj nesreći na autocesti kod Nove Gradiške uz dvoje poginulih i troje ozlijeđenih.
-Očevid i dalje traje, nakon što završi, bit će poznato više informacija.
-Tekst se nastavlja ispod oglasa
-"Dana 24.7.2023. g. u 23:32 u Operativno-komunikacijskom centru Policijske uprave brodsko-posavske zaprimljena je dojava da je na južnoj kolničkoj traci autoceste A3, kod 163. km (u blizini N. Gradiške), došlo do prometne nesreće u kojoj su sudjelovali teretno i osobno vozilo i u kojoj su dvije osobe smrtno stradale, dok su tri ozlijeđene i prevezene na ukazivanje liječničke pomoći u bolnicu u N. Gradiški.
-Angažirani su pripadnici HMP-a i vatrogasci radi izvlačenja ozlijeđenih osoba iz vozila. Policijski službenici na mjestu događaja osiguravaju protočnost prometa te u suradnji s Općinskim državnim odvjetništvom Slav. Brod nastavljaju daljnji rad i obavljanje očevida", izvijestila je jutros policija.</t>
+          <t>policija jutros izvijestiti sinoćnji prometni nesreća autocest kod nov gradiška dvoje poginuli troje ozlijeđen očevid daleko trajati što završiti biti htjeti poznat mnogo informacija tekst nastavljati ispod oglas dan centar policijski uprava zaprimiti dojava južan kolnički traka autocesta a3 kod km blizina gradiška doći prometan nesreća koji sudjelovati teretni osoban vozilo koji dva osoba smrtno stradati dok tri ozlijeđene prevezen ukazivanje liječnički pomoć bolnica gradiški angažiran pripadnik vatrogascin radi izvlačenje ozlijeđen osoba vozilo policijski službenik mjesto događaj osiguravati protočnost promet suradnja općinski državni odvjetništv slav brod nastavljati daljnji rad obavljanje očevid izvijestiti jutros policija</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -4753,36 +3101,23 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>nov gradiška, dan 24.7.2023, policijski uprava brodsko - posavske, A3, N. Gradiška, N. gradiški, HMP - a, Općinski državni odvjetništvo, Slav</t>
-        </is>
-      </c>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>0.1176470588235294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Brodsko-posavska policija izvijestila je o teškoj prometnoj nesreći koja se dogodila jučer oko 23, 32 sati na A3. Poginule su dvije osobe, dok su tri prevezene u bolnicu.
-VEZANI ČLANCI:
-Kako su izvijestila, komunikacijskom centru Policijske uprave brodsko-posavske, stigla je dojava da je na južnoj kolničkoj traci autoceste A3, kod 163 km (u blizini N. Gradiške), došlo do prometne nesreće u kojoj su sudjelovali teretno i osobno vozilo i u kojoj su dvije osobe smrtno stradale, dok su tri ozlijeđene i prevezene na ukazivanje liječničke pomoći u bolnicu u N. Gradiški.
-Angažirani su pripadnici HMP i vatrogasci radi izvlačenja ozlijeđenih osoba iz vozila. Policijski službenici na mjesto događaja osiguravaju protočnost prometa, te u zajedničkoj suradnji sa Općinskim državnim odvjetništvom Slav. Brod nastavljaju daljnji rad i obavljanje očevida.
-Video: Šleper se okretao na A1, vozač 'šišao' preko rotora: Pogledajte lude manevre na našim cestama</t>
+          <t>policija izvijestiti tešak prometni nesreća dogoditi jučer oko 23 32 sat a3 poginuti dva osoba dok tri prevezen bolnica vezan članak izvijestiti komunikacijski centar policijski uprava stići dojava južan kolnički traka autocesta a3 kod 163 km blizina gradiška doći prometan nesreća koji sudjelovati teretni osoban vozilo koji dva osoba smrtno stradati dok tri ozlijeđene prevezen ukazivanje liječnički pomoć bolnica gradiški angažiran pripadnik hmp vatrogascin radi izvlačenje ozlijeđen osoba vozilo policijski službenik mjesto događaj osiguravati protočnost promet zajednički suradnja općinski državni odvjetništv slav brod nastavljati daljnji rad obavljanje očevid video šleper okretati a1 vozač preko rotor pogledati lud manevar naš cesta</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -4793,35 +3128,27 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Brodsko - posavska policija, A3, policijski uprava brodsko - posavske, A3, N. Gradiška, N. gradiški, HMP, Općinski državni odvjetništvo, Slav, A1</t>
+          <t>a1</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.05555555555555555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Policija je jutros saopćila kako je u sinoćnjoj saobraćajnoj nesreći na autocesti kod Nove Gradiške uz dvoje poginulih i troje povrijeđenih.
-Uviđaj i dalje traje, nakon što završi, bit će poznato više informacija.
-- Dana 24. jula u 23:32 u Operativno-komunikacijskom centru Policijske uprave brodsko-posavske zaprimljena je dojava da je na južnoj kolničkoj traci autoceste A3, kod 163. km (u blizini Nove Gradiške), došlo do saobraćajne nesreće u kojoj su učestvovali teretno i osobno vozilo i u kojoj su dvije osobe smrtno stradale, dok su tri povrijeđene i prevezene na ukazivanje liječničke pomoći u bolnicu u Novoj Gradiški.
-Angažirani su pripadnici HMP-a i vatrogasci radi izvlačenja povrijeđenih osoba iz vozila. Policijski službenici na mjestu događaja osiguravaju protočnost saobraćaja te u saradnji s Općinskim državnim odvjetništvom Slavonski Brod nastavljaju daljnji rad i obavljanje uviđaja - saopćila je jutros policija.</t>
+          <t>policija jutros saopćiti sinoćnji saobraćajan nesreća autocest kod nov gradiška dvoje poginuli troje povrijeđen uviđaj daleko trajati što završiti biti htjeti poznat mnogo informacija dan jula centar policijski uprava zaprimiti dojava južan kolnički traka autocesta a3 kod km blizina nov gradiška doći saobraćajni nesreća koji učestvovati teretni osoban vozilo koji dva osoba smrtno stradati dok tri povrijeđen prevezen ukazivanje liječnički pomoć bolnica nov gradiški angažiran pripadnik vatrogascin radi izvlačenje povrijeđen osoba vozilo policijski službenik mjesto događaj osiguravati protočnost saobraćaj saradnja općinski državni odvjetništv slavonski brod nastavljati daljnji rad obavljanje uviđaj saopćiti jutros policija</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -4832,37 +3159,23 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>nov gradiška, policijski uprava brodsko - posavske, A3, nov gradiška, Novoj gradiški, HMP - a, Općinski državni odvjetništvo Slavonski Brod</t>
-        </is>
-      </c>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strašna prometnoj nesreći dogodila se u ponedjeljak kasno navečer, izvijestila je brodsko-posavska policija.
-Policija je javila kako je u 23:32 sati u Operativno-komunikacijskom centru Policijske uprave brodsko-posavske, zaprimljena dojava da je na južnoj kolničkoj traci autoceste A3, kod 163 km u smjeru Lipovca (nedaleko od Nove Gradiške), došlo do prometne nesreće u kojoj su sudjelovali teretno i osobno vozilo i u kojoj su dvije osobe smrtno stradale, dok su tri ozlijeđene i prevezene u OB Nova Gradiška radi ukazivanja liječničke pomoći.
-Angažirani su pripadnici HMP i vatrogasci radi izvlačenja ozlijeđenih osoba iz vozila, priopćila je Policijska uprava brodsko-posavska.
-Policijski službenici na mjesto događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-U tijeku je očevid kako bi se utvrdile okolnosti prometne nesreće.
-</t>
+          <t>strašan prometni nesreća dogoditi ponedjeljak kasno navečer izvijestiti policija policija javiti sat centar policijski uprava zaprimiti dojava južan kolnički traka autocesta a3 kod 163 km smjer lipovac nedaleko nov gradiška doći prometan nesreća koji sudjelovati teretni osoban vozilo koji dva osoba smrtno stradati dok tri ozlijediti prevezene ob nov gradiška radi ukazivanje liječnički pomoć angažiran pripadnik hmp vatrogascin radi izvlačenje ozlijeđen osoba vozilo priopćiti policijski uprava policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka tijek očevid utvrditi okolnost prometan nesreća</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -4873,36 +3186,23 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>policijski uprava brodsko - posavske, A3, Lipovca, nov gradiška, OB Nova Gradiška, HMP, Policijski uprava brodsko - posavska</t>
-        </is>
-      </c>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod Nove Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske.
-Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške.
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.</t>
+          <t>dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -4913,47 +3213,27 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>nov gradiška, pU Brodsko - posavske, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Crna noć na hrvatskim cestama, dogodile se užasne tragedije: Nepovratno izgubljena četiri života
-Autor: I.G.
-Četiri ljudska života noćas su se ugasila na prometnicama diljem Hrvatske, javlja policija. Tragedije su se odvile kod Nove Gradiške, u Splitu i kod Trogira.
-Strahote
-U Splitu se u utorak ujutro dogodila teška prometna nesreća u kojoj je poginula jedna osoba.
-“Jutros, 25. srpnja 2023.godine, oko 06:12 sati u Splitu na križanju ulica Mažuranićevo šetalište i ulice Slobode, došlo je prometne nesreće, sudara dva kombi vozila. Jedna osoba je preminula na mjestu događaja, dok je druga osoba prevezena na pružanje liječničke pomoći. O događaju obaviješteno nadležno državno odvjetništvo.
-Zamjenica općinskog državnog odvjetništva će rukovoditi očevidom”, izvijestila je policija.
-Cesta je na mjestu prometne nesreće zatvorena za sav promet. Policijski službenici na obližnja tri raskrižja preusmjeravaju promet i to na križanjima Mažuranićevo šetalište- Dubrovačka, ulica Slobode- Vukovarska i ulica Slobode Velebitska).
-“U cilju utvrđivanja svih činjenica i okolnosti koje su prethodile nastanku prometne nesreće, pozivamo svjedoke/ očevidce, kao i sve osobe koje imaju korisnih saznanja o nastanku navedene prometne nesreće da se jave u Postaju prometne policije Split na brojeve telefona 021 504-010, 021 504-036, ili pristupe osobno u postaju na adresi Plokita 81”, pozvala je policija.
-Prometna kod Trogira
-Još jedan stravičan incident dogodio se u noći s ponedjeljka na utorak. Kako poručuju iz Policije, na cesti D8, u Trogiru dogodila se prometna nesreća sudar osobnog vozila i motocikla. Vozač motocikla prevezen je u bolnicu na pružanje liječničke pomoći, ali je tijekom noći nažalost preminuo.
-O prometnoj nesreći je obavješteno nadležno državno odvjetništvo i na mjestu događaja je obavljen očevid.
-Nesreća i kod Nove Gradiške
-“Dana 24.07.2023.g. u 23,32 sati, u Operativno-komunikacijskom centru Policijske uprave brodsko-posavske, zaprimljena je dojava da je na južnoj kolničkoj traci autoceste A3, kod 163 km (u blizini N. Gradiške), došlo do prometne nesreće u kojoj su sudjelovali teretno i osobno vozilo i u kojoj su dvije osobe smrtno stradale, dok su 3 ozlijeđene i prevezene na ukazivanje liječničke pomoći u OB u N. Gradišku”, poručili su iz PU brodsko-posavske.
-Kako poručuju, angažirani su pripadnici HMP i vatrogasci radi izvlačenja ozlijeđenih osoba iz vozila.
-“Policijski službenici na mjesto događaja osiguravaju protočnost prometa, te u zajedničkoj suradnji sa ODO Slav. Brod nastavljaju daljnji rad i obavljanje očevida”, poručili su.</t>
+          <t>crn noć hrvatski cesta dogoditi užasan tragedija nepovratno izgubiti četiri život autor četiri ljudski život noćas ugasiti prometnica diljem hrvatski javljati policija tragedija odviti kod nov gradiška splitu kod trogirati strahota splitu utorak ujutro dogoditi tešak prometan nesreća koji poginuti osoba jutros srpanj oko sat splitu križanje ulica mažuranićevo šetalište ulica sloboda doći prometan nesreća sudar dva kombi vozilo osoba preminuti mjesto događaj dok drugi osoba prevezena pružanje liječnički pomoć događaj obaviješteno nadležno državni odvjetništvo zamjenica općinski državni odvjetništvo htjeti rukovoditi očevid izvijestiti policija cesta mjesto prometan nesreća zatvoriti sav promet policijski službenik obližnje tri raskrižje preusmjeravati promet križanj mažuranićevo dubrovački ulica vukovarski ulica sloboda velebitski cilj utvrđivanje sav činjenica okolnost prethoditi nastanak prometan nesreća pozivati očevidce osoba imati korisan saznanje nastanak naveden prometan nesreća javiti postaja prometan policija Split broj telefon 021 021 pristupe osobno postati adresa plokitati 81 pozvati policija prometan kod trogirati još jedan stravičan incident dogoditi noć ponedjeljak utorak poručivati policija cesta d8 trogir dogoditi prometan nesreća sudar osoban vozilo motocići vozač motocikao prevezen bolnica pružanje liječnički pomoć tijekom noć nažalost preminuti prometni nesreća obavještiti nadležn državni odvjetništvo mjesto događaj obaviti očevid nesreća kod nov gradiška dan sat centar policijski uprava zaprimiti dojava južan kolnički traka autocesta a3 kod 163 km blizina gradiška doći prometan nesreća koji sudjelovati teretni osoban vozilo koji dva osoba smrtno stradati dok 3 ozlijeđene prevezen ukazivanje liječnički pomoć ob gradišku poručiti pu poručivati angažiran pripadnik hmp vatrogascin radi izvlačenje ozlijeđen osoba vozilo policijski službenik mjesto događaj osiguravati protočnost promet zajednički suradnja odo slav brod nastavljati daljnji rad obavljanje očevid poručiti</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -4964,37 +3244,27 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>I.G. 
- četiri ljudski život noćas, Hrvatska, nov gradiška, Split, Trogir, Split, Split, Sloboda, Mažuranićevo šetalište- Dubrovačka, ulica Slobode- Vukovarsko, Sloboda Velebitsko, Split, plokita, Trogir, Trogir, nov gradiška, policijski uprava brodsko - posavske, A3, N. Gradiška, Gradišku, pU brodsko - posavske, HMP, oDO Slav</t>
+          <t>splitu, splitu, Split</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Policija je jutros izvijestila kako je u sinoćnjoj saobraćajnoj nesreći na autoputu kod Nove Gradiške uz dvoje poginulih i troje povrijeđenih.
-Uviđaj i dalje traje, nakon što završi, biće poznato više informacija.
-“Dana 24.7.2023 u 23:32 u Operativno-komunikacijskom centru Policijske uprave brodsko-posavske zaprimljena je dojava da je na južnoj kolničkoj traci autoceste A3, kod 163 km (u blizini Nove Gradiške), došlo do saobraćajne nesreće u kojoj su učestvovali i teretno i osobno vozilo i u kojoj su dvije osobe smrtno stradale, dok su tri povrijeđene i prevezene na ukazivanje ljekarske pomoći u bolnicu u Novoj Gradiški”, saopštila je policija.
-Angažovana su pripadnici HMP-a i vatrogasci radi izvlačenja povrijeđenih osoba iz vozila.
-“Policijski službenici na mjestu događaja osiguravaju protok saobraćaja te u saaradnji s Opštinskim državnim tužilaštvom Slavonski Brod nastavljaju dalji rad i obavljanje uviđaja”, izvijestila je jutros policija.</t>
+          <t>policija jutros izvijestiti sinoćnji saobraćajan nesreća autoput kod nov gradiška dvoje poginuli troje povrijeđen uviđaj daleko trajati što završiti biće poznat mnogo informacija dan centar policijski uprava zaprimiti dojava južan kolnički traka autocesta a3 kod 163 km blizina nov gradiška doći saobraćajni nesreća koji učestvovati teretni osoban vozilo koji dva osoba smrtno stradati dok tri povrijeđen prevezen ukazivanje ljekarski pomoć bolnica nov gradiški saopštiti policija angažovati pripadnik vatrogascin radi izvlačenje povrijeđen osoba vozilo policijski službenik mjesto događaj osiguravati protok saobraćaj saaradnja opštinski državni tužilaštv slavonski brod nastavljati dalj rad obavljanje uviđaj izvijestiti jutros policija</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -5005,35 +3275,23 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>nov gradiška, policijski uprava brodsko - posavske, A3, nov gradiška, Novoj gradiški, Angažovana, HMP - a, slavonski Brod</t>
-        </is>
-      </c>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške.
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.</t>
+          <t>pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -5044,36 +3302,23 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
-        </is>
-      </c>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod Nove Gradiške, u kojoj su sudjelovali teretno i osobno vozilo, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske, prenosi Jutarnji list.
-Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške.
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.</t>
+          <t>dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osoban vozilo ozlijediti još troje osoba javljati pu prenositi jutarnji list pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -5084,36 +3329,27 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>nov gradiška, pU Brodsko - posavske, Jutarnji list, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.5454545454545454</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod Nove Gradiške, u kojoj su sudjelovali teretno i osobno vozilo, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske, prenosi Jutarnji list.
-Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške.
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.</t>
+          <t>dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osoban vozilo ozlijediti još troje osoba javljati pu prenositi jutarnji list pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -5124,35 +3360,27 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>nov gradiška, pU Brodsko - posavske, Jutarnji list, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.5454545454545454</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Policija je jutros izvijestila kako je u sinoćnjoj prometnoj nesreći na autocesti kod Nove Gradiške uz dvoje poginulih i troje ozlijeđenih.
-Očevid i dalje traje, nakon što završi, bit će poznato više informacija.
-"Dana 24.7.2023. g. u 23:32 u Operativno-komunikacijskom centru Policijske uprave brodsko-posavske zaprimljena je dojava da je na južnoj kolničkoj traci autoceste A3, kod 163. km (u blizini N. Gradiške), došlo do prometne nesreće u kojoj su sudjelovali teretno i osobno vozilo i u kojoj su dvije osobe smrtno stradale, dok su tri ozlijeđene i prevezene na ukazivanje liječničke pomoći u bolnicu u N. Gradiški.
-Angažirani su pripadnici HMP-a i vatrogasci radi izvlačenja ozlijeđenih osoba iz vozila. Policijski službenici na mjestu događaja osiguravaju protočnost prometa te u suradnji s Općinskim državnim odvjetništvom Slav. Brod nastavljaju daljnji rad i obavljanje očevida", izvijestila je jutros policija.</t>
+          <t>policija jutros izvijestiti sinoćnji prometni nesreća autocest kod nov gradiška dvoje poginuli troje ozlijeđen očevid daleko trajati što završiti biti htjeti poznat mnogo informacija dan centar policijski uprava zaprimiti dojava južan kolnički traka autocesta a3 kod km blizina gradiška doći prometan nesreća koji sudjelovati teretni osoban vozilo koji dva osoba smrtno stradati dok tri ozlijeđene prevezen ukazivanje liječnički pomoć bolnica gradiški angažiran pripadnik vatrogascin radi izvlačenje ozlijeđen osoba vozilo policijski službenik mjesto događaj osiguravati protočnost promet suradnja općinski državni odvjetništv slav brod nastavljati daljnji rad obavljanje očevid izvijestiti jutros policija</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -5163,35 +3391,23 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>nov gradiška, dan 24.7.2023, policijski uprava brodsko - posavske, A3, N. Gradiška, N. gradiški, HMP - a, Općinski državni odvjetništvo, Slav</t>
-        </is>
-      </c>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>0.1176470588235294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Brodsko-posavska policija izvijestila je o teškoj prometnoj nesreći koja se dogodila jučer oko 23, 32 sati na A3. Poginule su dvije osobe, dok su tri prevezene u bolnicu.
-VEZANI ČLANCI:
-Kako neslužbeno doznaje RTL poginule su majka i kćer. Od ravnatelja novogradiške bolnice Josipa Kolodzieja doznaje se da su ozlijeđena djeca od 18 i 15 godina imaju ozlijede mozga i hitno su prebačeni u Osijek, dok je treća ozlijeđena osoba ostala u bolnici u Novoj Gradiški.
-Kako su izvijestili iz policije, komunikacijskom centru Policijske uprave brodsko-posavske, stigla je dojava da je na južnoj kolničkoj traci autoceste A3, kod 163 km (u blizini N. Gradiške), došlo do prometne nesreće u kojoj su sudjelovali teretno i osobno vozilo i u kojoj su dvije osobe smrtno stradale, dok su tri ozlijeđene i prevezene na ukazivanje liječničke pomoći u bolnicu u N. Gradiški.</t>
+          <t>policija izvijestiti tešak prometni nesreća dogoditi jučer oko 23 32 sat a3 poginuti dva osoba dok tri prevezen bolnica vezan članak neslužbeno doznaje rtl poginule majka kćer ravnatelj novogradiške bolnica josip kolodziej doznavati ozlijeđeni djeca 18 15 godina imati ozlijeda mozg hitno prebačeni osijek dok treći ozlijeđen osoba ostati bolnica nov gradiški izvijestiti policija komunikacijski centar policijski uprava stići dojava južan kolnički traka autocesta a3 kod 163 km blizina gradiška doći prometan nesreća koji sudjelovati teretni osoban vozilo koji dva osoba smrtno stradati dok tri ozlijeđene prevezen ukazivanje liječnički pomoć bolnica gradiški</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -5202,39 +3418,27 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brodsko - posavska policija, A3, RTL, Josip Kolodziej, Osijek, Novoj gradiški, policijski uprava brodsko - posavske, A3, N. Gradiška, N. gradiški</t>
+          <t>Josip kolodziej</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.05555555555555555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOVA GRADIŠKA, 25. srpnja 2023. (Hina) - Dvije su osobe poginule u ponedjeljak kasno navečer, u prometnoj nesreći na autocesti A3 kod NOve Gradiške, u kojoj su sudjelovali teretno i osobno vozila, a ozlijeđeno je još troje osoba, javljaju iz PU Brodsko-posavske. 
-	Pola sata prije ponoći, policija je primila dojavu o nesreći koja se dogodila kod 163. kilometra autoceste A3, u blizini Nove Gradiške. 
-Policijski službenici na mjestu događaja osiguravaju protočnost prometa, koji se odvija prometnim i zaustavnim trakom južne kolničke trake.
-Pripadnici hitne medicinske pomoći i vatrogasaca izvukli su ozlijeđene osobe iz vozila, koje potom prevezene na ukazivanje liječničke pomoći u Opću bolnicu Nova Gradiška.
-U suradnji sa Općinskim državnim odvjetništvo u Slavonskom Brodu, policija nastavlja rad na obavljanju očevida.
-</t>
+          <t>nov gradiška srpanj 2023 hin dva osoba poginuti ponedjeljak kasno navečer prometni nesreća autocest a3 kod nov gradiška koji sudjelovati teretni osobno vozilo ozlijediti još troje osoba javljati pu pola sat ponoć policija primiti dojava nesreća dogoditi kod kilometar autocesta a3 blizina nov gradiška policijski službenik mjesto događaj osiguravati protočnost promet odvijati prometan zaustavan trak južan kolnički traka pripadnik hitan medicinski pomoć vatrogasac izvući ozlijeđiti osoba vozilo potom preveziti ukazivanje liječnički pomoć opći bolnica nov gradiški suradnja općinski državni odvjetništvo slavonski brod policija nastavljati rad obavljanje očevid</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Užas koji se sinoć, pola sata prije ponoći, dogodio na 163. kilometru autoceste A3 kod Nove Gradiške, koji kilometar nakon odmorišta Dragalić, a prije Lužana, vidljiv je i danas, rano ujutro nakon nesreće u kojoj su dvije osobe smrtno stradale, a tri su ozlijeđene.
-Tegljač austrijskih nacionalnih oznaka, koji je u tovarnom prostoru prevozio kamion, ima neznatna oštećenja na stražnjem lijevom dijelu prikolice, no zato je crni BMW, moguće X5 ili X6, također stranih oznaka, koji je očito udario u njega, uništen do neprepoznatljivosti. Njegovu karoseriju je odvezla vučna služba, na travnatoj površini kraj zaustavne trake ostali su komadi lima - vrata, pragovi i ostali dijelovi koji svjedoče koliko je udar bio stravičan. Dio je otkinut nakon vatrogasne intervencije kojom su iz vozila izvlačeni ozlijeđeni.
-Tragovi na mjestu nesreće daju naslutiti da je tegljač vjerojatno stajao u zaustavnoj traci, a da je osobno vozilo na njega naletjelo punom brzinom. Kotač BMW-a otkinut je i ostao zaglavljen ispod kamionske prikolice, te se i sada tamo nalazi.
-Što se točno odigralo na autocesti u mrkloj noći, utvrdit će policija svojom istragom, koja je započela nakon okončanja očevida. Ozlijeđene iz BMW-a su izvlačili vatrogasci, a djelatnici Zavoda za hitnu medicinu odvezli na liječenje u bolnicu u Novoj Gradiški.
-Na odmorištu Lužani rekli su nam da im je u noćnoj smjeni banula krvava žena na benzinsku postaju.
-- Ona je naišla na nesreću i krenula je pomoći tim jadnim ljudima. Kod nas je stala da se opere od krvi - kažu nam djelatnici.
-Navode i da im je svjedokinja rekla kako je kamion u trenutku udara bio neosvijetljen, što bi se moglo pokazati kao vrlo značajan trag u istrazi. No, je li to točno, također će se utvrđivati policijskom istragom.
-U jutarnjim satima promet se u smjeru istoka odvijao na oba kolnička traka, dok je kamion koji je sudjelovao u nesreći još uvijek parkiran na zaustavnoj traci.</t>
+          <t>užas sinoć pola sat ponoć dogoditi kilometar autocesta a3 kod nov gradiška kilometar odmorište dragalić lužan vidljiv danas rano ujutro nesreća koji dva osoba smrtno stradati tri ozlijediti tegljač austrijski nacionalan oznaka tovarni prostor prevoziti kamion imati neznatan oštećenje stražnji lijev dio prikolica zato cran bmw moguć x5 x6 također stran oznaka očito udariti uništen neprepoznatljivost njegov karoserija odvezlati vučan služba travnati površina kraj zaustavan traka ostali komad le vrata prag ostali dijel svjedočiti koliko udar stravičan dio otkinuti vatrogasni intervencija koji vozilo izvlačeni ozlijeđen trag mjesto nesreća dati naslutiti tegljač vjerojatno stajati zaustavan traka osoban vozilo naletjeti pun brzina kotač otkinuti ostati zaglaviti ispod kamionski prikolica sada tamo nalaziti što točno odigrati autocest mrkloj noć utvrditi htjeti policija svoj istraga započeti okončanje očevid ozlijediti izvlačiti vatrogasac djelatnik zavod hitan medicina odvezli liječenje bolnica nov gradiški odmorište lužan reći oni noćan smjena banuti krvav žena benzinski postaja naići nesreća krenuti pomoći taj jadan čovjek kod stalo opera krv kazati djelatnik navoditi oni svjedokinja reći kamion trenutak udarati neosvijetljen što moći pokazati značajan trag istraga točno također htjeti utvrđivati policijski istraga jutarnji sat promet smjer istok odvijati oba kolnički traka dok kamion sudjelovati nesreća još uvijek parkirati zaustavn traka</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -5245,16 +3449,16 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>GRADIŠKA, Hina, gradiške, pU Brodsko - posavske, pola sat, A3, nov gradiška, opću bolnica Nova Gradiška, Općinski državni odvjetništvo u, Slavonski Brod</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>nov gradiška, Dragalić, Lužan, BMW, BMW - a, BMW - a, zavod za hitan medicina, Novoj gradiški, Lužan</t>
+          <t>cran Bmw, x6, zavod hitan medicina</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.0625</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
